--- a/SoTheoDoiThuChi_T10_2026.xlsx
+++ b/SoTheoDoiThuChi_T10_2026.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="300">
   <si>
     <t xml:space="preserve">HƯỚNG DẪN SỬ DỤNG</t>
   </si>
@@ -214,12 +214,13 @@
     <t xml:space="preserve">Rút</t>
   </si>
   <si>
+    <t xml:space="preserve">TỔNG
+(Nạp + Đơn − Rút)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nạp − Rút</t>
   </si>
   <si>
-    <t xml:space="preserve">Nạp + Đơn</t>
-  </si>
-  <si>
     <t xml:space="preserve">Số dòng GD</t>
   </si>
   <si>
@@ -250,6 +251,10 @@
     <t xml:space="preserve">Rút (TK)</t>
   </si>
   <si>
+    <t xml:space="preserve">TỔNG TK
+(Nạp + Đơn − Rút)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Không rõ ngày</t>
   </si>
   <si>
@@ -497,7 +502,7 @@
   </si>
   <si>
     <t xml:space="preserve">TỔNG NGÀY
-(Nạp + Đơn)</t>
+(Nạp + Đơn − Rút)</t>
   </si>
   <si>
     <t xml:space="preserve">TỔNG RÚT
@@ -1956,11 +1961,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1974,6 +1980,7 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
@@ -1986,6 +1993,7 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2"/>
@@ -1996,6 +2004,7 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
@@ -2010,6 +2019,7 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
@@ -2033,6 +2043,7 @@
         <v>43</v>
       </c>
       <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
@@ -2060,6 +2071,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
@@ -2087,6 +2099,7 @@
         <v>0.376097673021538</v>
       </c>
       <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
@@ -2114,6 +2127,7 @@
         <v>0.16122762690602</v>
       </c>
       <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
@@ -2136,6 +2150,7 @@
         <v>0.226566779157906</v>
       </c>
       <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
@@ -2158,6 +2173,7 @@
         <v>0.176687810307967</v>
       </c>
       <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
@@ -2180,6 +2196,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
@@ -2202,6 +2219,7 @@
         <v>0.0594201106065693</v>
       </c>
       <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
@@ -2223,6 +2241,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
@@ -2236,6 +2255,7 @@
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
@@ -2246,6 +2266,7 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
@@ -2258,8 +2279,9 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
         <v>49</v>
       </c>
@@ -2284,6 +2306,7 @@
       <c r="H17" s="24" t="s">
         <v>56</v>
       </c>
+      <c r="I17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="str">
@@ -2303,12 +2326,12 @@
         <v>2269</v>
       </c>
       <c r="E18" s="18" t="n">
+        <f aca="false">B18+C18-D18</f>
+        <v>71431</v>
+      </c>
+      <c r="F18" s="18" t="n">
         <f aca="false">B18-D18</f>
         <v>19431</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <f aca="false">B18+C18</f>
-        <v>73700</v>
       </c>
       <c r="G18" s="18" t="n">
         <f aca="false">COUNTIFS('Giao dịch TK'!$B$5:$B$504,$A18)</f>
@@ -2318,6 +2341,7 @@
         <f aca="false">SUMIFS('Thu Chi'!$E$5:$E$504,'Thu Chi'!$C$5:$C$504,"Hoa hồng",'Thu Chi'!$B$5:$B$504,"WINDY")</f>
         <v>23772</v>
       </c>
+      <c r="I18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="str">
@@ -2337,12 +2361,12 @@
         <v>1320</v>
       </c>
       <c r="E19" s="18" t="n">
+        <f aca="false">B19+C19-D19</f>
+        <v>56100</v>
+      </c>
+      <c r="F19" s="18" t="n">
         <f aca="false">B19-D19</f>
         <v>32910</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <f aca="false">B19+C19</f>
-        <v>57420</v>
       </c>
       <c r="G19" s="18" t="n">
         <f aca="false">COUNTIFS('Giao dịch TK'!$B$5:$B$504,$A19)</f>
@@ -2351,6 +2375,7 @@
       <c r="H19" s="25" t="n">
         <v>0</v>
       </c>
+      <c r="I19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="str">
@@ -2370,12 +2395,12 @@
         <v>751</v>
       </c>
       <c r="E20" s="18" t="n">
+        <f aca="false">B20+C20-D20</f>
+        <v>16659</v>
+      </c>
+      <c r="F20" s="18" t="n">
         <f aca="false">B20-D20</f>
         <v>7459</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <f aca="false">B20+C20</f>
-        <v>17410</v>
       </c>
       <c r="G20" s="18" t="n">
         <f aca="false">COUNTIFS('Giao dịch TK'!$B$5:$B$504,$A20)</f>
@@ -2384,6 +2409,7 @@
       <c r="H20" s="25" t="n">
         <v>0</v>
       </c>
+      <c r="I20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="str">
@@ -2403,12 +2429,12 @@
         <v>500</v>
       </c>
       <c r="E21" s="18" t="n">
+        <f aca="false">B21+C21-D21</f>
+        <v>250</v>
+      </c>
+      <c r="F21" s="18" t="n">
         <f aca="false">B21-D21</f>
         <v>250</v>
-      </c>
-      <c r="F21" s="18" t="n">
-        <f aca="false">B21+C21</f>
-        <v>750</v>
       </c>
       <c r="G21" s="18" t="n">
         <f aca="false">COUNTIFS('Giao dịch TK'!$B$5:$B$504,$A21)</f>
@@ -2417,6 +2443,7 @@
       <c r="H21" s="25" t="n">
         <v>0</v>
       </c>
+      <c r="I21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="str">
@@ -2436,11 +2463,11 @@
         <v>0</v>
       </c>
       <c r="E22" s="18" t="n">
+        <f aca="false">B22+C22-D22</f>
+        <v>4000</v>
+      </c>
+      <c r="F22" s="18" t="n">
         <f aca="false">B22-D22</f>
-        <v>4000</v>
-      </c>
-      <c r="F22" s="18" t="n">
-        <f aca="false">B22+C22</f>
         <v>4000</v>
       </c>
       <c r="G22" s="18" t="n">
@@ -2451,6 +2478,7 @@
         <f aca="false">SUMIFS('Thu Chi'!$E$5:$E$504,'Thu Chi'!$C$5:$C$504,"Hoa hồng",'Thu Chi'!$B$5:$B$504,"ĐẠI LÝ NGỌC LINH")</f>
         <v>5200</v>
       </c>
+      <c r="I22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="str">
@@ -2470,11 +2498,11 @@
         <v>0</v>
       </c>
       <c r="E23" s="18" t="n">
+        <f aca="false">B23+C23-D23</f>
+        <v>3500</v>
+      </c>
+      <c r="F23" s="18" t="n">
         <f aca="false">B23-D23</f>
-        <v>3500</v>
-      </c>
-      <c r="F23" s="18" t="n">
-        <f aca="false">B23+C23</f>
         <v>3500</v>
       </c>
       <c r="G23" s="18" t="n">
@@ -2484,6 +2512,7 @@
       <c r="H23" s="25" t="n">
         <v>0</v>
       </c>
+      <c r="I23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
@@ -2503,11 +2532,11 @@
       </c>
       <c r="E24" s="22" t="n">
         <f aca="false">SUM(E18:E23)</f>
-        <v>67550</v>
+        <v>151940</v>
       </c>
       <c r="F24" s="22" t="n">
         <f aca="false">SUM(F18:F23)</f>
-        <v>156780</v>
+        <v>67550</v>
       </c>
       <c r="G24" s="22" t="n">
         <f aca="false">SUM(G18:G23)</f>
@@ -2517,6 +2546,7 @@
         <f aca="false">SUM(H18:H23)</f>
         <v>28972</v>
       </c>
+      <c r="I24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
@@ -2529,6 +2559,7 @@
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
@@ -2539,6 +2570,7 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
@@ -2551,8 +2583,9 @@
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="24" t="s">
         <v>59</v>
       </c>
@@ -2576,6 +2609,9 @@
       </c>
       <c r="H28" s="24" t="s">
         <v>64</v>
+      </c>
+      <c r="I28" s="24" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2611,6 +2647,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A29)</f>
         <v>1359</v>
       </c>
+      <c r="I29" s="18" t="n">
+        <f aca="false">F29+G29-H29</f>
+        <v>42401</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="26" t="n">
@@ -2645,6 +2685,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A30)</f>
         <v>1161</v>
       </c>
+      <c r="I30" s="18" t="n">
+        <f aca="false">F30+G30-H30</f>
+        <v>18889</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="26" t="n">
@@ -2679,6 +2723,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A31)</f>
         <v>1620</v>
       </c>
+      <c r="I31" s="18" t="n">
+        <f aca="false">F31+G31-H31</f>
+        <v>37960</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="26" t="n">
@@ -2713,6 +2761,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A32)</f>
         <v>0</v>
       </c>
+      <c r="I32" s="18" t="n">
+        <f aca="false">F32+G32-H32</f>
+        <v>36690</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="26" t="n">
@@ -2747,6 +2799,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A33)</f>
         <v>700</v>
       </c>
+      <c r="I33" s="18" t="n">
+        <f aca="false">F33+G33-H33</f>
+        <v>12000</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="26" t="n">
@@ -2781,6 +2837,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A34)</f>
         <v>0</v>
       </c>
+      <c r="I34" s="18" t="n">
+        <f aca="false">F34+G34-H34</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="26" t="n">
@@ -2815,6 +2875,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A35)</f>
         <v>0</v>
       </c>
+      <c r="I35" s="18" t="n">
+        <f aca="false">F35+G35-H35</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="26" t="n">
@@ -2849,6 +2913,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A36)</f>
         <v>0</v>
       </c>
+      <c r="I36" s="18" t="n">
+        <f aca="false">F36+G36-H36</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="26" t="n">
@@ -2883,6 +2951,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A37)</f>
         <v>0</v>
       </c>
+      <c r="I37" s="18" t="n">
+        <f aca="false">F37+G37-H37</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="26" t="n">
@@ -2917,6 +2989,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A38)</f>
         <v>0</v>
       </c>
+      <c r="I38" s="18" t="n">
+        <f aca="false">F38+G38-H38</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="26" t="n">
@@ -2951,6 +3027,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A39)</f>
         <v>0</v>
       </c>
+      <c r="I39" s="18" t="n">
+        <f aca="false">F39+G39-H39</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="26" t="n">
@@ -2985,6 +3065,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A40)</f>
         <v>0</v>
       </c>
+      <c r="I40" s="18" t="n">
+        <f aca="false">F40+G40-H40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="26" t="n">
@@ -3019,6 +3103,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A41)</f>
         <v>0</v>
       </c>
+      <c r="I41" s="18" t="n">
+        <f aca="false">F41+G41-H41</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="26" t="n">
@@ -3053,6 +3141,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A42)</f>
         <v>0</v>
       </c>
+      <c r="I42" s="18" t="n">
+        <f aca="false">F42+G42-H42</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="26" t="n">
@@ -3087,6 +3179,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A43)</f>
         <v>0</v>
       </c>
+      <c r="I43" s="18" t="n">
+        <f aca="false">F43+G43-H43</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="26" t="n">
@@ -3121,6 +3217,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A44)</f>
         <v>0</v>
       </c>
+      <c r="I44" s="18" t="n">
+        <f aca="false">F44+G44-H44</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="26" t="n">
@@ -3155,6 +3255,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A45)</f>
         <v>0</v>
       </c>
+      <c r="I45" s="18" t="n">
+        <f aca="false">F45+G45-H45</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="26" t="n">
@@ -3189,6 +3293,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A46)</f>
         <v>0</v>
       </c>
+      <c r="I46" s="18" t="n">
+        <f aca="false">F46+G46-H46</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="26" t="n">
@@ -3223,6 +3331,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A47)</f>
         <v>0</v>
       </c>
+      <c r="I47" s="18" t="n">
+        <f aca="false">F47+G47-H47</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="26" t="n">
@@ -3257,6 +3369,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A48)</f>
         <v>0</v>
       </c>
+      <c r="I48" s="18" t="n">
+        <f aca="false">F48+G48-H48</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="26" t="n">
@@ -3291,6 +3407,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A49)</f>
         <v>0</v>
       </c>
+      <c r="I49" s="18" t="n">
+        <f aca="false">F49+G49-H49</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="26" t="n">
@@ -3325,6 +3445,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A50)</f>
         <v>0</v>
       </c>
+      <c r="I50" s="18" t="n">
+        <f aca="false">F50+G50-H50</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="26" t="n">
@@ -3359,6 +3483,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A51)</f>
         <v>0</v>
       </c>
+      <c r="I51" s="18" t="n">
+        <f aca="false">F51+G51-H51</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="26" t="n">
@@ -3393,6 +3521,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A52)</f>
         <v>0</v>
       </c>
+      <c r="I52" s="18" t="n">
+        <f aca="false">F52+G52-H52</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="26" t="n">
@@ -3427,6 +3559,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A53)</f>
         <v>0</v>
       </c>
+      <c r="I53" s="18" t="n">
+        <f aca="false">F53+G53-H53</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="26" t="n">
@@ -3461,6 +3597,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A54)</f>
         <v>0</v>
       </c>
+      <c r="I54" s="18" t="n">
+        <f aca="false">F54+G54-H54</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="26" t="n">
@@ -3495,6 +3635,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A55)</f>
         <v>0</v>
       </c>
+      <c r="I55" s="18" t="n">
+        <f aca="false">F55+G55-H55</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="26" t="n">
@@ -3529,6 +3673,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A56)</f>
         <v>0</v>
       </c>
+      <c r="I56" s="18" t="n">
+        <f aca="false">F56+G56-H56</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="26" t="n">
@@ -3563,6 +3711,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A57)</f>
         <v>0</v>
       </c>
+      <c r="I57" s="18" t="n">
+        <f aca="false">F57+G57-H57</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="26" t="n">
@@ -3597,6 +3749,10 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A58)</f>
         <v>0</v>
       </c>
+      <c r="I58" s="18" t="n">
+        <f aca="false">F58+G58-H58</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="26" t="n">
@@ -3631,10 +3787,14 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,$A59)</f>
         <v>0</v>
       </c>
+      <c r="I59" s="18" t="n">
+        <f aca="false">F59+G59-H59</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B60" s="28" t="n">
         <f aca="false">SUMIFS('Thu Chi'!$D$5:$D$504,'Thu Chi'!$A$5:$A$504,"",'Thu Chi'!$D$5:$D$504,"&lt;&gt;")</f>
@@ -3661,10 +3821,14 @@
         <f aca="false">SUMIFS('Giao dịch TK'!$F$5:$F$504,'Giao dịch TK'!$A$5:$A$504,"",'Giao dịch TK'!$B$5:$B$504,"&lt;&gt;")</f>
         <v>0</v>
       </c>
+      <c r="I60" s="28" t="n">
+        <f aca="false">F60+G60-H60</f>
+        <v>4000</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B61" s="22" t="n">
         <f aca="false">SUM(B29:B60)</f>
@@ -3694,9 +3858,13 @@
         <f aca="false">SUM(H29:H60)</f>
         <v>4840</v>
       </c>
+      <c r="I61" s="22" t="n">
+        <f aca="false">SUM(I29:I60)</f>
+        <v>151940</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A29:H59">
+  <conditionalFormatting sqref="A29:I59">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND($B29=0,$C29=0,$F29=0,$G29=0,$H29=0)</formula>
     </cfRule>
@@ -3726,7 +3894,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3736,7 +3904,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3757,10 +3925,10 @@
         <v>49</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -3768,17 +3936,17 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F5" s="30" t="n">
         <v>0</v>
@@ -3786,13 +3954,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -3800,13 +3968,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -3814,13 +3982,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -3828,13 +3996,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -3842,13 +4010,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -3857,10 +4025,10 @@
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
       <c r="B11" s="29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -3870,7 +4038,7 @@
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -3908,7 +4076,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3923,7 +4091,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3954,7 +4122,7 @@
         <v>59</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" s="31" t="s">
         <v>40</v>
@@ -3966,22 +4134,22 @@
         <v>42</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J4" s="31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K4" s="31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3989,10 +4157,10 @@
         <v>46296</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D5" s="25"/>
       <c r="E5" s="25" t="n">
@@ -4011,10 +4179,10 @@
         <v>14950</v>
       </c>
       <c r="I5" s="29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J5" s="34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K5" s="35"/>
     </row>
@@ -4023,10 +4191,10 @@
         <v>46296</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D6" s="25"/>
       <c r="E6" s="25" t="n">
@@ -4039,10 +4207,10 @@
       <c r="G6" s="33"/>
       <c r="H6" s="33"/>
       <c r="I6" s="29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J6" s="34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K6" s="35"/>
     </row>
@@ -4051,10 +4219,10 @@
         <v>46296</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="25" t="n">
@@ -4067,10 +4235,10 @@
       <c r="G7" s="33"/>
       <c r="H7" s="33"/>
       <c r="I7" s="29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J7" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K7" s="35"/>
     </row>
@@ -4079,10 +4247,10 @@
         <v>46296</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="25" t="n">
@@ -4095,10 +4263,10 @@
       <c r="G8" s="33"/>
       <c r="H8" s="33"/>
       <c r="I8" s="29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K8" s="35"/>
     </row>
@@ -4107,10 +4275,10 @@
         <v>46296</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="25" t="n">
@@ -4123,10 +4291,10 @@
       <c r="G9" s="33"/>
       <c r="H9" s="33"/>
       <c r="I9" s="29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J9" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K9" s="35"/>
     </row>
@@ -4135,10 +4303,10 @@
         <v>46296</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" s="25"/>
       <c r="E10" s="25" t="n">
@@ -4152,10 +4320,10 @@
       <c r="H10" s="33"/>
       <c r="I10" s="29"/>
       <c r="J10" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K10" s="35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4163,10 +4331,10 @@
         <v>46297</v>
       </c>
       <c r="B11" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="37" t="s">
         <v>73</v>
-      </c>
-      <c r="C11" s="37" t="s">
-        <v>72</v>
       </c>
       <c r="D11" s="38" t="n">
         <v>9200</v>
@@ -4186,7 +4354,7 @@
       </c>
       <c r="I11" s="37"/>
       <c r="J11" s="41" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K11" s="42"/>
     </row>
@@ -4195,10 +4363,10 @@
         <v>46297</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D12" s="25"/>
       <c r="E12" s="25" t="n">
@@ -4211,10 +4379,10 @@
       <c r="G12" s="40"/>
       <c r="H12" s="40"/>
       <c r="I12" s="29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J12" s="34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K12" s="35"/>
     </row>
@@ -4223,10 +4391,10 @@
         <v>46297</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D13" s="25"/>
       <c r="E13" s="25" t="n">
@@ -4239,13 +4407,13 @@
       <c r="G13" s="40"/>
       <c r="H13" s="40"/>
       <c r="I13" s="29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J13" s="34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K13" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4253,10 +4421,10 @@
         <v>46297</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D14" s="25"/>
       <c r="E14" s="25" t="n">
@@ -4269,10 +4437,10 @@
       <c r="G14" s="40"/>
       <c r="H14" s="40"/>
       <c r="I14" s="29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J14" s="34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K14" s="35"/>
     </row>
@@ -4281,10 +4449,10 @@
         <v>46297</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="25" t="n">
@@ -4297,10 +4465,10 @@
       <c r="G15" s="40"/>
       <c r="H15" s="40"/>
       <c r="I15" s="29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J15" s="34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K15" s="35"/>
     </row>
@@ -4309,10 +4477,10 @@
         <v>46297</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D16" s="25"/>
       <c r="E16" s="25" t="n">
@@ -4325,10 +4493,10 @@
       <c r="G16" s="40"/>
       <c r="H16" s="40"/>
       <c r="I16" s="29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J16" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K16" s="35"/>
     </row>
@@ -4337,10 +4505,10 @@
         <v>46298</v>
       </c>
       <c r="B17" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="37" t="s">
         <v>73</v>
-      </c>
-      <c r="C17" s="37" t="s">
-        <v>72</v>
       </c>
       <c r="D17" s="38" t="n">
         <v>25000</v>
@@ -4360,7 +4528,7 @@
       </c>
       <c r="I17" s="37"/>
       <c r="J17" s="41" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K17" s="42"/>
     </row>
@@ -4369,10 +4537,10 @@
         <v>46298</v>
       </c>
       <c r="B18" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="29" t="s">
         <v>73</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>72</v>
       </c>
       <c r="D18" s="25" t="n">
         <v>15000</v>
@@ -4386,7 +4554,7 @@
       <c r="H18" s="40"/>
       <c r="I18" s="29"/>
       <c r="J18" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K18" s="35"/>
     </row>
@@ -4395,10 +4563,10 @@
         <v>46298</v>
       </c>
       <c r="B19" s="29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="25" t="n">
@@ -4411,10 +4579,10 @@
       <c r="G19" s="40"/>
       <c r="H19" s="40"/>
       <c r="I19" s="29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J19" s="34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K19" s="35"/>
     </row>
@@ -4423,10 +4591,10 @@
         <v>46298</v>
       </c>
       <c r="B20" s="29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D20" s="25"/>
       <c r="E20" s="25" t="n">
@@ -4439,10 +4607,10 @@
       <c r="G20" s="40"/>
       <c r="H20" s="40"/>
       <c r="I20" s="29" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J20" s="34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K20" s="35"/>
     </row>
@@ -4451,10 +4619,10 @@
         <v>46298</v>
       </c>
       <c r="B21" s="29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D21" s="25"/>
       <c r="E21" s="25" t="n">
@@ -4467,10 +4635,10 @@
       <c r="G21" s="40"/>
       <c r="H21" s="40"/>
       <c r="I21" s="29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J21" s="34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K21" s="35"/>
     </row>
@@ -4479,10 +4647,10 @@
         <v>46298</v>
       </c>
       <c r="B22" s="29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D22" s="25"/>
       <c r="E22" s="25" t="n">
@@ -4495,10 +4663,10 @@
       <c r="G22" s="40"/>
       <c r="H22" s="40"/>
       <c r="I22" s="29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J22" s="34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K22" s="35"/>
     </row>
@@ -4507,10 +4675,10 @@
         <v>46298</v>
       </c>
       <c r="B23" s="29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D23" s="25"/>
       <c r="E23" s="25" t="n">
@@ -4523,13 +4691,13 @@
       <c r="G23" s="40"/>
       <c r="H23" s="40"/>
       <c r="I23" s="29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J23" s="34" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K23" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4537,10 +4705,10 @@
         <v>46299</v>
       </c>
       <c r="B24" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="44" t="s">
         <v>73</v>
-      </c>
-      <c r="C24" s="44" t="s">
-        <v>72</v>
       </c>
       <c r="D24" s="45" t="n">
         <v>300000</v>
@@ -4560,10 +4728,10 @@
       </c>
       <c r="I24" s="44"/>
       <c r="J24" s="47" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K24" s="48" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4571,10 +4739,10 @@
         <v>46299</v>
       </c>
       <c r="B25" s="29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D25" s="25"/>
       <c r="E25" s="25" t="n">
@@ -4588,10 +4756,10 @@
       <c r="H25" s="40"/>
       <c r="I25" s="29"/>
       <c r="J25" s="34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K25" s="35" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4599,10 +4767,10 @@
         <v>46299</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D26" s="25"/>
       <c r="E26" s="25" t="n">
@@ -4616,10 +4784,10 @@
       <c r="H26" s="40"/>
       <c r="I26" s="29"/>
       <c r="J26" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="K26" s="35" t="s">
         <v>135</v>
-      </c>
-      <c r="K26" s="35" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4627,10 +4795,10 @@
         <v>46299</v>
       </c>
       <c r="B27" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D27" s="25"/>
       <c r="E27" s="25" t="n">
@@ -4643,13 +4811,13 @@
       <c r="G27" s="40"/>
       <c r="H27" s="40"/>
       <c r="I27" s="29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J27" s="34" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K27" s="35" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4657,10 +4825,10 @@
         <v>46300</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C28" s="37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D28" s="38"/>
       <c r="E28" s="38" t="n">
@@ -4679,10 +4847,10 @@
         <v>22500</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J28" s="41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K28" s="42"/>
     </row>
@@ -4691,10 +4859,10 @@
         <v>46300</v>
       </c>
       <c r="B29" s="29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="25" t="n">
@@ -4708,10 +4876,10 @@
       <c r="H29" s="40"/>
       <c r="I29" s="29"/>
       <c r="J29" s="34" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K29" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4719,10 +4887,10 @@
         <v>46300</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D30" s="25"/>
       <c r="E30" s="25" t="n">
@@ -4736,10 +4904,10 @@
       <c r="H30" s="40"/>
       <c r="I30" s="29"/>
       <c r="J30" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="K30" s="35" t="s">
         <v>143</v>
-      </c>
-      <c r="K30" s="35" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15217,7 +15385,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="44"/>
@@ -15225,7 +15393,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15239,7 +15407,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -15271,7 +15439,7 @@
         <v>49</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D4" s="31" t="s">
         <v>50</v>
@@ -15283,16 +15451,16 @@
         <v>52</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J4" s="31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15300,10 +15468,10 @@
         <v>46296</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>50</v>
@@ -15311,15 +15479,15 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
       <c r="G5" s="33" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A5,$B$5:$B$504,B5)+SUMIFS($E$5:$E$504,$A$5:$A$504,A5,$B$5:$B$504,B5)</f>
-        <v>34550</v>
+        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A5,$B$5:$B$504,B5)+SUMIFS($E$5:$E$504,$A$5:$A$504,A5,$B$5:$B$504,B5)-SUMIFS($F$5:$F$504,$A$5:$A$504,A5,$B$5:$B$504,B5)</f>
+        <v>34142</v>
       </c>
       <c r="H5" s="33" t="n">
         <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A5,$B$5:$B$504,B5)</f>
         <v>408</v>
       </c>
       <c r="I5" s="34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J5" s="35"/>
     </row>
@@ -15328,10 +15496,10 @@
         <v>46296</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>5000</v>
@@ -15343,7 +15511,7 @@
       <c r="G6" s="33"/>
       <c r="H6" s="33"/>
       <c r="I6" s="34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J6" s="35"/>
     </row>
@@ -15352,10 +15520,10 @@
         <v>46296</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D7" s="25" t="n">
         <v>3000</v>
@@ -15365,7 +15533,7 @@
       <c r="G7" s="33"/>
       <c r="H7" s="33"/>
       <c r="I7" s="34" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J7" s="35"/>
     </row>
@@ -15374,10 +15542,10 @@
         <v>46296</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>50</v>
@@ -15389,7 +15557,7 @@
       <c r="G8" s="33"/>
       <c r="H8" s="33"/>
       <c r="I8" s="34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J8" s="35"/>
     </row>
@@ -15398,10 +15566,10 @@
         <v>46296</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D9" s="25" t="n">
         <v>5000</v>
@@ -15413,7 +15581,7 @@
       <c r="G9" s="33"/>
       <c r="H9" s="33"/>
       <c r="I9" s="34" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J9" s="35"/>
     </row>
@@ -15422,10 +15590,10 @@
         <v>46296</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D10" s="25" t="n">
         <v>100</v>
@@ -15437,7 +15605,7 @@
       <c r="G10" s="33"/>
       <c r="H10" s="33"/>
       <c r="I10" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J10" s="35"/>
     </row>
@@ -15446,10 +15614,10 @@
         <v>46296</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D11" s="25" t="n">
         <v>1000</v>
@@ -15459,7 +15627,7 @@
       <c r="G11" s="33"/>
       <c r="H11" s="33"/>
       <c r="I11" s="34" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J11" s="35"/>
     </row>
@@ -15468,10 +15636,10 @@
         <v>46296</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D12" s="25" t="n">
         <v>150</v>
@@ -15481,7 +15649,7 @@
       <c r="G12" s="33"/>
       <c r="H12" s="33"/>
       <c r="I12" s="34" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J12" s="35"/>
     </row>
@@ -15490,10 +15658,10 @@
         <v>46296</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D13" s="25" t="n">
         <v>200</v>
@@ -15503,7 +15671,7 @@
       <c r="G13" s="33"/>
       <c r="H13" s="33"/>
       <c r="I13" s="34" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J13" s="35"/>
     </row>
@@ -15512,10 +15680,10 @@
         <v>46297</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D14" s="38" t="n">
         <v>100</v>
@@ -15525,15 +15693,15 @@
         <v>206</v>
       </c>
       <c r="G14" s="40" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A14,$B$5:$B$504,B14)+SUMIFS($E$5:$E$504,$A$5:$A$504,A14,$B$5:$B$504,B14)</f>
-        <v>19850</v>
+        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A14,$B$5:$B$504,B14)+SUMIFS($E$5:$E$504,$A$5:$A$504,A14,$B$5:$B$504,B14)-SUMIFS($F$5:$F$504,$A$5:$A$504,A14,$B$5:$B$504,B14)</f>
+        <v>18689</v>
       </c>
       <c r="H14" s="40" t="n">
         <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A14,$B$5:$B$504,B14)</f>
         <v>1161</v>
       </c>
       <c r="I14" s="41" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J14" s="42"/>
     </row>
@@ -15542,10 +15710,10 @@
         <v>46297</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D15" s="25" t="n">
         <v>200</v>
@@ -15555,7 +15723,7 @@
       <c r="G15" s="40"/>
       <c r="H15" s="40"/>
       <c r="I15" s="34" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J15" s="35"/>
     </row>
@@ -15564,10 +15732,10 @@
         <v>46297</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D16" s="25" t="n">
         <v>100</v>
@@ -15577,7 +15745,7 @@
       <c r="G16" s="40"/>
       <c r="H16" s="40"/>
       <c r="I16" s="34" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J16" s="35"/>
     </row>
@@ -15586,10 +15754,10 @@
         <v>46297</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D17" s="25" t="n">
         <v>150</v>
@@ -15601,7 +15769,7 @@
       <c r="G17" s="40"/>
       <c r="H17" s="40"/>
       <c r="I17" s="34" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J17" s="35"/>
     </row>
@@ -15610,10 +15778,10 @@
         <v>46297</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D18" s="25" t="n">
         <v>3000</v>
@@ -15625,7 +15793,7 @@
       <c r="G18" s="40"/>
       <c r="H18" s="40"/>
       <c r="I18" s="34" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J18" s="35"/>
     </row>
@@ -15634,10 +15802,10 @@
         <v>46297</v>
       </c>
       <c r="B19" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D19" s="25" t="n">
         <v>300</v>
@@ -15649,7 +15817,7 @@
       <c r="G19" s="40"/>
       <c r="H19" s="40"/>
       <c r="I19" s="34" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J19" s="35"/>
     </row>
@@ -15658,10 +15826,10 @@
         <v>46298</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D20" s="38" t="n">
         <v>3000</v>
@@ -15671,7 +15839,7 @@
       </c>
       <c r="F20" s="38"/>
       <c r="G20" s="40" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A20,$B$5:$B$504,B20)+SUMIFS($E$5:$E$504,$A$5:$A$504,A20,$B$5:$B$504,B20)</f>
+        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A20,$B$5:$B$504,B20)+SUMIFS($E$5:$E$504,$A$5:$A$504,A20,$B$5:$B$504,B20)-SUMIFS($F$5:$F$504,$A$5:$A$504,A20,$B$5:$B$504,B20)</f>
         <v>9250</v>
       </c>
       <c r="H20" s="40" t="n">
@@ -15679,7 +15847,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="41" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J20" s="42"/>
     </row>
@@ -15688,10 +15856,10 @@
         <v>46298</v>
       </c>
       <c r="B21" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D21" s="25" t="n">
         <v>250</v>
@@ -15701,7 +15869,7 @@
       <c r="G21" s="40"/>
       <c r="H21" s="40"/>
       <c r="I21" s="34" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J21" s="35"/>
     </row>
@@ -15710,10 +15878,10 @@
         <v>46299</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D22" s="38"/>
       <c r="E22" s="38" t="n">
@@ -15721,7 +15889,7 @@
       </c>
       <c r="F22" s="38"/>
       <c r="G22" s="40" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A22,$B$5:$B$504,B22)+SUMIFS($E$5:$E$504,$A$5:$A$504,A22,$B$5:$B$504,B22)</f>
+        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A22,$B$5:$B$504,B22)+SUMIFS($E$5:$E$504,$A$5:$A$504,A22,$B$5:$B$504,B22)-SUMIFS($F$5:$F$504,$A$5:$A$504,A22,$B$5:$B$504,B22)</f>
         <v>10000</v>
       </c>
       <c r="H22" s="40" t="n">
@@ -15729,7 +15897,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="41" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J22" s="42"/>
     </row>
@@ -15738,10 +15906,10 @@
         <v>46300</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D23" s="38" t="n">
         <v>50</v>
@@ -15751,18 +15919,18 @@
         <v>700</v>
       </c>
       <c r="G23" s="40" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A23,$B$5:$B$504,B23)+SUMIFS($E$5:$E$504,$A$5:$A$504,A23,$B$5:$B$504,B23)</f>
-        <v>50</v>
+        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A23,$B$5:$B$504,B23)+SUMIFS($E$5:$E$504,$A$5:$A$504,A23,$B$5:$B$504,B23)-SUMIFS($F$5:$F$504,$A$5:$A$504,A23,$B$5:$B$504,B23)</f>
+        <v>-650</v>
       </c>
       <c r="H23" s="40" t="n">
         <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A23,$B$5:$B$504,B23)</f>
         <v>700</v>
       </c>
       <c r="I23" s="41" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J23" s="42" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15770,10 +15938,10 @@
         <v>46296</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D24" s="38" t="n">
         <v>200</v>
@@ -15783,18 +15951,18 @@
         <v>100</v>
       </c>
       <c r="G24" s="40" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A24,$B$5:$B$504,B24)+SUMIFS($E$5:$E$504,$A$5:$A$504,A24,$B$5:$B$504,B24)</f>
-        <v>8200</v>
+        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A24,$B$5:$B$504,B24)+SUMIFS($E$5:$E$504,$A$5:$A$504,A24,$B$5:$B$504,B24)-SUMIFS($F$5:$F$504,$A$5:$A$504,A24,$B$5:$B$504,B24)</f>
+        <v>8000</v>
       </c>
       <c r="H24" s="40" t="n">
         <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A24,$B$5:$B$504,B24)</f>
         <v>200</v>
       </c>
       <c r="I24" s="41" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J24" s="42" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15802,10 +15970,10 @@
         <v>46296</v>
       </c>
       <c r="B25" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D25" s="25" t="n">
         <v>3000</v>
@@ -15815,7 +15983,7 @@
       <c r="G25" s="40"/>
       <c r="H25" s="40"/>
       <c r="I25" s="34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J25" s="35"/>
     </row>
@@ -15824,10 +15992,10 @@
         <v>46296</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D26" s="25" t="n">
         <v>1000</v>
@@ -15837,7 +16005,7 @@
       <c r="G26" s="40"/>
       <c r="H26" s="40"/>
       <c r="I26" s="34" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J26" s="35"/>
     </row>
@@ -15846,10 +16014,10 @@
         <v>46296</v>
       </c>
       <c r="B27" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D27" s="25" t="n">
         <v>4000</v>
@@ -15859,7 +16027,7 @@
       <c r="G27" s="40"/>
       <c r="H27" s="40"/>
       <c r="I27" s="34" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J27" s="35"/>
     </row>
@@ -15868,10 +16036,10 @@
         <v>46296</v>
       </c>
       <c r="B28" s="50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D28" s="51"/>
       <c r="E28" s="51"/>
@@ -15881,10 +16049,10 @@
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
       <c r="I28" s="52" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J28" s="53" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15892,10 +16060,10 @@
         <v>46297</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C29" s="37" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D29" s="38" t="n">
         <v>50</v>
@@ -15903,7 +16071,7 @@
       <c r="E29" s="38"/>
       <c r="F29" s="38"/>
       <c r="G29" s="40" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A29,$B$5:$B$504,B29)+SUMIFS($E$5:$E$504,$A$5:$A$504,A29,$B$5:$B$504,B29)</f>
+        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A29,$B$5:$B$504,B29)+SUMIFS($E$5:$E$504,$A$5:$A$504,A29,$B$5:$B$504,B29)-SUMIFS($F$5:$F$504,$A$5:$A$504,A29,$B$5:$B$504,B29)</f>
         <v>150</v>
       </c>
       <c r="H29" s="40" t="n">
@@ -15911,7 +16079,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="41" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J29" s="42"/>
     </row>
@@ -15920,10 +16088,10 @@
         <v>46297</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D30" s="25" t="n">
         <v>100</v>
@@ -15933,7 +16101,7 @@
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
       <c r="I30" s="34" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J30" s="35"/>
     </row>
@@ -15942,10 +16110,10 @@
         <v>46298</v>
       </c>
       <c r="B31" s="37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D31" s="38" t="n">
         <v>100</v>
@@ -15953,15 +16121,15 @@
       <c r="E31" s="38"/>
       <c r="F31" s="38"/>
       <c r="G31" s="40" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A31,$B$5:$B$504,B31)+SUMIFS($E$5:$E$504,$A$5:$A$504,A31,$B$5:$B$504,B31)</f>
-        <v>17930</v>
+        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A31,$B$5:$B$504,B31)+SUMIFS($E$5:$E$504,$A$5:$A$504,A31,$B$5:$B$504,B31)-SUMIFS($F$5:$F$504,$A$5:$A$504,A31,$B$5:$B$504,B31)</f>
+        <v>16810</v>
       </c>
       <c r="H31" s="40" t="n">
         <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A31,$B$5:$B$504,B31)</f>
         <v>1120</v>
       </c>
       <c r="I31" s="41" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J31" s="42"/>
     </row>
@@ -15970,10 +16138,10 @@
         <v>46298</v>
       </c>
       <c r="B32" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D32" s="25" t="n">
         <v>2580</v>
@@ -15983,7 +16151,7 @@
       <c r="G32" s="40"/>
       <c r="H32" s="40"/>
       <c r="I32" s="34" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J32" s="35"/>
     </row>
@@ -15992,10 +16160,10 @@
         <v>46298</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D33" s="25" t="n">
         <v>4100</v>
@@ -16007,7 +16175,7 @@
       <c r="G33" s="40"/>
       <c r="H33" s="40"/>
       <c r="I33" s="34" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J33" s="35"/>
     </row>
@@ -16016,10 +16184,10 @@
         <v>46298</v>
       </c>
       <c r="B34" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D34" s="25" t="n">
         <v>1000</v>
@@ -16029,7 +16197,7 @@
       <c r="G34" s="40"/>
       <c r="H34" s="40"/>
       <c r="I34" s="34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J34" s="35"/>
     </row>
@@ -16038,10 +16206,10 @@
         <v>46298</v>
       </c>
       <c r="B35" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D35" s="25" t="n">
         <v>50</v>
@@ -16051,7 +16219,7 @@
       <c r="G35" s="40"/>
       <c r="H35" s="40"/>
       <c r="I35" s="34" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J35" s="35"/>
     </row>
@@ -16060,10 +16228,10 @@
         <v>46298</v>
       </c>
       <c r="B36" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D36" s="25" t="n">
         <v>10000</v>
@@ -16073,7 +16241,7 @@
       <c r="G36" s="40"/>
       <c r="H36" s="40"/>
       <c r="I36" s="34" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J36" s="35"/>
     </row>
@@ -16082,10 +16250,10 @@
         <v>46298</v>
       </c>
       <c r="B37" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D37" s="25" t="n">
         <v>100</v>
@@ -16095,7 +16263,7 @@
       <c r="G37" s="40"/>
       <c r="H37" s="40"/>
       <c r="I37" s="34" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J37" s="35"/>
     </row>
@@ -16104,10 +16272,10 @@
         <v>46299</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D38" s="38" t="n">
         <v>2000</v>
@@ -16115,7 +16283,7 @@
       <c r="E38" s="38"/>
       <c r="F38" s="38"/>
       <c r="G38" s="40" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A38,$B$5:$B$504,B38)+SUMIFS($E$5:$E$504,$A$5:$A$504,A38,$B$5:$B$504,B38)</f>
+        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A38,$B$5:$B$504,B38)+SUMIFS($E$5:$E$504,$A$5:$A$504,A38,$B$5:$B$504,B38)-SUMIFS($F$5:$F$504,$A$5:$A$504,A38,$B$5:$B$504,B38)</f>
         <v>25590</v>
       </c>
       <c r="H38" s="40" t="n">
@@ -16123,7 +16291,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="41" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J38" s="42"/>
     </row>
@@ -16132,10 +16300,10 @@
         <v>46299</v>
       </c>
       <c r="B39" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D39" s="25" t="n">
         <v>150</v>
@@ -16145,7 +16313,7 @@
       <c r="G39" s="40"/>
       <c r="H39" s="40"/>
       <c r="I39" s="34" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J39" s="35"/>
     </row>
@@ -16154,10 +16322,10 @@
         <v>46299</v>
       </c>
       <c r="B40" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D40" s="25" t="n">
         <v>1000</v>
@@ -16167,7 +16335,7 @@
       <c r="G40" s="40"/>
       <c r="H40" s="40"/>
       <c r="I40" s="34" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J40" s="35"/>
     </row>
@@ -16176,10 +16344,10 @@
         <v>46299</v>
       </c>
       <c r="B41" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D41" s="25" t="n">
         <v>1200</v>
@@ -16189,7 +16357,7 @@
       <c r="G41" s="40"/>
       <c r="H41" s="40"/>
       <c r="I41" s="34" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J41" s="35"/>
     </row>
@@ -16198,10 +16366,10 @@
         <v>46299</v>
       </c>
       <c r="B42" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D42" s="25" t="n">
         <v>500</v>
@@ -16211,7 +16379,7 @@
       <c r="G42" s="40"/>
       <c r="H42" s="40"/>
       <c r="I42" s="34" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J42" s="35"/>
     </row>
@@ -16220,10 +16388,10 @@
         <v>46299</v>
       </c>
       <c r="B43" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D43" s="25"/>
       <c r="E43" s="25" t="n">
@@ -16233,7 +16401,7 @@
       <c r="G43" s="40"/>
       <c r="H43" s="40"/>
       <c r="I43" s="34" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J43" s="35"/>
     </row>
@@ -16242,10 +16410,10 @@
         <v>46299</v>
       </c>
       <c r="B44" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D44" s="25" t="n">
         <v>500</v>
@@ -16255,7 +16423,7 @@
       <c r="G44" s="40"/>
       <c r="H44" s="40"/>
       <c r="I44" s="34" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J44" s="35"/>
     </row>
@@ -16264,10 +16432,10 @@
         <v>46299</v>
       </c>
       <c r="B45" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D45" s="25" t="n">
         <v>1000</v>
@@ -16277,7 +16445,7 @@
       <c r="G45" s="40"/>
       <c r="H45" s="40"/>
       <c r="I45" s="34" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J45" s="35"/>
     </row>
@@ -16286,10 +16454,10 @@
         <v>46299</v>
       </c>
       <c r="B46" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D46" s="25" t="n">
         <v>50</v>
@@ -16299,7 +16467,7 @@
       <c r="G46" s="40"/>
       <c r="H46" s="40"/>
       <c r="I46" s="34" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J46" s="35"/>
     </row>
@@ -16308,10 +16476,10 @@
         <v>46300</v>
       </c>
       <c r="B47" s="37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C47" s="37" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D47" s="38" t="n">
         <v>500</v>
@@ -16319,7 +16487,7 @@
       <c r="E47" s="38"/>
       <c r="F47" s="38"/>
       <c r="G47" s="40" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A47,$B$5:$B$504,B47)+SUMIFS($E$5:$E$504,$A$5:$A$504,A47,$B$5:$B$504,B47)</f>
+        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A47,$B$5:$B$504,B47)+SUMIFS($E$5:$E$504,$A$5:$A$504,A47,$B$5:$B$504,B47)-SUMIFS($F$5:$F$504,$A$5:$A$504,A47,$B$5:$B$504,B47)</f>
         <v>5550</v>
       </c>
       <c r="H47" s="40" t="n">
@@ -16327,7 +16495,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="41" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J47" s="42"/>
     </row>
@@ -16336,10 +16504,10 @@
         <v>46300</v>
       </c>
       <c r="B48" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C48" s="29" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D48" s="25" t="n">
         <v>50</v>
@@ -16349,7 +16517,7 @@
       <c r="G48" s="40"/>
       <c r="H48" s="40"/>
       <c r="I48" s="34" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J48" s="35"/>
     </row>
@@ -16358,10 +16526,10 @@
         <v>46300</v>
       </c>
       <c r="B49" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D49" s="25" t="n">
         <v>1000</v>
@@ -16373,7 +16541,7 @@
       <c r="G49" s="40"/>
       <c r="H49" s="40"/>
       <c r="I49" s="34" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J49" s="35"/>
     </row>
@@ -16382,10 +16550,10 @@
         <v>46296</v>
       </c>
       <c r="B50" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C50" s="37" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D50" s="38" t="n">
         <v>160</v>
@@ -16393,15 +16561,15 @@
       <c r="E50" s="38"/>
       <c r="F50" s="38"/>
       <c r="G50" s="40" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A50,$B$5:$B$504,B50)+SUMIFS($E$5:$E$504,$A$5:$A$504,A50,$B$5:$B$504,B50)</f>
-        <v>260</v>
+        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A50,$B$5:$B$504,B50)+SUMIFS($E$5:$E$504,$A$5:$A$504,A50,$B$5:$B$504,B50)-SUMIFS($F$5:$F$504,$A$5:$A$504,A50,$B$5:$B$504,B50)</f>
+        <v>9</v>
       </c>
       <c r="H50" s="40" t="n">
         <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A50,$B$5:$B$504,B50)</f>
         <v>251</v>
       </c>
       <c r="I50" s="41" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J50" s="42"/>
     </row>
@@ -16410,10 +16578,10 @@
         <v>46296</v>
       </c>
       <c r="B51" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C51" s="29" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D51" s="25" t="n">
         <v>100</v>
@@ -16425,7 +16593,7 @@
       <c r="G51" s="40"/>
       <c r="H51" s="40"/>
       <c r="I51" s="34" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J51" s="35"/>
     </row>
@@ -16434,10 +16602,10 @@
         <v>46297</v>
       </c>
       <c r="B52" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C52" s="37" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D52" s="38" t="n">
         <v>50</v>
@@ -16445,7 +16613,7 @@
       <c r="E52" s="38"/>
       <c r="F52" s="38"/>
       <c r="G52" s="40" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A52,$B$5:$B$504,B52)+SUMIFS($E$5:$E$504,$A$5:$A$504,A52,$B$5:$B$504,B52)</f>
+        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A52,$B$5:$B$504,B52)+SUMIFS($E$5:$E$504,$A$5:$A$504,A52,$B$5:$B$504,B52)-SUMIFS($F$5:$F$504,$A$5:$A$504,A52,$B$5:$B$504,B52)</f>
         <v>50</v>
       </c>
       <c r="H52" s="40" t="n">
@@ -16453,7 +16621,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="41" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J52" s="42"/>
     </row>
@@ -16462,10 +16630,10 @@
         <v>46298</v>
       </c>
       <c r="B53" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C53" s="37" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D53" s="38" t="n">
         <v>7800</v>
@@ -16477,15 +16645,15 @@
         <v>500</v>
       </c>
       <c r="G53" s="40" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A53,$B$5:$B$504,B53)+SUMIFS($E$5:$E$504,$A$5:$A$504,A53,$B$5:$B$504,B53)</f>
-        <v>12400</v>
+        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A53,$B$5:$B$504,B53)+SUMIFS($E$5:$E$504,$A$5:$A$504,A53,$B$5:$B$504,B53)-SUMIFS($F$5:$F$504,$A$5:$A$504,A53,$B$5:$B$504,B53)</f>
+        <v>11900</v>
       </c>
       <c r="H53" s="40" t="n">
         <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A53,$B$5:$B$504,B53)</f>
         <v>500</v>
       </c>
       <c r="I53" s="41" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J53" s="42"/>
     </row>
@@ -16494,10 +16662,10 @@
         <v>46299</v>
       </c>
       <c r="B54" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C54" s="37" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D54" s="38" t="n">
         <v>100</v>
@@ -16505,7 +16673,7 @@
       <c r="E54" s="38"/>
       <c r="F54" s="38"/>
       <c r="G54" s="40" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A54,$B$5:$B$504,B54)+SUMIFS($E$5:$E$504,$A$5:$A$504,A54,$B$5:$B$504,B54)</f>
+        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A54,$B$5:$B$504,B54)+SUMIFS($E$5:$E$504,$A$5:$A$504,A54,$B$5:$B$504,B54)-SUMIFS($F$5:$F$504,$A$5:$A$504,A54,$B$5:$B$504,B54)</f>
         <v>100</v>
       </c>
       <c r="H54" s="40" t="n">
@@ -16513,7 +16681,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="41" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J54" s="42"/>
     </row>
@@ -16522,10 +16690,10 @@
         <v>46300</v>
       </c>
       <c r="B55" s="44" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C55" s="44" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D55" s="45"/>
       <c r="E55" s="45" t="n">
@@ -16533,7 +16701,7 @@
       </c>
       <c r="F55" s="45"/>
       <c r="G55" s="40" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A55,$B$5:$B$504,B55)+SUMIFS($E$5:$E$504,$A$5:$A$504,A55,$B$5:$B$504,B55)</f>
+        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A55,$B$5:$B$504,B55)+SUMIFS($E$5:$E$504,$A$5:$A$504,A55,$B$5:$B$504,B55)-SUMIFS($F$5:$F$504,$A$5:$A$504,A55,$B$5:$B$504,B55)</f>
         <v>4600</v>
       </c>
       <c r="H55" s="40" t="n">
@@ -16541,10 +16709,10 @@
         <v>0</v>
       </c>
       <c r="I55" s="47" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J55" s="48" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16552,10 +16720,10 @@
         <v>46296</v>
       </c>
       <c r="B56" s="37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C56" s="37" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D56" s="38" t="n">
         <v>200</v>
@@ -16563,15 +16731,15 @@
       <c r="E56" s="38"/>
       <c r="F56" s="38"/>
       <c r="G56" s="40" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A56,$B$5:$B$504,B56)+SUMIFS($E$5:$E$504,$A$5:$A$504,A56,$B$5:$B$504,B56)</f>
-        <v>750</v>
+        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A56,$B$5:$B$504,B56)+SUMIFS($E$5:$E$504,$A$5:$A$504,A56,$B$5:$B$504,B56)-SUMIFS($F$5:$F$504,$A$5:$A$504,A56,$B$5:$B$504,B56)</f>
+        <v>250</v>
       </c>
       <c r="H56" s="40" t="n">
         <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A56,$B$5:$B$504,B56)</f>
         <v>500</v>
       </c>
       <c r="I56" s="41" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J56" s="42"/>
     </row>
@@ -16580,10 +16748,10 @@
         <v>46296</v>
       </c>
       <c r="B57" s="50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D57" s="51" t="n">
         <v>500</v>
@@ -16595,10 +16763,10 @@
       <c r="G57" s="40"/>
       <c r="H57" s="40"/>
       <c r="I57" s="52" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J57" s="53" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16606,10 +16774,10 @@
         <v>46296</v>
       </c>
       <c r="B58" s="29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C58" s="29" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D58" s="25" t="n">
         <v>50</v>
@@ -16619,17 +16787,17 @@
       <c r="G58" s="40"/>
       <c r="H58" s="40"/>
       <c r="I58" s="34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J58" s="35"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="43"/>
       <c r="B59" s="44" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C59" s="44" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D59" s="45" t="n">
         <v>1000</v>
@@ -16637,7 +16805,7 @@
       <c r="E59" s="45"/>
       <c r="F59" s="45"/>
       <c r="G59" s="40" t="n">
-        <f aca="false">SUM(D59:D60)+SUM(E59:E60)</f>
+        <f aca="false">SUM(D59:D60)+SUM(E59:E60)-SUM(F59:F60)</f>
         <v>4000</v>
       </c>
       <c r="H59" s="40" t="n">
@@ -16645,19 +16813,19 @@
         <v>0</v>
       </c>
       <c r="I59" s="47" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J59" s="48" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49"/>
       <c r="B60" s="50" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D60" s="51" t="n">
         <v>3000</v>
@@ -16667,10 +16835,10 @@
       <c r="G60" s="40"/>
       <c r="H60" s="40"/>
       <c r="I60" s="52" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J60" s="53" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16678,10 +16846,10 @@
         <v>46299</v>
       </c>
       <c r="B61" s="37" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C61" s="37" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D61" s="38" t="n">
         <v>1000</v>
@@ -16689,7 +16857,7 @@
       <c r="E61" s="38"/>
       <c r="F61" s="38"/>
       <c r="G61" s="40" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A61,$B$5:$B$504,B61)+SUMIFS($E$5:$E$504,$A$5:$A$504,A61,$B$5:$B$504,B61)</f>
+        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A61,$B$5:$B$504,B61)+SUMIFS($E$5:$E$504,$A$5:$A$504,A61,$B$5:$B$504,B61)-SUMIFS($F$5:$F$504,$A$5:$A$504,A61,$B$5:$B$504,B61)</f>
         <v>1000</v>
       </c>
       <c r="H61" s="40" t="n">
@@ -16697,7 +16865,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="41" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J61" s="42"/>
     </row>
@@ -16706,10 +16874,10 @@
         <v>46300</v>
       </c>
       <c r="B62" s="37" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C62" s="37" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D62" s="38" t="n">
         <v>2500</v>
@@ -16717,7 +16885,7 @@
       <c r="E62" s="38"/>
       <c r="F62" s="38"/>
       <c r="G62" s="40" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A62,$B$5:$B$504,B62)+SUMIFS($E$5:$E$504,$A$5:$A$504,A62,$B$5:$B$504,B62)</f>
+        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A62,$B$5:$B$504,B62)+SUMIFS($E$5:$E$504,$A$5:$A$504,A62,$B$5:$B$504,B62)-SUMIFS($F$5:$F$504,$A$5:$A$504,A62,$B$5:$B$504,B62)</f>
         <v>2500</v>
       </c>
       <c r="H62" s="40" t="n">
@@ -16725,7 +16893,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="41" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J62" s="42"/>
     </row>
@@ -16737,7 +16905,7 @@
       <c r="E63" s="25"/>
       <c r="F63" s="25"/>
       <c r="G63" s="33" t="str">
-        <f aca="false">IF(OR(B63="",AND(A63=A62 ,B63=B62)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A63,$B$5:$B$504,B63)+SUMIFS($E$5:$E$504,$A$5:$A$504,A63,$B$5:$B$504,B63))</f>
+        <f aca="false">IF(OR(B63="",AND(A63=A62 ,B63=B62)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A63,$B$5:$B$504,B63)+SUMIFS($E$5:$E$504,$A$5:$A$504,A63,$B$5:$B$504,B63)-SUMIFS($F$5:$F$504,$A$5:$A$504,A63,$B$5:$B$504,B63))</f>
         <v/>
       </c>
       <c r="H63" s="33" t="str">
@@ -16755,7 +16923,7 @@
       <c r="E64" s="25"/>
       <c r="F64" s="25"/>
       <c r="G64" s="33" t="str">
-        <f aca="false">IF(OR(B64="",AND(A64=A63 ,B64=B63)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A64,$B$5:$B$504,B64)+SUMIFS($E$5:$E$504,$A$5:$A$504,A64,$B$5:$B$504,B64))</f>
+        <f aca="false">IF(OR(B64="",AND(A64=A63 ,B64=B63)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A64,$B$5:$B$504,B64)+SUMIFS($E$5:$E$504,$A$5:$A$504,A64,$B$5:$B$504,B64)-SUMIFS($F$5:$F$504,$A$5:$A$504,A64,$B$5:$B$504,B64))</f>
         <v/>
       </c>
       <c r="H64" s="33" t="str">
@@ -16773,7 +16941,7 @@
       <c r="E65" s="25"/>
       <c r="F65" s="25"/>
       <c r="G65" s="33" t="str">
-        <f aca="false">IF(OR(B65="",AND(A65=A64 ,B65=B64)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A65,$B$5:$B$504,B65)+SUMIFS($E$5:$E$504,$A$5:$A$504,A65,$B$5:$B$504,B65))</f>
+        <f aca="false">IF(OR(B65="",AND(A65=A64 ,B65=B64)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A65,$B$5:$B$504,B65)+SUMIFS($E$5:$E$504,$A$5:$A$504,A65,$B$5:$B$504,B65)-SUMIFS($F$5:$F$504,$A$5:$A$504,A65,$B$5:$B$504,B65))</f>
         <v/>
       </c>
       <c r="H65" s="33" t="str">
@@ -16791,7 +16959,7 @@
       <c r="E66" s="25"/>
       <c r="F66" s="25"/>
       <c r="G66" s="33" t="str">
-        <f aca="false">IF(OR(B66="",AND(A66=A65 ,B66=B65)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A66,$B$5:$B$504,B66)+SUMIFS($E$5:$E$504,$A$5:$A$504,A66,$B$5:$B$504,B66))</f>
+        <f aca="false">IF(OR(B66="",AND(A66=A65 ,B66=B65)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A66,$B$5:$B$504,B66)+SUMIFS($E$5:$E$504,$A$5:$A$504,A66,$B$5:$B$504,B66)-SUMIFS($F$5:$F$504,$A$5:$A$504,A66,$B$5:$B$504,B66))</f>
         <v/>
       </c>
       <c r="H66" s="33" t="str">
@@ -16809,7 +16977,7 @@
       <c r="E67" s="25"/>
       <c r="F67" s="25"/>
       <c r="G67" s="33" t="str">
-        <f aca="false">IF(OR(B67="",AND(A67=A66 ,B67=B66)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A67,$B$5:$B$504,B67)+SUMIFS($E$5:$E$504,$A$5:$A$504,A67,$B$5:$B$504,B67))</f>
+        <f aca="false">IF(OR(B67="",AND(A67=A66 ,B67=B66)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A67,$B$5:$B$504,B67)+SUMIFS($E$5:$E$504,$A$5:$A$504,A67,$B$5:$B$504,B67)-SUMIFS($F$5:$F$504,$A$5:$A$504,A67,$B$5:$B$504,B67))</f>
         <v/>
       </c>
       <c r="H67" s="33" t="str">
@@ -16827,7 +16995,7 @@
       <c r="E68" s="25"/>
       <c r="F68" s="25"/>
       <c r="G68" s="33" t="str">
-        <f aca="false">IF(OR(B68="",AND(A68=A67 ,B68=B67)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A68,$B$5:$B$504,B68)+SUMIFS($E$5:$E$504,$A$5:$A$504,A68,$B$5:$B$504,B68))</f>
+        <f aca="false">IF(OR(B68="",AND(A68=A67 ,B68=B67)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A68,$B$5:$B$504,B68)+SUMIFS($E$5:$E$504,$A$5:$A$504,A68,$B$5:$B$504,B68)-SUMIFS($F$5:$F$504,$A$5:$A$504,A68,$B$5:$B$504,B68))</f>
         <v/>
       </c>
       <c r="H68" s="33" t="str">
@@ -16845,7 +17013,7 @@
       <c r="E69" s="25"/>
       <c r="F69" s="25"/>
       <c r="G69" s="33" t="str">
-        <f aca="false">IF(OR(B69="",AND(A69=A68 ,B69=B68)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A69,$B$5:$B$504,B69)+SUMIFS($E$5:$E$504,$A$5:$A$504,A69,$B$5:$B$504,B69))</f>
+        <f aca="false">IF(OR(B69="",AND(A69=A68 ,B69=B68)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A69,$B$5:$B$504,B69)+SUMIFS($E$5:$E$504,$A$5:$A$504,A69,$B$5:$B$504,B69)-SUMIFS($F$5:$F$504,$A$5:$A$504,A69,$B$5:$B$504,B69))</f>
         <v/>
       </c>
       <c r="H69" s="33" t="str">
@@ -16863,7 +17031,7 @@
       <c r="E70" s="25"/>
       <c r="F70" s="25"/>
       <c r="G70" s="33" t="str">
-        <f aca="false">IF(OR(B70="",AND(A70=A69 ,B70=B69)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A70,$B$5:$B$504,B70)+SUMIFS($E$5:$E$504,$A$5:$A$504,A70,$B$5:$B$504,B70))</f>
+        <f aca="false">IF(OR(B70="",AND(A70=A69 ,B70=B69)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A70,$B$5:$B$504,B70)+SUMIFS($E$5:$E$504,$A$5:$A$504,A70,$B$5:$B$504,B70)-SUMIFS($F$5:$F$504,$A$5:$A$504,A70,$B$5:$B$504,B70))</f>
         <v/>
       </c>
       <c r="H70" s="33" t="str">
@@ -16881,7 +17049,7 @@
       <c r="E71" s="25"/>
       <c r="F71" s="25"/>
       <c r="G71" s="33" t="str">
-        <f aca="false">IF(OR(B71="",AND(A71=A70 ,B71=B70)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A71,$B$5:$B$504,B71)+SUMIFS($E$5:$E$504,$A$5:$A$504,A71,$B$5:$B$504,B71))</f>
+        <f aca="false">IF(OR(B71="",AND(A71=A70 ,B71=B70)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A71,$B$5:$B$504,B71)+SUMIFS($E$5:$E$504,$A$5:$A$504,A71,$B$5:$B$504,B71)-SUMIFS($F$5:$F$504,$A$5:$A$504,A71,$B$5:$B$504,B71))</f>
         <v/>
       </c>
       <c r="H71" s="33" t="str">
@@ -16899,7 +17067,7 @@
       <c r="E72" s="25"/>
       <c r="F72" s="25"/>
       <c r="G72" s="33" t="str">
-        <f aca="false">IF(OR(B72="",AND(A72=A71 ,B72=B71)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A72,$B$5:$B$504,B72)+SUMIFS($E$5:$E$504,$A$5:$A$504,A72,$B$5:$B$504,B72))</f>
+        <f aca="false">IF(OR(B72="",AND(A72=A71 ,B72=B71)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A72,$B$5:$B$504,B72)+SUMIFS($E$5:$E$504,$A$5:$A$504,A72,$B$5:$B$504,B72)-SUMIFS($F$5:$F$504,$A$5:$A$504,A72,$B$5:$B$504,B72))</f>
         <v/>
       </c>
       <c r="H72" s="33" t="str">
@@ -16917,7 +17085,7 @@
       <c r="E73" s="25"/>
       <c r="F73" s="25"/>
       <c r="G73" s="33" t="str">
-        <f aca="false">IF(OR(B73="",AND(A73=A72 ,B73=B72)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A73,$B$5:$B$504,B73)+SUMIFS($E$5:$E$504,$A$5:$A$504,A73,$B$5:$B$504,B73))</f>
+        <f aca="false">IF(OR(B73="",AND(A73=A72 ,B73=B72)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A73,$B$5:$B$504,B73)+SUMIFS($E$5:$E$504,$A$5:$A$504,A73,$B$5:$B$504,B73)-SUMIFS($F$5:$F$504,$A$5:$A$504,A73,$B$5:$B$504,B73))</f>
         <v/>
       </c>
       <c r="H73" s="33" t="str">
@@ -16935,7 +17103,7 @@
       <c r="E74" s="25"/>
       <c r="F74" s="25"/>
       <c r="G74" s="33" t="str">
-        <f aca="false">IF(OR(B74="",AND(A74=A73 ,B74=B73)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A74,$B$5:$B$504,B74)+SUMIFS($E$5:$E$504,$A$5:$A$504,A74,$B$5:$B$504,B74))</f>
+        <f aca="false">IF(OR(B74="",AND(A74=A73 ,B74=B73)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A74,$B$5:$B$504,B74)+SUMIFS($E$5:$E$504,$A$5:$A$504,A74,$B$5:$B$504,B74)-SUMIFS($F$5:$F$504,$A$5:$A$504,A74,$B$5:$B$504,B74))</f>
         <v/>
       </c>
       <c r="H74" s="33" t="str">
@@ -16953,7 +17121,7 @@
       <c r="E75" s="25"/>
       <c r="F75" s="25"/>
       <c r="G75" s="33" t="str">
-        <f aca="false">IF(OR(B75="",AND(A75=A74 ,B75=B74)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A75,$B$5:$B$504,B75)+SUMIFS($E$5:$E$504,$A$5:$A$504,A75,$B$5:$B$504,B75))</f>
+        <f aca="false">IF(OR(B75="",AND(A75=A74 ,B75=B74)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A75,$B$5:$B$504,B75)+SUMIFS($E$5:$E$504,$A$5:$A$504,A75,$B$5:$B$504,B75)-SUMIFS($F$5:$F$504,$A$5:$A$504,A75,$B$5:$B$504,B75))</f>
         <v/>
       </c>
       <c r="H75" s="33" t="str">
@@ -16971,7 +17139,7 @@
       <c r="E76" s="25"/>
       <c r="F76" s="25"/>
       <c r="G76" s="33" t="str">
-        <f aca="false">IF(OR(B76="",AND(A76=A75 ,B76=B75)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A76,$B$5:$B$504,B76)+SUMIFS($E$5:$E$504,$A$5:$A$504,A76,$B$5:$B$504,B76))</f>
+        <f aca="false">IF(OR(B76="",AND(A76=A75 ,B76=B75)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A76,$B$5:$B$504,B76)+SUMIFS($E$5:$E$504,$A$5:$A$504,A76,$B$5:$B$504,B76)-SUMIFS($F$5:$F$504,$A$5:$A$504,A76,$B$5:$B$504,B76))</f>
         <v/>
       </c>
       <c r="H76" s="33" t="str">
@@ -16989,7 +17157,7 @@
       <c r="E77" s="25"/>
       <c r="F77" s="25"/>
       <c r="G77" s="33" t="str">
-        <f aca="false">IF(OR(B77="",AND(A77=A76 ,B77=B76)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A77,$B$5:$B$504,B77)+SUMIFS($E$5:$E$504,$A$5:$A$504,A77,$B$5:$B$504,B77))</f>
+        <f aca="false">IF(OR(B77="",AND(A77=A76 ,B77=B76)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A77,$B$5:$B$504,B77)+SUMIFS($E$5:$E$504,$A$5:$A$504,A77,$B$5:$B$504,B77)-SUMIFS($F$5:$F$504,$A$5:$A$504,A77,$B$5:$B$504,B77))</f>
         <v/>
       </c>
       <c r="H77" s="33" t="str">
@@ -17007,7 +17175,7 @@
       <c r="E78" s="25"/>
       <c r="F78" s="25"/>
       <c r="G78" s="33" t="str">
-        <f aca="false">IF(OR(B78="",AND(A78=A77 ,B78=B77)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A78,$B$5:$B$504,B78)+SUMIFS($E$5:$E$504,$A$5:$A$504,A78,$B$5:$B$504,B78))</f>
+        <f aca="false">IF(OR(B78="",AND(A78=A77 ,B78=B77)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A78,$B$5:$B$504,B78)+SUMIFS($E$5:$E$504,$A$5:$A$504,A78,$B$5:$B$504,B78)-SUMIFS($F$5:$F$504,$A$5:$A$504,A78,$B$5:$B$504,B78))</f>
         <v/>
       </c>
       <c r="H78" s="33" t="str">
@@ -17025,7 +17193,7 @@
       <c r="E79" s="25"/>
       <c r="F79" s="25"/>
       <c r="G79" s="33" t="str">
-        <f aca="false">IF(OR(B79="",AND(A79=A78 ,B79=B78)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A79,$B$5:$B$504,B79)+SUMIFS($E$5:$E$504,$A$5:$A$504,A79,$B$5:$B$504,B79))</f>
+        <f aca="false">IF(OR(B79="",AND(A79=A78 ,B79=B78)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A79,$B$5:$B$504,B79)+SUMIFS($E$5:$E$504,$A$5:$A$504,A79,$B$5:$B$504,B79)-SUMIFS($F$5:$F$504,$A$5:$A$504,A79,$B$5:$B$504,B79))</f>
         <v/>
       </c>
       <c r="H79" s="33" t="str">
@@ -17043,7 +17211,7 @@
       <c r="E80" s="25"/>
       <c r="F80" s="25"/>
       <c r="G80" s="33" t="str">
-        <f aca="false">IF(OR(B80="",AND(A80=A79 ,B80=B79)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A80,$B$5:$B$504,B80)+SUMIFS($E$5:$E$504,$A$5:$A$504,A80,$B$5:$B$504,B80))</f>
+        <f aca="false">IF(OR(B80="",AND(A80=A79 ,B80=B79)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A80,$B$5:$B$504,B80)+SUMIFS($E$5:$E$504,$A$5:$A$504,A80,$B$5:$B$504,B80)-SUMIFS($F$5:$F$504,$A$5:$A$504,A80,$B$5:$B$504,B80))</f>
         <v/>
       </c>
       <c r="H80" s="33" t="str">
@@ -17061,7 +17229,7 @@
       <c r="E81" s="25"/>
       <c r="F81" s="25"/>
       <c r="G81" s="33" t="str">
-        <f aca="false">IF(OR(B81="",AND(A81=A80 ,B81=B80)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A81,$B$5:$B$504,B81)+SUMIFS($E$5:$E$504,$A$5:$A$504,A81,$B$5:$B$504,B81))</f>
+        <f aca="false">IF(OR(B81="",AND(A81=A80 ,B81=B80)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A81,$B$5:$B$504,B81)+SUMIFS($E$5:$E$504,$A$5:$A$504,A81,$B$5:$B$504,B81)-SUMIFS($F$5:$F$504,$A$5:$A$504,A81,$B$5:$B$504,B81))</f>
         <v/>
       </c>
       <c r="H81" s="33" t="str">
@@ -17079,7 +17247,7 @@
       <c r="E82" s="25"/>
       <c r="F82" s="25"/>
       <c r="G82" s="33" t="str">
-        <f aca="false">IF(OR(B82="",AND(A82=A81 ,B82=B81)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A82,$B$5:$B$504,B82)+SUMIFS($E$5:$E$504,$A$5:$A$504,A82,$B$5:$B$504,B82))</f>
+        <f aca="false">IF(OR(B82="",AND(A82=A81 ,B82=B81)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A82,$B$5:$B$504,B82)+SUMIFS($E$5:$E$504,$A$5:$A$504,A82,$B$5:$B$504,B82)-SUMIFS($F$5:$F$504,$A$5:$A$504,A82,$B$5:$B$504,B82))</f>
         <v/>
       </c>
       <c r="H82" s="33" t="str">
@@ -17097,7 +17265,7 @@
       <c r="E83" s="25"/>
       <c r="F83" s="25"/>
       <c r="G83" s="33" t="str">
-        <f aca="false">IF(OR(B83="",AND(A83=A82 ,B83=B82)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A83,$B$5:$B$504,B83)+SUMIFS($E$5:$E$504,$A$5:$A$504,A83,$B$5:$B$504,B83))</f>
+        <f aca="false">IF(OR(B83="",AND(A83=A82 ,B83=B82)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A83,$B$5:$B$504,B83)+SUMIFS($E$5:$E$504,$A$5:$A$504,A83,$B$5:$B$504,B83)-SUMIFS($F$5:$F$504,$A$5:$A$504,A83,$B$5:$B$504,B83))</f>
         <v/>
       </c>
       <c r="H83" s="33" t="str">
@@ -17115,7 +17283,7 @@
       <c r="E84" s="25"/>
       <c r="F84" s="25"/>
       <c r="G84" s="33" t="str">
-        <f aca="false">IF(OR(B84="",AND(A84=A83 ,B84=B83)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A84,$B$5:$B$504,B84)+SUMIFS($E$5:$E$504,$A$5:$A$504,A84,$B$5:$B$504,B84))</f>
+        <f aca="false">IF(OR(B84="",AND(A84=A83 ,B84=B83)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A84,$B$5:$B$504,B84)+SUMIFS($E$5:$E$504,$A$5:$A$504,A84,$B$5:$B$504,B84)-SUMIFS($F$5:$F$504,$A$5:$A$504,A84,$B$5:$B$504,B84))</f>
         <v/>
       </c>
       <c r="H84" s="33" t="str">
@@ -17133,7 +17301,7 @@
       <c r="E85" s="25"/>
       <c r="F85" s="25"/>
       <c r="G85" s="33" t="str">
-        <f aca="false">IF(OR(B85="",AND(A85=A84 ,B85=B84)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A85,$B$5:$B$504,B85)+SUMIFS($E$5:$E$504,$A$5:$A$504,A85,$B$5:$B$504,B85))</f>
+        <f aca="false">IF(OR(B85="",AND(A85=A84 ,B85=B84)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A85,$B$5:$B$504,B85)+SUMIFS($E$5:$E$504,$A$5:$A$504,A85,$B$5:$B$504,B85)-SUMIFS($F$5:$F$504,$A$5:$A$504,A85,$B$5:$B$504,B85))</f>
         <v/>
       </c>
       <c r="H85" s="33" t="str">
@@ -17151,7 +17319,7 @@
       <c r="E86" s="25"/>
       <c r="F86" s="25"/>
       <c r="G86" s="33" t="str">
-        <f aca="false">IF(OR(B86="",AND(A86=A85 ,B86=B85)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A86,$B$5:$B$504,B86)+SUMIFS($E$5:$E$504,$A$5:$A$504,A86,$B$5:$B$504,B86))</f>
+        <f aca="false">IF(OR(B86="",AND(A86=A85 ,B86=B85)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A86,$B$5:$B$504,B86)+SUMIFS($E$5:$E$504,$A$5:$A$504,A86,$B$5:$B$504,B86)-SUMIFS($F$5:$F$504,$A$5:$A$504,A86,$B$5:$B$504,B86))</f>
         <v/>
       </c>
       <c r="H86" s="33" t="str">
@@ -17169,7 +17337,7 @@
       <c r="E87" s="25"/>
       <c r="F87" s="25"/>
       <c r="G87" s="33" t="str">
-        <f aca="false">IF(OR(B87="",AND(A87=A86 ,B87=B86)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A87,$B$5:$B$504,B87)+SUMIFS($E$5:$E$504,$A$5:$A$504,A87,$B$5:$B$504,B87))</f>
+        <f aca="false">IF(OR(B87="",AND(A87=A86 ,B87=B86)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A87,$B$5:$B$504,B87)+SUMIFS($E$5:$E$504,$A$5:$A$504,A87,$B$5:$B$504,B87)-SUMIFS($F$5:$F$504,$A$5:$A$504,A87,$B$5:$B$504,B87))</f>
         <v/>
       </c>
       <c r="H87" s="33" t="str">
@@ -17187,7 +17355,7 @@
       <c r="E88" s="25"/>
       <c r="F88" s="25"/>
       <c r="G88" s="33" t="str">
-        <f aca="false">IF(OR(B88="",AND(A88=A87 ,B88=B87)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A88,$B$5:$B$504,B88)+SUMIFS($E$5:$E$504,$A$5:$A$504,A88,$B$5:$B$504,B88))</f>
+        <f aca="false">IF(OR(B88="",AND(A88=A87 ,B88=B87)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A88,$B$5:$B$504,B88)+SUMIFS($E$5:$E$504,$A$5:$A$504,A88,$B$5:$B$504,B88)-SUMIFS($F$5:$F$504,$A$5:$A$504,A88,$B$5:$B$504,B88))</f>
         <v/>
       </c>
       <c r="H88" s="33" t="str">
@@ -17205,7 +17373,7 @@
       <c r="E89" s="25"/>
       <c r="F89" s="25"/>
       <c r="G89" s="33" t="str">
-        <f aca="false">IF(OR(B89="",AND(A89=A88 ,B89=B88)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A89,$B$5:$B$504,B89)+SUMIFS($E$5:$E$504,$A$5:$A$504,A89,$B$5:$B$504,B89))</f>
+        <f aca="false">IF(OR(B89="",AND(A89=A88 ,B89=B88)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A89,$B$5:$B$504,B89)+SUMIFS($E$5:$E$504,$A$5:$A$504,A89,$B$5:$B$504,B89)-SUMIFS($F$5:$F$504,$A$5:$A$504,A89,$B$5:$B$504,B89))</f>
         <v/>
       </c>
       <c r="H89" s="33" t="str">
@@ -17223,7 +17391,7 @@
       <c r="E90" s="25"/>
       <c r="F90" s="25"/>
       <c r="G90" s="33" t="str">
-        <f aca="false">IF(OR(B90="",AND(A90=A89 ,B90=B89)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A90,$B$5:$B$504,B90)+SUMIFS($E$5:$E$504,$A$5:$A$504,A90,$B$5:$B$504,B90))</f>
+        <f aca="false">IF(OR(B90="",AND(A90=A89 ,B90=B89)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A90,$B$5:$B$504,B90)+SUMIFS($E$5:$E$504,$A$5:$A$504,A90,$B$5:$B$504,B90)-SUMIFS($F$5:$F$504,$A$5:$A$504,A90,$B$5:$B$504,B90))</f>
         <v/>
       </c>
       <c r="H90" s="33" t="str">
@@ -17241,7 +17409,7 @@
       <c r="E91" s="25"/>
       <c r="F91" s="25"/>
       <c r="G91" s="33" t="str">
-        <f aca="false">IF(OR(B91="",AND(A91=A90 ,B91=B90)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A91,$B$5:$B$504,B91)+SUMIFS($E$5:$E$504,$A$5:$A$504,A91,$B$5:$B$504,B91))</f>
+        <f aca="false">IF(OR(B91="",AND(A91=A90 ,B91=B90)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A91,$B$5:$B$504,B91)+SUMIFS($E$5:$E$504,$A$5:$A$504,A91,$B$5:$B$504,B91)-SUMIFS($F$5:$F$504,$A$5:$A$504,A91,$B$5:$B$504,B91))</f>
         <v/>
       </c>
       <c r="H91" s="33" t="str">
@@ -17259,7 +17427,7 @@
       <c r="E92" s="25"/>
       <c r="F92" s="25"/>
       <c r="G92" s="33" t="str">
-        <f aca="false">IF(OR(B92="",AND(A92=A91 ,B92=B91)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A92,$B$5:$B$504,B92)+SUMIFS($E$5:$E$504,$A$5:$A$504,A92,$B$5:$B$504,B92))</f>
+        <f aca="false">IF(OR(B92="",AND(A92=A91 ,B92=B91)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A92,$B$5:$B$504,B92)+SUMIFS($E$5:$E$504,$A$5:$A$504,A92,$B$5:$B$504,B92)-SUMIFS($F$5:$F$504,$A$5:$A$504,A92,$B$5:$B$504,B92))</f>
         <v/>
       </c>
       <c r="H92" s="33" t="str">
@@ -17277,7 +17445,7 @@
       <c r="E93" s="25"/>
       <c r="F93" s="25"/>
       <c r="G93" s="33" t="str">
-        <f aca="false">IF(OR(B93="",AND(A93=A92 ,B93=B92)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A93,$B$5:$B$504,B93)+SUMIFS($E$5:$E$504,$A$5:$A$504,A93,$B$5:$B$504,B93))</f>
+        <f aca="false">IF(OR(B93="",AND(A93=A92 ,B93=B92)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A93,$B$5:$B$504,B93)+SUMIFS($E$5:$E$504,$A$5:$A$504,A93,$B$5:$B$504,B93)-SUMIFS($F$5:$F$504,$A$5:$A$504,A93,$B$5:$B$504,B93))</f>
         <v/>
       </c>
       <c r="H93" s="33" t="str">
@@ -17295,7 +17463,7 @@
       <c r="E94" s="25"/>
       <c r="F94" s="25"/>
       <c r="G94" s="33" t="str">
-        <f aca="false">IF(OR(B94="",AND(A94=A93 ,B94=B93)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A94,$B$5:$B$504,B94)+SUMIFS($E$5:$E$504,$A$5:$A$504,A94,$B$5:$B$504,B94))</f>
+        <f aca="false">IF(OR(B94="",AND(A94=A93 ,B94=B93)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A94,$B$5:$B$504,B94)+SUMIFS($E$5:$E$504,$A$5:$A$504,A94,$B$5:$B$504,B94)-SUMIFS($F$5:$F$504,$A$5:$A$504,A94,$B$5:$B$504,B94))</f>
         <v/>
       </c>
       <c r="H94" s="33" t="str">
@@ -17313,7 +17481,7 @@
       <c r="E95" s="25"/>
       <c r="F95" s="25"/>
       <c r="G95" s="33" t="str">
-        <f aca="false">IF(OR(B95="",AND(A95=A94 ,B95=B94)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A95,$B$5:$B$504,B95)+SUMIFS($E$5:$E$504,$A$5:$A$504,A95,$B$5:$B$504,B95))</f>
+        <f aca="false">IF(OR(B95="",AND(A95=A94 ,B95=B94)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A95,$B$5:$B$504,B95)+SUMIFS($E$5:$E$504,$A$5:$A$504,A95,$B$5:$B$504,B95)-SUMIFS($F$5:$F$504,$A$5:$A$504,A95,$B$5:$B$504,B95))</f>
         <v/>
       </c>
       <c r="H95" s="33" t="str">
@@ -17331,7 +17499,7 @@
       <c r="E96" s="25"/>
       <c r="F96" s="25"/>
       <c r="G96" s="33" t="str">
-        <f aca="false">IF(OR(B96="",AND(A96=A95 ,B96=B95)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A96,$B$5:$B$504,B96)+SUMIFS($E$5:$E$504,$A$5:$A$504,A96,$B$5:$B$504,B96))</f>
+        <f aca="false">IF(OR(B96="",AND(A96=A95 ,B96=B95)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A96,$B$5:$B$504,B96)+SUMIFS($E$5:$E$504,$A$5:$A$504,A96,$B$5:$B$504,B96)-SUMIFS($F$5:$F$504,$A$5:$A$504,A96,$B$5:$B$504,B96))</f>
         <v/>
       </c>
       <c r="H96" s="33" t="str">
@@ -17349,7 +17517,7 @@
       <c r="E97" s="25"/>
       <c r="F97" s="25"/>
       <c r="G97" s="33" t="str">
-        <f aca="false">IF(OR(B97="",AND(A97=A96 ,B97=B96)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A97,$B$5:$B$504,B97)+SUMIFS($E$5:$E$504,$A$5:$A$504,A97,$B$5:$B$504,B97))</f>
+        <f aca="false">IF(OR(B97="",AND(A97=A96 ,B97=B96)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A97,$B$5:$B$504,B97)+SUMIFS($E$5:$E$504,$A$5:$A$504,A97,$B$5:$B$504,B97)-SUMIFS($F$5:$F$504,$A$5:$A$504,A97,$B$5:$B$504,B97))</f>
         <v/>
       </c>
       <c r="H97" s="33" t="str">
@@ -17367,7 +17535,7 @@
       <c r="E98" s="25"/>
       <c r="F98" s="25"/>
       <c r="G98" s="33" t="str">
-        <f aca="false">IF(OR(B98="",AND(A98=A97 ,B98=B97)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A98,$B$5:$B$504,B98)+SUMIFS($E$5:$E$504,$A$5:$A$504,A98,$B$5:$B$504,B98))</f>
+        <f aca="false">IF(OR(B98="",AND(A98=A97 ,B98=B97)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A98,$B$5:$B$504,B98)+SUMIFS($E$5:$E$504,$A$5:$A$504,A98,$B$5:$B$504,B98)-SUMIFS($F$5:$F$504,$A$5:$A$504,A98,$B$5:$B$504,B98))</f>
         <v/>
       </c>
       <c r="H98" s="33" t="str">
@@ -17385,7 +17553,7 @@
       <c r="E99" s="25"/>
       <c r="F99" s="25"/>
       <c r="G99" s="33" t="str">
-        <f aca="false">IF(OR(B99="",AND(A99=A98 ,B99=B98)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A99,$B$5:$B$504,B99)+SUMIFS($E$5:$E$504,$A$5:$A$504,A99,$B$5:$B$504,B99))</f>
+        <f aca="false">IF(OR(B99="",AND(A99=A98 ,B99=B98)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A99,$B$5:$B$504,B99)+SUMIFS($E$5:$E$504,$A$5:$A$504,A99,$B$5:$B$504,B99)-SUMIFS($F$5:$F$504,$A$5:$A$504,A99,$B$5:$B$504,B99))</f>
         <v/>
       </c>
       <c r="H99" s="33" t="str">
@@ -17403,7 +17571,7 @@
       <c r="E100" s="25"/>
       <c r="F100" s="25"/>
       <c r="G100" s="33" t="str">
-        <f aca="false">IF(OR(B100="",AND(A100=A99 ,B100=B99)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A100,$B$5:$B$504,B100)+SUMIFS($E$5:$E$504,$A$5:$A$504,A100,$B$5:$B$504,B100))</f>
+        <f aca="false">IF(OR(B100="",AND(A100=A99 ,B100=B99)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A100,$B$5:$B$504,B100)+SUMIFS($E$5:$E$504,$A$5:$A$504,A100,$B$5:$B$504,B100)-SUMIFS($F$5:$F$504,$A$5:$A$504,A100,$B$5:$B$504,B100))</f>
         <v/>
       </c>
       <c r="H100" s="33" t="str">
@@ -17421,7 +17589,7 @@
       <c r="E101" s="25"/>
       <c r="F101" s="25"/>
       <c r="G101" s="33" t="str">
-        <f aca="false">IF(OR(B101="",AND(A101=A100 ,B101=B100)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A101,$B$5:$B$504,B101)+SUMIFS($E$5:$E$504,$A$5:$A$504,A101,$B$5:$B$504,B101))</f>
+        <f aca="false">IF(OR(B101="",AND(A101=A100 ,B101=B100)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A101,$B$5:$B$504,B101)+SUMIFS($E$5:$E$504,$A$5:$A$504,A101,$B$5:$B$504,B101)-SUMIFS($F$5:$F$504,$A$5:$A$504,A101,$B$5:$B$504,B101))</f>
         <v/>
       </c>
       <c r="H101" s="33" t="str">
@@ -17439,7 +17607,7 @@
       <c r="E102" s="25"/>
       <c r="F102" s="25"/>
       <c r="G102" s="33" t="str">
-        <f aca="false">IF(OR(B102="",AND(A102=A101 ,B102=B101)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A102,$B$5:$B$504,B102)+SUMIFS($E$5:$E$504,$A$5:$A$504,A102,$B$5:$B$504,B102))</f>
+        <f aca="false">IF(OR(B102="",AND(A102=A101 ,B102=B101)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A102,$B$5:$B$504,B102)+SUMIFS($E$5:$E$504,$A$5:$A$504,A102,$B$5:$B$504,B102)-SUMIFS($F$5:$F$504,$A$5:$A$504,A102,$B$5:$B$504,B102))</f>
         <v/>
       </c>
       <c r="H102" s="33" t="str">
@@ -17457,7 +17625,7 @@
       <c r="E103" s="25"/>
       <c r="F103" s="25"/>
       <c r="G103" s="33" t="str">
-        <f aca="false">IF(OR(B103="",AND(A103=A102 ,B103=B102)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A103,$B$5:$B$504,B103)+SUMIFS($E$5:$E$504,$A$5:$A$504,A103,$B$5:$B$504,B103))</f>
+        <f aca="false">IF(OR(B103="",AND(A103=A102 ,B103=B102)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A103,$B$5:$B$504,B103)+SUMIFS($E$5:$E$504,$A$5:$A$504,A103,$B$5:$B$504,B103)-SUMIFS($F$5:$F$504,$A$5:$A$504,A103,$B$5:$B$504,B103))</f>
         <v/>
       </c>
       <c r="H103" s="33" t="str">
@@ -17475,7 +17643,7 @@
       <c r="E104" s="25"/>
       <c r="F104" s="25"/>
       <c r="G104" s="33" t="str">
-        <f aca="false">IF(OR(B104="",AND(A104=A103 ,B104=B103)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A104,$B$5:$B$504,B104)+SUMIFS($E$5:$E$504,$A$5:$A$504,A104,$B$5:$B$504,B104))</f>
+        <f aca="false">IF(OR(B104="",AND(A104=A103 ,B104=B103)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A104,$B$5:$B$504,B104)+SUMIFS($E$5:$E$504,$A$5:$A$504,A104,$B$5:$B$504,B104)-SUMIFS($F$5:$F$504,$A$5:$A$504,A104,$B$5:$B$504,B104))</f>
         <v/>
       </c>
       <c r="H104" s="33" t="str">
@@ -17493,7 +17661,7 @@
       <c r="E105" s="25"/>
       <c r="F105" s="25"/>
       <c r="G105" s="33" t="str">
-        <f aca="false">IF(OR(B105="",AND(A105=A104 ,B105=B104)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A105,$B$5:$B$504,B105)+SUMIFS($E$5:$E$504,$A$5:$A$504,A105,$B$5:$B$504,B105))</f>
+        <f aca="false">IF(OR(B105="",AND(A105=A104 ,B105=B104)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A105,$B$5:$B$504,B105)+SUMIFS($E$5:$E$504,$A$5:$A$504,A105,$B$5:$B$504,B105)-SUMIFS($F$5:$F$504,$A$5:$A$504,A105,$B$5:$B$504,B105))</f>
         <v/>
       </c>
       <c r="H105" s="33" t="str">
@@ -17511,7 +17679,7 @@
       <c r="E106" s="25"/>
       <c r="F106" s="25"/>
       <c r="G106" s="33" t="str">
-        <f aca="false">IF(OR(B106="",AND(A106=A105 ,B106=B105)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A106,$B$5:$B$504,B106)+SUMIFS($E$5:$E$504,$A$5:$A$504,A106,$B$5:$B$504,B106))</f>
+        <f aca="false">IF(OR(B106="",AND(A106=A105 ,B106=B105)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A106,$B$5:$B$504,B106)+SUMIFS($E$5:$E$504,$A$5:$A$504,A106,$B$5:$B$504,B106)-SUMIFS($F$5:$F$504,$A$5:$A$504,A106,$B$5:$B$504,B106))</f>
         <v/>
       </c>
       <c r="H106" s="33" t="str">
@@ -17529,7 +17697,7 @@
       <c r="E107" s="25"/>
       <c r="F107" s="25"/>
       <c r="G107" s="33" t="str">
-        <f aca="false">IF(OR(B107="",AND(A107=A106 ,B107=B106)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A107,$B$5:$B$504,B107)+SUMIFS($E$5:$E$504,$A$5:$A$504,A107,$B$5:$B$504,B107))</f>
+        <f aca="false">IF(OR(B107="",AND(A107=A106 ,B107=B106)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A107,$B$5:$B$504,B107)+SUMIFS($E$5:$E$504,$A$5:$A$504,A107,$B$5:$B$504,B107)-SUMIFS($F$5:$F$504,$A$5:$A$504,A107,$B$5:$B$504,B107))</f>
         <v/>
       </c>
       <c r="H107" s="33" t="str">
@@ -17547,7 +17715,7 @@
       <c r="E108" s="25"/>
       <c r="F108" s="25"/>
       <c r="G108" s="33" t="str">
-        <f aca="false">IF(OR(B108="",AND(A108=A107 ,B108=B107)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A108,$B$5:$B$504,B108)+SUMIFS($E$5:$E$504,$A$5:$A$504,A108,$B$5:$B$504,B108))</f>
+        <f aca="false">IF(OR(B108="",AND(A108=A107 ,B108=B107)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A108,$B$5:$B$504,B108)+SUMIFS($E$5:$E$504,$A$5:$A$504,A108,$B$5:$B$504,B108)-SUMIFS($F$5:$F$504,$A$5:$A$504,A108,$B$5:$B$504,B108))</f>
         <v/>
       </c>
       <c r="H108" s="33" t="str">
@@ -17565,7 +17733,7 @@
       <c r="E109" s="25"/>
       <c r="F109" s="25"/>
       <c r="G109" s="33" t="str">
-        <f aca="false">IF(OR(B109="",AND(A109=A108 ,B109=B108)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A109,$B$5:$B$504,B109)+SUMIFS($E$5:$E$504,$A$5:$A$504,A109,$B$5:$B$504,B109))</f>
+        <f aca="false">IF(OR(B109="",AND(A109=A108 ,B109=B108)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A109,$B$5:$B$504,B109)+SUMIFS($E$5:$E$504,$A$5:$A$504,A109,$B$5:$B$504,B109)-SUMIFS($F$5:$F$504,$A$5:$A$504,A109,$B$5:$B$504,B109))</f>
         <v/>
       </c>
       <c r="H109" s="33" t="str">
@@ -17583,7 +17751,7 @@
       <c r="E110" s="25"/>
       <c r="F110" s="25"/>
       <c r="G110" s="33" t="str">
-        <f aca="false">IF(OR(B110="",AND(A110=A109 ,B110=B109)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A110,$B$5:$B$504,B110)+SUMIFS($E$5:$E$504,$A$5:$A$504,A110,$B$5:$B$504,B110))</f>
+        <f aca="false">IF(OR(B110="",AND(A110=A109 ,B110=B109)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A110,$B$5:$B$504,B110)+SUMIFS($E$5:$E$504,$A$5:$A$504,A110,$B$5:$B$504,B110)-SUMIFS($F$5:$F$504,$A$5:$A$504,A110,$B$5:$B$504,B110))</f>
         <v/>
       </c>
       <c r="H110" s="33" t="str">
@@ -17601,7 +17769,7 @@
       <c r="E111" s="25"/>
       <c r="F111" s="25"/>
       <c r="G111" s="33" t="str">
-        <f aca="false">IF(OR(B111="",AND(A111=A110 ,B111=B110)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A111,$B$5:$B$504,B111)+SUMIFS($E$5:$E$504,$A$5:$A$504,A111,$B$5:$B$504,B111))</f>
+        <f aca="false">IF(OR(B111="",AND(A111=A110 ,B111=B110)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A111,$B$5:$B$504,B111)+SUMIFS($E$5:$E$504,$A$5:$A$504,A111,$B$5:$B$504,B111)-SUMIFS($F$5:$F$504,$A$5:$A$504,A111,$B$5:$B$504,B111))</f>
         <v/>
       </c>
       <c r="H111" s="33" t="str">
@@ -17619,7 +17787,7 @@
       <c r="E112" s="25"/>
       <c r="F112" s="25"/>
       <c r="G112" s="33" t="str">
-        <f aca="false">IF(OR(B112="",AND(A112=A111 ,B112=B111)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A112,$B$5:$B$504,B112)+SUMIFS($E$5:$E$504,$A$5:$A$504,A112,$B$5:$B$504,B112))</f>
+        <f aca="false">IF(OR(B112="",AND(A112=A111 ,B112=B111)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A112,$B$5:$B$504,B112)+SUMIFS($E$5:$E$504,$A$5:$A$504,A112,$B$5:$B$504,B112)-SUMIFS($F$5:$F$504,$A$5:$A$504,A112,$B$5:$B$504,B112))</f>
         <v/>
       </c>
       <c r="H112" s="33" t="str">
@@ -17637,7 +17805,7 @@
       <c r="E113" s="25"/>
       <c r="F113" s="25"/>
       <c r="G113" s="33" t="str">
-        <f aca="false">IF(OR(B113="",AND(A113=A112 ,B113=B112)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A113,$B$5:$B$504,B113)+SUMIFS($E$5:$E$504,$A$5:$A$504,A113,$B$5:$B$504,B113))</f>
+        <f aca="false">IF(OR(B113="",AND(A113=A112 ,B113=B112)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A113,$B$5:$B$504,B113)+SUMIFS($E$5:$E$504,$A$5:$A$504,A113,$B$5:$B$504,B113)-SUMIFS($F$5:$F$504,$A$5:$A$504,A113,$B$5:$B$504,B113))</f>
         <v/>
       </c>
       <c r="H113" s="33" t="str">
@@ -17655,7 +17823,7 @@
       <c r="E114" s="25"/>
       <c r="F114" s="25"/>
       <c r="G114" s="33" t="str">
-        <f aca="false">IF(OR(B114="",AND(A114=A113 ,B114=B113)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A114,$B$5:$B$504,B114)+SUMIFS($E$5:$E$504,$A$5:$A$504,A114,$B$5:$B$504,B114))</f>
+        <f aca="false">IF(OR(B114="",AND(A114=A113 ,B114=B113)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A114,$B$5:$B$504,B114)+SUMIFS($E$5:$E$504,$A$5:$A$504,A114,$B$5:$B$504,B114)-SUMIFS($F$5:$F$504,$A$5:$A$504,A114,$B$5:$B$504,B114))</f>
         <v/>
       </c>
       <c r="H114" s="33" t="str">
@@ -17673,7 +17841,7 @@
       <c r="E115" s="25"/>
       <c r="F115" s="25"/>
       <c r="G115" s="33" t="str">
-        <f aca="false">IF(OR(B115="",AND(A115=A114 ,B115=B114)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A115,$B$5:$B$504,B115)+SUMIFS($E$5:$E$504,$A$5:$A$504,A115,$B$5:$B$504,B115))</f>
+        <f aca="false">IF(OR(B115="",AND(A115=A114 ,B115=B114)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A115,$B$5:$B$504,B115)+SUMIFS($E$5:$E$504,$A$5:$A$504,A115,$B$5:$B$504,B115)-SUMIFS($F$5:$F$504,$A$5:$A$504,A115,$B$5:$B$504,B115))</f>
         <v/>
       </c>
       <c r="H115" s="33" t="str">
@@ -17691,7 +17859,7 @@
       <c r="E116" s="25"/>
       <c r="F116" s="25"/>
       <c r="G116" s="33" t="str">
-        <f aca="false">IF(OR(B116="",AND(A116=A115 ,B116=B115)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A116,$B$5:$B$504,B116)+SUMIFS($E$5:$E$504,$A$5:$A$504,A116,$B$5:$B$504,B116))</f>
+        <f aca="false">IF(OR(B116="",AND(A116=A115 ,B116=B115)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A116,$B$5:$B$504,B116)+SUMIFS($E$5:$E$504,$A$5:$A$504,A116,$B$5:$B$504,B116)-SUMIFS($F$5:$F$504,$A$5:$A$504,A116,$B$5:$B$504,B116))</f>
         <v/>
       </c>
       <c r="H116" s="33" t="str">
@@ -17709,7 +17877,7 @@
       <c r="E117" s="25"/>
       <c r="F117" s="25"/>
       <c r="G117" s="33" t="str">
-        <f aca="false">IF(OR(B117="",AND(A117=A116 ,B117=B116)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A117,$B$5:$B$504,B117)+SUMIFS($E$5:$E$504,$A$5:$A$504,A117,$B$5:$B$504,B117))</f>
+        <f aca="false">IF(OR(B117="",AND(A117=A116 ,B117=B116)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A117,$B$5:$B$504,B117)+SUMIFS($E$5:$E$504,$A$5:$A$504,A117,$B$5:$B$504,B117)-SUMIFS($F$5:$F$504,$A$5:$A$504,A117,$B$5:$B$504,B117))</f>
         <v/>
       </c>
       <c r="H117" s="33" t="str">
@@ -17727,7 +17895,7 @@
       <c r="E118" s="25"/>
       <c r="F118" s="25"/>
       <c r="G118" s="33" t="str">
-        <f aca="false">IF(OR(B118="",AND(A118=A117 ,B118=B117)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A118,$B$5:$B$504,B118)+SUMIFS($E$5:$E$504,$A$5:$A$504,A118,$B$5:$B$504,B118))</f>
+        <f aca="false">IF(OR(B118="",AND(A118=A117 ,B118=B117)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A118,$B$5:$B$504,B118)+SUMIFS($E$5:$E$504,$A$5:$A$504,A118,$B$5:$B$504,B118)-SUMIFS($F$5:$F$504,$A$5:$A$504,A118,$B$5:$B$504,B118))</f>
         <v/>
       </c>
       <c r="H118" s="33" t="str">
@@ -17745,7 +17913,7 @@
       <c r="E119" s="25"/>
       <c r="F119" s="25"/>
       <c r="G119" s="33" t="str">
-        <f aca="false">IF(OR(B119="",AND(A119=A118 ,B119=B118)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A119,$B$5:$B$504,B119)+SUMIFS($E$5:$E$504,$A$5:$A$504,A119,$B$5:$B$504,B119))</f>
+        <f aca="false">IF(OR(B119="",AND(A119=A118 ,B119=B118)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A119,$B$5:$B$504,B119)+SUMIFS($E$5:$E$504,$A$5:$A$504,A119,$B$5:$B$504,B119)-SUMIFS($F$5:$F$504,$A$5:$A$504,A119,$B$5:$B$504,B119))</f>
         <v/>
       </c>
       <c r="H119" s="33" t="str">
@@ -17763,7 +17931,7 @@
       <c r="E120" s="25"/>
       <c r="F120" s="25"/>
       <c r="G120" s="33" t="str">
-        <f aca="false">IF(OR(B120="",AND(A120=A119 ,B120=B119)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A120,$B$5:$B$504,B120)+SUMIFS($E$5:$E$504,$A$5:$A$504,A120,$B$5:$B$504,B120))</f>
+        <f aca="false">IF(OR(B120="",AND(A120=A119 ,B120=B119)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A120,$B$5:$B$504,B120)+SUMIFS($E$5:$E$504,$A$5:$A$504,A120,$B$5:$B$504,B120)-SUMIFS($F$5:$F$504,$A$5:$A$504,A120,$B$5:$B$504,B120))</f>
         <v/>
       </c>
       <c r="H120" s="33" t="str">
@@ -17781,7 +17949,7 @@
       <c r="E121" s="25"/>
       <c r="F121" s="25"/>
       <c r="G121" s="33" t="str">
-        <f aca="false">IF(OR(B121="",AND(A121=A120 ,B121=B120)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A121,$B$5:$B$504,B121)+SUMIFS($E$5:$E$504,$A$5:$A$504,A121,$B$5:$B$504,B121))</f>
+        <f aca="false">IF(OR(B121="",AND(A121=A120 ,B121=B120)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A121,$B$5:$B$504,B121)+SUMIFS($E$5:$E$504,$A$5:$A$504,A121,$B$5:$B$504,B121)-SUMIFS($F$5:$F$504,$A$5:$A$504,A121,$B$5:$B$504,B121))</f>
         <v/>
       </c>
       <c r="H121" s="33" t="str">
@@ -17799,7 +17967,7 @@
       <c r="E122" s="25"/>
       <c r="F122" s="25"/>
       <c r="G122" s="33" t="str">
-        <f aca="false">IF(OR(B122="",AND(A122=A121 ,B122=B121)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A122,$B$5:$B$504,B122)+SUMIFS($E$5:$E$504,$A$5:$A$504,A122,$B$5:$B$504,B122))</f>
+        <f aca="false">IF(OR(B122="",AND(A122=A121 ,B122=B121)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A122,$B$5:$B$504,B122)+SUMIFS($E$5:$E$504,$A$5:$A$504,A122,$B$5:$B$504,B122)-SUMIFS($F$5:$F$504,$A$5:$A$504,A122,$B$5:$B$504,B122))</f>
         <v/>
       </c>
       <c r="H122" s="33" t="str">
@@ -17817,7 +17985,7 @@
       <c r="E123" s="25"/>
       <c r="F123" s="25"/>
       <c r="G123" s="33" t="str">
-        <f aca="false">IF(OR(B123="",AND(A123=A122 ,B123=B122)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A123,$B$5:$B$504,B123)+SUMIFS($E$5:$E$504,$A$5:$A$504,A123,$B$5:$B$504,B123))</f>
+        <f aca="false">IF(OR(B123="",AND(A123=A122 ,B123=B122)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A123,$B$5:$B$504,B123)+SUMIFS($E$5:$E$504,$A$5:$A$504,A123,$B$5:$B$504,B123)-SUMIFS($F$5:$F$504,$A$5:$A$504,A123,$B$5:$B$504,B123))</f>
         <v/>
       </c>
       <c r="H123" s="33" t="str">
@@ -17835,7 +18003,7 @@
       <c r="E124" s="25"/>
       <c r="F124" s="25"/>
       <c r="G124" s="33" t="str">
-        <f aca="false">IF(OR(B124="",AND(A124=A123 ,B124=B123)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A124,$B$5:$B$504,B124)+SUMIFS($E$5:$E$504,$A$5:$A$504,A124,$B$5:$B$504,B124))</f>
+        <f aca="false">IF(OR(B124="",AND(A124=A123 ,B124=B123)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A124,$B$5:$B$504,B124)+SUMIFS($E$5:$E$504,$A$5:$A$504,A124,$B$5:$B$504,B124)-SUMIFS($F$5:$F$504,$A$5:$A$504,A124,$B$5:$B$504,B124))</f>
         <v/>
       </c>
       <c r="H124" s="33" t="str">
@@ -17853,7 +18021,7 @@
       <c r="E125" s="25"/>
       <c r="F125" s="25"/>
       <c r="G125" s="33" t="str">
-        <f aca="false">IF(OR(B125="",AND(A125=A124 ,B125=B124)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A125,$B$5:$B$504,B125)+SUMIFS($E$5:$E$504,$A$5:$A$504,A125,$B$5:$B$504,B125))</f>
+        <f aca="false">IF(OR(B125="",AND(A125=A124 ,B125=B124)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A125,$B$5:$B$504,B125)+SUMIFS($E$5:$E$504,$A$5:$A$504,A125,$B$5:$B$504,B125)-SUMIFS($F$5:$F$504,$A$5:$A$504,A125,$B$5:$B$504,B125))</f>
         <v/>
       </c>
       <c r="H125" s="33" t="str">
@@ -17871,7 +18039,7 @@
       <c r="E126" s="25"/>
       <c r="F126" s="25"/>
       <c r="G126" s="33" t="str">
-        <f aca="false">IF(OR(B126="",AND(A126=A125 ,B126=B125)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A126,$B$5:$B$504,B126)+SUMIFS($E$5:$E$504,$A$5:$A$504,A126,$B$5:$B$504,B126))</f>
+        <f aca="false">IF(OR(B126="",AND(A126=A125 ,B126=B125)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A126,$B$5:$B$504,B126)+SUMIFS($E$5:$E$504,$A$5:$A$504,A126,$B$5:$B$504,B126)-SUMIFS($F$5:$F$504,$A$5:$A$504,A126,$B$5:$B$504,B126))</f>
         <v/>
       </c>
       <c r="H126" s="33" t="str">
@@ -17889,7 +18057,7 @@
       <c r="E127" s="25"/>
       <c r="F127" s="25"/>
       <c r="G127" s="33" t="str">
-        <f aca="false">IF(OR(B127="",AND(A127=A126 ,B127=B126)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A127,$B$5:$B$504,B127)+SUMIFS($E$5:$E$504,$A$5:$A$504,A127,$B$5:$B$504,B127))</f>
+        <f aca="false">IF(OR(B127="",AND(A127=A126 ,B127=B126)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A127,$B$5:$B$504,B127)+SUMIFS($E$5:$E$504,$A$5:$A$504,A127,$B$5:$B$504,B127)-SUMIFS($F$5:$F$504,$A$5:$A$504,A127,$B$5:$B$504,B127))</f>
         <v/>
       </c>
       <c r="H127" s="33" t="str">
@@ -17907,7 +18075,7 @@
       <c r="E128" s="25"/>
       <c r="F128" s="25"/>
       <c r="G128" s="33" t="str">
-        <f aca="false">IF(OR(B128="",AND(A128=A127 ,B128=B127)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A128,$B$5:$B$504,B128)+SUMIFS($E$5:$E$504,$A$5:$A$504,A128,$B$5:$B$504,B128))</f>
+        <f aca="false">IF(OR(B128="",AND(A128=A127 ,B128=B127)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A128,$B$5:$B$504,B128)+SUMIFS($E$5:$E$504,$A$5:$A$504,A128,$B$5:$B$504,B128)-SUMIFS($F$5:$F$504,$A$5:$A$504,A128,$B$5:$B$504,B128))</f>
         <v/>
       </c>
       <c r="H128" s="33" t="str">
@@ -17925,7 +18093,7 @@
       <c r="E129" s="25"/>
       <c r="F129" s="25"/>
       <c r="G129" s="33" t="str">
-        <f aca="false">IF(OR(B129="",AND(A129=A128 ,B129=B128)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A129,$B$5:$B$504,B129)+SUMIFS($E$5:$E$504,$A$5:$A$504,A129,$B$5:$B$504,B129))</f>
+        <f aca="false">IF(OR(B129="",AND(A129=A128 ,B129=B128)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A129,$B$5:$B$504,B129)+SUMIFS($E$5:$E$504,$A$5:$A$504,A129,$B$5:$B$504,B129)-SUMIFS($F$5:$F$504,$A$5:$A$504,A129,$B$5:$B$504,B129))</f>
         <v/>
       </c>
       <c r="H129" s="33" t="str">
@@ -17943,7 +18111,7 @@
       <c r="E130" s="25"/>
       <c r="F130" s="25"/>
       <c r="G130" s="33" t="str">
-        <f aca="false">IF(OR(B130="",AND(A130=A129 ,B130=B129)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A130,$B$5:$B$504,B130)+SUMIFS($E$5:$E$504,$A$5:$A$504,A130,$B$5:$B$504,B130))</f>
+        <f aca="false">IF(OR(B130="",AND(A130=A129 ,B130=B129)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A130,$B$5:$B$504,B130)+SUMIFS($E$5:$E$504,$A$5:$A$504,A130,$B$5:$B$504,B130)-SUMIFS($F$5:$F$504,$A$5:$A$504,A130,$B$5:$B$504,B130))</f>
         <v/>
       </c>
       <c r="H130" s="33" t="str">
@@ -17961,7 +18129,7 @@
       <c r="E131" s="25"/>
       <c r="F131" s="25"/>
       <c r="G131" s="33" t="str">
-        <f aca="false">IF(OR(B131="",AND(A131=A130 ,B131=B130)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A131,$B$5:$B$504,B131)+SUMIFS($E$5:$E$504,$A$5:$A$504,A131,$B$5:$B$504,B131))</f>
+        <f aca="false">IF(OR(B131="",AND(A131=A130 ,B131=B130)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A131,$B$5:$B$504,B131)+SUMIFS($E$5:$E$504,$A$5:$A$504,A131,$B$5:$B$504,B131)-SUMIFS($F$5:$F$504,$A$5:$A$504,A131,$B$5:$B$504,B131))</f>
         <v/>
       </c>
       <c r="H131" s="33" t="str">
@@ -17979,7 +18147,7 @@
       <c r="E132" s="25"/>
       <c r="F132" s="25"/>
       <c r="G132" s="33" t="str">
-        <f aca="false">IF(OR(B132="",AND(A132=A131 ,B132=B131)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A132,$B$5:$B$504,B132)+SUMIFS($E$5:$E$504,$A$5:$A$504,A132,$B$5:$B$504,B132))</f>
+        <f aca="false">IF(OR(B132="",AND(A132=A131 ,B132=B131)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A132,$B$5:$B$504,B132)+SUMIFS($E$5:$E$504,$A$5:$A$504,A132,$B$5:$B$504,B132)-SUMIFS($F$5:$F$504,$A$5:$A$504,A132,$B$5:$B$504,B132))</f>
         <v/>
       </c>
       <c r="H132" s="33" t="str">
@@ -17997,7 +18165,7 @@
       <c r="E133" s="25"/>
       <c r="F133" s="25"/>
       <c r="G133" s="33" t="str">
-        <f aca="false">IF(OR(B133="",AND(A133=A132 ,B133=B132)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A133,$B$5:$B$504,B133)+SUMIFS($E$5:$E$504,$A$5:$A$504,A133,$B$5:$B$504,B133))</f>
+        <f aca="false">IF(OR(B133="",AND(A133=A132 ,B133=B132)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A133,$B$5:$B$504,B133)+SUMIFS($E$5:$E$504,$A$5:$A$504,A133,$B$5:$B$504,B133)-SUMIFS($F$5:$F$504,$A$5:$A$504,A133,$B$5:$B$504,B133))</f>
         <v/>
       </c>
       <c r="H133" s="33" t="str">
@@ -18015,7 +18183,7 @@
       <c r="E134" s="25"/>
       <c r="F134" s="25"/>
       <c r="G134" s="33" t="str">
-        <f aca="false">IF(OR(B134="",AND(A134=A133 ,B134=B133)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A134,$B$5:$B$504,B134)+SUMIFS($E$5:$E$504,$A$5:$A$504,A134,$B$5:$B$504,B134))</f>
+        <f aca="false">IF(OR(B134="",AND(A134=A133 ,B134=B133)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A134,$B$5:$B$504,B134)+SUMIFS($E$5:$E$504,$A$5:$A$504,A134,$B$5:$B$504,B134)-SUMIFS($F$5:$F$504,$A$5:$A$504,A134,$B$5:$B$504,B134))</f>
         <v/>
       </c>
       <c r="H134" s="33" t="str">
@@ -18033,7 +18201,7 @@
       <c r="E135" s="25"/>
       <c r="F135" s="25"/>
       <c r="G135" s="33" t="str">
-        <f aca="false">IF(OR(B135="",AND(A135=A134 ,B135=B134)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A135,$B$5:$B$504,B135)+SUMIFS($E$5:$E$504,$A$5:$A$504,A135,$B$5:$B$504,B135))</f>
+        <f aca="false">IF(OR(B135="",AND(A135=A134 ,B135=B134)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A135,$B$5:$B$504,B135)+SUMIFS($E$5:$E$504,$A$5:$A$504,A135,$B$5:$B$504,B135)-SUMIFS($F$5:$F$504,$A$5:$A$504,A135,$B$5:$B$504,B135))</f>
         <v/>
       </c>
       <c r="H135" s="33" t="str">
@@ -18051,7 +18219,7 @@
       <c r="E136" s="25"/>
       <c r="F136" s="25"/>
       <c r="G136" s="33" t="str">
-        <f aca="false">IF(OR(B136="",AND(A136=A135 ,B136=B135)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A136,$B$5:$B$504,B136)+SUMIFS($E$5:$E$504,$A$5:$A$504,A136,$B$5:$B$504,B136))</f>
+        <f aca="false">IF(OR(B136="",AND(A136=A135 ,B136=B135)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A136,$B$5:$B$504,B136)+SUMIFS($E$5:$E$504,$A$5:$A$504,A136,$B$5:$B$504,B136)-SUMIFS($F$5:$F$504,$A$5:$A$504,A136,$B$5:$B$504,B136))</f>
         <v/>
       </c>
       <c r="H136" s="33" t="str">
@@ -18069,7 +18237,7 @@
       <c r="E137" s="25"/>
       <c r="F137" s="25"/>
       <c r="G137" s="33" t="str">
-        <f aca="false">IF(OR(B137="",AND(A137=A136 ,B137=B136)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A137,$B$5:$B$504,B137)+SUMIFS($E$5:$E$504,$A$5:$A$504,A137,$B$5:$B$504,B137))</f>
+        <f aca="false">IF(OR(B137="",AND(A137=A136 ,B137=B136)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A137,$B$5:$B$504,B137)+SUMIFS($E$5:$E$504,$A$5:$A$504,A137,$B$5:$B$504,B137)-SUMIFS($F$5:$F$504,$A$5:$A$504,A137,$B$5:$B$504,B137))</f>
         <v/>
       </c>
       <c r="H137" s="33" t="str">
@@ -18087,7 +18255,7 @@
       <c r="E138" s="25"/>
       <c r="F138" s="25"/>
       <c r="G138" s="33" t="str">
-        <f aca="false">IF(OR(B138="",AND(A138=A137 ,B138=B137)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A138,$B$5:$B$504,B138)+SUMIFS($E$5:$E$504,$A$5:$A$504,A138,$B$5:$B$504,B138))</f>
+        <f aca="false">IF(OR(B138="",AND(A138=A137 ,B138=B137)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A138,$B$5:$B$504,B138)+SUMIFS($E$5:$E$504,$A$5:$A$504,A138,$B$5:$B$504,B138)-SUMIFS($F$5:$F$504,$A$5:$A$504,A138,$B$5:$B$504,B138))</f>
         <v/>
       </c>
       <c r="H138" s="33" t="str">
@@ -18105,7 +18273,7 @@
       <c r="E139" s="25"/>
       <c r="F139" s="25"/>
       <c r="G139" s="33" t="str">
-        <f aca="false">IF(OR(B139="",AND(A139=A138 ,B139=B138)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A139,$B$5:$B$504,B139)+SUMIFS($E$5:$E$504,$A$5:$A$504,A139,$B$5:$B$504,B139))</f>
+        <f aca="false">IF(OR(B139="",AND(A139=A138 ,B139=B138)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A139,$B$5:$B$504,B139)+SUMIFS($E$5:$E$504,$A$5:$A$504,A139,$B$5:$B$504,B139)-SUMIFS($F$5:$F$504,$A$5:$A$504,A139,$B$5:$B$504,B139))</f>
         <v/>
       </c>
       <c r="H139" s="33" t="str">
@@ -18123,7 +18291,7 @@
       <c r="E140" s="25"/>
       <c r="F140" s="25"/>
       <c r="G140" s="33" t="str">
-        <f aca="false">IF(OR(B140="",AND(A140=A139 ,B140=B139)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A140,$B$5:$B$504,B140)+SUMIFS($E$5:$E$504,$A$5:$A$504,A140,$B$5:$B$504,B140))</f>
+        <f aca="false">IF(OR(B140="",AND(A140=A139 ,B140=B139)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A140,$B$5:$B$504,B140)+SUMIFS($E$5:$E$504,$A$5:$A$504,A140,$B$5:$B$504,B140)-SUMIFS($F$5:$F$504,$A$5:$A$504,A140,$B$5:$B$504,B140))</f>
         <v/>
       </c>
       <c r="H140" s="33" t="str">
@@ -18141,7 +18309,7 @@
       <c r="E141" s="25"/>
       <c r="F141" s="25"/>
       <c r="G141" s="33" t="str">
-        <f aca="false">IF(OR(B141="",AND(A141=A140 ,B141=B140)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A141,$B$5:$B$504,B141)+SUMIFS($E$5:$E$504,$A$5:$A$504,A141,$B$5:$B$504,B141))</f>
+        <f aca="false">IF(OR(B141="",AND(A141=A140 ,B141=B140)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A141,$B$5:$B$504,B141)+SUMIFS($E$5:$E$504,$A$5:$A$504,A141,$B$5:$B$504,B141)-SUMIFS($F$5:$F$504,$A$5:$A$504,A141,$B$5:$B$504,B141))</f>
         <v/>
       </c>
       <c r="H141" s="33" t="str">
@@ -18159,7 +18327,7 @@
       <c r="E142" s="25"/>
       <c r="F142" s="25"/>
       <c r="G142" s="33" t="str">
-        <f aca="false">IF(OR(B142="",AND(A142=A141 ,B142=B141)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A142,$B$5:$B$504,B142)+SUMIFS($E$5:$E$504,$A$5:$A$504,A142,$B$5:$B$504,B142))</f>
+        <f aca="false">IF(OR(B142="",AND(A142=A141 ,B142=B141)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A142,$B$5:$B$504,B142)+SUMIFS($E$5:$E$504,$A$5:$A$504,A142,$B$5:$B$504,B142)-SUMIFS($F$5:$F$504,$A$5:$A$504,A142,$B$5:$B$504,B142))</f>
         <v/>
       </c>
       <c r="H142" s="33" t="str">
@@ -18177,7 +18345,7 @@
       <c r="E143" s="25"/>
       <c r="F143" s="25"/>
       <c r="G143" s="33" t="str">
-        <f aca="false">IF(OR(B143="",AND(A143=A142 ,B143=B142)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A143,$B$5:$B$504,B143)+SUMIFS($E$5:$E$504,$A$5:$A$504,A143,$B$5:$B$504,B143))</f>
+        <f aca="false">IF(OR(B143="",AND(A143=A142 ,B143=B142)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A143,$B$5:$B$504,B143)+SUMIFS($E$5:$E$504,$A$5:$A$504,A143,$B$5:$B$504,B143)-SUMIFS($F$5:$F$504,$A$5:$A$504,A143,$B$5:$B$504,B143))</f>
         <v/>
       </c>
       <c r="H143" s="33" t="str">
@@ -18195,7 +18363,7 @@
       <c r="E144" s="25"/>
       <c r="F144" s="25"/>
       <c r="G144" s="33" t="str">
-        <f aca="false">IF(OR(B144="",AND(A144=A143 ,B144=B143)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A144,$B$5:$B$504,B144)+SUMIFS($E$5:$E$504,$A$5:$A$504,A144,$B$5:$B$504,B144))</f>
+        <f aca="false">IF(OR(B144="",AND(A144=A143 ,B144=B143)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A144,$B$5:$B$504,B144)+SUMIFS($E$5:$E$504,$A$5:$A$504,A144,$B$5:$B$504,B144)-SUMIFS($F$5:$F$504,$A$5:$A$504,A144,$B$5:$B$504,B144))</f>
         <v/>
       </c>
       <c r="H144" s="33" t="str">
@@ -18213,7 +18381,7 @@
       <c r="E145" s="25"/>
       <c r="F145" s="25"/>
       <c r="G145" s="33" t="str">
-        <f aca="false">IF(OR(B145="",AND(A145=A144 ,B145=B144)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A145,$B$5:$B$504,B145)+SUMIFS($E$5:$E$504,$A$5:$A$504,A145,$B$5:$B$504,B145))</f>
+        <f aca="false">IF(OR(B145="",AND(A145=A144 ,B145=B144)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A145,$B$5:$B$504,B145)+SUMIFS($E$5:$E$504,$A$5:$A$504,A145,$B$5:$B$504,B145)-SUMIFS($F$5:$F$504,$A$5:$A$504,A145,$B$5:$B$504,B145))</f>
         <v/>
       </c>
       <c r="H145" s="33" t="str">
@@ -18231,7 +18399,7 @@
       <c r="E146" s="25"/>
       <c r="F146" s="25"/>
       <c r="G146" s="33" t="str">
-        <f aca="false">IF(OR(B146="",AND(A146=A145 ,B146=B145)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A146,$B$5:$B$504,B146)+SUMIFS($E$5:$E$504,$A$5:$A$504,A146,$B$5:$B$504,B146))</f>
+        <f aca="false">IF(OR(B146="",AND(A146=A145 ,B146=B145)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A146,$B$5:$B$504,B146)+SUMIFS($E$5:$E$504,$A$5:$A$504,A146,$B$5:$B$504,B146)-SUMIFS($F$5:$F$504,$A$5:$A$504,A146,$B$5:$B$504,B146))</f>
         <v/>
       </c>
       <c r="H146" s="33" t="str">
@@ -18249,7 +18417,7 @@
       <c r="E147" s="25"/>
       <c r="F147" s="25"/>
       <c r="G147" s="33" t="str">
-        <f aca="false">IF(OR(B147="",AND(A147=A146 ,B147=B146)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A147,$B$5:$B$504,B147)+SUMIFS($E$5:$E$504,$A$5:$A$504,A147,$B$5:$B$504,B147))</f>
+        <f aca="false">IF(OR(B147="",AND(A147=A146 ,B147=B146)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A147,$B$5:$B$504,B147)+SUMIFS($E$5:$E$504,$A$5:$A$504,A147,$B$5:$B$504,B147)-SUMIFS($F$5:$F$504,$A$5:$A$504,A147,$B$5:$B$504,B147))</f>
         <v/>
       </c>
       <c r="H147" s="33" t="str">
@@ -18267,7 +18435,7 @@
       <c r="E148" s="25"/>
       <c r="F148" s="25"/>
       <c r="G148" s="33" t="str">
-        <f aca="false">IF(OR(B148="",AND(A148=A147 ,B148=B147)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A148,$B$5:$B$504,B148)+SUMIFS($E$5:$E$504,$A$5:$A$504,A148,$B$5:$B$504,B148))</f>
+        <f aca="false">IF(OR(B148="",AND(A148=A147 ,B148=B147)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A148,$B$5:$B$504,B148)+SUMIFS($E$5:$E$504,$A$5:$A$504,A148,$B$5:$B$504,B148)-SUMIFS($F$5:$F$504,$A$5:$A$504,A148,$B$5:$B$504,B148))</f>
         <v/>
       </c>
       <c r="H148" s="33" t="str">
@@ -18285,7 +18453,7 @@
       <c r="E149" s="25"/>
       <c r="F149" s="25"/>
       <c r="G149" s="33" t="str">
-        <f aca="false">IF(OR(B149="",AND(A149=A148 ,B149=B148)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A149,$B$5:$B$504,B149)+SUMIFS($E$5:$E$504,$A$5:$A$504,A149,$B$5:$B$504,B149))</f>
+        <f aca="false">IF(OR(B149="",AND(A149=A148 ,B149=B148)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A149,$B$5:$B$504,B149)+SUMIFS($E$5:$E$504,$A$5:$A$504,A149,$B$5:$B$504,B149)-SUMIFS($F$5:$F$504,$A$5:$A$504,A149,$B$5:$B$504,B149))</f>
         <v/>
       </c>
       <c r="H149" s="33" t="str">
@@ -18303,7 +18471,7 @@
       <c r="E150" s="25"/>
       <c r="F150" s="25"/>
       <c r="G150" s="33" t="str">
-        <f aca="false">IF(OR(B150="",AND(A150=A149 ,B150=B149)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A150,$B$5:$B$504,B150)+SUMIFS($E$5:$E$504,$A$5:$A$504,A150,$B$5:$B$504,B150))</f>
+        <f aca="false">IF(OR(B150="",AND(A150=A149 ,B150=B149)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A150,$B$5:$B$504,B150)+SUMIFS($E$5:$E$504,$A$5:$A$504,A150,$B$5:$B$504,B150)-SUMIFS($F$5:$F$504,$A$5:$A$504,A150,$B$5:$B$504,B150))</f>
         <v/>
       </c>
       <c r="H150" s="33" t="str">
@@ -18321,7 +18489,7 @@
       <c r="E151" s="25"/>
       <c r="F151" s="25"/>
       <c r="G151" s="33" t="str">
-        <f aca="false">IF(OR(B151="",AND(A151=A150 ,B151=B150)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A151,$B$5:$B$504,B151)+SUMIFS($E$5:$E$504,$A$5:$A$504,A151,$B$5:$B$504,B151))</f>
+        <f aca="false">IF(OR(B151="",AND(A151=A150 ,B151=B150)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A151,$B$5:$B$504,B151)+SUMIFS($E$5:$E$504,$A$5:$A$504,A151,$B$5:$B$504,B151)-SUMIFS($F$5:$F$504,$A$5:$A$504,A151,$B$5:$B$504,B151))</f>
         <v/>
       </c>
       <c r="H151" s="33" t="str">
@@ -18339,7 +18507,7 @@
       <c r="E152" s="25"/>
       <c r="F152" s="25"/>
       <c r="G152" s="33" t="str">
-        <f aca="false">IF(OR(B152="",AND(A152=A151 ,B152=B151)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A152,$B$5:$B$504,B152)+SUMIFS($E$5:$E$504,$A$5:$A$504,A152,$B$5:$B$504,B152))</f>
+        <f aca="false">IF(OR(B152="",AND(A152=A151 ,B152=B151)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A152,$B$5:$B$504,B152)+SUMIFS($E$5:$E$504,$A$5:$A$504,A152,$B$5:$B$504,B152)-SUMIFS($F$5:$F$504,$A$5:$A$504,A152,$B$5:$B$504,B152))</f>
         <v/>
       </c>
       <c r="H152" s="33" t="str">
@@ -18357,7 +18525,7 @@
       <c r="E153" s="25"/>
       <c r="F153" s="25"/>
       <c r="G153" s="33" t="str">
-        <f aca="false">IF(OR(B153="",AND(A153=A152 ,B153=B152)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A153,$B$5:$B$504,B153)+SUMIFS($E$5:$E$504,$A$5:$A$504,A153,$B$5:$B$504,B153))</f>
+        <f aca="false">IF(OR(B153="",AND(A153=A152 ,B153=B152)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A153,$B$5:$B$504,B153)+SUMIFS($E$5:$E$504,$A$5:$A$504,A153,$B$5:$B$504,B153)-SUMIFS($F$5:$F$504,$A$5:$A$504,A153,$B$5:$B$504,B153))</f>
         <v/>
       </c>
       <c r="H153" s="33" t="str">
@@ -18375,7 +18543,7 @@
       <c r="E154" s="25"/>
       <c r="F154" s="25"/>
       <c r="G154" s="33" t="str">
-        <f aca="false">IF(OR(B154="",AND(A154=A153 ,B154=B153)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A154,$B$5:$B$504,B154)+SUMIFS($E$5:$E$504,$A$5:$A$504,A154,$B$5:$B$504,B154))</f>
+        <f aca="false">IF(OR(B154="",AND(A154=A153 ,B154=B153)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A154,$B$5:$B$504,B154)+SUMIFS($E$5:$E$504,$A$5:$A$504,A154,$B$5:$B$504,B154)-SUMIFS($F$5:$F$504,$A$5:$A$504,A154,$B$5:$B$504,B154))</f>
         <v/>
       </c>
       <c r="H154" s="33" t="str">
@@ -18393,7 +18561,7 @@
       <c r="E155" s="25"/>
       <c r="F155" s="25"/>
       <c r="G155" s="33" t="str">
-        <f aca="false">IF(OR(B155="",AND(A155=A154 ,B155=B154)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A155,$B$5:$B$504,B155)+SUMIFS($E$5:$E$504,$A$5:$A$504,A155,$B$5:$B$504,B155))</f>
+        <f aca="false">IF(OR(B155="",AND(A155=A154 ,B155=B154)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A155,$B$5:$B$504,B155)+SUMIFS($E$5:$E$504,$A$5:$A$504,A155,$B$5:$B$504,B155)-SUMIFS($F$5:$F$504,$A$5:$A$504,A155,$B$5:$B$504,B155))</f>
         <v/>
       </c>
       <c r="H155" s="33" t="str">
@@ -18411,7 +18579,7 @@
       <c r="E156" s="25"/>
       <c r="F156" s="25"/>
       <c r="G156" s="33" t="str">
-        <f aca="false">IF(OR(B156="",AND(A156=A155 ,B156=B155)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A156,$B$5:$B$504,B156)+SUMIFS($E$5:$E$504,$A$5:$A$504,A156,$B$5:$B$504,B156))</f>
+        <f aca="false">IF(OR(B156="",AND(A156=A155 ,B156=B155)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A156,$B$5:$B$504,B156)+SUMIFS($E$5:$E$504,$A$5:$A$504,A156,$B$5:$B$504,B156)-SUMIFS($F$5:$F$504,$A$5:$A$504,A156,$B$5:$B$504,B156))</f>
         <v/>
       </c>
       <c r="H156" s="33" t="str">
@@ -18429,7 +18597,7 @@
       <c r="E157" s="25"/>
       <c r="F157" s="25"/>
       <c r="G157" s="33" t="str">
-        <f aca="false">IF(OR(B157="",AND(A157=A156 ,B157=B156)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A157,$B$5:$B$504,B157)+SUMIFS($E$5:$E$504,$A$5:$A$504,A157,$B$5:$B$504,B157))</f>
+        <f aca="false">IF(OR(B157="",AND(A157=A156 ,B157=B156)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A157,$B$5:$B$504,B157)+SUMIFS($E$5:$E$504,$A$5:$A$504,A157,$B$5:$B$504,B157)-SUMIFS($F$5:$F$504,$A$5:$A$504,A157,$B$5:$B$504,B157))</f>
         <v/>
       </c>
       <c r="H157" s="33" t="str">
@@ -18447,7 +18615,7 @@
       <c r="E158" s="25"/>
       <c r="F158" s="25"/>
       <c r="G158" s="33" t="str">
-        <f aca="false">IF(OR(B158="",AND(A158=A157 ,B158=B157)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A158,$B$5:$B$504,B158)+SUMIFS($E$5:$E$504,$A$5:$A$504,A158,$B$5:$B$504,B158))</f>
+        <f aca="false">IF(OR(B158="",AND(A158=A157 ,B158=B157)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A158,$B$5:$B$504,B158)+SUMIFS($E$5:$E$504,$A$5:$A$504,A158,$B$5:$B$504,B158)-SUMIFS($F$5:$F$504,$A$5:$A$504,A158,$B$5:$B$504,B158))</f>
         <v/>
       </c>
       <c r="H158" s="33" t="str">
@@ -18465,7 +18633,7 @@
       <c r="E159" s="25"/>
       <c r="F159" s="25"/>
       <c r="G159" s="33" t="str">
-        <f aca="false">IF(OR(B159="",AND(A159=A158 ,B159=B158)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A159,$B$5:$B$504,B159)+SUMIFS($E$5:$E$504,$A$5:$A$504,A159,$B$5:$B$504,B159))</f>
+        <f aca="false">IF(OR(B159="",AND(A159=A158 ,B159=B158)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A159,$B$5:$B$504,B159)+SUMIFS($E$5:$E$504,$A$5:$A$504,A159,$B$5:$B$504,B159)-SUMIFS($F$5:$F$504,$A$5:$A$504,A159,$B$5:$B$504,B159))</f>
         <v/>
       </c>
       <c r="H159" s="33" t="str">
@@ -18483,7 +18651,7 @@
       <c r="E160" s="25"/>
       <c r="F160" s="25"/>
       <c r="G160" s="33" t="str">
-        <f aca="false">IF(OR(B160="",AND(A160=A159 ,B160=B159)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A160,$B$5:$B$504,B160)+SUMIFS($E$5:$E$504,$A$5:$A$504,A160,$B$5:$B$504,B160))</f>
+        <f aca="false">IF(OR(B160="",AND(A160=A159 ,B160=B159)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A160,$B$5:$B$504,B160)+SUMIFS($E$5:$E$504,$A$5:$A$504,A160,$B$5:$B$504,B160)-SUMIFS($F$5:$F$504,$A$5:$A$504,A160,$B$5:$B$504,B160))</f>
         <v/>
       </c>
       <c r="H160" s="33" t="str">
@@ -18501,7 +18669,7 @@
       <c r="E161" s="25"/>
       <c r="F161" s="25"/>
       <c r="G161" s="33" t="str">
-        <f aca="false">IF(OR(B161="",AND(A161=A160 ,B161=B160)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A161,$B$5:$B$504,B161)+SUMIFS($E$5:$E$504,$A$5:$A$504,A161,$B$5:$B$504,B161))</f>
+        <f aca="false">IF(OR(B161="",AND(A161=A160 ,B161=B160)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A161,$B$5:$B$504,B161)+SUMIFS($E$5:$E$504,$A$5:$A$504,A161,$B$5:$B$504,B161)-SUMIFS($F$5:$F$504,$A$5:$A$504,A161,$B$5:$B$504,B161))</f>
         <v/>
       </c>
       <c r="H161" s="33" t="str">
@@ -18519,7 +18687,7 @@
       <c r="E162" s="25"/>
       <c r="F162" s="25"/>
       <c r="G162" s="33" t="str">
-        <f aca="false">IF(OR(B162="",AND(A162=A161 ,B162=B161)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A162,$B$5:$B$504,B162)+SUMIFS($E$5:$E$504,$A$5:$A$504,A162,$B$5:$B$504,B162))</f>
+        <f aca="false">IF(OR(B162="",AND(A162=A161 ,B162=B161)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A162,$B$5:$B$504,B162)+SUMIFS($E$5:$E$504,$A$5:$A$504,A162,$B$5:$B$504,B162)-SUMIFS($F$5:$F$504,$A$5:$A$504,A162,$B$5:$B$504,B162))</f>
         <v/>
       </c>
       <c r="H162" s="33" t="str">
@@ -18537,7 +18705,7 @@
       <c r="E163" s="25"/>
       <c r="F163" s="25"/>
       <c r="G163" s="33" t="str">
-        <f aca="false">IF(OR(B163="",AND(A163=A162 ,B163=B162)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A163,$B$5:$B$504,B163)+SUMIFS($E$5:$E$504,$A$5:$A$504,A163,$B$5:$B$504,B163))</f>
+        <f aca="false">IF(OR(B163="",AND(A163=A162 ,B163=B162)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A163,$B$5:$B$504,B163)+SUMIFS($E$5:$E$504,$A$5:$A$504,A163,$B$5:$B$504,B163)-SUMIFS($F$5:$F$504,$A$5:$A$504,A163,$B$5:$B$504,B163))</f>
         <v/>
       </c>
       <c r="H163" s="33" t="str">
@@ -18555,7 +18723,7 @@
       <c r="E164" s="25"/>
       <c r="F164" s="25"/>
       <c r="G164" s="33" t="str">
-        <f aca="false">IF(OR(B164="",AND(A164=A163 ,B164=B163)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A164,$B$5:$B$504,B164)+SUMIFS($E$5:$E$504,$A$5:$A$504,A164,$B$5:$B$504,B164))</f>
+        <f aca="false">IF(OR(B164="",AND(A164=A163 ,B164=B163)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A164,$B$5:$B$504,B164)+SUMIFS($E$5:$E$504,$A$5:$A$504,A164,$B$5:$B$504,B164)-SUMIFS($F$5:$F$504,$A$5:$A$504,A164,$B$5:$B$504,B164))</f>
         <v/>
       </c>
       <c r="H164" s="33" t="str">
@@ -18573,7 +18741,7 @@
       <c r="E165" s="25"/>
       <c r="F165" s="25"/>
       <c r="G165" s="33" t="str">
-        <f aca="false">IF(OR(B165="",AND(A165=A164 ,B165=B164)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A165,$B$5:$B$504,B165)+SUMIFS($E$5:$E$504,$A$5:$A$504,A165,$B$5:$B$504,B165))</f>
+        <f aca="false">IF(OR(B165="",AND(A165=A164 ,B165=B164)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A165,$B$5:$B$504,B165)+SUMIFS($E$5:$E$504,$A$5:$A$504,A165,$B$5:$B$504,B165)-SUMIFS($F$5:$F$504,$A$5:$A$504,A165,$B$5:$B$504,B165))</f>
         <v/>
       </c>
       <c r="H165" s="33" t="str">
@@ -18591,7 +18759,7 @@
       <c r="E166" s="25"/>
       <c r="F166" s="25"/>
       <c r="G166" s="33" t="str">
-        <f aca="false">IF(OR(B166="",AND(A166=A165 ,B166=B165)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A166,$B$5:$B$504,B166)+SUMIFS($E$5:$E$504,$A$5:$A$504,A166,$B$5:$B$504,B166))</f>
+        <f aca="false">IF(OR(B166="",AND(A166=A165 ,B166=B165)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A166,$B$5:$B$504,B166)+SUMIFS($E$5:$E$504,$A$5:$A$504,A166,$B$5:$B$504,B166)-SUMIFS($F$5:$F$504,$A$5:$A$504,A166,$B$5:$B$504,B166))</f>
         <v/>
       </c>
       <c r="H166" s="33" t="str">
@@ -18609,7 +18777,7 @@
       <c r="E167" s="25"/>
       <c r="F167" s="25"/>
       <c r="G167" s="33" t="str">
-        <f aca="false">IF(OR(B167="",AND(A167=A166 ,B167=B166)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A167,$B$5:$B$504,B167)+SUMIFS($E$5:$E$504,$A$5:$A$504,A167,$B$5:$B$504,B167))</f>
+        <f aca="false">IF(OR(B167="",AND(A167=A166 ,B167=B166)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A167,$B$5:$B$504,B167)+SUMIFS($E$5:$E$504,$A$5:$A$504,A167,$B$5:$B$504,B167)-SUMIFS($F$5:$F$504,$A$5:$A$504,A167,$B$5:$B$504,B167))</f>
         <v/>
       </c>
       <c r="H167" s="33" t="str">
@@ -18627,7 +18795,7 @@
       <c r="E168" s="25"/>
       <c r="F168" s="25"/>
       <c r="G168" s="33" t="str">
-        <f aca="false">IF(OR(B168="",AND(A168=A167 ,B168=B167)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A168,$B$5:$B$504,B168)+SUMIFS($E$5:$E$504,$A$5:$A$504,A168,$B$5:$B$504,B168))</f>
+        <f aca="false">IF(OR(B168="",AND(A168=A167 ,B168=B167)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A168,$B$5:$B$504,B168)+SUMIFS($E$5:$E$504,$A$5:$A$504,A168,$B$5:$B$504,B168)-SUMIFS($F$5:$F$504,$A$5:$A$504,A168,$B$5:$B$504,B168))</f>
         <v/>
       </c>
       <c r="H168" s="33" t="str">
@@ -18645,7 +18813,7 @@
       <c r="E169" s="25"/>
       <c r="F169" s="25"/>
       <c r="G169" s="33" t="str">
-        <f aca="false">IF(OR(B169="",AND(A169=A168 ,B169=B168)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A169,$B$5:$B$504,B169)+SUMIFS($E$5:$E$504,$A$5:$A$504,A169,$B$5:$B$504,B169))</f>
+        <f aca="false">IF(OR(B169="",AND(A169=A168 ,B169=B168)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A169,$B$5:$B$504,B169)+SUMIFS($E$5:$E$504,$A$5:$A$504,A169,$B$5:$B$504,B169)-SUMIFS($F$5:$F$504,$A$5:$A$504,A169,$B$5:$B$504,B169))</f>
         <v/>
       </c>
       <c r="H169" s="33" t="str">
@@ -18663,7 +18831,7 @@
       <c r="E170" s="25"/>
       <c r="F170" s="25"/>
       <c r="G170" s="33" t="str">
-        <f aca="false">IF(OR(B170="",AND(A170=A169 ,B170=B169)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A170,$B$5:$B$504,B170)+SUMIFS($E$5:$E$504,$A$5:$A$504,A170,$B$5:$B$504,B170))</f>
+        <f aca="false">IF(OR(B170="",AND(A170=A169 ,B170=B169)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A170,$B$5:$B$504,B170)+SUMIFS($E$5:$E$504,$A$5:$A$504,A170,$B$5:$B$504,B170)-SUMIFS($F$5:$F$504,$A$5:$A$504,A170,$B$5:$B$504,B170))</f>
         <v/>
       </c>
       <c r="H170" s="33" t="str">
@@ -18681,7 +18849,7 @@
       <c r="E171" s="25"/>
       <c r="F171" s="25"/>
       <c r="G171" s="33" t="str">
-        <f aca="false">IF(OR(B171="",AND(A171=A170 ,B171=B170)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A171,$B$5:$B$504,B171)+SUMIFS($E$5:$E$504,$A$5:$A$504,A171,$B$5:$B$504,B171))</f>
+        <f aca="false">IF(OR(B171="",AND(A171=A170 ,B171=B170)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A171,$B$5:$B$504,B171)+SUMIFS($E$5:$E$504,$A$5:$A$504,A171,$B$5:$B$504,B171)-SUMIFS($F$5:$F$504,$A$5:$A$504,A171,$B$5:$B$504,B171))</f>
         <v/>
       </c>
       <c r="H171" s="33" t="str">
@@ -18699,7 +18867,7 @@
       <c r="E172" s="25"/>
       <c r="F172" s="25"/>
       <c r="G172" s="33" t="str">
-        <f aca="false">IF(OR(B172="",AND(A172=A171 ,B172=B171)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A172,$B$5:$B$504,B172)+SUMIFS($E$5:$E$504,$A$5:$A$504,A172,$B$5:$B$504,B172))</f>
+        <f aca="false">IF(OR(B172="",AND(A172=A171 ,B172=B171)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A172,$B$5:$B$504,B172)+SUMIFS($E$5:$E$504,$A$5:$A$504,A172,$B$5:$B$504,B172)-SUMIFS($F$5:$F$504,$A$5:$A$504,A172,$B$5:$B$504,B172))</f>
         <v/>
       </c>
       <c r="H172" s="33" t="str">
@@ -18717,7 +18885,7 @@
       <c r="E173" s="25"/>
       <c r="F173" s="25"/>
       <c r="G173" s="33" t="str">
-        <f aca="false">IF(OR(B173="",AND(A173=A172 ,B173=B172)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A173,$B$5:$B$504,B173)+SUMIFS($E$5:$E$504,$A$5:$A$504,A173,$B$5:$B$504,B173))</f>
+        <f aca="false">IF(OR(B173="",AND(A173=A172 ,B173=B172)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A173,$B$5:$B$504,B173)+SUMIFS($E$5:$E$504,$A$5:$A$504,A173,$B$5:$B$504,B173)-SUMIFS($F$5:$F$504,$A$5:$A$504,A173,$B$5:$B$504,B173))</f>
         <v/>
       </c>
       <c r="H173" s="33" t="str">
@@ -18735,7 +18903,7 @@
       <c r="E174" s="25"/>
       <c r="F174" s="25"/>
       <c r="G174" s="33" t="str">
-        <f aca="false">IF(OR(B174="",AND(A174=A173 ,B174=B173)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A174,$B$5:$B$504,B174)+SUMIFS($E$5:$E$504,$A$5:$A$504,A174,$B$5:$B$504,B174))</f>
+        <f aca="false">IF(OR(B174="",AND(A174=A173 ,B174=B173)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A174,$B$5:$B$504,B174)+SUMIFS($E$5:$E$504,$A$5:$A$504,A174,$B$5:$B$504,B174)-SUMIFS($F$5:$F$504,$A$5:$A$504,A174,$B$5:$B$504,B174))</f>
         <v/>
       </c>
       <c r="H174" s="33" t="str">
@@ -18753,7 +18921,7 @@
       <c r="E175" s="25"/>
       <c r="F175" s="25"/>
       <c r="G175" s="33" t="str">
-        <f aca="false">IF(OR(B175="",AND(A175=A174 ,B175=B174)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A175,$B$5:$B$504,B175)+SUMIFS($E$5:$E$504,$A$5:$A$504,A175,$B$5:$B$504,B175))</f>
+        <f aca="false">IF(OR(B175="",AND(A175=A174 ,B175=B174)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A175,$B$5:$B$504,B175)+SUMIFS($E$5:$E$504,$A$5:$A$504,A175,$B$5:$B$504,B175)-SUMIFS($F$5:$F$504,$A$5:$A$504,A175,$B$5:$B$504,B175))</f>
         <v/>
       </c>
       <c r="H175" s="33" t="str">
@@ -18771,7 +18939,7 @@
       <c r="E176" s="25"/>
       <c r="F176" s="25"/>
       <c r="G176" s="33" t="str">
-        <f aca="false">IF(OR(B176="",AND(A176=A175 ,B176=B175)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A176,$B$5:$B$504,B176)+SUMIFS($E$5:$E$504,$A$5:$A$504,A176,$B$5:$B$504,B176))</f>
+        <f aca="false">IF(OR(B176="",AND(A176=A175 ,B176=B175)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A176,$B$5:$B$504,B176)+SUMIFS($E$5:$E$504,$A$5:$A$504,A176,$B$5:$B$504,B176)-SUMIFS($F$5:$F$504,$A$5:$A$504,A176,$B$5:$B$504,B176))</f>
         <v/>
       </c>
       <c r="H176" s="33" t="str">
@@ -18789,7 +18957,7 @@
       <c r="E177" s="25"/>
       <c r="F177" s="25"/>
       <c r="G177" s="33" t="str">
-        <f aca="false">IF(OR(B177="",AND(A177=A176 ,B177=B176)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A177,$B$5:$B$504,B177)+SUMIFS($E$5:$E$504,$A$5:$A$504,A177,$B$5:$B$504,B177))</f>
+        <f aca="false">IF(OR(B177="",AND(A177=A176 ,B177=B176)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A177,$B$5:$B$504,B177)+SUMIFS($E$5:$E$504,$A$5:$A$504,A177,$B$5:$B$504,B177)-SUMIFS($F$5:$F$504,$A$5:$A$504,A177,$B$5:$B$504,B177))</f>
         <v/>
       </c>
       <c r="H177" s="33" t="str">
@@ -18807,7 +18975,7 @@
       <c r="E178" s="25"/>
       <c r="F178" s="25"/>
       <c r="G178" s="33" t="str">
-        <f aca="false">IF(OR(B178="",AND(A178=A177 ,B178=B177)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A178,$B$5:$B$504,B178)+SUMIFS($E$5:$E$504,$A$5:$A$504,A178,$B$5:$B$504,B178))</f>
+        <f aca="false">IF(OR(B178="",AND(A178=A177 ,B178=B177)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A178,$B$5:$B$504,B178)+SUMIFS($E$5:$E$504,$A$5:$A$504,A178,$B$5:$B$504,B178)-SUMIFS($F$5:$F$504,$A$5:$A$504,A178,$B$5:$B$504,B178))</f>
         <v/>
       </c>
       <c r="H178" s="33" t="str">
@@ -18825,7 +18993,7 @@
       <c r="E179" s="25"/>
       <c r="F179" s="25"/>
       <c r="G179" s="33" t="str">
-        <f aca="false">IF(OR(B179="",AND(A179=A178 ,B179=B178)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A179,$B$5:$B$504,B179)+SUMIFS($E$5:$E$504,$A$5:$A$504,A179,$B$5:$B$504,B179))</f>
+        <f aca="false">IF(OR(B179="",AND(A179=A178 ,B179=B178)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A179,$B$5:$B$504,B179)+SUMIFS($E$5:$E$504,$A$5:$A$504,A179,$B$5:$B$504,B179)-SUMIFS($F$5:$F$504,$A$5:$A$504,A179,$B$5:$B$504,B179))</f>
         <v/>
       </c>
       <c r="H179" s="33" t="str">
@@ -18843,7 +19011,7 @@
       <c r="E180" s="25"/>
       <c r="F180" s="25"/>
       <c r="G180" s="33" t="str">
-        <f aca="false">IF(OR(B180="",AND(A180=A179 ,B180=B179)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A180,$B$5:$B$504,B180)+SUMIFS($E$5:$E$504,$A$5:$A$504,A180,$B$5:$B$504,B180))</f>
+        <f aca="false">IF(OR(B180="",AND(A180=A179 ,B180=B179)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A180,$B$5:$B$504,B180)+SUMIFS($E$5:$E$504,$A$5:$A$504,A180,$B$5:$B$504,B180)-SUMIFS($F$5:$F$504,$A$5:$A$504,A180,$B$5:$B$504,B180))</f>
         <v/>
       </c>
       <c r="H180" s="33" t="str">
@@ -18861,7 +19029,7 @@
       <c r="E181" s="25"/>
       <c r="F181" s="25"/>
       <c r="G181" s="33" t="str">
-        <f aca="false">IF(OR(B181="",AND(A181=A180 ,B181=B180)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A181,$B$5:$B$504,B181)+SUMIFS($E$5:$E$504,$A$5:$A$504,A181,$B$5:$B$504,B181))</f>
+        <f aca="false">IF(OR(B181="",AND(A181=A180 ,B181=B180)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A181,$B$5:$B$504,B181)+SUMIFS($E$5:$E$504,$A$5:$A$504,A181,$B$5:$B$504,B181)-SUMIFS($F$5:$F$504,$A$5:$A$504,A181,$B$5:$B$504,B181))</f>
         <v/>
       </c>
       <c r="H181" s="33" t="str">
@@ -18879,7 +19047,7 @@
       <c r="E182" s="25"/>
       <c r="F182" s="25"/>
       <c r="G182" s="33" t="str">
-        <f aca="false">IF(OR(B182="",AND(A182=A181 ,B182=B181)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A182,$B$5:$B$504,B182)+SUMIFS($E$5:$E$504,$A$5:$A$504,A182,$B$5:$B$504,B182))</f>
+        <f aca="false">IF(OR(B182="",AND(A182=A181 ,B182=B181)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A182,$B$5:$B$504,B182)+SUMIFS($E$5:$E$504,$A$5:$A$504,A182,$B$5:$B$504,B182)-SUMIFS($F$5:$F$504,$A$5:$A$504,A182,$B$5:$B$504,B182))</f>
         <v/>
       </c>
       <c r="H182" s="33" t="str">
@@ -18897,7 +19065,7 @@
       <c r="E183" s="25"/>
       <c r="F183" s="25"/>
       <c r="G183" s="33" t="str">
-        <f aca="false">IF(OR(B183="",AND(A183=A182 ,B183=B182)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A183,$B$5:$B$504,B183)+SUMIFS($E$5:$E$504,$A$5:$A$504,A183,$B$5:$B$504,B183))</f>
+        <f aca="false">IF(OR(B183="",AND(A183=A182 ,B183=B182)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A183,$B$5:$B$504,B183)+SUMIFS($E$5:$E$504,$A$5:$A$504,A183,$B$5:$B$504,B183)-SUMIFS($F$5:$F$504,$A$5:$A$504,A183,$B$5:$B$504,B183))</f>
         <v/>
       </c>
       <c r="H183" s="33" t="str">
@@ -18915,7 +19083,7 @@
       <c r="E184" s="25"/>
       <c r="F184" s="25"/>
       <c r="G184" s="33" t="str">
-        <f aca="false">IF(OR(B184="",AND(A184=A183 ,B184=B183)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A184,$B$5:$B$504,B184)+SUMIFS($E$5:$E$504,$A$5:$A$504,A184,$B$5:$B$504,B184))</f>
+        <f aca="false">IF(OR(B184="",AND(A184=A183 ,B184=B183)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A184,$B$5:$B$504,B184)+SUMIFS($E$5:$E$504,$A$5:$A$504,A184,$B$5:$B$504,B184)-SUMIFS($F$5:$F$504,$A$5:$A$504,A184,$B$5:$B$504,B184))</f>
         <v/>
       </c>
       <c r="H184" s="33" t="str">
@@ -18933,7 +19101,7 @@
       <c r="E185" s="25"/>
       <c r="F185" s="25"/>
       <c r="G185" s="33" t="str">
-        <f aca="false">IF(OR(B185="",AND(A185=A184 ,B185=B184)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A185,$B$5:$B$504,B185)+SUMIFS($E$5:$E$504,$A$5:$A$504,A185,$B$5:$B$504,B185))</f>
+        <f aca="false">IF(OR(B185="",AND(A185=A184 ,B185=B184)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A185,$B$5:$B$504,B185)+SUMIFS($E$5:$E$504,$A$5:$A$504,A185,$B$5:$B$504,B185)-SUMIFS($F$5:$F$504,$A$5:$A$504,A185,$B$5:$B$504,B185))</f>
         <v/>
       </c>
       <c r="H185" s="33" t="str">
@@ -18951,7 +19119,7 @@
       <c r="E186" s="25"/>
       <c r="F186" s="25"/>
       <c r="G186" s="33" t="str">
-        <f aca="false">IF(OR(B186="",AND(A186=A185 ,B186=B185)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A186,$B$5:$B$504,B186)+SUMIFS($E$5:$E$504,$A$5:$A$504,A186,$B$5:$B$504,B186))</f>
+        <f aca="false">IF(OR(B186="",AND(A186=A185 ,B186=B185)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A186,$B$5:$B$504,B186)+SUMIFS($E$5:$E$504,$A$5:$A$504,A186,$B$5:$B$504,B186)-SUMIFS($F$5:$F$504,$A$5:$A$504,A186,$B$5:$B$504,B186))</f>
         <v/>
       </c>
       <c r="H186" s="33" t="str">
@@ -18969,7 +19137,7 @@
       <c r="E187" s="25"/>
       <c r="F187" s="25"/>
       <c r="G187" s="33" t="str">
-        <f aca="false">IF(OR(B187="",AND(A187=A186 ,B187=B186)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A187,$B$5:$B$504,B187)+SUMIFS($E$5:$E$504,$A$5:$A$504,A187,$B$5:$B$504,B187))</f>
+        <f aca="false">IF(OR(B187="",AND(A187=A186 ,B187=B186)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A187,$B$5:$B$504,B187)+SUMIFS($E$5:$E$504,$A$5:$A$504,A187,$B$5:$B$504,B187)-SUMIFS($F$5:$F$504,$A$5:$A$504,A187,$B$5:$B$504,B187))</f>
         <v/>
       </c>
       <c r="H187" s="33" t="str">
@@ -18987,7 +19155,7 @@
       <c r="E188" s="25"/>
       <c r="F188" s="25"/>
       <c r="G188" s="33" t="str">
-        <f aca="false">IF(OR(B188="",AND(A188=A187 ,B188=B187)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A188,$B$5:$B$504,B188)+SUMIFS($E$5:$E$504,$A$5:$A$504,A188,$B$5:$B$504,B188))</f>
+        <f aca="false">IF(OR(B188="",AND(A188=A187 ,B188=B187)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A188,$B$5:$B$504,B188)+SUMIFS($E$5:$E$504,$A$5:$A$504,A188,$B$5:$B$504,B188)-SUMIFS($F$5:$F$504,$A$5:$A$504,A188,$B$5:$B$504,B188))</f>
         <v/>
       </c>
       <c r="H188" s="33" t="str">
@@ -19005,7 +19173,7 @@
       <c r="E189" s="25"/>
       <c r="F189" s="25"/>
       <c r="G189" s="33" t="str">
-        <f aca="false">IF(OR(B189="",AND(A189=A188 ,B189=B188)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A189,$B$5:$B$504,B189)+SUMIFS($E$5:$E$504,$A$5:$A$504,A189,$B$5:$B$504,B189))</f>
+        <f aca="false">IF(OR(B189="",AND(A189=A188 ,B189=B188)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A189,$B$5:$B$504,B189)+SUMIFS($E$5:$E$504,$A$5:$A$504,A189,$B$5:$B$504,B189)-SUMIFS($F$5:$F$504,$A$5:$A$504,A189,$B$5:$B$504,B189))</f>
         <v/>
       </c>
       <c r="H189" s="33" t="str">
@@ -19023,7 +19191,7 @@
       <c r="E190" s="25"/>
       <c r="F190" s="25"/>
       <c r="G190" s="33" t="str">
-        <f aca="false">IF(OR(B190="",AND(A190=A189 ,B190=B189)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A190,$B$5:$B$504,B190)+SUMIFS($E$5:$E$504,$A$5:$A$504,A190,$B$5:$B$504,B190))</f>
+        <f aca="false">IF(OR(B190="",AND(A190=A189 ,B190=B189)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A190,$B$5:$B$504,B190)+SUMIFS($E$5:$E$504,$A$5:$A$504,A190,$B$5:$B$504,B190)-SUMIFS($F$5:$F$504,$A$5:$A$504,A190,$B$5:$B$504,B190))</f>
         <v/>
       </c>
       <c r="H190" s="33" t="str">
@@ -19041,7 +19209,7 @@
       <c r="E191" s="25"/>
       <c r="F191" s="25"/>
       <c r="G191" s="33" t="str">
-        <f aca="false">IF(OR(B191="",AND(A191=A190 ,B191=B190)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A191,$B$5:$B$504,B191)+SUMIFS($E$5:$E$504,$A$5:$A$504,A191,$B$5:$B$504,B191))</f>
+        <f aca="false">IF(OR(B191="",AND(A191=A190 ,B191=B190)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A191,$B$5:$B$504,B191)+SUMIFS($E$5:$E$504,$A$5:$A$504,A191,$B$5:$B$504,B191)-SUMIFS($F$5:$F$504,$A$5:$A$504,A191,$B$5:$B$504,B191))</f>
         <v/>
       </c>
       <c r="H191" s="33" t="str">
@@ -19059,7 +19227,7 @@
       <c r="E192" s="25"/>
       <c r="F192" s="25"/>
       <c r="G192" s="33" t="str">
-        <f aca="false">IF(OR(B192="",AND(A192=A191 ,B192=B191)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A192,$B$5:$B$504,B192)+SUMIFS($E$5:$E$504,$A$5:$A$504,A192,$B$5:$B$504,B192))</f>
+        <f aca="false">IF(OR(B192="",AND(A192=A191 ,B192=B191)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A192,$B$5:$B$504,B192)+SUMIFS($E$5:$E$504,$A$5:$A$504,A192,$B$5:$B$504,B192)-SUMIFS($F$5:$F$504,$A$5:$A$504,A192,$B$5:$B$504,B192))</f>
         <v/>
       </c>
       <c r="H192" s="33" t="str">
@@ -19077,7 +19245,7 @@
       <c r="E193" s="25"/>
       <c r="F193" s="25"/>
       <c r="G193" s="33" t="str">
-        <f aca="false">IF(OR(B193="",AND(A193=A192 ,B193=B192)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A193,$B$5:$B$504,B193)+SUMIFS($E$5:$E$504,$A$5:$A$504,A193,$B$5:$B$504,B193))</f>
+        <f aca="false">IF(OR(B193="",AND(A193=A192 ,B193=B192)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A193,$B$5:$B$504,B193)+SUMIFS($E$5:$E$504,$A$5:$A$504,A193,$B$5:$B$504,B193)-SUMIFS($F$5:$F$504,$A$5:$A$504,A193,$B$5:$B$504,B193))</f>
         <v/>
       </c>
       <c r="H193" s="33" t="str">
@@ -19095,7 +19263,7 @@
       <c r="E194" s="25"/>
       <c r="F194" s="25"/>
       <c r="G194" s="33" t="str">
-        <f aca="false">IF(OR(B194="",AND(A194=A193 ,B194=B193)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A194,$B$5:$B$504,B194)+SUMIFS($E$5:$E$504,$A$5:$A$504,A194,$B$5:$B$504,B194))</f>
+        <f aca="false">IF(OR(B194="",AND(A194=A193 ,B194=B193)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A194,$B$5:$B$504,B194)+SUMIFS($E$5:$E$504,$A$5:$A$504,A194,$B$5:$B$504,B194)-SUMIFS($F$5:$F$504,$A$5:$A$504,A194,$B$5:$B$504,B194))</f>
         <v/>
       </c>
       <c r="H194" s="33" t="str">
@@ -19113,7 +19281,7 @@
       <c r="E195" s="25"/>
       <c r="F195" s="25"/>
       <c r="G195" s="33" t="str">
-        <f aca="false">IF(OR(B195="",AND(A195=A194 ,B195=B194)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A195,$B$5:$B$504,B195)+SUMIFS($E$5:$E$504,$A$5:$A$504,A195,$B$5:$B$504,B195))</f>
+        <f aca="false">IF(OR(B195="",AND(A195=A194 ,B195=B194)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A195,$B$5:$B$504,B195)+SUMIFS($E$5:$E$504,$A$5:$A$504,A195,$B$5:$B$504,B195)-SUMIFS($F$5:$F$504,$A$5:$A$504,A195,$B$5:$B$504,B195))</f>
         <v/>
       </c>
       <c r="H195" s="33" t="str">
@@ -19131,7 +19299,7 @@
       <c r="E196" s="25"/>
       <c r="F196" s="25"/>
       <c r="G196" s="33" t="str">
-        <f aca="false">IF(OR(B196="",AND(A196=A195 ,B196=B195)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A196,$B$5:$B$504,B196)+SUMIFS($E$5:$E$504,$A$5:$A$504,A196,$B$5:$B$504,B196))</f>
+        <f aca="false">IF(OR(B196="",AND(A196=A195 ,B196=B195)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A196,$B$5:$B$504,B196)+SUMIFS($E$5:$E$504,$A$5:$A$504,A196,$B$5:$B$504,B196)-SUMIFS($F$5:$F$504,$A$5:$A$504,A196,$B$5:$B$504,B196))</f>
         <v/>
       </c>
       <c r="H196" s="33" t="str">
@@ -19149,7 +19317,7 @@
       <c r="E197" s="25"/>
       <c r="F197" s="25"/>
       <c r="G197" s="33" t="str">
-        <f aca="false">IF(OR(B197="",AND(A197=A196 ,B197=B196)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A197,$B$5:$B$504,B197)+SUMIFS($E$5:$E$504,$A$5:$A$504,A197,$B$5:$B$504,B197))</f>
+        <f aca="false">IF(OR(B197="",AND(A197=A196 ,B197=B196)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A197,$B$5:$B$504,B197)+SUMIFS($E$5:$E$504,$A$5:$A$504,A197,$B$5:$B$504,B197)-SUMIFS($F$5:$F$504,$A$5:$A$504,A197,$B$5:$B$504,B197))</f>
         <v/>
       </c>
       <c r="H197" s="33" t="str">
@@ -19167,7 +19335,7 @@
       <c r="E198" s="25"/>
       <c r="F198" s="25"/>
       <c r="G198" s="33" t="str">
-        <f aca="false">IF(OR(B198="",AND(A198=A197 ,B198=B197)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A198,$B$5:$B$504,B198)+SUMIFS($E$5:$E$504,$A$5:$A$504,A198,$B$5:$B$504,B198))</f>
+        <f aca="false">IF(OR(B198="",AND(A198=A197 ,B198=B197)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A198,$B$5:$B$504,B198)+SUMIFS($E$5:$E$504,$A$5:$A$504,A198,$B$5:$B$504,B198)-SUMIFS($F$5:$F$504,$A$5:$A$504,A198,$B$5:$B$504,B198))</f>
         <v/>
       </c>
       <c r="H198" s="33" t="str">
@@ -19185,7 +19353,7 @@
       <c r="E199" s="25"/>
       <c r="F199" s="25"/>
       <c r="G199" s="33" t="str">
-        <f aca="false">IF(OR(B199="",AND(A199=A198 ,B199=B198)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A199,$B$5:$B$504,B199)+SUMIFS($E$5:$E$504,$A$5:$A$504,A199,$B$5:$B$504,B199))</f>
+        <f aca="false">IF(OR(B199="",AND(A199=A198 ,B199=B198)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A199,$B$5:$B$504,B199)+SUMIFS($E$5:$E$504,$A$5:$A$504,A199,$B$5:$B$504,B199)-SUMIFS($F$5:$F$504,$A$5:$A$504,A199,$B$5:$B$504,B199))</f>
         <v/>
       </c>
       <c r="H199" s="33" t="str">
@@ -19203,7 +19371,7 @@
       <c r="E200" s="25"/>
       <c r="F200" s="25"/>
       <c r="G200" s="33" t="str">
-        <f aca="false">IF(OR(B200="",AND(A200=A199 ,B200=B199)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A200,$B$5:$B$504,B200)+SUMIFS($E$5:$E$504,$A$5:$A$504,A200,$B$5:$B$504,B200))</f>
+        <f aca="false">IF(OR(B200="",AND(A200=A199 ,B200=B199)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A200,$B$5:$B$504,B200)+SUMIFS($E$5:$E$504,$A$5:$A$504,A200,$B$5:$B$504,B200)-SUMIFS($F$5:$F$504,$A$5:$A$504,A200,$B$5:$B$504,B200))</f>
         <v/>
       </c>
       <c r="H200" s="33" t="str">
@@ -19221,7 +19389,7 @@
       <c r="E201" s="25"/>
       <c r="F201" s="25"/>
       <c r="G201" s="33" t="str">
-        <f aca="false">IF(OR(B201="",AND(A201=A200 ,B201=B200)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A201,$B$5:$B$504,B201)+SUMIFS($E$5:$E$504,$A$5:$A$504,A201,$B$5:$B$504,B201))</f>
+        <f aca="false">IF(OR(B201="",AND(A201=A200 ,B201=B200)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A201,$B$5:$B$504,B201)+SUMIFS($E$5:$E$504,$A$5:$A$504,A201,$B$5:$B$504,B201)-SUMIFS($F$5:$F$504,$A$5:$A$504,A201,$B$5:$B$504,B201))</f>
         <v/>
       </c>
       <c r="H201" s="33" t="str">
@@ -19239,7 +19407,7 @@
       <c r="E202" s="25"/>
       <c r="F202" s="25"/>
       <c r="G202" s="33" t="str">
-        <f aca="false">IF(OR(B202="",AND(A202=A201 ,B202=B201)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A202,$B$5:$B$504,B202)+SUMIFS($E$5:$E$504,$A$5:$A$504,A202,$B$5:$B$504,B202))</f>
+        <f aca="false">IF(OR(B202="",AND(A202=A201 ,B202=B201)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A202,$B$5:$B$504,B202)+SUMIFS($E$5:$E$504,$A$5:$A$504,A202,$B$5:$B$504,B202)-SUMIFS($F$5:$F$504,$A$5:$A$504,A202,$B$5:$B$504,B202))</f>
         <v/>
       </c>
       <c r="H202" s="33" t="str">
@@ -19257,7 +19425,7 @@
       <c r="E203" s="25"/>
       <c r="F203" s="25"/>
       <c r="G203" s="33" t="str">
-        <f aca="false">IF(OR(B203="",AND(A203=A202 ,B203=B202)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A203,$B$5:$B$504,B203)+SUMIFS($E$5:$E$504,$A$5:$A$504,A203,$B$5:$B$504,B203))</f>
+        <f aca="false">IF(OR(B203="",AND(A203=A202 ,B203=B202)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A203,$B$5:$B$504,B203)+SUMIFS($E$5:$E$504,$A$5:$A$504,A203,$B$5:$B$504,B203)-SUMIFS($F$5:$F$504,$A$5:$A$504,A203,$B$5:$B$504,B203))</f>
         <v/>
       </c>
       <c r="H203" s="33" t="str">
@@ -19275,7 +19443,7 @@
       <c r="E204" s="25"/>
       <c r="F204" s="25"/>
       <c r="G204" s="33" t="str">
-        <f aca="false">IF(OR(B204="",AND(A204=A203 ,B204=B203)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A204,$B$5:$B$504,B204)+SUMIFS($E$5:$E$504,$A$5:$A$504,A204,$B$5:$B$504,B204))</f>
+        <f aca="false">IF(OR(B204="",AND(A204=A203 ,B204=B203)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A204,$B$5:$B$504,B204)+SUMIFS($E$5:$E$504,$A$5:$A$504,A204,$B$5:$B$504,B204)-SUMIFS($F$5:$F$504,$A$5:$A$504,A204,$B$5:$B$504,B204))</f>
         <v/>
       </c>
       <c r="H204" s="33" t="str">
@@ -19293,7 +19461,7 @@
       <c r="E205" s="25"/>
       <c r="F205" s="25"/>
       <c r="G205" s="33" t="str">
-        <f aca="false">IF(OR(B205="",AND(A205=A204 ,B205=B204)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A205,$B$5:$B$504,B205)+SUMIFS($E$5:$E$504,$A$5:$A$504,A205,$B$5:$B$504,B205))</f>
+        <f aca="false">IF(OR(B205="",AND(A205=A204 ,B205=B204)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A205,$B$5:$B$504,B205)+SUMIFS($E$5:$E$504,$A$5:$A$504,A205,$B$5:$B$504,B205)-SUMIFS($F$5:$F$504,$A$5:$A$504,A205,$B$5:$B$504,B205))</f>
         <v/>
       </c>
       <c r="H205" s="33" t="str">
@@ -19311,7 +19479,7 @@
       <c r="E206" s="25"/>
       <c r="F206" s="25"/>
       <c r="G206" s="33" t="str">
-        <f aca="false">IF(OR(B206="",AND(A206=A205 ,B206=B205)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A206,$B$5:$B$504,B206)+SUMIFS($E$5:$E$504,$A$5:$A$504,A206,$B$5:$B$504,B206))</f>
+        <f aca="false">IF(OR(B206="",AND(A206=A205 ,B206=B205)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A206,$B$5:$B$504,B206)+SUMIFS($E$5:$E$504,$A$5:$A$504,A206,$B$5:$B$504,B206)-SUMIFS($F$5:$F$504,$A$5:$A$504,A206,$B$5:$B$504,B206))</f>
         <v/>
       </c>
       <c r="H206" s="33" t="str">
@@ -19329,7 +19497,7 @@
       <c r="E207" s="25"/>
       <c r="F207" s="25"/>
       <c r="G207" s="33" t="str">
-        <f aca="false">IF(OR(B207="",AND(A207=A206 ,B207=B206)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A207,$B$5:$B$504,B207)+SUMIFS($E$5:$E$504,$A$5:$A$504,A207,$B$5:$B$504,B207))</f>
+        <f aca="false">IF(OR(B207="",AND(A207=A206 ,B207=B206)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A207,$B$5:$B$504,B207)+SUMIFS($E$5:$E$504,$A$5:$A$504,A207,$B$5:$B$504,B207)-SUMIFS($F$5:$F$504,$A$5:$A$504,A207,$B$5:$B$504,B207))</f>
         <v/>
       </c>
       <c r="H207" s="33" t="str">
@@ -19347,7 +19515,7 @@
       <c r="E208" s="25"/>
       <c r="F208" s="25"/>
       <c r="G208" s="33" t="str">
-        <f aca="false">IF(OR(B208="",AND(A208=A207 ,B208=B207)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A208,$B$5:$B$504,B208)+SUMIFS($E$5:$E$504,$A$5:$A$504,A208,$B$5:$B$504,B208))</f>
+        <f aca="false">IF(OR(B208="",AND(A208=A207 ,B208=B207)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A208,$B$5:$B$504,B208)+SUMIFS($E$5:$E$504,$A$5:$A$504,A208,$B$5:$B$504,B208)-SUMIFS($F$5:$F$504,$A$5:$A$504,A208,$B$5:$B$504,B208))</f>
         <v/>
       </c>
       <c r="H208" s="33" t="str">
@@ -19365,7 +19533,7 @@
       <c r="E209" s="25"/>
       <c r="F209" s="25"/>
       <c r="G209" s="33" t="str">
-        <f aca="false">IF(OR(B209="",AND(A209=A208 ,B209=B208)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A209,$B$5:$B$504,B209)+SUMIFS($E$5:$E$504,$A$5:$A$504,A209,$B$5:$B$504,B209))</f>
+        <f aca="false">IF(OR(B209="",AND(A209=A208 ,B209=B208)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A209,$B$5:$B$504,B209)+SUMIFS($E$5:$E$504,$A$5:$A$504,A209,$B$5:$B$504,B209)-SUMIFS($F$5:$F$504,$A$5:$A$504,A209,$B$5:$B$504,B209))</f>
         <v/>
       </c>
       <c r="H209" s="33" t="str">
@@ -19383,7 +19551,7 @@
       <c r="E210" s="25"/>
       <c r="F210" s="25"/>
       <c r="G210" s="33" t="str">
-        <f aca="false">IF(OR(B210="",AND(A210=A209 ,B210=B209)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A210,$B$5:$B$504,B210)+SUMIFS($E$5:$E$504,$A$5:$A$504,A210,$B$5:$B$504,B210))</f>
+        <f aca="false">IF(OR(B210="",AND(A210=A209 ,B210=B209)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A210,$B$5:$B$504,B210)+SUMIFS($E$5:$E$504,$A$5:$A$504,A210,$B$5:$B$504,B210)-SUMIFS($F$5:$F$504,$A$5:$A$504,A210,$B$5:$B$504,B210))</f>
         <v/>
       </c>
       <c r="H210" s="33" t="str">
@@ -19401,7 +19569,7 @@
       <c r="E211" s="25"/>
       <c r="F211" s="25"/>
       <c r="G211" s="33" t="str">
-        <f aca="false">IF(OR(B211="",AND(A211=A210 ,B211=B210)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A211,$B$5:$B$504,B211)+SUMIFS($E$5:$E$504,$A$5:$A$504,A211,$B$5:$B$504,B211))</f>
+        <f aca="false">IF(OR(B211="",AND(A211=A210 ,B211=B210)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A211,$B$5:$B$504,B211)+SUMIFS($E$5:$E$504,$A$5:$A$504,A211,$B$5:$B$504,B211)-SUMIFS($F$5:$F$504,$A$5:$A$504,A211,$B$5:$B$504,B211))</f>
         <v/>
       </c>
       <c r="H211" s="33" t="str">
@@ -19419,7 +19587,7 @@
       <c r="E212" s="25"/>
       <c r="F212" s="25"/>
       <c r="G212" s="33" t="str">
-        <f aca="false">IF(OR(B212="",AND(A212=A211 ,B212=B211)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A212,$B$5:$B$504,B212)+SUMIFS($E$5:$E$504,$A$5:$A$504,A212,$B$5:$B$504,B212))</f>
+        <f aca="false">IF(OR(B212="",AND(A212=A211 ,B212=B211)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A212,$B$5:$B$504,B212)+SUMIFS($E$5:$E$504,$A$5:$A$504,A212,$B$5:$B$504,B212)-SUMIFS($F$5:$F$504,$A$5:$A$504,A212,$B$5:$B$504,B212))</f>
         <v/>
       </c>
       <c r="H212" s="33" t="str">
@@ -19437,7 +19605,7 @@
       <c r="E213" s="25"/>
       <c r="F213" s="25"/>
       <c r="G213" s="33" t="str">
-        <f aca="false">IF(OR(B213="",AND(A213=A212 ,B213=B212)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A213,$B$5:$B$504,B213)+SUMIFS($E$5:$E$504,$A$5:$A$504,A213,$B$5:$B$504,B213))</f>
+        <f aca="false">IF(OR(B213="",AND(A213=A212 ,B213=B212)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A213,$B$5:$B$504,B213)+SUMIFS($E$5:$E$504,$A$5:$A$504,A213,$B$5:$B$504,B213)-SUMIFS($F$5:$F$504,$A$5:$A$504,A213,$B$5:$B$504,B213))</f>
         <v/>
       </c>
       <c r="H213" s="33" t="str">
@@ -19455,7 +19623,7 @@
       <c r="E214" s="25"/>
       <c r="F214" s="25"/>
       <c r="G214" s="33" t="str">
-        <f aca="false">IF(OR(B214="",AND(A214=A213 ,B214=B213)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A214,$B$5:$B$504,B214)+SUMIFS($E$5:$E$504,$A$5:$A$504,A214,$B$5:$B$504,B214))</f>
+        <f aca="false">IF(OR(B214="",AND(A214=A213 ,B214=B213)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A214,$B$5:$B$504,B214)+SUMIFS($E$5:$E$504,$A$5:$A$504,A214,$B$5:$B$504,B214)-SUMIFS($F$5:$F$504,$A$5:$A$504,A214,$B$5:$B$504,B214))</f>
         <v/>
       </c>
       <c r="H214" s="33" t="str">
@@ -19473,7 +19641,7 @@
       <c r="E215" s="25"/>
       <c r="F215" s="25"/>
       <c r="G215" s="33" t="str">
-        <f aca="false">IF(OR(B215="",AND(A215=A214 ,B215=B214)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A215,$B$5:$B$504,B215)+SUMIFS($E$5:$E$504,$A$5:$A$504,A215,$B$5:$B$504,B215))</f>
+        <f aca="false">IF(OR(B215="",AND(A215=A214 ,B215=B214)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A215,$B$5:$B$504,B215)+SUMIFS($E$5:$E$504,$A$5:$A$504,A215,$B$5:$B$504,B215)-SUMIFS($F$5:$F$504,$A$5:$A$504,A215,$B$5:$B$504,B215))</f>
         <v/>
       </c>
       <c r="H215" s="33" t="str">
@@ -19491,7 +19659,7 @@
       <c r="E216" s="25"/>
       <c r="F216" s="25"/>
       <c r="G216" s="33" t="str">
-        <f aca="false">IF(OR(B216="",AND(A216=A215 ,B216=B215)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A216,$B$5:$B$504,B216)+SUMIFS($E$5:$E$504,$A$5:$A$504,A216,$B$5:$B$504,B216))</f>
+        <f aca="false">IF(OR(B216="",AND(A216=A215 ,B216=B215)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A216,$B$5:$B$504,B216)+SUMIFS($E$5:$E$504,$A$5:$A$504,A216,$B$5:$B$504,B216)-SUMIFS($F$5:$F$504,$A$5:$A$504,A216,$B$5:$B$504,B216))</f>
         <v/>
       </c>
       <c r="H216" s="33" t="str">
@@ -19509,7 +19677,7 @@
       <c r="E217" s="25"/>
       <c r="F217" s="25"/>
       <c r="G217" s="33" t="str">
-        <f aca="false">IF(OR(B217="",AND(A217=A216 ,B217=B216)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A217,$B$5:$B$504,B217)+SUMIFS($E$5:$E$504,$A$5:$A$504,A217,$B$5:$B$504,B217))</f>
+        <f aca="false">IF(OR(B217="",AND(A217=A216 ,B217=B216)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A217,$B$5:$B$504,B217)+SUMIFS($E$5:$E$504,$A$5:$A$504,A217,$B$5:$B$504,B217)-SUMIFS($F$5:$F$504,$A$5:$A$504,A217,$B$5:$B$504,B217))</f>
         <v/>
       </c>
       <c r="H217" s="33" t="str">
@@ -19527,7 +19695,7 @@
       <c r="E218" s="25"/>
       <c r="F218" s="25"/>
       <c r="G218" s="33" t="str">
-        <f aca="false">IF(OR(B218="",AND(A218=A217 ,B218=B217)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A218,$B$5:$B$504,B218)+SUMIFS($E$5:$E$504,$A$5:$A$504,A218,$B$5:$B$504,B218))</f>
+        <f aca="false">IF(OR(B218="",AND(A218=A217 ,B218=B217)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A218,$B$5:$B$504,B218)+SUMIFS($E$5:$E$504,$A$5:$A$504,A218,$B$5:$B$504,B218)-SUMIFS($F$5:$F$504,$A$5:$A$504,A218,$B$5:$B$504,B218))</f>
         <v/>
       </c>
       <c r="H218" s="33" t="str">
@@ -19545,7 +19713,7 @@
       <c r="E219" s="25"/>
       <c r="F219" s="25"/>
       <c r="G219" s="33" t="str">
-        <f aca="false">IF(OR(B219="",AND(A219=A218 ,B219=B218)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A219,$B$5:$B$504,B219)+SUMIFS($E$5:$E$504,$A$5:$A$504,A219,$B$5:$B$504,B219))</f>
+        <f aca="false">IF(OR(B219="",AND(A219=A218 ,B219=B218)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A219,$B$5:$B$504,B219)+SUMIFS($E$5:$E$504,$A$5:$A$504,A219,$B$5:$B$504,B219)-SUMIFS($F$5:$F$504,$A$5:$A$504,A219,$B$5:$B$504,B219))</f>
         <v/>
       </c>
       <c r="H219" s="33" t="str">
@@ -19563,7 +19731,7 @@
       <c r="E220" s="25"/>
       <c r="F220" s="25"/>
       <c r="G220" s="33" t="str">
-        <f aca="false">IF(OR(B220="",AND(A220=A219 ,B220=B219)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A220,$B$5:$B$504,B220)+SUMIFS($E$5:$E$504,$A$5:$A$504,A220,$B$5:$B$504,B220))</f>
+        <f aca="false">IF(OR(B220="",AND(A220=A219 ,B220=B219)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A220,$B$5:$B$504,B220)+SUMIFS($E$5:$E$504,$A$5:$A$504,A220,$B$5:$B$504,B220)-SUMIFS($F$5:$F$504,$A$5:$A$504,A220,$B$5:$B$504,B220))</f>
         <v/>
       </c>
       <c r="H220" s="33" t="str">
@@ -19581,7 +19749,7 @@
       <c r="E221" s="25"/>
       <c r="F221" s="25"/>
       <c r="G221" s="33" t="str">
-        <f aca="false">IF(OR(B221="",AND(A221=A220 ,B221=B220)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A221,$B$5:$B$504,B221)+SUMIFS($E$5:$E$504,$A$5:$A$504,A221,$B$5:$B$504,B221))</f>
+        <f aca="false">IF(OR(B221="",AND(A221=A220 ,B221=B220)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A221,$B$5:$B$504,B221)+SUMIFS($E$5:$E$504,$A$5:$A$504,A221,$B$5:$B$504,B221)-SUMIFS($F$5:$F$504,$A$5:$A$504,A221,$B$5:$B$504,B221))</f>
         <v/>
       </c>
       <c r="H221" s="33" t="str">
@@ -19599,7 +19767,7 @@
       <c r="E222" s="25"/>
       <c r="F222" s="25"/>
       <c r="G222" s="33" t="str">
-        <f aca="false">IF(OR(B222="",AND(A222=A221 ,B222=B221)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A222,$B$5:$B$504,B222)+SUMIFS($E$5:$E$504,$A$5:$A$504,A222,$B$5:$B$504,B222))</f>
+        <f aca="false">IF(OR(B222="",AND(A222=A221 ,B222=B221)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A222,$B$5:$B$504,B222)+SUMIFS($E$5:$E$504,$A$5:$A$504,A222,$B$5:$B$504,B222)-SUMIFS($F$5:$F$504,$A$5:$A$504,A222,$B$5:$B$504,B222))</f>
         <v/>
       </c>
       <c r="H222" s="33" t="str">
@@ -19617,7 +19785,7 @@
       <c r="E223" s="25"/>
       <c r="F223" s="25"/>
       <c r="G223" s="33" t="str">
-        <f aca="false">IF(OR(B223="",AND(A223=A222 ,B223=B222)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A223,$B$5:$B$504,B223)+SUMIFS($E$5:$E$504,$A$5:$A$504,A223,$B$5:$B$504,B223))</f>
+        <f aca="false">IF(OR(B223="",AND(A223=A222 ,B223=B222)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A223,$B$5:$B$504,B223)+SUMIFS($E$5:$E$504,$A$5:$A$504,A223,$B$5:$B$504,B223)-SUMIFS($F$5:$F$504,$A$5:$A$504,A223,$B$5:$B$504,B223))</f>
         <v/>
       </c>
       <c r="H223" s="33" t="str">
@@ -19635,7 +19803,7 @@
       <c r="E224" s="25"/>
       <c r="F224" s="25"/>
       <c r="G224" s="33" t="str">
-        <f aca="false">IF(OR(B224="",AND(A224=A223 ,B224=B223)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A224,$B$5:$B$504,B224)+SUMIFS($E$5:$E$504,$A$5:$A$504,A224,$B$5:$B$504,B224))</f>
+        <f aca="false">IF(OR(B224="",AND(A224=A223 ,B224=B223)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A224,$B$5:$B$504,B224)+SUMIFS($E$5:$E$504,$A$5:$A$504,A224,$B$5:$B$504,B224)-SUMIFS($F$5:$F$504,$A$5:$A$504,A224,$B$5:$B$504,B224))</f>
         <v/>
       </c>
       <c r="H224" s="33" t="str">
@@ -19653,7 +19821,7 @@
       <c r="E225" s="25"/>
       <c r="F225" s="25"/>
       <c r="G225" s="33" t="str">
-        <f aca="false">IF(OR(B225="",AND(A225=A224 ,B225=B224)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A225,$B$5:$B$504,B225)+SUMIFS($E$5:$E$504,$A$5:$A$504,A225,$B$5:$B$504,B225))</f>
+        <f aca="false">IF(OR(B225="",AND(A225=A224 ,B225=B224)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A225,$B$5:$B$504,B225)+SUMIFS($E$5:$E$504,$A$5:$A$504,A225,$B$5:$B$504,B225)-SUMIFS($F$5:$F$504,$A$5:$A$504,A225,$B$5:$B$504,B225))</f>
         <v/>
       </c>
       <c r="H225" s="33" t="str">
@@ -19671,7 +19839,7 @@
       <c r="E226" s="25"/>
       <c r="F226" s="25"/>
       <c r="G226" s="33" t="str">
-        <f aca="false">IF(OR(B226="",AND(A226=A225 ,B226=B225)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A226,$B$5:$B$504,B226)+SUMIFS($E$5:$E$504,$A$5:$A$504,A226,$B$5:$B$504,B226))</f>
+        <f aca="false">IF(OR(B226="",AND(A226=A225 ,B226=B225)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A226,$B$5:$B$504,B226)+SUMIFS($E$5:$E$504,$A$5:$A$504,A226,$B$5:$B$504,B226)-SUMIFS($F$5:$F$504,$A$5:$A$504,A226,$B$5:$B$504,B226))</f>
         <v/>
       </c>
       <c r="H226" s="33" t="str">
@@ -19689,7 +19857,7 @@
       <c r="E227" s="25"/>
       <c r="F227" s="25"/>
       <c r="G227" s="33" t="str">
-        <f aca="false">IF(OR(B227="",AND(A227=A226 ,B227=B226)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A227,$B$5:$B$504,B227)+SUMIFS($E$5:$E$504,$A$5:$A$504,A227,$B$5:$B$504,B227))</f>
+        <f aca="false">IF(OR(B227="",AND(A227=A226 ,B227=B226)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A227,$B$5:$B$504,B227)+SUMIFS($E$5:$E$504,$A$5:$A$504,A227,$B$5:$B$504,B227)-SUMIFS($F$5:$F$504,$A$5:$A$504,A227,$B$5:$B$504,B227))</f>
         <v/>
       </c>
       <c r="H227" s="33" t="str">
@@ -19707,7 +19875,7 @@
       <c r="E228" s="25"/>
       <c r="F228" s="25"/>
       <c r="G228" s="33" t="str">
-        <f aca="false">IF(OR(B228="",AND(A228=A227 ,B228=B227)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A228,$B$5:$B$504,B228)+SUMIFS($E$5:$E$504,$A$5:$A$504,A228,$B$5:$B$504,B228))</f>
+        <f aca="false">IF(OR(B228="",AND(A228=A227 ,B228=B227)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A228,$B$5:$B$504,B228)+SUMIFS($E$5:$E$504,$A$5:$A$504,A228,$B$5:$B$504,B228)-SUMIFS($F$5:$F$504,$A$5:$A$504,A228,$B$5:$B$504,B228))</f>
         <v/>
       </c>
       <c r="H228" s="33" t="str">
@@ -19725,7 +19893,7 @@
       <c r="E229" s="25"/>
       <c r="F229" s="25"/>
       <c r="G229" s="33" t="str">
-        <f aca="false">IF(OR(B229="",AND(A229=A228 ,B229=B228)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A229,$B$5:$B$504,B229)+SUMIFS($E$5:$E$504,$A$5:$A$504,A229,$B$5:$B$504,B229))</f>
+        <f aca="false">IF(OR(B229="",AND(A229=A228 ,B229=B228)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A229,$B$5:$B$504,B229)+SUMIFS($E$5:$E$504,$A$5:$A$504,A229,$B$5:$B$504,B229)-SUMIFS($F$5:$F$504,$A$5:$A$504,A229,$B$5:$B$504,B229))</f>
         <v/>
       </c>
       <c r="H229" s="33" t="str">
@@ -19743,7 +19911,7 @@
       <c r="E230" s="25"/>
       <c r="F230" s="25"/>
       <c r="G230" s="33" t="str">
-        <f aca="false">IF(OR(B230="",AND(A230=A229 ,B230=B229)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A230,$B$5:$B$504,B230)+SUMIFS($E$5:$E$504,$A$5:$A$504,A230,$B$5:$B$504,B230))</f>
+        <f aca="false">IF(OR(B230="",AND(A230=A229 ,B230=B229)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A230,$B$5:$B$504,B230)+SUMIFS($E$5:$E$504,$A$5:$A$504,A230,$B$5:$B$504,B230)-SUMIFS($F$5:$F$504,$A$5:$A$504,A230,$B$5:$B$504,B230))</f>
         <v/>
       </c>
       <c r="H230" s="33" t="str">
@@ -19761,7 +19929,7 @@
       <c r="E231" s="25"/>
       <c r="F231" s="25"/>
       <c r="G231" s="33" t="str">
-        <f aca="false">IF(OR(B231="",AND(A231=A230 ,B231=B230)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A231,$B$5:$B$504,B231)+SUMIFS($E$5:$E$504,$A$5:$A$504,A231,$B$5:$B$504,B231))</f>
+        <f aca="false">IF(OR(B231="",AND(A231=A230 ,B231=B230)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A231,$B$5:$B$504,B231)+SUMIFS($E$5:$E$504,$A$5:$A$504,A231,$B$5:$B$504,B231)-SUMIFS($F$5:$F$504,$A$5:$A$504,A231,$B$5:$B$504,B231))</f>
         <v/>
       </c>
       <c r="H231" s="33" t="str">
@@ -19779,7 +19947,7 @@
       <c r="E232" s="25"/>
       <c r="F232" s="25"/>
       <c r="G232" s="33" t="str">
-        <f aca="false">IF(OR(B232="",AND(A232=A231 ,B232=B231)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A232,$B$5:$B$504,B232)+SUMIFS($E$5:$E$504,$A$5:$A$504,A232,$B$5:$B$504,B232))</f>
+        <f aca="false">IF(OR(B232="",AND(A232=A231 ,B232=B231)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A232,$B$5:$B$504,B232)+SUMIFS($E$5:$E$504,$A$5:$A$504,A232,$B$5:$B$504,B232)-SUMIFS($F$5:$F$504,$A$5:$A$504,A232,$B$5:$B$504,B232))</f>
         <v/>
       </c>
       <c r="H232" s="33" t="str">
@@ -19797,7 +19965,7 @@
       <c r="E233" s="25"/>
       <c r="F233" s="25"/>
       <c r="G233" s="33" t="str">
-        <f aca="false">IF(OR(B233="",AND(A233=A232 ,B233=B232)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A233,$B$5:$B$504,B233)+SUMIFS($E$5:$E$504,$A$5:$A$504,A233,$B$5:$B$504,B233))</f>
+        <f aca="false">IF(OR(B233="",AND(A233=A232 ,B233=B232)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A233,$B$5:$B$504,B233)+SUMIFS($E$5:$E$504,$A$5:$A$504,A233,$B$5:$B$504,B233)-SUMIFS($F$5:$F$504,$A$5:$A$504,A233,$B$5:$B$504,B233))</f>
         <v/>
       </c>
       <c r="H233" s="33" t="str">
@@ -19815,7 +19983,7 @@
       <c r="E234" s="25"/>
       <c r="F234" s="25"/>
       <c r="G234" s="33" t="str">
-        <f aca="false">IF(OR(B234="",AND(A234=A233 ,B234=B233)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A234,$B$5:$B$504,B234)+SUMIFS($E$5:$E$504,$A$5:$A$504,A234,$B$5:$B$504,B234))</f>
+        <f aca="false">IF(OR(B234="",AND(A234=A233 ,B234=B233)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A234,$B$5:$B$504,B234)+SUMIFS($E$5:$E$504,$A$5:$A$504,A234,$B$5:$B$504,B234)-SUMIFS($F$5:$F$504,$A$5:$A$504,A234,$B$5:$B$504,B234))</f>
         <v/>
       </c>
       <c r="H234" s="33" t="str">
@@ -19833,7 +20001,7 @@
       <c r="E235" s="25"/>
       <c r="F235" s="25"/>
       <c r="G235" s="33" t="str">
-        <f aca="false">IF(OR(B235="",AND(A235=A234 ,B235=B234)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A235,$B$5:$B$504,B235)+SUMIFS($E$5:$E$504,$A$5:$A$504,A235,$B$5:$B$504,B235))</f>
+        <f aca="false">IF(OR(B235="",AND(A235=A234 ,B235=B234)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A235,$B$5:$B$504,B235)+SUMIFS($E$5:$E$504,$A$5:$A$504,A235,$B$5:$B$504,B235)-SUMIFS($F$5:$F$504,$A$5:$A$504,A235,$B$5:$B$504,B235))</f>
         <v/>
       </c>
       <c r="H235" s="33" t="str">
@@ -19851,7 +20019,7 @@
       <c r="E236" s="25"/>
       <c r="F236" s="25"/>
       <c r="G236" s="33" t="str">
-        <f aca="false">IF(OR(B236="",AND(A236=A235 ,B236=B235)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A236,$B$5:$B$504,B236)+SUMIFS($E$5:$E$504,$A$5:$A$504,A236,$B$5:$B$504,B236))</f>
+        <f aca="false">IF(OR(B236="",AND(A236=A235 ,B236=B235)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A236,$B$5:$B$504,B236)+SUMIFS($E$5:$E$504,$A$5:$A$504,A236,$B$5:$B$504,B236)-SUMIFS($F$5:$F$504,$A$5:$A$504,A236,$B$5:$B$504,B236))</f>
         <v/>
       </c>
       <c r="H236" s="33" t="str">
@@ -19869,7 +20037,7 @@
       <c r="E237" s="25"/>
       <c r="F237" s="25"/>
       <c r="G237" s="33" t="str">
-        <f aca="false">IF(OR(B237="",AND(A237=A236 ,B237=B236)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A237,$B$5:$B$504,B237)+SUMIFS($E$5:$E$504,$A$5:$A$504,A237,$B$5:$B$504,B237))</f>
+        <f aca="false">IF(OR(B237="",AND(A237=A236 ,B237=B236)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A237,$B$5:$B$504,B237)+SUMIFS($E$5:$E$504,$A$5:$A$504,A237,$B$5:$B$504,B237)-SUMIFS($F$5:$F$504,$A$5:$A$504,A237,$B$5:$B$504,B237))</f>
         <v/>
       </c>
       <c r="H237" s="33" t="str">
@@ -19887,7 +20055,7 @@
       <c r="E238" s="25"/>
       <c r="F238" s="25"/>
       <c r="G238" s="33" t="str">
-        <f aca="false">IF(OR(B238="",AND(A238=A237 ,B238=B237)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A238,$B$5:$B$504,B238)+SUMIFS($E$5:$E$504,$A$5:$A$504,A238,$B$5:$B$504,B238))</f>
+        <f aca="false">IF(OR(B238="",AND(A238=A237 ,B238=B237)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A238,$B$5:$B$504,B238)+SUMIFS($E$5:$E$504,$A$5:$A$504,A238,$B$5:$B$504,B238)-SUMIFS($F$5:$F$504,$A$5:$A$504,A238,$B$5:$B$504,B238))</f>
         <v/>
       </c>
       <c r="H238" s="33" t="str">
@@ -19905,7 +20073,7 @@
       <c r="E239" s="25"/>
       <c r="F239" s="25"/>
       <c r="G239" s="33" t="str">
-        <f aca="false">IF(OR(B239="",AND(A239=A238 ,B239=B238)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A239,$B$5:$B$504,B239)+SUMIFS($E$5:$E$504,$A$5:$A$504,A239,$B$5:$B$504,B239))</f>
+        <f aca="false">IF(OR(B239="",AND(A239=A238 ,B239=B238)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A239,$B$5:$B$504,B239)+SUMIFS($E$5:$E$504,$A$5:$A$504,A239,$B$5:$B$504,B239)-SUMIFS($F$5:$F$504,$A$5:$A$504,A239,$B$5:$B$504,B239))</f>
         <v/>
       </c>
       <c r="H239" s="33" t="str">
@@ -19923,7 +20091,7 @@
       <c r="E240" s="25"/>
       <c r="F240" s="25"/>
       <c r="G240" s="33" t="str">
-        <f aca="false">IF(OR(B240="",AND(A240=A239 ,B240=B239)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A240,$B$5:$B$504,B240)+SUMIFS($E$5:$E$504,$A$5:$A$504,A240,$B$5:$B$504,B240))</f>
+        <f aca="false">IF(OR(B240="",AND(A240=A239 ,B240=B239)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A240,$B$5:$B$504,B240)+SUMIFS($E$5:$E$504,$A$5:$A$504,A240,$B$5:$B$504,B240)-SUMIFS($F$5:$F$504,$A$5:$A$504,A240,$B$5:$B$504,B240))</f>
         <v/>
       </c>
       <c r="H240" s="33" t="str">
@@ -19941,7 +20109,7 @@
       <c r="E241" s="25"/>
       <c r="F241" s="25"/>
       <c r="G241" s="33" t="str">
-        <f aca="false">IF(OR(B241="",AND(A241=A240 ,B241=B240)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A241,$B$5:$B$504,B241)+SUMIFS($E$5:$E$504,$A$5:$A$504,A241,$B$5:$B$504,B241))</f>
+        <f aca="false">IF(OR(B241="",AND(A241=A240 ,B241=B240)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A241,$B$5:$B$504,B241)+SUMIFS($E$5:$E$504,$A$5:$A$504,A241,$B$5:$B$504,B241)-SUMIFS($F$5:$F$504,$A$5:$A$504,A241,$B$5:$B$504,B241))</f>
         <v/>
       </c>
       <c r="H241" s="33" t="str">
@@ -19959,7 +20127,7 @@
       <c r="E242" s="25"/>
       <c r="F242" s="25"/>
       <c r="G242" s="33" t="str">
-        <f aca="false">IF(OR(B242="",AND(A242=A241 ,B242=B241)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A242,$B$5:$B$504,B242)+SUMIFS($E$5:$E$504,$A$5:$A$504,A242,$B$5:$B$504,B242))</f>
+        <f aca="false">IF(OR(B242="",AND(A242=A241 ,B242=B241)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A242,$B$5:$B$504,B242)+SUMIFS($E$5:$E$504,$A$5:$A$504,A242,$B$5:$B$504,B242)-SUMIFS($F$5:$F$504,$A$5:$A$504,A242,$B$5:$B$504,B242))</f>
         <v/>
       </c>
       <c r="H242" s="33" t="str">
@@ -19977,7 +20145,7 @@
       <c r="E243" s="25"/>
       <c r="F243" s="25"/>
       <c r="G243" s="33" t="str">
-        <f aca="false">IF(OR(B243="",AND(A243=A242 ,B243=B242)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A243,$B$5:$B$504,B243)+SUMIFS($E$5:$E$504,$A$5:$A$504,A243,$B$5:$B$504,B243))</f>
+        <f aca="false">IF(OR(B243="",AND(A243=A242 ,B243=B242)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A243,$B$5:$B$504,B243)+SUMIFS($E$5:$E$504,$A$5:$A$504,A243,$B$5:$B$504,B243)-SUMIFS($F$5:$F$504,$A$5:$A$504,A243,$B$5:$B$504,B243))</f>
         <v/>
       </c>
       <c r="H243" s="33" t="str">
@@ -19995,7 +20163,7 @@
       <c r="E244" s="25"/>
       <c r="F244" s="25"/>
       <c r="G244" s="33" t="str">
-        <f aca="false">IF(OR(B244="",AND(A244=A243 ,B244=B243)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A244,$B$5:$B$504,B244)+SUMIFS($E$5:$E$504,$A$5:$A$504,A244,$B$5:$B$504,B244))</f>
+        <f aca="false">IF(OR(B244="",AND(A244=A243 ,B244=B243)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A244,$B$5:$B$504,B244)+SUMIFS($E$5:$E$504,$A$5:$A$504,A244,$B$5:$B$504,B244)-SUMIFS($F$5:$F$504,$A$5:$A$504,A244,$B$5:$B$504,B244))</f>
         <v/>
       </c>
       <c r="H244" s="33" t="str">
@@ -20013,7 +20181,7 @@
       <c r="E245" s="25"/>
       <c r="F245" s="25"/>
       <c r="G245" s="33" t="str">
-        <f aca="false">IF(OR(B245="",AND(A245=A244 ,B245=B244)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A245,$B$5:$B$504,B245)+SUMIFS($E$5:$E$504,$A$5:$A$504,A245,$B$5:$B$504,B245))</f>
+        <f aca="false">IF(OR(B245="",AND(A245=A244 ,B245=B244)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A245,$B$5:$B$504,B245)+SUMIFS($E$5:$E$504,$A$5:$A$504,A245,$B$5:$B$504,B245)-SUMIFS($F$5:$F$504,$A$5:$A$504,A245,$B$5:$B$504,B245))</f>
         <v/>
       </c>
       <c r="H245" s="33" t="str">
@@ -20031,7 +20199,7 @@
       <c r="E246" s="25"/>
       <c r="F246" s="25"/>
       <c r="G246" s="33" t="str">
-        <f aca="false">IF(OR(B246="",AND(A246=A245 ,B246=B245)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A246,$B$5:$B$504,B246)+SUMIFS($E$5:$E$504,$A$5:$A$504,A246,$B$5:$B$504,B246))</f>
+        <f aca="false">IF(OR(B246="",AND(A246=A245 ,B246=B245)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A246,$B$5:$B$504,B246)+SUMIFS($E$5:$E$504,$A$5:$A$504,A246,$B$5:$B$504,B246)-SUMIFS($F$5:$F$504,$A$5:$A$504,A246,$B$5:$B$504,B246))</f>
         <v/>
       </c>
       <c r="H246" s="33" t="str">
@@ -20049,7 +20217,7 @@
       <c r="E247" s="25"/>
       <c r="F247" s="25"/>
       <c r="G247" s="33" t="str">
-        <f aca="false">IF(OR(B247="",AND(A247=A246 ,B247=B246)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A247,$B$5:$B$504,B247)+SUMIFS($E$5:$E$504,$A$5:$A$504,A247,$B$5:$B$504,B247))</f>
+        <f aca="false">IF(OR(B247="",AND(A247=A246 ,B247=B246)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A247,$B$5:$B$504,B247)+SUMIFS($E$5:$E$504,$A$5:$A$504,A247,$B$5:$B$504,B247)-SUMIFS($F$5:$F$504,$A$5:$A$504,A247,$B$5:$B$504,B247))</f>
         <v/>
       </c>
       <c r="H247" s="33" t="str">
@@ -20067,7 +20235,7 @@
       <c r="E248" s="25"/>
       <c r="F248" s="25"/>
       <c r="G248" s="33" t="str">
-        <f aca="false">IF(OR(B248="",AND(A248=A247 ,B248=B247)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A248,$B$5:$B$504,B248)+SUMIFS($E$5:$E$504,$A$5:$A$504,A248,$B$5:$B$504,B248))</f>
+        <f aca="false">IF(OR(B248="",AND(A248=A247 ,B248=B247)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A248,$B$5:$B$504,B248)+SUMIFS($E$5:$E$504,$A$5:$A$504,A248,$B$5:$B$504,B248)-SUMIFS($F$5:$F$504,$A$5:$A$504,A248,$B$5:$B$504,B248))</f>
         <v/>
       </c>
       <c r="H248" s="33" t="str">
@@ -20085,7 +20253,7 @@
       <c r="E249" s="25"/>
       <c r="F249" s="25"/>
       <c r="G249" s="33" t="str">
-        <f aca="false">IF(OR(B249="",AND(A249=A248 ,B249=B248)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A249,$B$5:$B$504,B249)+SUMIFS($E$5:$E$504,$A$5:$A$504,A249,$B$5:$B$504,B249))</f>
+        <f aca="false">IF(OR(B249="",AND(A249=A248 ,B249=B248)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A249,$B$5:$B$504,B249)+SUMIFS($E$5:$E$504,$A$5:$A$504,A249,$B$5:$B$504,B249)-SUMIFS($F$5:$F$504,$A$5:$A$504,A249,$B$5:$B$504,B249))</f>
         <v/>
       </c>
       <c r="H249" s="33" t="str">
@@ -20103,7 +20271,7 @@
       <c r="E250" s="25"/>
       <c r="F250" s="25"/>
       <c r="G250" s="33" t="str">
-        <f aca="false">IF(OR(B250="",AND(A250=A249 ,B250=B249)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A250,$B$5:$B$504,B250)+SUMIFS($E$5:$E$504,$A$5:$A$504,A250,$B$5:$B$504,B250))</f>
+        <f aca="false">IF(OR(B250="",AND(A250=A249 ,B250=B249)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A250,$B$5:$B$504,B250)+SUMIFS($E$5:$E$504,$A$5:$A$504,A250,$B$5:$B$504,B250)-SUMIFS($F$5:$F$504,$A$5:$A$504,A250,$B$5:$B$504,B250))</f>
         <v/>
       </c>
       <c r="H250" s="33" t="str">
@@ -20121,7 +20289,7 @@
       <c r="E251" s="25"/>
       <c r="F251" s="25"/>
       <c r="G251" s="33" t="str">
-        <f aca="false">IF(OR(B251="",AND(A251=A250 ,B251=B250)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A251,$B$5:$B$504,B251)+SUMIFS($E$5:$E$504,$A$5:$A$504,A251,$B$5:$B$504,B251))</f>
+        <f aca="false">IF(OR(B251="",AND(A251=A250 ,B251=B250)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A251,$B$5:$B$504,B251)+SUMIFS($E$5:$E$504,$A$5:$A$504,A251,$B$5:$B$504,B251)-SUMIFS($F$5:$F$504,$A$5:$A$504,A251,$B$5:$B$504,B251))</f>
         <v/>
       </c>
       <c r="H251" s="33" t="str">
@@ -20139,7 +20307,7 @@
       <c r="E252" s="25"/>
       <c r="F252" s="25"/>
       <c r="G252" s="33" t="str">
-        <f aca="false">IF(OR(B252="",AND(A252=A251 ,B252=B251)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A252,$B$5:$B$504,B252)+SUMIFS($E$5:$E$504,$A$5:$A$504,A252,$B$5:$B$504,B252))</f>
+        <f aca="false">IF(OR(B252="",AND(A252=A251 ,B252=B251)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A252,$B$5:$B$504,B252)+SUMIFS($E$5:$E$504,$A$5:$A$504,A252,$B$5:$B$504,B252)-SUMIFS($F$5:$F$504,$A$5:$A$504,A252,$B$5:$B$504,B252))</f>
         <v/>
       </c>
       <c r="H252" s="33" t="str">
@@ -20157,7 +20325,7 @@
       <c r="E253" s="25"/>
       <c r="F253" s="25"/>
       <c r="G253" s="33" t="str">
-        <f aca="false">IF(OR(B253="",AND(A253=A252 ,B253=B252)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A253,$B$5:$B$504,B253)+SUMIFS($E$5:$E$504,$A$5:$A$504,A253,$B$5:$B$504,B253))</f>
+        <f aca="false">IF(OR(B253="",AND(A253=A252 ,B253=B252)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A253,$B$5:$B$504,B253)+SUMIFS($E$5:$E$504,$A$5:$A$504,A253,$B$5:$B$504,B253)-SUMIFS($F$5:$F$504,$A$5:$A$504,A253,$B$5:$B$504,B253))</f>
         <v/>
       </c>
       <c r="H253" s="33" t="str">
@@ -20175,7 +20343,7 @@
       <c r="E254" s="25"/>
       <c r="F254" s="25"/>
       <c r="G254" s="33" t="str">
-        <f aca="false">IF(OR(B254="",AND(A254=A253 ,B254=B253)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A254,$B$5:$B$504,B254)+SUMIFS($E$5:$E$504,$A$5:$A$504,A254,$B$5:$B$504,B254))</f>
+        <f aca="false">IF(OR(B254="",AND(A254=A253 ,B254=B253)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A254,$B$5:$B$504,B254)+SUMIFS($E$5:$E$504,$A$5:$A$504,A254,$B$5:$B$504,B254)-SUMIFS($F$5:$F$504,$A$5:$A$504,A254,$B$5:$B$504,B254))</f>
         <v/>
       </c>
       <c r="H254" s="33" t="str">
@@ -20193,7 +20361,7 @@
       <c r="E255" s="25"/>
       <c r="F255" s="25"/>
       <c r="G255" s="33" t="str">
-        <f aca="false">IF(OR(B255="",AND(A255=A254 ,B255=B254)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A255,$B$5:$B$504,B255)+SUMIFS($E$5:$E$504,$A$5:$A$504,A255,$B$5:$B$504,B255))</f>
+        <f aca="false">IF(OR(B255="",AND(A255=A254 ,B255=B254)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A255,$B$5:$B$504,B255)+SUMIFS($E$5:$E$504,$A$5:$A$504,A255,$B$5:$B$504,B255)-SUMIFS($F$5:$F$504,$A$5:$A$504,A255,$B$5:$B$504,B255))</f>
         <v/>
       </c>
       <c r="H255" s="33" t="str">
@@ -20211,7 +20379,7 @@
       <c r="E256" s="25"/>
       <c r="F256" s="25"/>
       <c r="G256" s="33" t="str">
-        <f aca="false">IF(OR(B256="",AND(A256=A255 ,B256=B255)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A256,$B$5:$B$504,B256)+SUMIFS($E$5:$E$504,$A$5:$A$504,A256,$B$5:$B$504,B256))</f>
+        <f aca="false">IF(OR(B256="",AND(A256=A255 ,B256=B255)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A256,$B$5:$B$504,B256)+SUMIFS($E$5:$E$504,$A$5:$A$504,A256,$B$5:$B$504,B256)-SUMIFS($F$5:$F$504,$A$5:$A$504,A256,$B$5:$B$504,B256))</f>
         <v/>
       </c>
       <c r="H256" s="33" t="str">
@@ -20229,7 +20397,7 @@
       <c r="E257" s="25"/>
       <c r="F257" s="25"/>
       <c r="G257" s="33" t="str">
-        <f aca="false">IF(OR(B257="",AND(A257=A256 ,B257=B256)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A257,$B$5:$B$504,B257)+SUMIFS($E$5:$E$504,$A$5:$A$504,A257,$B$5:$B$504,B257))</f>
+        <f aca="false">IF(OR(B257="",AND(A257=A256 ,B257=B256)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A257,$B$5:$B$504,B257)+SUMIFS($E$5:$E$504,$A$5:$A$504,A257,$B$5:$B$504,B257)-SUMIFS($F$5:$F$504,$A$5:$A$504,A257,$B$5:$B$504,B257))</f>
         <v/>
       </c>
       <c r="H257" s="33" t="str">
@@ -20247,7 +20415,7 @@
       <c r="E258" s="25"/>
       <c r="F258" s="25"/>
       <c r="G258" s="33" t="str">
-        <f aca="false">IF(OR(B258="",AND(A258=A257 ,B258=B257)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A258,$B$5:$B$504,B258)+SUMIFS($E$5:$E$504,$A$5:$A$504,A258,$B$5:$B$504,B258))</f>
+        <f aca="false">IF(OR(B258="",AND(A258=A257 ,B258=B257)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A258,$B$5:$B$504,B258)+SUMIFS($E$5:$E$504,$A$5:$A$504,A258,$B$5:$B$504,B258)-SUMIFS($F$5:$F$504,$A$5:$A$504,A258,$B$5:$B$504,B258))</f>
         <v/>
       </c>
       <c r="H258" s="33" t="str">
@@ -20265,7 +20433,7 @@
       <c r="E259" s="25"/>
       <c r="F259" s="25"/>
       <c r="G259" s="33" t="str">
-        <f aca="false">IF(OR(B259="",AND(A259=A258 ,B259=B258)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A259,$B$5:$B$504,B259)+SUMIFS($E$5:$E$504,$A$5:$A$504,A259,$B$5:$B$504,B259))</f>
+        <f aca="false">IF(OR(B259="",AND(A259=A258 ,B259=B258)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A259,$B$5:$B$504,B259)+SUMIFS($E$5:$E$504,$A$5:$A$504,A259,$B$5:$B$504,B259)-SUMIFS($F$5:$F$504,$A$5:$A$504,A259,$B$5:$B$504,B259))</f>
         <v/>
       </c>
       <c r="H259" s="33" t="str">
@@ -20283,7 +20451,7 @@
       <c r="E260" s="25"/>
       <c r="F260" s="25"/>
       <c r="G260" s="33" t="str">
-        <f aca="false">IF(OR(B260="",AND(A260=A259 ,B260=B259)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A260,$B$5:$B$504,B260)+SUMIFS($E$5:$E$504,$A$5:$A$504,A260,$B$5:$B$504,B260))</f>
+        <f aca="false">IF(OR(B260="",AND(A260=A259 ,B260=B259)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A260,$B$5:$B$504,B260)+SUMIFS($E$5:$E$504,$A$5:$A$504,A260,$B$5:$B$504,B260)-SUMIFS($F$5:$F$504,$A$5:$A$504,A260,$B$5:$B$504,B260))</f>
         <v/>
       </c>
       <c r="H260" s="33" t="str">
@@ -20301,7 +20469,7 @@
       <c r="E261" s="25"/>
       <c r="F261" s="25"/>
       <c r="G261" s="33" t="str">
-        <f aca="false">IF(OR(B261="",AND(A261=A260 ,B261=B260)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A261,$B$5:$B$504,B261)+SUMIFS($E$5:$E$504,$A$5:$A$504,A261,$B$5:$B$504,B261))</f>
+        <f aca="false">IF(OR(B261="",AND(A261=A260 ,B261=B260)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A261,$B$5:$B$504,B261)+SUMIFS($E$5:$E$504,$A$5:$A$504,A261,$B$5:$B$504,B261)-SUMIFS($F$5:$F$504,$A$5:$A$504,A261,$B$5:$B$504,B261))</f>
         <v/>
       </c>
       <c r="H261" s="33" t="str">
@@ -20319,7 +20487,7 @@
       <c r="E262" s="25"/>
       <c r="F262" s="25"/>
       <c r="G262" s="33" t="str">
-        <f aca="false">IF(OR(B262="",AND(A262=A261 ,B262=B261)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A262,$B$5:$B$504,B262)+SUMIFS($E$5:$E$504,$A$5:$A$504,A262,$B$5:$B$504,B262))</f>
+        <f aca="false">IF(OR(B262="",AND(A262=A261 ,B262=B261)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A262,$B$5:$B$504,B262)+SUMIFS($E$5:$E$504,$A$5:$A$504,A262,$B$5:$B$504,B262)-SUMIFS($F$5:$F$504,$A$5:$A$504,A262,$B$5:$B$504,B262))</f>
         <v/>
       </c>
       <c r="H262" s="33" t="str">
@@ -20337,7 +20505,7 @@
       <c r="E263" s="25"/>
       <c r="F263" s="25"/>
       <c r="G263" s="33" t="str">
-        <f aca="false">IF(OR(B263="",AND(A263=A262 ,B263=B262)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A263,$B$5:$B$504,B263)+SUMIFS($E$5:$E$504,$A$5:$A$504,A263,$B$5:$B$504,B263))</f>
+        <f aca="false">IF(OR(B263="",AND(A263=A262 ,B263=B262)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A263,$B$5:$B$504,B263)+SUMIFS($E$5:$E$504,$A$5:$A$504,A263,$B$5:$B$504,B263)-SUMIFS($F$5:$F$504,$A$5:$A$504,A263,$B$5:$B$504,B263))</f>
         <v/>
       </c>
       <c r="H263" s="33" t="str">
@@ -20355,7 +20523,7 @@
       <c r="E264" s="25"/>
       <c r="F264" s="25"/>
       <c r="G264" s="33" t="str">
-        <f aca="false">IF(OR(B264="",AND(A264=A263 ,B264=B263)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A264,$B$5:$B$504,B264)+SUMIFS($E$5:$E$504,$A$5:$A$504,A264,$B$5:$B$504,B264))</f>
+        <f aca="false">IF(OR(B264="",AND(A264=A263 ,B264=B263)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A264,$B$5:$B$504,B264)+SUMIFS($E$5:$E$504,$A$5:$A$504,A264,$B$5:$B$504,B264)-SUMIFS($F$5:$F$504,$A$5:$A$504,A264,$B$5:$B$504,B264))</f>
         <v/>
       </c>
       <c r="H264" s="33" t="str">
@@ -20373,7 +20541,7 @@
       <c r="E265" s="25"/>
       <c r="F265" s="25"/>
       <c r="G265" s="33" t="str">
-        <f aca="false">IF(OR(B265="",AND(A265=A264 ,B265=B264)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A265,$B$5:$B$504,B265)+SUMIFS($E$5:$E$504,$A$5:$A$504,A265,$B$5:$B$504,B265))</f>
+        <f aca="false">IF(OR(B265="",AND(A265=A264 ,B265=B264)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A265,$B$5:$B$504,B265)+SUMIFS($E$5:$E$504,$A$5:$A$504,A265,$B$5:$B$504,B265)-SUMIFS($F$5:$F$504,$A$5:$A$504,A265,$B$5:$B$504,B265))</f>
         <v/>
       </c>
       <c r="H265" s="33" t="str">
@@ -20391,7 +20559,7 @@
       <c r="E266" s="25"/>
       <c r="F266" s="25"/>
       <c r="G266" s="33" t="str">
-        <f aca="false">IF(OR(B266="",AND(A266=A265 ,B266=B265)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A266,$B$5:$B$504,B266)+SUMIFS($E$5:$E$504,$A$5:$A$504,A266,$B$5:$B$504,B266))</f>
+        <f aca="false">IF(OR(B266="",AND(A266=A265 ,B266=B265)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A266,$B$5:$B$504,B266)+SUMIFS($E$5:$E$504,$A$5:$A$504,A266,$B$5:$B$504,B266)-SUMIFS($F$5:$F$504,$A$5:$A$504,A266,$B$5:$B$504,B266))</f>
         <v/>
       </c>
       <c r="H266" s="33" t="str">
@@ -20409,7 +20577,7 @@
       <c r="E267" s="25"/>
       <c r="F267" s="25"/>
       <c r="G267" s="33" t="str">
-        <f aca="false">IF(OR(B267="",AND(A267=A266 ,B267=B266)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A267,$B$5:$B$504,B267)+SUMIFS($E$5:$E$504,$A$5:$A$504,A267,$B$5:$B$504,B267))</f>
+        <f aca="false">IF(OR(B267="",AND(A267=A266 ,B267=B266)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A267,$B$5:$B$504,B267)+SUMIFS($E$5:$E$504,$A$5:$A$504,A267,$B$5:$B$504,B267)-SUMIFS($F$5:$F$504,$A$5:$A$504,A267,$B$5:$B$504,B267))</f>
         <v/>
       </c>
       <c r="H267" s="33" t="str">
@@ -20427,7 +20595,7 @@
       <c r="E268" s="25"/>
       <c r="F268" s="25"/>
       <c r="G268" s="33" t="str">
-        <f aca="false">IF(OR(B268="",AND(A268=A267 ,B268=B267)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A268,$B$5:$B$504,B268)+SUMIFS($E$5:$E$504,$A$5:$A$504,A268,$B$5:$B$504,B268))</f>
+        <f aca="false">IF(OR(B268="",AND(A268=A267 ,B268=B267)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A268,$B$5:$B$504,B268)+SUMIFS($E$5:$E$504,$A$5:$A$504,A268,$B$5:$B$504,B268)-SUMIFS($F$5:$F$504,$A$5:$A$504,A268,$B$5:$B$504,B268))</f>
         <v/>
       </c>
       <c r="H268" s="33" t="str">
@@ -20445,7 +20613,7 @@
       <c r="E269" s="25"/>
       <c r="F269" s="25"/>
       <c r="G269" s="33" t="str">
-        <f aca="false">IF(OR(B269="",AND(A269=A268 ,B269=B268)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A269,$B$5:$B$504,B269)+SUMIFS($E$5:$E$504,$A$5:$A$504,A269,$B$5:$B$504,B269))</f>
+        <f aca="false">IF(OR(B269="",AND(A269=A268 ,B269=B268)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A269,$B$5:$B$504,B269)+SUMIFS($E$5:$E$504,$A$5:$A$504,A269,$B$5:$B$504,B269)-SUMIFS($F$5:$F$504,$A$5:$A$504,A269,$B$5:$B$504,B269))</f>
         <v/>
       </c>
       <c r="H269" s="33" t="str">
@@ -20463,7 +20631,7 @@
       <c r="E270" s="25"/>
       <c r="F270" s="25"/>
       <c r="G270" s="33" t="str">
-        <f aca="false">IF(OR(B270="",AND(A270=A269 ,B270=B269)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A270,$B$5:$B$504,B270)+SUMIFS($E$5:$E$504,$A$5:$A$504,A270,$B$5:$B$504,B270))</f>
+        <f aca="false">IF(OR(B270="",AND(A270=A269 ,B270=B269)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A270,$B$5:$B$504,B270)+SUMIFS($E$5:$E$504,$A$5:$A$504,A270,$B$5:$B$504,B270)-SUMIFS($F$5:$F$504,$A$5:$A$504,A270,$B$5:$B$504,B270))</f>
         <v/>
       </c>
       <c r="H270" s="33" t="str">
@@ -20481,7 +20649,7 @@
       <c r="E271" s="25"/>
       <c r="F271" s="25"/>
       <c r="G271" s="33" t="str">
-        <f aca="false">IF(OR(B271="",AND(A271=A270 ,B271=B270)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A271,$B$5:$B$504,B271)+SUMIFS($E$5:$E$504,$A$5:$A$504,A271,$B$5:$B$504,B271))</f>
+        <f aca="false">IF(OR(B271="",AND(A271=A270 ,B271=B270)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A271,$B$5:$B$504,B271)+SUMIFS($E$5:$E$504,$A$5:$A$504,A271,$B$5:$B$504,B271)-SUMIFS($F$5:$F$504,$A$5:$A$504,A271,$B$5:$B$504,B271))</f>
         <v/>
       </c>
       <c r="H271" s="33" t="str">
@@ -20499,7 +20667,7 @@
       <c r="E272" s="25"/>
       <c r="F272" s="25"/>
       <c r="G272" s="33" t="str">
-        <f aca="false">IF(OR(B272="",AND(A272=A271 ,B272=B271)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A272,$B$5:$B$504,B272)+SUMIFS($E$5:$E$504,$A$5:$A$504,A272,$B$5:$B$504,B272))</f>
+        <f aca="false">IF(OR(B272="",AND(A272=A271 ,B272=B271)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A272,$B$5:$B$504,B272)+SUMIFS($E$5:$E$504,$A$5:$A$504,A272,$B$5:$B$504,B272)-SUMIFS($F$5:$F$504,$A$5:$A$504,A272,$B$5:$B$504,B272))</f>
         <v/>
       </c>
       <c r="H272" s="33" t="str">
@@ -20517,7 +20685,7 @@
       <c r="E273" s="25"/>
       <c r="F273" s="25"/>
       <c r="G273" s="33" t="str">
-        <f aca="false">IF(OR(B273="",AND(A273=A272 ,B273=B272)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A273,$B$5:$B$504,B273)+SUMIFS($E$5:$E$504,$A$5:$A$504,A273,$B$5:$B$504,B273))</f>
+        <f aca="false">IF(OR(B273="",AND(A273=A272 ,B273=B272)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A273,$B$5:$B$504,B273)+SUMIFS($E$5:$E$504,$A$5:$A$504,A273,$B$5:$B$504,B273)-SUMIFS($F$5:$F$504,$A$5:$A$504,A273,$B$5:$B$504,B273))</f>
         <v/>
       </c>
       <c r="H273" s="33" t="str">
@@ -20535,7 +20703,7 @@
       <c r="E274" s="25"/>
       <c r="F274" s="25"/>
       <c r="G274" s="33" t="str">
-        <f aca="false">IF(OR(B274="",AND(A274=A273 ,B274=B273)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A274,$B$5:$B$504,B274)+SUMIFS($E$5:$E$504,$A$5:$A$504,A274,$B$5:$B$504,B274))</f>
+        <f aca="false">IF(OR(B274="",AND(A274=A273 ,B274=B273)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A274,$B$5:$B$504,B274)+SUMIFS($E$5:$E$504,$A$5:$A$504,A274,$B$5:$B$504,B274)-SUMIFS($F$5:$F$504,$A$5:$A$504,A274,$B$5:$B$504,B274))</f>
         <v/>
       </c>
       <c r="H274" s="33" t="str">
@@ -20553,7 +20721,7 @@
       <c r="E275" s="25"/>
       <c r="F275" s="25"/>
       <c r="G275" s="33" t="str">
-        <f aca="false">IF(OR(B275="",AND(A275=A274 ,B275=B274)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A275,$B$5:$B$504,B275)+SUMIFS($E$5:$E$504,$A$5:$A$504,A275,$B$5:$B$504,B275))</f>
+        <f aca="false">IF(OR(B275="",AND(A275=A274 ,B275=B274)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A275,$B$5:$B$504,B275)+SUMIFS($E$5:$E$504,$A$5:$A$504,A275,$B$5:$B$504,B275)-SUMIFS($F$5:$F$504,$A$5:$A$504,A275,$B$5:$B$504,B275))</f>
         <v/>
       </c>
       <c r="H275" s="33" t="str">
@@ -20571,7 +20739,7 @@
       <c r="E276" s="25"/>
       <c r="F276" s="25"/>
       <c r="G276" s="33" t="str">
-        <f aca="false">IF(OR(B276="",AND(A276=A275 ,B276=B275)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A276,$B$5:$B$504,B276)+SUMIFS($E$5:$E$504,$A$5:$A$504,A276,$B$5:$B$504,B276))</f>
+        <f aca="false">IF(OR(B276="",AND(A276=A275 ,B276=B275)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A276,$B$5:$B$504,B276)+SUMIFS($E$5:$E$504,$A$5:$A$504,A276,$B$5:$B$504,B276)-SUMIFS($F$5:$F$504,$A$5:$A$504,A276,$B$5:$B$504,B276))</f>
         <v/>
       </c>
       <c r="H276" s="33" t="str">
@@ -20589,7 +20757,7 @@
       <c r="E277" s="25"/>
       <c r="F277" s="25"/>
       <c r="G277" s="33" t="str">
-        <f aca="false">IF(OR(B277="",AND(A277=A276 ,B277=B276)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A277,$B$5:$B$504,B277)+SUMIFS($E$5:$E$504,$A$5:$A$504,A277,$B$5:$B$504,B277))</f>
+        <f aca="false">IF(OR(B277="",AND(A277=A276 ,B277=B276)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A277,$B$5:$B$504,B277)+SUMIFS($E$5:$E$504,$A$5:$A$504,A277,$B$5:$B$504,B277)-SUMIFS($F$5:$F$504,$A$5:$A$504,A277,$B$5:$B$504,B277))</f>
         <v/>
       </c>
       <c r="H277" s="33" t="str">
@@ -20607,7 +20775,7 @@
       <c r="E278" s="25"/>
       <c r="F278" s="25"/>
       <c r="G278" s="33" t="str">
-        <f aca="false">IF(OR(B278="",AND(A278=A277 ,B278=B277)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A278,$B$5:$B$504,B278)+SUMIFS($E$5:$E$504,$A$5:$A$504,A278,$B$5:$B$504,B278))</f>
+        <f aca="false">IF(OR(B278="",AND(A278=A277 ,B278=B277)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A278,$B$5:$B$504,B278)+SUMIFS($E$5:$E$504,$A$5:$A$504,A278,$B$5:$B$504,B278)-SUMIFS($F$5:$F$504,$A$5:$A$504,A278,$B$5:$B$504,B278))</f>
         <v/>
       </c>
       <c r="H278" s="33" t="str">
@@ -20625,7 +20793,7 @@
       <c r="E279" s="25"/>
       <c r="F279" s="25"/>
       <c r="G279" s="33" t="str">
-        <f aca="false">IF(OR(B279="",AND(A279=A278 ,B279=B278)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A279,$B$5:$B$504,B279)+SUMIFS($E$5:$E$504,$A$5:$A$504,A279,$B$5:$B$504,B279))</f>
+        <f aca="false">IF(OR(B279="",AND(A279=A278 ,B279=B278)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A279,$B$5:$B$504,B279)+SUMIFS($E$5:$E$504,$A$5:$A$504,A279,$B$5:$B$504,B279)-SUMIFS($F$5:$F$504,$A$5:$A$504,A279,$B$5:$B$504,B279))</f>
         <v/>
       </c>
       <c r="H279" s="33" t="str">
@@ -20643,7 +20811,7 @@
       <c r="E280" s="25"/>
       <c r="F280" s="25"/>
       <c r="G280" s="33" t="str">
-        <f aca="false">IF(OR(B280="",AND(A280=A279 ,B280=B279)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A280,$B$5:$B$504,B280)+SUMIFS($E$5:$E$504,$A$5:$A$504,A280,$B$5:$B$504,B280))</f>
+        <f aca="false">IF(OR(B280="",AND(A280=A279 ,B280=B279)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A280,$B$5:$B$504,B280)+SUMIFS($E$5:$E$504,$A$5:$A$504,A280,$B$5:$B$504,B280)-SUMIFS($F$5:$F$504,$A$5:$A$504,A280,$B$5:$B$504,B280))</f>
         <v/>
       </c>
       <c r="H280" s="33" t="str">
@@ -20661,7 +20829,7 @@
       <c r="E281" s="25"/>
       <c r="F281" s="25"/>
       <c r="G281" s="33" t="str">
-        <f aca="false">IF(OR(B281="",AND(A281=A280 ,B281=B280)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A281,$B$5:$B$504,B281)+SUMIFS($E$5:$E$504,$A$5:$A$504,A281,$B$5:$B$504,B281))</f>
+        <f aca="false">IF(OR(B281="",AND(A281=A280 ,B281=B280)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A281,$B$5:$B$504,B281)+SUMIFS($E$5:$E$504,$A$5:$A$504,A281,$B$5:$B$504,B281)-SUMIFS($F$5:$F$504,$A$5:$A$504,A281,$B$5:$B$504,B281))</f>
         <v/>
       </c>
       <c r="H281" s="33" t="str">
@@ -20679,7 +20847,7 @@
       <c r="E282" s="25"/>
       <c r="F282" s="25"/>
       <c r="G282" s="33" t="str">
-        <f aca="false">IF(OR(B282="",AND(A282=A281 ,B282=B281)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A282,$B$5:$B$504,B282)+SUMIFS($E$5:$E$504,$A$5:$A$504,A282,$B$5:$B$504,B282))</f>
+        <f aca="false">IF(OR(B282="",AND(A282=A281 ,B282=B281)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A282,$B$5:$B$504,B282)+SUMIFS($E$5:$E$504,$A$5:$A$504,A282,$B$5:$B$504,B282)-SUMIFS($F$5:$F$504,$A$5:$A$504,A282,$B$5:$B$504,B282))</f>
         <v/>
       </c>
       <c r="H282" s="33" t="str">
@@ -20697,7 +20865,7 @@
       <c r="E283" s="25"/>
       <c r="F283" s="25"/>
       <c r="G283" s="33" t="str">
-        <f aca="false">IF(OR(B283="",AND(A283=A282 ,B283=B282)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A283,$B$5:$B$504,B283)+SUMIFS($E$5:$E$504,$A$5:$A$504,A283,$B$5:$B$504,B283))</f>
+        <f aca="false">IF(OR(B283="",AND(A283=A282 ,B283=B282)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A283,$B$5:$B$504,B283)+SUMIFS($E$5:$E$504,$A$5:$A$504,A283,$B$5:$B$504,B283)-SUMIFS($F$5:$F$504,$A$5:$A$504,A283,$B$5:$B$504,B283))</f>
         <v/>
       </c>
       <c r="H283" s="33" t="str">
@@ -20715,7 +20883,7 @@
       <c r="E284" s="25"/>
       <c r="F284" s="25"/>
       <c r="G284" s="33" t="str">
-        <f aca="false">IF(OR(B284="",AND(A284=A283 ,B284=B283)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A284,$B$5:$B$504,B284)+SUMIFS($E$5:$E$504,$A$5:$A$504,A284,$B$5:$B$504,B284))</f>
+        <f aca="false">IF(OR(B284="",AND(A284=A283 ,B284=B283)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A284,$B$5:$B$504,B284)+SUMIFS($E$5:$E$504,$A$5:$A$504,A284,$B$5:$B$504,B284)-SUMIFS($F$5:$F$504,$A$5:$A$504,A284,$B$5:$B$504,B284))</f>
         <v/>
       </c>
       <c r="H284" s="33" t="str">
@@ -20733,7 +20901,7 @@
       <c r="E285" s="25"/>
       <c r="F285" s="25"/>
       <c r="G285" s="33" t="str">
-        <f aca="false">IF(OR(B285="",AND(A285=A284 ,B285=B284)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A285,$B$5:$B$504,B285)+SUMIFS($E$5:$E$504,$A$5:$A$504,A285,$B$5:$B$504,B285))</f>
+        <f aca="false">IF(OR(B285="",AND(A285=A284 ,B285=B284)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A285,$B$5:$B$504,B285)+SUMIFS($E$5:$E$504,$A$5:$A$504,A285,$B$5:$B$504,B285)-SUMIFS($F$5:$F$504,$A$5:$A$504,A285,$B$5:$B$504,B285))</f>
         <v/>
       </c>
       <c r="H285" s="33" t="str">
@@ -20751,7 +20919,7 @@
       <c r="E286" s="25"/>
       <c r="F286" s="25"/>
       <c r="G286" s="33" t="str">
-        <f aca="false">IF(OR(B286="",AND(A286=A285 ,B286=B285)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A286,$B$5:$B$504,B286)+SUMIFS($E$5:$E$504,$A$5:$A$504,A286,$B$5:$B$504,B286))</f>
+        <f aca="false">IF(OR(B286="",AND(A286=A285 ,B286=B285)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A286,$B$5:$B$504,B286)+SUMIFS($E$5:$E$504,$A$5:$A$504,A286,$B$5:$B$504,B286)-SUMIFS($F$5:$F$504,$A$5:$A$504,A286,$B$5:$B$504,B286))</f>
         <v/>
       </c>
       <c r="H286" s="33" t="str">
@@ -20769,7 +20937,7 @@
       <c r="E287" s="25"/>
       <c r="F287" s="25"/>
       <c r="G287" s="33" t="str">
-        <f aca="false">IF(OR(B287="",AND(A287=A286 ,B287=B286)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A287,$B$5:$B$504,B287)+SUMIFS($E$5:$E$504,$A$5:$A$504,A287,$B$5:$B$504,B287))</f>
+        <f aca="false">IF(OR(B287="",AND(A287=A286 ,B287=B286)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A287,$B$5:$B$504,B287)+SUMIFS($E$5:$E$504,$A$5:$A$504,A287,$B$5:$B$504,B287)-SUMIFS($F$5:$F$504,$A$5:$A$504,A287,$B$5:$B$504,B287))</f>
         <v/>
       </c>
       <c r="H287" s="33" t="str">
@@ -20787,7 +20955,7 @@
       <c r="E288" s="25"/>
       <c r="F288" s="25"/>
       <c r="G288" s="33" t="str">
-        <f aca="false">IF(OR(B288="",AND(A288=A287 ,B288=B287)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A288,$B$5:$B$504,B288)+SUMIFS($E$5:$E$504,$A$5:$A$504,A288,$B$5:$B$504,B288))</f>
+        <f aca="false">IF(OR(B288="",AND(A288=A287 ,B288=B287)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A288,$B$5:$B$504,B288)+SUMIFS($E$5:$E$504,$A$5:$A$504,A288,$B$5:$B$504,B288)-SUMIFS($F$5:$F$504,$A$5:$A$504,A288,$B$5:$B$504,B288))</f>
         <v/>
       </c>
       <c r="H288" s="33" t="str">
@@ -20805,7 +20973,7 @@
       <c r="E289" s="25"/>
       <c r="F289" s="25"/>
       <c r="G289" s="33" t="str">
-        <f aca="false">IF(OR(B289="",AND(A289=A288 ,B289=B288)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A289,$B$5:$B$504,B289)+SUMIFS($E$5:$E$504,$A$5:$A$504,A289,$B$5:$B$504,B289))</f>
+        <f aca="false">IF(OR(B289="",AND(A289=A288 ,B289=B288)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A289,$B$5:$B$504,B289)+SUMIFS($E$5:$E$504,$A$5:$A$504,A289,$B$5:$B$504,B289)-SUMIFS($F$5:$F$504,$A$5:$A$504,A289,$B$5:$B$504,B289))</f>
         <v/>
       </c>
       <c r="H289" s="33" t="str">
@@ -20823,7 +20991,7 @@
       <c r="E290" s="25"/>
       <c r="F290" s="25"/>
       <c r="G290" s="33" t="str">
-        <f aca="false">IF(OR(B290="",AND(A290=A289 ,B290=B289)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A290,$B$5:$B$504,B290)+SUMIFS($E$5:$E$504,$A$5:$A$504,A290,$B$5:$B$504,B290))</f>
+        <f aca="false">IF(OR(B290="",AND(A290=A289 ,B290=B289)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A290,$B$5:$B$504,B290)+SUMIFS($E$5:$E$504,$A$5:$A$504,A290,$B$5:$B$504,B290)-SUMIFS($F$5:$F$504,$A$5:$A$504,A290,$B$5:$B$504,B290))</f>
         <v/>
       </c>
       <c r="H290" s="33" t="str">
@@ -20841,7 +21009,7 @@
       <c r="E291" s="25"/>
       <c r="F291" s="25"/>
       <c r="G291" s="33" t="str">
-        <f aca="false">IF(OR(B291="",AND(A291=A290 ,B291=B290)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A291,$B$5:$B$504,B291)+SUMIFS($E$5:$E$504,$A$5:$A$504,A291,$B$5:$B$504,B291))</f>
+        <f aca="false">IF(OR(B291="",AND(A291=A290 ,B291=B290)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A291,$B$5:$B$504,B291)+SUMIFS($E$5:$E$504,$A$5:$A$504,A291,$B$5:$B$504,B291)-SUMIFS($F$5:$F$504,$A$5:$A$504,A291,$B$5:$B$504,B291))</f>
         <v/>
       </c>
       <c r="H291" s="33" t="str">
@@ -20859,7 +21027,7 @@
       <c r="E292" s="25"/>
       <c r="F292" s="25"/>
       <c r="G292" s="33" t="str">
-        <f aca="false">IF(OR(B292="",AND(A292=A291 ,B292=B291)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A292,$B$5:$B$504,B292)+SUMIFS($E$5:$E$504,$A$5:$A$504,A292,$B$5:$B$504,B292))</f>
+        <f aca="false">IF(OR(B292="",AND(A292=A291 ,B292=B291)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A292,$B$5:$B$504,B292)+SUMIFS($E$5:$E$504,$A$5:$A$504,A292,$B$5:$B$504,B292)-SUMIFS($F$5:$F$504,$A$5:$A$504,A292,$B$5:$B$504,B292))</f>
         <v/>
       </c>
       <c r="H292" s="33" t="str">
@@ -20877,7 +21045,7 @@
       <c r="E293" s="25"/>
       <c r="F293" s="25"/>
       <c r="G293" s="33" t="str">
-        <f aca="false">IF(OR(B293="",AND(A293=A292 ,B293=B292)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A293,$B$5:$B$504,B293)+SUMIFS($E$5:$E$504,$A$5:$A$504,A293,$B$5:$B$504,B293))</f>
+        <f aca="false">IF(OR(B293="",AND(A293=A292 ,B293=B292)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A293,$B$5:$B$504,B293)+SUMIFS($E$5:$E$504,$A$5:$A$504,A293,$B$5:$B$504,B293)-SUMIFS($F$5:$F$504,$A$5:$A$504,A293,$B$5:$B$504,B293))</f>
         <v/>
       </c>
       <c r="H293" s="33" t="str">
@@ -20895,7 +21063,7 @@
       <c r="E294" s="25"/>
       <c r="F294" s="25"/>
       <c r="G294" s="33" t="str">
-        <f aca="false">IF(OR(B294="",AND(A294=A293 ,B294=B293)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A294,$B$5:$B$504,B294)+SUMIFS($E$5:$E$504,$A$5:$A$504,A294,$B$5:$B$504,B294))</f>
+        <f aca="false">IF(OR(B294="",AND(A294=A293 ,B294=B293)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A294,$B$5:$B$504,B294)+SUMIFS($E$5:$E$504,$A$5:$A$504,A294,$B$5:$B$504,B294)-SUMIFS($F$5:$F$504,$A$5:$A$504,A294,$B$5:$B$504,B294))</f>
         <v/>
       </c>
       <c r="H294" s="33" t="str">
@@ -20913,7 +21081,7 @@
       <c r="E295" s="25"/>
       <c r="F295" s="25"/>
       <c r="G295" s="33" t="str">
-        <f aca="false">IF(OR(B295="",AND(A295=A294 ,B295=B294)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A295,$B$5:$B$504,B295)+SUMIFS($E$5:$E$504,$A$5:$A$504,A295,$B$5:$B$504,B295))</f>
+        <f aca="false">IF(OR(B295="",AND(A295=A294 ,B295=B294)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A295,$B$5:$B$504,B295)+SUMIFS($E$5:$E$504,$A$5:$A$504,A295,$B$5:$B$504,B295)-SUMIFS($F$5:$F$504,$A$5:$A$504,A295,$B$5:$B$504,B295))</f>
         <v/>
       </c>
       <c r="H295" s="33" t="str">
@@ -20931,7 +21099,7 @@
       <c r="E296" s="25"/>
       <c r="F296" s="25"/>
       <c r="G296" s="33" t="str">
-        <f aca="false">IF(OR(B296="",AND(A296=A295 ,B296=B295)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A296,$B$5:$B$504,B296)+SUMIFS($E$5:$E$504,$A$5:$A$504,A296,$B$5:$B$504,B296))</f>
+        <f aca="false">IF(OR(B296="",AND(A296=A295 ,B296=B295)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A296,$B$5:$B$504,B296)+SUMIFS($E$5:$E$504,$A$5:$A$504,A296,$B$5:$B$504,B296)-SUMIFS($F$5:$F$504,$A$5:$A$504,A296,$B$5:$B$504,B296))</f>
         <v/>
       </c>
       <c r="H296" s="33" t="str">
@@ -20949,7 +21117,7 @@
       <c r="E297" s="25"/>
       <c r="F297" s="25"/>
       <c r="G297" s="33" t="str">
-        <f aca="false">IF(OR(B297="",AND(A297=A296 ,B297=B296)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A297,$B$5:$B$504,B297)+SUMIFS($E$5:$E$504,$A$5:$A$504,A297,$B$5:$B$504,B297))</f>
+        <f aca="false">IF(OR(B297="",AND(A297=A296 ,B297=B296)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A297,$B$5:$B$504,B297)+SUMIFS($E$5:$E$504,$A$5:$A$504,A297,$B$5:$B$504,B297)-SUMIFS($F$5:$F$504,$A$5:$A$504,A297,$B$5:$B$504,B297))</f>
         <v/>
       </c>
       <c r="H297" s="33" t="str">
@@ -20967,7 +21135,7 @@
       <c r="E298" s="25"/>
       <c r="F298" s="25"/>
       <c r="G298" s="33" t="str">
-        <f aca="false">IF(OR(B298="",AND(A298=A297 ,B298=B297)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A298,$B$5:$B$504,B298)+SUMIFS($E$5:$E$504,$A$5:$A$504,A298,$B$5:$B$504,B298))</f>
+        <f aca="false">IF(OR(B298="",AND(A298=A297 ,B298=B297)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A298,$B$5:$B$504,B298)+SUMIFS($E$5:$E$504,$A$5:$A$504,A298,$B$5:$B$504,B298)-SUMIFS($F$5:$F$504,$A$5:$A$504,A298,$B$5:$B$504,B298))</f>
         <v/>
       </c>
       <c r="H298" s="33" t="str">
@@ -20985,7 +21153,7 @@
       <c r="E299" s="25"/>
       <c r="F299" s="25"/>
       <c r="G299" s="33" t="str">
-        <f aca="false">IF(OR(B299="",AND(A299=A298 ,B299=B298)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A299,$B$5:$B$504,B299)+SUMIFS($E$5:$E$504,$A$5:$A$504,A299,$B$5:$B$504,B299))</f>
+        <f aca="false">IF(OR(B299="",AND(A299=A298 ,B299=B298)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A299,$B$5:$B$504,B299)+SUMIFS($E$5:$E$504,$A$5:$A$504,A299,$B$5:$B$504,B299)-SUMIFS($F$5:$F$504,$A$5:$A$504,A299,$B$5:$B$504,B299))</f>
         <v/>
       </c>
       <c r="H299" s="33" t="str">
@@ -21003,7 +21171,7 @@
       <c r="E300" s="25"/>
       <c r="F300" s="25"/>
       <c r="G300" s="33" t="str">
-        <f aca="false">IF(OR(B300="",AND(A300=A299 ,B300=B299)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A300,$B$5:$B$504,B300)+SUMIFS($E$5:$E$504,$A$5:$A$504,A300,$B$5:$B$504,B300))</f>
+        <f aca="false">IF(OR(B300="",AND(A300=A299 ,B300=B299)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A300,$B$5:$B$504,B300)+SUMIFS($E$5:$E$504,$A$5:$A$504,A300,$B$5:$B$504,B300)-SUMIFS($F$5:$F$504,$A$5:$A$504,A300,$B$5:$B$504,B300))</f>
         <v/>
       </c>
       <c r="H300" s="33" t="str">
@@ -21021,7 +21189,7 @@
       <c r="E301" s="25"/>
       <c r="F301" s="25"/>
       <c r="G301" s="33" t="str">
-        <f aca="false">IF(OR(B301="",AND(A301=A300 ,B301=B300)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A301,$B$5:$B$504,B301)+SUMIFS($E$5:$E$504,$A$5:$A$504,A301,$B$5:$B$504,B301))</f>
+        <f aca="false">IF(OR(B301="",AND(A301=A300 ,B301=B300)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A301,$B$5:$B$504,B301)+SUMIFS($E$5:$E$504,$A$5:$A$504,A301,$B$5:$B$504,B301)-SUMIFS($F$5:$F$504,$A$5:$A$504,A301,$B$5:$B$504,B301))</f>
         <v/>
       </c>
       <c r="H301" s="33" t="str">
@@ -21039,7 +21207,7 @@
       <c r="E302" s="25"/>
       <c r="F302" s="25"/>
       <c r="G302" s="33" t="str">
-        <f aca="false">IF(OR(B302="",AND(A302=A301 ,B302=B301)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A302,$B$5:$B$504,B302)+SUMIFS($E$5:$E$504,$A$5:$A$504,A302,$B$5:$B$504,B302))</f>
+        <f aca="false">IF(OR(B302="",AND(A302=A301 ,B302=B301)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A302,$B$5:$B$504,B302)+SUMIFS($E$5:$E$504,$A$5:$A$504,A302,$B$5:$B$504,B302)-SUMIFS($F$5:$F$504,$A$5:$A$504,A302,$B$5:$B$504,B302))</f>
         <v/>
       </c>
       <c r="H302" s="33" t="str">
@@ -21057,7 +21225,7 @@
       <c r="E303" s="25"/>
       <c r="F303" s="25"/>
       <c r="G303" s="33" t="str">
-        <f aca="false">IF(OR(B303="",AND(A303=A302 ,B303=B302)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A303,$B$5:$B$504,B303)+SUMIFS($E$5:$E$504,$A$5:$A$504,A303,$B$5:$B$504,B303))</f>
+        <f aca="false">IF(OR(B303="",AND(A303=A302 ,B303=B302)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A303,$B$5:$B$504,B303)+SUMIFS($E$5:$E$504,$A$5:$A$504,A303,$B$5:$B$504,B303)-SUMIFS($F$5:$F$504,$A$5:$A$504,A303,$B$5:$B$504,B303))</f>
         <v/>
       </c>
       <c r="H303" s="33" t="str">
@@ -21075,7 +21243,7 @@
       <c r="E304" s="25"/>
       <c r="F304" s="25"/>
       <c r="G304" s="33" t="str">
-        <f aca="false">IF(OR(B304="",AND(A304=A303 ,B304=B303)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A304,$B$5:$B$504,B304)+SUMIFS($E$5:$E$504,$A$5:$A$504,A304,$B$5:$B$504,B304))</f>
+        <f aca="false">IF(OR(B304="",AND(A304=A303 ,B304=B303)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A304,$B$5:$B$504,B304)+SUMIFS($E$5:$E$504,$A$5:$A$504,A304,$B$5:$B$504,B304)-SUMIFS($F$5:$F$504,$A$5:$A$504,A304,$B$5:$B$504,B304))</f>
         <v/>
       </c>
       <c r="H304" s="33" t="str">
@@ -21093,7 +21261,7 @@
       <c r="E305" s="25"/>
       <c r="F305" s="25"/>
       <c r="G305" s="33" t="str">
-        <f aca="false">IF(OR(B305="",AND(A305=A304 ,B305=B304)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A305,$B$5:$B$504,B305)+SUMIFS($E$5:$E$504,$A$5:$A$504,A305,$B$5:$B$504,B305))</f>
+        <f aca="false">IF(OR(B305="",AND(A305=A304 ,B305=B304)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A305,$B$5:$B$504,B305)+SUMIFS($E$5:$E$504,$A$5:$A$504,A305,$B$5:$B$504,B305)-SUMIFS($F$5:$F$504,$A$5:$A$504,A305,$B$5:$B$504,B305))</f>
         <v/>
       </c>
       <c r="H305" s="33" t="str">
@@ -21111,7 +21279,7 @@
       <c r="E306" s="25"/>
       <c r="F306" s="25"/>
       <c r="G306" s="33" t="str">
-        <f aca="false">IF(OR(B306="",AND(A306=A305 ,B306=B305)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A306,$B$5:$B$504,B306)+SUMIFS($E$5:$E$504,$A$5:$A$504,A306,$B$5:$B$504,B306))</f>
+        <f aca="false">IF(OR(B306="",AND(A306=A305 ,B306=B305)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A306,$B$5:$B$504,B306)+SUMIFS($E$5:$E$504,$A$5:$A$504,A306,$B$5:$B$504,B306)-SUMIFS($F$5:$F$504,$A$5:$A$504,A306,$B$5:$B$504,B306))</f>
         <v/>
       </c>
       <c r="H306" s="33" t="str">
@@ -21129,7 +21297,7 @@
       <c r="E307" s="25"/>
       <c r="F307" s="25"/>
       <c r="G307" s="33" t="str">
-        <f aca="false">IF(OR(B307="",AND(A307=A306 ,B307=B306)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A307,$B$5:$B$504,B307)+SUMIFS($E$5:$E$504,$A$5:$A$504,A307,$B$5:$B$504,B307))</f>
+        <f aca="false">IF(OR(B307="",AND(A307=A306 ,B307=B306)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A307,$B$5:$B$504,B307)+SUMIFS($E$5:$E$504,$A$5:$A$504,A307,$B$5:$B$504,B307)-SUMIFS($F$5:$F$504,$A$5:$A$504,A307,$B$5:$B$504,B307))</f>
         <v/>
       </c>
       <c r="H307" s="33" t="str">
@@ -21147,7 +21315,7 @@
       <c r="E308" s="25"/>
       <c r="F308" s="25"/>
       <c r="G308" s="33" t="str">
-        <f aca="false">IF(OR(B308="",AND(A308=A307 ,B308=B307)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A308,$B$5:$B$504,B308)+SUMIFS($E$5:$E$504,$A$5:$A$504,A308,$B$5:$B$504,B308))</f>
+        <f aca="false">IF(OR(B308="",AND(A308=A307 ,B308=B307)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A308,$B$5:$B$504,B308)+SUMIFS($E$5:$E$504,$A$5:$A$504,A308,$B$5:$B$504,B308)-SUMIFS($F$5:$F$504,$A$5:$A$504,A308,$B$5:$B$504,B308))</f>
         <v/>
       </c>
       <c r="H308" s="33" t="str">
@@ -21165,7 +21333,7 @@
       <c r="E309" s="25"/>
       <c r="F309" s="25"/>
       <c r="G309" s="33" t="str">
-        <f aca="false">IF(OR(B309="",AND(A309=A308 ,B309=B308)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A309,$B$5:$B$504,B309)+SUMIFS($E$5:$E$504,$A$5:$A$504,A309,$B$5:$B$504,B309))</f>
+        <f aca="false">IF(OR(B309="",AND(A309=A308 ,B309=B308)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A309,$B$5:$B$504,B309)+SUMIFS($E$5:$E$504,$A$5:$A$504,A309,$B$5:$B$504,B309)-SUMIFS($F$5:$F$504,$A$5:$A$504,A309,$B$5:$B$504,B309))</f>
         <v/>
       </c>
       <c r="H309" s="33" t="str">
@@ -21183,7 +21351,7 @@
       <c r="E310" s="25"/>
       <c r="F310" s="25"/>
       <c r="G310" s="33" t="str">
-        <f aca="false">IF(OR(B310="",AND(A310=A309 ,B310=B309)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A310,$B$5:$B$504,B310)+SUMIFS($E$5:$E$504,$A$5:$A$504,A310,$B$5:$B$504,B310))</f>
+        <f aca="false">IF(OR(B310="",AND(A310=A309 ,B310=B309)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A310,$B$5:$B$504,B310)+SUMIFS($E$5:$E$504,$A$5:$A$504,A310,$B$5:$B$504,B310)-SUMIFS($F$5:$F$504,$A$5:$A$504,A310,$B$5:$B$504,B310))</f>
         <v/>
       </c>
       <c r="H310" s="33" t="str">
@@ -21201,7 +21369,7 @@
       <c r="E311" s="25"/>
       <c r="F311" s="25"/>
       <c r="G311" s="33" t="str">
-        <f aca="false">IF(OR(B311="",AND(A311=A310 ,B311=B310)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A311,$B$5:$B$504,B311)+SUMIFS($E$5:$E$504,$A$5:$A$504,A311,$B$5:$B$504,B311))</f>
+        <f aca="false">IF(OR(B311="",AND(A311=A310 ,B311=B310)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A311,$B$5:$B$504,B311)+SUMIFS($E$5:$E$504,$A$5:$A$504,A311,$B$5:$B$504,B311)-SUMIFS($F$5:$F$504,$A$5:$A$504,A311,$B$5:$B$504,B311))</f>
         <v/>
       </c>
       <c r="H311" s="33" t="str">
@@ -21219,7 +21387,7 @@
       <c r="E312" s="25"/>
       <c r="F312" s="25"/>
       <c r="G312" s="33" t="str">
-        <f aca="false">IF(OR(B312="",AND(A312=A311 ,B312=B311)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A312,$B$5:$B$504,B312)+SUMIFS($E$5:$E$504,$A$5:$A$504,A312,$B$5:$B$504,B312))</f>
+        <f aca="false">IF(OR(B312="",AND(A312=A311 ,B312=B311)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A312,$B$5:$B$504,B312)+SUMIFS($E$5:$E$504,$A$5:$A$504,A312,$B$5:$B$504,B312)-SUMIFS($F$5:$F$504,$A$5:$A$504,A312,$B$5:$B$504,B312))</f>
         <v/>
       </c>
       <c r="H312" s="33" t="str">
@@ -21237,7 +21405,7 @@
       <c r="E313" s="25"/>
       <c r="F313" s="25"/>
       <c r="G313" s="33" t="str">
-        <f aca="false">IF(OR(B313="",AND(A313=A312 ,B313=B312)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A313,$B$5:$B$504,B313)+SUMIFS($E$5:$E$504,$A$5:$A$504,A313,$B$5:$B$504,B313))</f>
+        <f aca="false">IF(OR(B313="",AND(A313=A312 ,B313=B312)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A313,$B$5:$B$504,B313)+SUMIFS($E$5:$E$504,$A$5:$A$504,A313,$B$5:$B$504,B313)-SUMIFS($F$5:$F$504,$A$5:$A$504,A313,$B$5:$B$504,B313))</f>
         <v/>
       </c>
       <c r="H313" s="33" t="str">
@@ -21255,7 +21423,7 @@
       <c r="E314" s="25"/>
       <c r="F314" s="25"/>
       <c r="G314" s="33" t="str">
-        <f aca="false">IF(OR(B314="",AND(A314=A313 ,B314=B313)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A314,$B$5:$B$504,B314)+SUMIFS($E$5:$E$504,$A$5:$A$504,A314,$B$5:$B$504,B314))</f>
+        <f aca="false">IF(OR(B314="",AND(A314=A313 ,B314=B313)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A314,$B$5:$B$504,B314)+SUMIFS($E$5:$E$504,$A$5:$A$504,A314,$B$5:$B$504,B314)-SUMIFS($F$5:$F$504,$A$5:$A$504,A314,$B$5:$B$504,B314))</f>
         <v/>
       </c>
       <c r="H314" s="33" t="str">
@@ -21273,7 +21441,7 @@
       <c r="E315" s="25"/>
       <c r="F315" s="25"/>
       <c r="G315" s="33" t="str">
-        <f aca="false">IF(OR(B315="",AND(A315=A314 ,B315=B314)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A315,$B$5:$B$504,B315)+SUMIFS($E$5:$E$504,$A$5:$A$504,A315,$B$5:$B$504,B315))</f>
+        <f aca="false">IF(OR(B315="",AND(A315=A314 ,B315=B314)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A315,$B$5:$B$504,B315)+SUMIFS($E$5:$E$504,$A$5:$A$504,A315,$B$5:$B$504,B315)-SUMIFS($F$5:$F$504,$A$5:$A$504,A315,$B$5:$B$504,B315))</f>
         <v/>
       </c>
       <c r="H315" s="33" t="str">
@@ -21291,7 +21459,7 @@
       <c r="E316" s="25"/>
       <c r="F316" s="25"/>
       <c r="G316" s="33" t="str">
-        <f aca="false">IF(OR(B316="",AND(A316=A315 ,B316=B315)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A316,$B$5:$B$504,B316)+SUMIFS($E$5:$E$504,$A$5:$A$504,A316,$B$5:$B$504,B316))</f>
+        <f aca="false">IF(OR(B316="",AND(A316=A315 ,B316=B315)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A316,$B$5:$B$504,B316)+SUMIFS($E$5:$E$504,$A$5:$A$504,A316,$B$5:$B$504,B316)-SUMIFS($F$5:$F$504,$A$5:$A$504,A316,$B$5:$B$504,B316))</f>
         <v/>
       </c>
       <c r="H316" s="33" t="str">
@@ -21309,7 +21477,7 @@
       <c r="E317" s="25"/>
       <c r="F317" s="25"/>
       <c r="G317" s="33" t="str">
-        <f aca="false">IF(OR(B317="",AND(A317=A316 ,B317=B316)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A317,$B$5:$B$504,B317)+SUMIFS($E$5:$E$504,$A$5:$A$504,A317,$B$5:$B$504,B317))</f>
+        <f aca="false">IF(OR(B317="",AND(A317=A316 ,B317=B316)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A317,$B$5:$B$504,B317)+SUMIFS($E$5:$E$504,$A$5:$A$504,A317,$B$5:$B$504,B317)-SUMIFS($F$5:$F$504,$A$5:$A$504,A317,$B$5:$B$504,B317))</f>
         <v/>
       </c>
       <c r="H317" s="33" t="str">
@@ -21327,7 +21495,7 @@
       <c r="E318" s="25"/>
       <c r="F318" s="25"/>
       <c r="G318" s="33" t="str">
-        <f aca="false">IF(OR(B318="",AND(A318=A317 ,B318=B317)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A318,$B$5:$B$504,B318)+SUMIFS($E$5:$E$504,$A$5:$A$504,A318,$B$5:$B$504,B318))</f>
+        <f aca="false">IF(OR(B318="",AND(A318=A317 ,B318=B317)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A318,$B$5:$B$504,B318)+SUMIFS($E$5:$E$504,$A$5:$A$504,A318,$B$5:$B$504,B318)-SUMIFS($F$5:$F$504,$A$5:$A$504,A318,$B$5:$B$504,B318))</f>
         <v/>
       </c>
       <c r="H318" s="33" t="str">
@@ -21345,7 +21513,7 @@
       <c r="E319" s="25"/>
       <c r="F319" s="25"/>
       <c r="G319" s="33" t="str">
-        <f aca="false">IF(OR(B319="",AND(A319=A318 ,B319=B318)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A319,$B$5:$B$504,B319)+SUMIFS($E$5:$E$504,$A$5:$A$504,A319,$B$5:$B$504,B319))</f>
+        <f aca="false">IF(OR(B319="",AND(A319=A318 ,B319=B318)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A319,$B$5:$B$504,B319)+SUMIFS($E$5:$E$504,$A$5:$A$504,A319,$B$5:$B$504,B319)-SUMIFS($F$5:$F$504,$A$5:$A$504,A319,$B$5:$B$504,B319))</f>
         <v/>
       </c>
       <c r="H319" s="33" t="str">
@@ -21363,7 +21531,7 @@
       <c r="E320" s="25"/>
       <c r="F320" s="25"/>
       <c r="G320" s="33" t="str">
-        <f aca="false">IF(OR(B320="",AND(A320=A319 ,B320=B319)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A320,$B$5:$B$504,B320)+SUMIFS($E$5:$E$504,$A$5:$A$504,A320,$B$5:$B$504,B320))</f>
+        <f aca="false">IF(OR(B320="",AND(A320=A319 ,B320=B319)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A320,$B$5:$B$504,B320)+SUMIFS($E$5:$E$504,$A$5:$A$504,A320,$B$5:$B$504,B320)-SUMIFS($F$5:$F$504,$A$5:$A$504,A320,$B$5:$B$504,B320))</f>
         <v/>
       </c>
       <c r="H320" s="33" t="str">
@@ -21381,7 +21549,7 @@
       <c r="E321" s="25"/>
       <c r="F321" s="25"/>
       <c r="G321" s="33" t="str">
-        <f aca="false">IF(OR(B321="",AND(A321=A320 ,B321=B320)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A321,$B$5:$B$504,B321)+SUMIFS($E$5:$E$504,$A$5:$A$504,A321,$B$5:$B$504,B321))</f>
+        <f aca="false">IF(OR(B321="",AND(A321=A320 ,B321=B320)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A321,$B$5:$B$504,B321)+SUMIFS($E$5:$E$504,$A$5:$A$504,A321,$B$5:$B$504,B321)-SUMIFS($F$5:$F$504,$A$5:$A$504,A321,$B$5:$B$504,B321))</f>
         <v/>
       </c>
       <c r="H321" s="33" t="str">
@@ -21399,7 +21567,7 @@
       <c r="E322" s="25"/>
       <c r="F322" s="25"/>
       <c r="G322" s="33" t="str">
-        <f aca="false">IF(OR(B322="",AND(A322=A321 ,B322=B321)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A322,$B$5:$B$504,B322)+SUMIFS($E$5:$E$504,$A$5:$A$504,A322,$B$5:$B$504,B322))</f>
+        <f aca="false">IF(OR(B322="",AND(A322=A321 ,B322=B321)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A322,$B$5:$B$504,B322)+SUMIFS($E$5:$E$504,$A$5:$A$504,A322,$B$5:$B$504,B322)-SUMIFS($F$5:$F$504,$A$5:$A$504,A322,$B$5:$B$504,B322))</f>
         <v/>
       </c>
       <c r="H322" s="33" t="str">
@@ -21417,7 +21585,7 @@
       <c r="E323" s="25"/>
       <c r="F323" s="25"/>
       <c r="G323" s="33" t="str">
-        <f aca="false">IF(OR(B323="",AND(A323=A322 ,B323=B322)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A323,$B$5:$B$504,B323)+SUMIFS($E$5:$E$504,$A$5:$A$504,A323,$B$5:$B$504,B323))</f>
+        <f aca="false">IF(OR(B323="",AND(A323=A322 ,B323=B322)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A323,$B$5:$B$504,B323)+SUMIFS($E$5:$E$504,$A$5:$A$504,A323,$B$5:$B$504,B323)-SUMIFS($F$5:$F$504,$A$5:$A$504,A323,$B$5:$B$504,B323))</f>
         <v/>
       </c>
       <c r="H323" s="33" t="str">
@@ -21435,7 +21603,7 @@
       <c r="E324" s="25"/>
       <c r="F324" s="25"/>
       <c r="G324" s="33" t="str">
-        <f aca="false">IF(OR(B324="",AND(A324=A323 ,B324=B323)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A324,$B$5:$B$504,B324)+SUMIFS($E$5:$E$504,$A$5:$A$504,A324,$B$5:$B$504,B324))</f>
+        <f aca="false">IF(OR(B324="",AND(A324=A323 ,B324=B323)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A324,$B$5:$B$504,B324)+SUMIFS($E$5:$E$504,$A$5:$A$504,A324,$B$5:$B$504,B324)-SUMIFS($F$5:$F$504,$A$5:$A$504,A324,$B$5:$B$504,B324))</f>
         <v/>
       </c>
       <c r="H324" s="33" t="str">
@@ -21453,7 +21621,7 @@
       <c r="E325" s="25"/>
       <c r="F325" s="25"/>
       <c r="G325" s="33" t="str">
-        <f aca="false">IF(OR(B325="",AND(A325=A324 ,B325=B324)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A325,$B$5:$B$504,B325)+SUMIFS($E$5:$E$504,$A$5:$A$504,A325,$B$5:$B$504,B325))</f>
+        <f aca="false">IF(OR(B325="",AND(A325=A324 ,B325=B324)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A325,$B$5:$B$504,B325)+SUMIFS($E$5:$E$504,$A$5:$A$504,A325,$B$5:$B$504,B325)-SUMIFS($F$5:$F$504,$A$5:$A$504,A325,$B$5:$B$504,B325))</f>
         <v/>
       </c>
       <c r="H325" s="33" t="str">
@@ -21471,7 +21639,7 @@
       <c r="E326" s="25"/>
       <c r="F326" s="25"/>
       <c r="G326" s="33" t="str">
-        <f aca="false">IF(OR(B326="",AND(A326=A325 ,B326=B325)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A326,$B$5:$B$504,B326)+SUMIFS($E$5:$E$504,$A$5:$A$504,A326,$B$5:$B$504,B326))</f>
+        <f aca="false">IF(OR(B326="",AND(A326=A325 ,B326=B325)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A326,$B$5:$B$504,B326)+SUMIFS($E$5:$E$504,$A$5:$A$504,A326,$B$5:$B$504,B326)-SUMIFS($F$5:$F$504,$A$5:$A$504,A326,$B$5:$B$504,B326))</f>
         <v/>
       </c>
       <c r="H326" s="33" t="str">
@@ -21489,7 +21657,7 @@
       <c r="E327" s="25"/>
       <c r="F327" s="25"/>
       <c r="G327" s="33" t="str">
-        <f aca="false">IF(OR(B327="",AND(A327=A326 ,B327=B326)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A327,$B$5:$B$504,B327)+SUMIFS($E$5:$E$504,$A$5:$A$504,A327,$B$5:$B$504,B327))</f>
+        <f aca="false">IF(OR(B327="",AND(A327=A326 ,B327=B326)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A327,$B$5:$B$504,B327)+SUMIFS($E$5:$E$504,$A$5:$A$504,A327,$B$5:$B$504,B327)-SUMIFS($F$5:$F$504,$A$5:$A$504,A327,$B$5:$B$504,B327))</f>
         <v/>
       </c>
       <c r="H327" s="33" t="str">
@@ -21507,7 +21675,7 @@
       <c r="E328" s="25"/>
       <c r="F328" s="25"/>
       <c r="G328" s="33" t="str">
-        <f aca="false">IF(OR(B328="",AND(A328=A327 ,B328=B327)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A328,$B$5:$B$504,B328)+SUMIFS($E$5:$E$504,$A$5:$A$504,A328,$B$5:$B$504,B328))</f>
+        <f aca="false">IF(OR(B328="",AND(A328=A327 ,B328=B327)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A328,$B$5:$B$504,B328)+SUMIFS($E$5:$E$504,$A$5:$A$504,A328,$B$5:$B$504,B328)-SUMIFS($F$5:$F$504,$A$5:$A$504,A328,$B$5:$B$504,B328))</f>
         <v/>
       </c>
       <c r="H328" s="33" t="str">
@@ -21525,7 +21693,7 @@
       <c r="E329" s="25"/>
       <c r="F329" s="25"/>
       <c r="G329" s="33" t="str">
-        <f aca="false">IF(OR(B329="",AND(A329=A328 ,B329=B328)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A329,$B$5:$B$504,B329)+SUMIFS($E$5:$E$504,$A$5:$A$504,A329,$B$5:$B$504,B329))</f>
+        <f aca="false">IF(OR(B329="",AND(A329=A328 ,B329=B328)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A329,$B$5:$B$504,B329)+SUMIFS($E$5:$E$504,$A$5:$A$504,A329,$B$5:$B$504,B329)-SUMIFS($F$5:$F$504,$A$5:$A$504,A329,$B$5:$B$504,B329))</f>
         <v/>
       </c>
       <c r="H329" s="33" t="str">
@@ -21543,7 +21711,7 @@
       <c r="E330" s="25"/>
       <c r="F330" s="25"/>
       <c r="G330" s="33" t="str">
-        <f aca="false">IF(OR(B330="",AND(A330=A329 ,B330=B329)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A330,$B$5:$B$504,B330)+SUMIFS($E$5:$E$504,$A$5:$A$504,A330,$B$5:$B$504,B330))</f>
+        <f aca="false">IF(OR(B330="",AND(A330=A329 ,B330=B329)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A330,$B$5:$B$504,B330)+SUMIFS($E$5:$E$504,$A$5:$A$504,A330,$B$5:$B$504,B330)-SUMIFS($F$5:$F$504,$A$5:$A$504,A330,$B$5:$B$504,B330))</f>
         <v/>
       </c>
       <c r="H330" s="33" t="str">
@@ -21561,7 +21729,7 @@
       <c r="E331" s="25"/>
       <c r="F331" s="25"/>
       <c r="G331" s="33" t="str">
-        <f aca="false">IF(OR(B331="",AND(A331=A330 ,B331=B330)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A331,$B$5:$B$504,B331)+SUMIFS($E$5:$E$504,$A$5:$A$504,A331,$B$5:$B$504,B331))</f>
+        <f aca="false">IF(OR(B331="",AND(A331=A330 ,B331=B330)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A331,$B$5:$B$504,B331)+SUMIFS($E$5:$E$504,$A$5:$A$504,A331,$B$5:$B$504,B331)-SUMIFS($F$5:$F$504,$A$5:$A$504,A331,$B$5:$B$504,B331))</f>
         <v/>
       </c>
       <c r="H331" s="33" t="str">
@@ -21579,7 +21747,7 @@
       <c r="E332" s="25"/>
       <c r="F332" s="25"/>
       <c r="G332" s="33" t="str">
-        <f aca="false">IF(OR(B332="",AND(A332=A331 ,B332=B331)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A332,$B$5:$B$504,B332)+SUMIFS($E$5:$E$504,$A$5:$A$504,A332,$B$5:$B$504,B332))</f>
+        <f aca="false">IF(OR(B332="",AND(A332=A331 ,B332=B331)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A332,$B$5:$B$504,B332)+SUMIFS($E$5:$E$504,$A$5:$A$504,A332,$B$5:$B$504,B332)-SUMIFS($F$5:$F$504,$A$5:$A$504,A332,$B$5:$B$504,B332))</f>
         <v/>
       </c>
       <c r="H332" s="33" t="str">
@@ -21597,7 +21765,7 @@
       <c r="E333" s="25"/>
       <c r="F333" s="25"/>
       <c r="G333" s="33" t="str">
-        <f aca="false">IF(OR(B333="",AND(A333=A332 ,B333=B332)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A333,$B$5:$B$504,B333)+SUMIFS($E$5:$E$504,$A$5:$A$504,A333,$B$5:$B$504,B333))</f>
+        <f aca="false">IF(OR(B333="",AND(A333=A332 ,B333=B332)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A333,$B$5:$B$504,B333)+SUMIFS($E$5:$E$504,$A$5:$A$504,A333,$B$5:$B$504,B333)-SUMIFS($F$5:$F$504,$A$5:$A$504,A333,$B$5:$B$504,B333))</f>
         <v/>
       </c>
       <c r="H333" s="33" t="str">
@@ -21615,7 +21783,7 @@
       <c r="E334" s="25"/>
       <c r="F334" s="25"/>
       <c r="G334" s="33" t="str">
-        <f aca="false">IF(OR(B334="",AND(A334=A333 ,B334=B333)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A334,$B$5:$B$504,B334)+SUMIFS($E$5:$E$504,$A$5:$A$504,A334,$B$5:$B$504,B334))</f>
+        <f aca="false">IF(OR(B334="",AND(A334=A333 ,B334=B333)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A334,$B$5:$B$504,B334)+SUMIFS($E$5:$E$504,$A$5:$A$504,A334,$B$5:$B$504,B334)-SUMIFS($F$5:$F$504,$A$5:$A$504,A334,$B$5:$B$504,B334))</f>
         <v/>
       </c>
       <c r="H334" s="33" t="str">
@@ -21633,7 +21801,7 @@
       <c r="E335" s="25"/>
       <c r="F335" s="25"/>
       <c r="G335" s="33" t="str">
-        <f aca="false">IF(OR(B335="",AND(A335=A334 ,B335=B334)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A335,$B$5:$B$504,B335)+SUMIFS($E$5:$E$504,$A$5:$A$504,A335,$B$5:$B$504,B335))</f>
+        <f aca="false">IF(OR(B335="",AND(A335=A334 ,B335=B334)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A335,$B$5:$B$504,B335)+SUMIFS($E$5:$E$504,$A$5:$A$504,A335,$B$5:$B$504,B335)-SUMIFS($F$5:$F$504,$A$5:$A$504,A335,$B$5:$B$504,B335))</f>
         <v/>
       </c>
       <c r="H335" s="33" t="str">
@@ -21651,7 +21819,7 @@
       <c r="E336" s="25"/>
       <c r="F336" s="25"/>
       <c r="G336" s="33" t="str">
-        <f aca="false">IF(OR(B336="",AND(A336=A335 ,B336=B335)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A336,$B$5:$B$504,B336)+SUMIFS($E$5:$E$504,$A$5:$A$504,A336,$B$5:$B$504,B336))</f>
+        <f aca="false">IF(OR(B336="",AND(A336=A335 ,B336=B335)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A336,$B$5:$B$504,B336)+SUMIFS($E$5:$E$504,$A$5:$A$504,A336,$B$5:$B$504,B336)-SUMIFS($F$5:$F$504,$A$5:$A$504,A336,$B$5:$B$504,B336))</f>
         <v/>
       </c>
       <c r="H336" s="33" t="str">
@@ -21669,7 +21837,7 @@
       <c r="E337" s="25"/>
       <c r="F337" s="25"/>
       <c r="G337" s="33" t="str">
-        <f aca="false">IF(OR(B337="",AND(A337=A336 ,B337=B336)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A337,$B$5:$B$504,B337)+SUMIFS($E$5:$E$504,$A$5:$A$504,A337,$B$5:$B$504,B337))</f>
+        <f aca="false">IF(OR(B337="",AND(A337=A336 ,B337=B336)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A337,$B$5:$B$504,B337)+SUMIFS($E$5:$E$504,$A$5:$A$504,A337,$B$5:$B$504,B337)-SUMIFS($F$5:$F$504,$A$5:$A$504,A337,$B$5:$B$504,B337))</f>
         <v/>
       </c>
       <c r="H337" s="33" t="str">
@@ -21687,7 +21855,7 @@
       <c r="E338" s="25"/>
       <c r="F338" s="25"/>
       <c r="G338" s="33" t="str">
-        <f aca="false">IF(OR(B338="",AND(A338=A337 ,B338=B337)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A338,$B$5:$B$504,B338)+SUMIFS($E$5:$E$504,$A$5:$A$504,A338,$B$5:$B$504,B338))</f>
+        <f aca="false">IF(OR(B338="",AND(A338=A337 ,B338=B337)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A338,$B$5:$B$504,B338)+SUMIFS($E$5:$E$504,$A$5:$A$504,A338,$B$5:$B$504,B338)-SUMIFS($F$5:$F$504,$A$5:$A$504,A338,$B$5:$B$504,B338))</f>
         <v/>
       </c>
       <c r="H338" s="33" t="str">
@@ -21705,7 +21873,7 @@
       <c r="E339" s="25"/>
       <c r="F339" s="25"/>
       <c r="G339" s="33" t="str">
-        <f aca="false">IF(OR(B339="",AND(A339=A338 ,B339=B338)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A339,$B$5:$B$504,B339)+SUMIFS($E$5:$E$504,$A$5:$A$504,A339,$B$5:$B$504,B339))</f>
+        <f aca="false">IF(OR(B339="",AND(A339=A338 ,B339=B338)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A339,$B$5:$B$504,B339)+SUMIFS($E$5:$E$504,$A$5:$A$504,A339,$B$5:$B$504,B339)-SUMIFS($F$5:$F$504,$A$5:$A$504,A339,$B$5:$B$504,B339))</f>
         <v/>
       </c>
       <c r="H339" s="33" t="str">
@@ -21723,7 +21891,7 @@
       <c r="E340" s="25"/>
       <c r="F340" s="25"/>
       <c r="G340" s="33" t="str">
-        <f aca="false">IF(OR(B340="",AND(A340=A339 ,B340=B339)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A340,$B$5:$B$504,B340)+SUMIFS($E$5:$E$504,$A$5:$A$504,A340,$B$5:$B$504,B340))</f>
+        <f aca="false">IF(OR(B340="",AND(A340=A339 ,B340=B339)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A340,$B$5:$B$504,B340)+SUMIFS($E$5:$E$504,$A$5:$A$504,A340,$B$5:$B$504,B340)-SUMIFS($F$5:$F$504,$A$5:$A$504,A340,$B$5:$B$504,B340))</f>
         <v/>
       </c>
       <c r="H340" s="33" t="str">
@@ -21741,7 +21909,7 @@
       <c r="E341" s="25"/>
       <c r="F341" s="25"/>
       <c r="G341" s="33" t="str">
-        <f aca="false">IF(OR(B341="",AND(A341=A340 ,B341=B340)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A341,$B$5:$B$504,B341)+SUMIFS($E$5:$E$504,$A$5:$A$504,A341,$B$5:$B$504,B341))</f>
+        <f aca="false">IF(OR(B341="",AND(A341=A340 ,B341=B340)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A341,$B$5:$B$504,B341)+SUMIFS($E$5:$E$504,$A$5:$A$504,A341,$B$5:$B$504,B341)-SUMIFS($F$5:$F$504,$A$5:$A$504,A341,$B$5:$B$504,B341))</f>
         <v/>
       </c>
       <c r="H341" s="33" t="str">
@@ -21759,7 +21927,7 @@
       <c r="E342" s="25"/>
       <c r="F342" s="25"/>
       <c r="G342" s="33" t="str">
-        <f aca="false">IF(OR(B342="",AND(A342=A341 ,B342=B341)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A342,$B$5:$B$504,B342)+SUMIFS($E$5:$E$504,$A$5:$A$504,A342,$B$5:$B$504,B342))</f>
+        <f aca="false">IF(OR(B342="",AND(A342=A341 ,B342=B341)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A342,$B$5:$B$504,B342)+SUMIFS($E$5:$E$504,$A$5:$A$504,A342,$B$5:$B$504,B342)-SUMIFS($F$5:$F$504,$A$5:$A$504,A342,$B$5:$B$504,B342))</f>
         <v/>
       </c>
       <c r="H342" s="33" t="str">
@@ -21777,7 +21945,7 @@
       <c r="E343" s="25"/>
       <c r="F343" s="25"/>
       <c r="G343" s="33" t="str">
-        <f aca="false">IF(OR(B343="",AND(A343=A342 ,B343=B342)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A343,$B$5:$B$504,B343)+SUMIFS($E$5:$E$504,$A$5:$A$504,A343,$B$5:$B$504,B343))</f>
+        <f aca="false">IF(OR(B343="",AND(A343=A342 ,B343=B342)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A343,$B$5:$B$504,B343)+SUMIFS($E$5:$E$504,$A$5:$A$504,A343,$B$5:$B$504,B343)-SUMIFS($F$5:$F$504,$A$5:$A$504,A343,$B$5:$B$504,B343))</f>
         <v/>
       </c>
       <c r="H343" s="33" t="str">
@@ -21795,7 +21963,7 @@
       <c r="E344" s="25"/>
       <c r="F344" s="25"/>
       <c r="G344" s="33" t="str">
-        <f aca="false">IF(OR(B344="",AND(A344=A343 ,B344=B343)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A344,$B$5:$B$504,B344)+SUMIFS($E$5:$E$504,$A$5:$A$504,A344,$B$5:$B$504,B344))</f>
+        <f aca="false">IF(OR(B344="",AND(A344=A343 ,B344=B343)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A344,$B$5:$B$504,B344)+SUMIFS($E$5:$E$504,$A$5:$A$504,A344,$B$5:$B$504,B344)-SUMIFS($F$5:$F$504,$A$5:$A$504,A344,$B$5:$B$504,B344))</f>
         <v/>
       </c>
       <c r="H344" s="33" t="str">
@@ -21813,7 +21981,7 @@
       <c r="E345" s="25"/>
       <c r="F345" s="25"/>
       <c r="G345" s="33" t="str">
-        <f aca="false">IF(OR(B345="",AND(A345=A344 ,B345=B344)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A345,$B$5:$B$504,B345)+SUMIFS($E$5:$E$504,$A$5:$A$504,A345,$B$5:$B$504,B345))</f>
+        <f aca="false">IF(OR(B345="",AND(A345=A344 ,B345=B344)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A345,$B$5:$B$504,B345)+SUMIFS($E$5:$E$504,$A$5:$A$504,A345,$B$5:$B$504,B345)-SUMIFS($F$5:$F$504,$A$5:$A$504,A345,$B$5:$B$504,B345))</f>
         <v/>
       </c>
       <c r="H345" s="33" t="str">
@@ -21831,7 +21999,7 @@
       <c r="E346" s="25"/>
       <c r="F346" s="25"/>
       <c r="G346" s="33" t="str">
-        <f aca="false">IF(OR(B346="",AND(A346=A345 ,B346=B345)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A346,$B$5:$B$504,B346)+SUMIFS($E$5:$E$504,$A$5:$A$504,A346,$B$5:$B$504,B346))</f>
+        <f aca="false">IF(OR(B346="",AND(A346=A345 ,B346=B345)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A346,$B$5:$B$504,B346)+SUMIFS($E$5:$E$504,$A$5:$A$504,A346,$B$5:$B$504,B346)-SUMIFS($F$5:$F$504,$A$5:$A$504,A346,$B$5:$B$504,B346))</f>
         <v/>
       </c>
       <c r="H346" s="33" t="str">
@@ -21849,7 +22017,7 @@
       <c r="E347" s="25"/>
       <c r="F347" s="25"/>
       <c r="G347" s="33" t="str">
-        <f aca="false">IF(OR(B347="",AND(A347=A346 ,B347=B346)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A347,$B$5:$B$504,B347)+SUMIFS($E$5:$E$504,$A$5:$A$504,A347,$B$5:$B$504,B347))</f>
+        <f aca="false">IF(OR(B347="",AND(A347=A346 ,B347=B346)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A347,$B$5:$B$504,B347)+SUMIFS($E$5:$E$504,$A$5:$A$504,A347,$B$5:$B$504,B347)-SUMIFS($F$5:$F$504,$A$5:$A$504,A347,$B$5:$B$504,B347))</f>
         <v/>
       </c>
       <c r="H347" s="33" t="str">
@@ -21867,7 +22035,7 @@
       <c r="E348" s="25"/>
       <c r="F348" s="25"/>
       <c r="G348" s="33" t="str">
-        <f aca="false">IF(OR(B348="",AND(A348=A347 ,B348=B347)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A348,$B$5:$B$504,B348)+SUMIFS($E$5:$E$504,$A$5:$A$504,A348,$B$5:$B$504,B348))</f>
+        <f aca="false">IF(OR(B348="",AND(A348=A347 ,B348=B347)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A348,$B$5:$B$504,B348)+SUMIFS($E$5:$E$504,$A$5:$A$504,A348,$B$5:$B$504,B348)-SUMIFS($F$5:$F$504,$A$5:$A$504,A348,$B$5:$B$504,B348))</f>
         <v/>
       </c>
       <c r="H348" s="33" t="str">
@@ -21885,7 +22053,7 @@
       <c r="E349" s="25"/>
       <c r="F349" s="25"/>
       <c r="G349" s="33" t="str">
-        <f aca="false">IF(OR(B349="",AND(A349=A348 ,B349=B348)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A349,$B$5:$B$504,B349)+SUMIFS($E$5:$E$504,$A$5:$A$504,A349,$B$5:$B$504,B349))</f>
+        <f aca="false">IF(OR(B349="",AND(A349=A348 ,B349=B348)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A349,$B$5:$B$504,B349)+SUMIFS($E$5:$E$504,$A$5:$A$504,A349,$B$5:$B$504,B349)-SUMIFS($F$5:$F$504,$A$5:$A$504,A349,$B$5:$B$504,B349))</f>
         <v/>
       </c>
       <c r="H349" s="33" t="str">
@@ -21903,7 +22071,7 @@
       <c r="E350" s="25"/>
       <c r="F350" s="25"/>
       <c r="G350" s="33" t="str">
-        <f aca="false">IF(OR(B350="",AND(A350=A349 ,B350=B349)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A350,$B$5:$B$504,B350)+SUMIFS($E$5:$E$504,$A$5:$A$504,A350,$B$5:$B$504,B350))</f>
+        <f aca="false">IF(OR(B350="",AND(A350=A349 ,B350=B349)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A350,$B$5:$B$504,B350)+SUMIFS($E$5:$E$504,$A$5:$A$504,A350,$B$5:$B$504,B350)-SUMIFS($F$5:$F$504,$A$5:$A$504,A350,$B$5:$B$504,B350))</f>
         <v/>
       </c>
       <c r="H350" s="33" t="str">
@@ -21921,7 +22089,7 @@
       <c r="E351" s="25"/>
       <c r="F351" s="25"/>
       <c r="G351" s="33" t="str">
-        <f aca="false">IF(OR(B351="",AND(A351=A350 ,B351=B350)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A351,$B$5:$B$504,B351)+SUMIFS($E$5:$E$504,$A$5:$A$504,A351,$B$5:$B$504,B351))</f>
+        <f aca="false">IF(OR(B351="",AND(A351=A350 ,B351=B350)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A351,$B$5:$B$504,B351)+SUMIFS($E$5:$E$504,$A$5:$A$504,A351,$B$5:$B$504,B351)-SUMIFS($F$5:$F$504,$A$5:$A$504,A351,$B$5:$B$504,B351))</f>
         <v/>
       </c>
       <c r="H351" s="33" t="str">
@@ -21939,7 +22107,7 @@
       <c r="E352" s="25"/>
       <c r="F352" s="25"/>
       <c r="G352" s="33" t="str">
-        <f aca="false">IF(OR(B352="",AND(A352=A351 ,B352=B351)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A352,$B$5:$B$504,B352)+SUMIFS($E$5:$E$504,$A$5:$A$504,A352,$B$5:$B$504,B352))</f>
+        <f aca="false">IF(OR(B352="",AND(A352=A351 ,B352=B351)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A352,$B$5:$B$504,B352)+SUMIFS($E$5:$E$504,$A$5:$A$504,A352,$B$5:$B$504,B352)-SUMIFS($F$5:$F$504,$A$5:$A$504,A352,$B$5:$B$504,B352))</f>
         <v/>
       </c>
       <c r="H352" s="33" t="str">
@@ -21957,7 +22125,7 @@
       <c r="E353" s="25"/>
       <c r="F353" s="25"/>
       <c r="G353" s="33" t="str">
-        <f aca="false">IF(OR(B353="",AND(A353=A352 ,B353=B352)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A353,$B$5:$B$504,B353)+SUMIFS($E$5:$E$504,$A$5:$A$504,A353,$B$5:$B$504,B353))</f>
+        <f aca="false">IF(OR(B353="",AND(A353=A352 ,B353=B352)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A353,$B$5:$B$504,B353)+SUMIFS($E$5:$E$504,$A$5:$A$504,A353,$B$5:$B$504,B353)-SUMIFS($F$5:$F$504,$A$5:$A$504,A353,$B$5:$B$504,B353))</f>
         <v/>
       </c>
       <c r="H353" s="33" t="str">
@@ -21975,7 +22143,7 @@
       <c r="E354" s="25"/>
       <c r="F354" s="25"/>
       <c r="G354" s="33" t="str">
-        <f aca="false">IF(OR(B354="",AND(A354=A353 ,B354=B353)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A354,$B$5:$B$504,B354)+SUMIFS($E$5:$E$504,$A$5:$A$504,A354,$B$5:$B$504,B354))</f>
+        <f aca="false">IF(OR(B354="",AND(A354=A353 ,B354=B353)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A354,$B$5:$B$504,B354)+SUMIFS($E$5:$E$504,$A$5:$A$504,A354,$B$5:$B$504,B354)-SUMIFS($F$5:$F$504,$A$5:$A$504,A354,$B$5:$B$504,B354))</f>
         <v/>
       </c>
       <c r="H354" s="33" t="str">
@@ -21993,7 +22161,7 @@
       <c r="E355" s="25"/>
       <c r="F355" s="25"/>
       <c r="G355" s="33" t="str">
-        <f aca="false">IF(OR(B355="",AND(A355=A354 ,B355=B354)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A355,$B$5:$B$504,B355)+SUMIFS($E$5:$E$504,$A$5:$A$504,A355,$B$5:$B$504,B355))</f>
+        <f aca="false">IF(OR(B355="",AND(A355=A354 ,B355=B354)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A355,$B$5:$B$504,B355)+SUMIFS($E$5:$E$504,$A$5:$A$504,A355,$B$5:$B$504,B355)-SUMIFS($F$5:$F$504,$A$5:$A$504,A355,$B$5:$B$504,B355))</f>
         <v/>
       </c>
       <c r="H355" s="33" t="str">
@@ -22011,7 +22179,7 @@
       <c r="E356" s="25"/>
       <c r="F356" s="25"/>
       <c r="G356" s="33" t="str">
-        <f aca="false">IF(OR(B356="",AND(A356=A355 ,B356=B355)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A356,$B$5:$B$504,B356)+SUMIFS($E$5:$E$504,$A$5:$A$504,A356,$B$5:$B$504,B356))</f>
+        <f aca="false">IF(OR(B356="",AND(A356=A355 ,B356=B355)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A356,$B$5:$B$504,B356)+SUMIFS($E$5:$E$504,$A$5:$A$504,A356,$B$5:$B$504,B356)-SUMIFS($F$5:$F$504,$A$5:$A$504,A356,$B$5:$B$504,B356))</f>
         <v/>
       </c>
       <c r="H356" s="33" t="str">
@@ -22029,7 +22197,7 @@
       <c r="E357" s="25"/>
       <c r="F357" s="25"/>
       <c r="G357" s="33" t="str">
-        <f aca="false">IF(OR(B357="",AND(A357=A356 ,B357=B356)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A357,$B$5:$B$504,B357)+SUMIFS($E$5:$E$504,$A$5:$A$504,A357,$B$5:$B$504,B357))</f>
+        <f aca="false">IF(OR(B357="",AND(A357=A356 ,B357=B356)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A357,$B$5:$B$504,B357)+SUMIFS($E$5:$E$504,$A$5:$A$504,A357,$B$5:$B$504,B357)-SUMIFS($F$5:$F$504,$A$5:$A$504,A357,$B$5:$B$504,B357))</f>
         <v/>
       </c>
       <c r="H357" s="33" t="str">
@@ -22047,7 +22215,7 @@
       <c r="E358" s="25"/>
       <c r="F358" s="25"/>
       <c r="G358" s="33" t="str">
-        <f aca="false">IF(OR(B358="",AND(A358=A357 ,B358=B357)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A358,$B$5:$B$504,B358)+SUMIFS($E$5:$E$504,$A$5:$A$504,A358,$B$5:$B$504,B358))</f>
+        <f aca="false">IF(OR(B358="",AND(A358=A357 ,B358=B357)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A358,$B$5:$B$504,B358)+SUMIFS($E$5:$E$504,$A$5:$A$504,A358,$B$5:$B$504,B358)-SUMIFS($F$5:$F$504,$A$5:$A$504,A358,$B$5:$B$504,B358))</f>
         <v/>
       </c>
       <c r="H358" s="33" t="str">
@@ -22065,7 +22233,7 @@
       <c r="E359" s="25"/>
       <c r="F359" s="25"/>
       <c r="G359" s="33" t="str">
-        <f aca="false">IF(OR(B359="",AND(A359=A358 ,B359=B358)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A359,$B$5:$B$504,B359)+SUMIFS($E$5:$E$504,$A$5:$A$504,A359,$B$5:$B$504,B359))</f>
+        <f aca="false">IF(OR(B359="",AND(A359=A358 ,B359=B358)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A359,$B$5:$B$504,B359)+SUMIFS($E$5:$E$504,$A$5:$A$504,A359,$B$5:$B$504,B359)-SUMIFS($F$5:$F$504,$A$5:$A$504,A359,$B$5:$B$504,B359))</f>
         <v/>
       </c>
       <c r="H359" s="33" t="str">
@@ -22083,7 +22251,7 @@
       <c r="E360" s="25"/>
       <c r="F360" s="25"/>
       <c r="G360" s="33" t="str">
-        <f aca="false">IF(OR(B360="",AND(A360=A359 ,B360=B359)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A360,$B$5:$B$504,B360)+SUMIFS($E$5:$E$504,$A$5:$A$504,A360,$B$5:$B$504,B360))</f>
+        <f aca="false">IF(OR(B360="",AND(A360=A359 ,B360=B359)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A360,$B$5:$B$504,B360)+SUMIFS($E$5:$E$504,$A$5:$A$504,A360,$B$5:$B$504,B360)-SUMIFS($F$5:$F$504,$A$5:$A$504,A360,$B$5:$B$504,B360))</f>
         <v/>
       </c>
       <c r="H360" s="33" t="str">
@@ -22101,7 +22269,7 @@
       <c r="E361" s="25"/>
       <c r="F361" s="25"/>
       <c r="G361" s="33" t="str">
-        <f aca="false">IF(OR(B361="",AND(A361=A360 ,B361=B360)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A361,$B$5:$B$504,B361)+SUMIFS($E$5:$E$504,$A$5:$A$504,A361,$B$5:$B$504,B361))</f>
+        <f aca="false">IF(OR(B361="",AND(A361=A360 ,B361=B360)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A361,$B$5:$B$504,B361)+SUMIFS($E$5:$E$504,$A$5:$A$504,A361,$B$5:$B$504,B361)-SUMIFS($F$5:$F$504,$A$5:$A$504,A361,$B$5:$B$504,B361))</f>
         <v/>
       </c>
       <c r="H361" s="33" t="str">
@@ -22119,7 +22287,7 @@
       <c r="E362" s="25"/>
       <c r="F362" s="25"/>
       <c r="G362" s="33" t="str">
-        <f aca="false">IF(OR(B362="",AND(A362=A361 ,B362=B361)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A362,$B$5:$B$504,B362)+SUMIFS($E$5:$E$504,$A$5:$A$504,A362,$B$5:$B$504,B362))</f>
+        <f aca="false">IF(OR(B362="",AND(A362=A361 ,B362=B361)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A362,$B$5:$B$504,B362)+SUMIFS($E$5:$E$504,$A$5:$A$504,A362,$B$5:$B$504,B362)-SUMIFS($F$5:$F$504,$A$5:$A$504,A362,$B$5:$B$504,B362))</f>
         <v/>
       </c>
       <c r="H362" s="33" t="str">
@@ -22137,7 +22305,7 @@
       <c r="E363" s="25"/>
       <c r="F363" s="25"/>
       <c r="G363" s="33" t="str">
-        <f aca="false">IF(OR(B363="",AND(A363=A362 ,B363=B362)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A363,$B$5:$B$504,B363)+SUMIFS($E$5:$E$504,$A$5:$A$504,A363,$B$5:$B$504,B363))</f>
+        <f aca="false">IF(OR(B363="",AND(A363=A362 ,B363=B362)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A363,$B$5:$B$504,B363)+SUMIFS($E$5:$E$504,$A$5:$A$504,A363,$B$5:$B$504,B363)-SUMIFS($F$5:$F$504,$A$5:$A$504,A363,$B$5:$B$504,B363))</f>
         <v/>
       </c>
       <c r="H363" s="33" t="str">
@@ -22155,7 +22323,7 @@
       <c r="E364" s="25"/>
       <c r="F364" s="25"/>
       <c r="G364" s="33" t="str">
-        <f aca="false">IF(OR(B364="",AND(A364=A363 ,B364=B363)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A364,$B$5:$B$504,B364)+SUMIFS($E$5:$E$504,$A$5:$A$504,A364,$B$5:$B$504,B364))</f>
+        <f aca="false">IF(OR(B364="",AND(A364=A363 ,B364=B363)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A364,$B$5:$B$504,B364)+SUMIFS($E$5:$E$504,$A$5:$A$504,A364,$B$5:$B$504,B364)-SUMIFS($F$5:$F$504,$A$5:$A$504,A364,$B$5:$B$504,B364))</f>
         <v/>
       </c>
       <c r="H364" s="33" t="str">
@@ -22173,7 +22341,7 @@
       <c r="E365" s="25"/>
       <c r="F365" s="25"/>
       <c r="G365" s="33" t="str">
-        <f aca="false">IF(OR(B365="",AND(A365=A364 ,B365=B364)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A365,$B$5:$B$504,B365)+SUMIFS($E$5:$E$504,$A$5:$A$504,A365,$B$5:$B$504,B365))</f>
+        <f aca="false">IF(OR(B365="",AND(A365=A364 ,B365=B364)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A365,$B$5:$B$504,B365)+SUMIFS($E$5:$E$504,$A$5:$A$504,A365,$B$5:$B$504,B365)-SUMIFS($F$5:$F$504,$A$5:$A$504,A365,$B$5:$B$504,B365))</f>
         <v/>
       </c>
       <c r="H365" s="33" t="str">
@@ -22191,7 +22359,7 @@
       <c r="E366" s="25"/>
       <c r="F366" s="25"/>
       <c r="G366" s="33" t="str">
-        <f aca="false">IF(OR(B366="",AND(A366=A365 ,B366=B365)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A366,$B$5:$B$504,B366)+SUMIFS($E$5:$E$504,$A$5:$A$504,A366,$B$5:$B$504,B366))</f>
+        <f aca="false">IF(OR(B366="",AND(A366=A365 ,B366=B365)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A366,$B$5:$B$504,B366)+SUMIFS($E$5:$E$504,$A$5:$A$504,A366,$B$5:$B$504,B366)-SUMIFS($F$5:$F$504,$A$5:$A$504,A366,$B$5:$B$504,B366))</f>
         <v/>
       </c>
       <c r="H366" s="33" t="str">
@@ -22209,7 +22377,7 @@
       <c r="E367" s="25"/>
       <c r="F367" s="25"/>
       <c r="G367" s="33" t="str">
-        <f aca="false">IF(OR(B367="",AND(A367=A366 ,B367=B366)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A367,$B$5:$B$504,B367)+SUMIFS($E$5:$E$504,$A$5:$A$504,A367,$B$5:$B$504,B367))</f>
+        <f aca="false">IF(OR(B367="",AND(A367=A366 ,B367=B366)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A367,$B$5:$B$504,B367)+SUMIFS($E$5:$E$504,$A$5:$A$504,A367,$B$5:$B$504,B367)-SUMIFS($F$5:$F$504,$A$5:$A$504,A367,$B$5:$B$504,B367))</f>
         <v/>
       </c>
       <c r="H367" s="33" t="str">
@@ -22227,7 +22395,7 @@
       <c r="E368" s="25"/>
       <c r="F368" s="25"/>
       <c r="G368" s="33" t="str">
-        <f aca="false">IF(OR(B368="",AND(A368=A367 ,B368=B367)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A368,$B$5:$B$504,B368)+SUMIFS($E$5:$E$504,$A$5:$A$504,A368,$B$5:$B$504,B368))</f>
+        <f aca="false">IF(OR(B368="",AND(A368=A367 ,B368=B367)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A368,$B$5:$B$504,B368)+SUMIFS($E$5:$E$504,$A$5:$A$504,A368,$B$5:$B$504,B368)-SUMIFS($F$5:$F$504,$A$5:$A$504,A368,$B$5:$B$504,B368))</f>
         <v/>
       </c>
       <c r="H368" s="33" t="str">
@@ -22245,7 +22413,7 @@
       <c r="E369" s="25"/>
       <c r="F369" s="25"/>
       <c r="G369" s="33" t="str">
-        <f aca="false">IF(OR(B369="",AND(A369=A368 ,B369=B368)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A369,$B$5:$B$504,B369)+SUMIFS($E$5:$E$504,$A$5:$A$504,A369,$B$5:$B$504,B369))</f>
+        <f aca="false">IF(OR(B369="",AND(A369=A368 ,B369=B368)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A369,$B$5:$B$504,B369)+SUMIFS($E$5:$E$504,$A$5:$A$504,A369,$B$5:$B$504,B369)-SUMIFS($F$5:$F$504,$A$5:$A$504,A369,$B$5:$B$504,B369))</f>
         <v/>
       </c>
       <c r="H369" s="33" t="str">
@@ -22263,7 +22431,7 @@
       <c r="E370" s="25"/>
       <c r="F370" s="25"/>
       <c r="G370" s="33" t="str">
-        <f aca="false">IF(OR(B370="",AND(A370=A369 ,B370=B369)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A370,$B$5:$B$504,B370)+SUMIFS($E$5:$E$504,$A$5:$A$504,A370,$B$5:$B$504,B370))</f>
+        <f aca="false">IF(OR(B370="",AND(A370=A369 ,B370=B369)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A370,$B$5:$B$504,B370)+SUMIFS($E$5:$E$504,$A$5:$A$504,A370,$B$5:$B$504,B370)-SUMIFS($F$5:$F$504,$A$5:$A$504,A370,$B$5:$B$504,B370))</f>
         <v/>
       </c>
       <c r="H370" s="33" t="str">
@@ -22281,7 +22449,7 @@
       <c r="E371" s="25"/>
       <c r="F371" s="25"/>
       <c r="G371" s="33" t="str">
-        <f aca="false">IF(OR(B371="",AND(A371=A370 ,B371=B370)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A371,$B$5:$B$504,B371)+SUMIFS($E$5:$E$504,$A$5:$A$504,A371,$B$5:$B$504,B371))</f>
+        <f aca="false">IF(OR(B371="",AND(A371=A370 ,B371=B370)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A371,$B$5:$B$504,B371)+SUMIFS($E$5:$E$504,$A$5:$A$504,A371,$B$5:$B$504,B371)-SUMIFS($F$5:$F$504,$A$5:$A$504,A371,$B$5:$B$504,B371))</f>
         <v/>
       </c>
       <c r="H371" s="33" t="str">
@@ -22299,7 +22467,7 @@
       <c r="E372" s="25"/>
       <c r="F372" s="25"/>
       <c r="G372" s="33" t="str">
-        <f aca="false">IF(OR(B372="",AND(A372=A371 ,B372=B371)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A372,$B$5:$B$504,B372)+SUMIFS($E$5:$E$504,$A$5:$A$504,A372,$B$5:$B$504,B372))</f>
+        <f aca="false">IF(OR(B372="",AND(A372=A371 ,B372=B371)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A372,$B$5:$B$504,B372)+SUMIFS($E$5:$E$504,$A$5:$A$504,A372,$B$5:$B$504,B372)-SUMIFS($F$5:$F$504,$A$5:$A$504,A372,$B$5:$B$504,B372))</f>
         <v/>
       </c>
       <c r="H372" s="33" t="str">
@@ -22317,7 +22485,7 @@
       <c r="E373" s="25"/>
       <c r="F373" s="25"/>
       <c r="G373" s="33" t="str">
-        <f aca="false">IF(OR(B373="",AND(A373=A372 ,B373=B372)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A373,$B$5:$B$504,B373)+SUMIFS($E$5:$E$504,$A$5:$A$504,A373,$B$5:$B$504,B373))</f>
+        <f aca="false">IF(OR(B373="",AND(A373=A372 ,B373=B372)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A373,$B$5:$B$504,B373)+SUMIFS($E$5:$E$504,$A$5:$A$504,A373,$B$5:$B$504,B373)-SUMIFS($F$5:$F$504,$A$5:$A$504,A373,$B$5:$B$504,B373))</f>
         <v/>
       </c>
       <c r="H373" s="33" t="str">
@@ -22335,7 +22503,7 @@
       <c r="E374" s="25"/>
       <c r="F374" s="25"/>
       <c r="G374" s="33" t="str">
-        <f aca="false">IF(OR(B374="",AND(A374=A373 ,B374=B373)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A374,$B$5:$B$504,B374)+SUMIFS($E$5:$E$504,$A$5:$A$504,A374,$B$5:$B$504,B374))</f>
+        <f aca="false">IF(OR(B374="",AND(A374=A373 ,B374=B373)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A374,$B$5:$B$504,B374)+SUMIFS($E$5:$E$504,$A$5:$A$504,A374,$B$5:$B$504,B374)-SUMIFS($F$5:$F$504,$A$5:$A$504,A374,$B$5:$B$504,B374))</f>
         <v/>
       </c>
       <c r="H374" s="33" t="str">
@@ -22353,7 +22521,7 @@
       <c r="E375" s="25"/>
       <c r="F375" s="25"/>
       <c r="G375" s="33" t="str">
-        <f aca="false">IF(OR(B375="",AND(A375=A374 ,B375=B374)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A375,$B$5:$B$504,B375)+SUMIFS($E$5:$E$504,$A$5:$A$504,A375,$B$5:$B$504,B375))</f>
+        <f aca="false">IF(OR(B375="",AND(A375=A374 ,B375=B374)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A375,$B$5:$B$504,B375)+SUMIFS($E$5:$E$504,$A$5:$A$504,A375,$B$5:$B$504,B375)-SUMIFS($F$5:$F$504,$A$5:$A$504,A375,$B$5:$B$504,B375))</f>
         <v/>
       </c>
       <c r="H375" s="33" t="str">
@@ -22371,7 +22539,7 @@
       <c r="E376" s="25"/>
       <c r="F376" s="25"/>
       <c r="G376" s="33" t="str">
-        <f aca="false">IF(OR(B376="",AND(A376=A375 ,B376=B375)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A376,$B$5:$B$504,B376)+SUMIFS($E$5:$E$504,$A$5:$A$504,A376,$B$5:$B$504,B376))</f>
+        <f aca="false">IF(OR(B376="",AND(A376=A375 ,B376=B375)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A376,$B$5:$B$504,B376)+SUMIFS($E$5:$E$504,$A$5:$A$504,A376,$B$5:$B$504,B376)-SUMIFS($F$5:$F$504,$A$5:$A$504,A376,$B$5:$B$504,B376))</f>
         <v/>
       </c>
       <c r="H376" s="33" t="str">
@@ -22389,7 +22557,7 @@
       <c r="E377" s="25"/>
       <c r="F377" s="25"/>
       <c r="G377" s="33" t="str">
-        <f aca="false">IF(OR(B377="",AND(A377=A376 ,B377=B376)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A377,$B$5:$B$504,B377)+SUMIFS($E$5:$E$504,$A$5:$A$504,A377,$B$5:$B$504,B377))</f>
+        <f aca="false">IF(OR(B377="",AND(A377=A376 ,B377=B376)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A377,$B$5:$B$504,B377)+SUMIFS($E$5:$E$504,$A$5:$A$504,A377,$B$5:$B$504,B377)-SUMIFS($F$5:$F$504,$A$5:$A$504,A377,$B$5:$B$504,B377))</f>
         <v/>
       </c>
       <c r="H377" s="33" t="str">
@@ -22407,7 +22575,7 @@
       <c r="E378" s="25"/>
       <c r="F378" s="25"/>
       <c r="G378" s="33" t="str">
-        <f aca="false">IF(OR(B378="",AND(A378=A377 ,B378=B377)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A378,$B$5:$B$504,B378)+SUMIFS($E$5:$E$504,$A$5:$A$504,A378,$B$5:$B$504,B378))</f>
+        <f aca="false">IF(OR(B378="",AND(A378=A377 ,B378=B377)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A378,$B$5:$B$504,B378)+SUMIFS($E$5:$E$504,$A$5:$A$504,A378,$B$5:$B$504,B378)-SUMIFS($F$5:$F$504,$A$5:$A$504,A378,$B$5:$B$504,B378))</f>
         <v/>
       </c>
       <c r="H378" s="33" t="str">
@@ -22425,7 +22593,7 @@
       <c r="E379" s="25"/>
       <c r="F379" s="25"/>
       <c r="G379" s="33" t="str">
-        <f aca="false">IF(OR(B379="",AND(A379=A378 ,B379=B378)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A379,$B$5:$B$504,B379)+SUMIFS($E$5:$E$504,$A$5:$A$504,A379,$B$5:$B$504,B379))</f>
+        <f aca="false">IF(OR(B379="",AND(A379=A378 ,B379=B378)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A379,$B$5:$B$504,B379)+SUMIFS($E$5:$E$504,$A$5:$A$504,A379,$B$5:$B$504,B379)-SUMIFS($F$5:$F$504,$A$5:$A$504,A379,$B$5:$B$504,B379))</f>
         <v/>
       </c>
       <c r="H379" s="33" t="str">
@@ -22443,7 +22611,7 @@
       <c r="E380" s="25"/>
       <c r="F380" s="25"/>
       <c r="G380" s="33" t="str">
-        <f aca="false">IF(OR(B380="",AND(A380=A379 ,B380=B379)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A380,$B$5:$B$504,B380)+SUMIFS($E$5:$E$504,$A$5:$A$504,A380,$B$5:$B$504,B380))</f>
+        <f aca="false">IF(OR(B380="",AND(A380=A379 ,B380=B379)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A380,$B$5:$B$504,B380)+SUMIFS($E$5:$E$504,$A$5:$A$504,A380,$B$5:$B$504,B380)-SUMIFS($F$5:$F$504,$A$5:$A$504,A380,$B$5:$B$504,B380))</f>
         <v/>
       </c>
       <c r="H380" s="33" t="str">
@@ -22461,7 +22629,7 @@
       <c r="E381" s="25"/>
       <c r="F381" s="25"/>
       <c r="G381" s="33" t="str">
-        <f aca="false">IF(OR(B381="",AND(A381=A380 ,B381=B380)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A381,$B$5:$B$504,B381)+SUMIFS($E$5:$E$504,$A$5:$A$504,A381,$B$5:$B$504,B381))</f>
+        <f aca="false">IF(OR(B381="",AND(A381=A380 ,B381=B380)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A381,$B$5:$B$504,B381)+SUMIFS($E$5:$E$504,$A$5:$A$504,A381,$B$5:$B$504,B381)-SUMIFS($F$5:$F$504,$A$5:$A$504,A381,$B$5:$B$504,B381))</f>
         <v/>
       </c>
       <c r="H381" s="33" t="str">
@@ -22479,7 +22647,7 @@
       <c r="E382" s="25"/>
       <c r="F382" s="25"/>
       <c r="G382" s="33" t="str">
-        <f aca="false">IF(OR(B382="",AND(A382=A381 ,B382=B381)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A382,$B$5:$B$504,B382)+SUMIFS($E$5:$E$504,$A$5:$A$504,A382,$B$5:$B$504,B382))</f>
+        <f aca="false">IF(OR(B382="",AND(A382=A381 ,B382=B381)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A382,$B$5:$B$504,B382)+SUMIFS($E$5:$E$504,$A$5:$A$504,A382,$B$5:$B$504,B382)-SUMIFS($F$5:$F$504,$A$5:$A$504,A382,$B$5:$B$504,B382))</f>
         <v/>
       </c>
       <c r="H382" s="33" t="str">
@@ -22497,7 +22665,7 @@
       <c r="E383" s="25"/>
       <c r="F383" s="25"/>
       <c r="G383" s="33" t="str">
-        <f aca="false">IF(OR(B383="",AND(A383=A382 ,B383=B382)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A383,$B$5:$B$504,B383)+SUMIFS($E$5:$E$504,$A$5:$A$504,A383,$B$5:$B$504,B383))</f>
+        <f aca="false">IF(OR(B383="",AND(A383=A382 ,B383=B382)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A383,$B$5:$B$504,B383)+SUMIFS($E$5:$E$504,$A$5:$A$504,A383,$B$5:$B$504,B383)-SUMIFS($F$5:$F$504,$A$5:$A$504,A383,$B$5:$B$504,B383))</f>
         <v/>
       </c>
       <c r="H383" s="33" t="str">
@@ -22515,7 +22683,7 @@
       <c r="E384" s="25"/>
       <c r="F384" s="25"/>
       <c r="G384" s="33" t="str">
-        <f aca="false">IF(OR(B384="",AND(A384=A383 ,B384=B383)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A384,$B$5:$B$504,B384)+SUMIFS($E$5:$E$504,$A$5:$A$504,A384,$B$5:$B$504,B384))</f>
+        <f aca="false">IF(OR(B384="",AND(A384=A383 ,B384=B383)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A384,$B$5:$B$504,B384)+SUMIFS($E$5:$E$504,$A$5:$A$504,A384,$B$5:$B$504,B384)-SUMIFS($F$5:$F$504,$A$5:$A$504,A384,$B$5:$B$504,B384))</f>
         <v/>
       </c>
       <c r="H384" s="33" t="str">
@@ -22533,7 +22701,7 @@
       <c r="E385" s="25"/>
       <c r="F385" s="25"/>
       <c r="G385" s="33" t="str">
-        <f aca="false">IF(OR(B385="",AND(A385=A384 ,B385=B384)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A385,$B$5:$B$504,B385)+SUMIFS($E$5:$E$504,$A$5:$A$504,A385,$B$5:$B$504,B385))</f>
+        <f aca="false">IF(OR(B385="",AND(A385=A384 ,B385=B384)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A385,$B$5:$B$504,B385)+SUMIFS($E$5:$E$504,$A$5:$A$504,A385,$B$5:$B$504,B385)-SUMIFS($F$5:$F$504,$A$5:$A$504,A385,$B$5:$B$504,B385))</f>
         <v/>
       </c>
       <c r="H385" s="33" t="str">
@@ -22551,7 +22719,7 @@
       <c r="E386" s="25"/>
       <c r="F386" s="25"/>
       <c r="G386" s="33" t="str">
-        <f aca="false">IF(OR(B386="",AND(A386=A385 ,B386=B385)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A386,$B$5:$B$504,B386)+SUMIFS($E$5:$E$504,$A$5:$A$504,A386,$B$5:$B$504,B386))</f>
+        <f aca="false">IF(OR(B386="",AND(A386=A385 ,B386=B385)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A386,$B$5:$B$504,B386)+SUMIFS($E$5:$E$504,$A$5:$A$504,A386,$B$5:$B$504,B386)-SUMIFS($F$5:$F$504,$A$5:$A$504,A386,$B$5:$B$504,B386))</f>
         <v/>
       </c>
       <c r="H386" s="33" t="str">
@@ -22569,7 +22737,7 @@
       <c r="E387" s="25"/>
       <c r="F387" s="25"/>
       <c r="G387" s="33" t="str">
-        <f aca="false">IF(OR(B387="",AND(A387=A386 ,B387=B386)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A387,$B$5:$B$504,B387)+SUMIFS($E$5:$E$504,$A$5:$A$504,A387,$B$5:$B$504,B387))</f>
+        <f aca="false">IF(OR(B387="",AND(A387=A386 ,B387=B386)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A387,$B$5:$B$504,B387)+SUMIFS($E$5:$E$504,$A$5:$A$504,A387,$B$5:$B$504,B387)-SUMIFS($F$5:$F$504,$A$5:$A$504,A387,$B$5:$B$504,B387))</f>
         <v/>
       </c>
       <c r="H387" s="33" t="str">
@@ -22587,7 +22755,7 @@
       <c r="E388" s="25"/>
       <c r="F388" s="25"/>
       <c r="G388" s="33" t="str">
-        <f aca="false">IF(OR(B388="",AND(A388=A387 ,B388=B387)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A388,$B$5:$B$504,B388)+SUMIFS($E$5:$E$504,$A$5:$A$504,A388,$B$5:$B$504,B388))</f>
+        <f aca="false">IF(OR(B388="",AND(A388=A387 ,B388=B387)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A388,$B$5:$B$504,B388)+SUMIFS($E$5:$E$504,$A$5:$A$504,A388,$B$5:$B$504,B388)-SUMIFS($F$5:$F$504,$A$5:$A$504,A388,$B$5:$B$504,B388))</f>
         <v/>
       </c>
       <c r="H388" s="33" t="str">
@@ -22605,7 +22773,7 @@
       <c r="E389" s="25"/>
       <c r="F389" s="25"/>
       <c r="G389" s="33" t="str">
-        <f aca="false">IF(OR(B389="",AND(A389=A388 ,B389=B388)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A389,$B$5:$B$504,B389)+SUMIFS($E$5:$E$504,$A$5:$A$504,A389,$B$5:$B$504,B389))</f>
+        <f aca="false">IF(OR(B389="",AND(A389=A388 ,B389=B388)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A389,$B$5:$B$504,B389)+SUMIFS($E$5:$E$504,$A$5:$A$504,A389,$B$5:$B$504,B389)-SUMIFS($F$5:$F$504,$A$5:$A$504,A389,$B$5:$B$504,B389))</f>
         <v/>
       </c>
       <c r="H389" s="33" t="str">
@@ -22623,7 +22791,7 @@
       <c r="E390" s="25"/>
       <c r="F390" s="25"/>
       <c r="G390" s="33" t="str">
-        <f aca="false">IF(OR(B390="",AND(A390=A389 ,B390=B389)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A390,$B$5:$B$504,B390)+SUMIFS($E$5:$E$504,$A$5:$A$504,A390,$B$5:$B$504,B390))</f>
+        <f aca="false">IF(OR(B390="",AND(A390=A389 ,B390=B389)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A390,$B$5:$B$504,B390)+SUMIFS($E$5:$E$504,$A$5:$A$504,A390,$B$5:$B$504,B390)-SUMIFS($F$5:$F$504,$A$5:$A$504,A390,$B$5:$B$504,B390))</f>
         <v/>
       </c>
       <c r="H390" s="33" t="str">
@@ -22641,7 +22809,7 @@
       <c r="E391" s="25"/>
       <c r="F391" s="25"/>
       <c r="G391" s="33" t="str">
-        <f aca="false">IF(OR(B391="",AND(A391=A390 ,B391=B390)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A391,$B$5:$B$504,B391)+SUMIFS($E$5:$E$504,$A$5:$A$504,A391,$B$5:$B$504,B391))</f>
+        <f aca="false">IF(OR(B391="",AND(A391=A390 ,B391=B390)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A391,$B$5:$B$504,B391)+SUMIFS($E$5:$E$504,$A$5:$A$504,A391,$B$5:$B$504,B391)-SUMIFS($F$5:$F$504,$A$5:$A$504,A391,$B$5:$B$504,B391))</f>
         <v/>
       </c>
       <c r="H391" s="33" t="str">
@@ -22659,7 +22827,7 @@
       <c r="E392" s="25"/>
       <c r="F392" s="25"/>
       <c r="G392" s="33" t="str">
-        <f aca="false">IF(OR(B392="",AND(A392=A391 ,B392=B391)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A392,$B$5:$B$504,B392)+SUMIFS($E$5:$E$504,$A$5:$A$504,A392,$B$5:$B$504,B392))</f>
+        <f aca="false">IF(OR(B392="",AND(A392=A391 ,B392=B391)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A392,$B$5:$B$504,B392)+SUMIFS($E$5:$E$504,$A$5:$A$504,A392,$B$5:$B$504,B392)-SUMIFS($F$5:$F$504,$A$5:$A$504,A392,$B$5:$B$504,B392))</f>
         <v/>
       </c>
       <c r="H392" s="33" t="str">
@@ -22677,7 +22845,7 @@
       <c r="E393" s="25"/>
       <c r="F393" s="25"/>
       <c r="G393" s="33" t="str">
-        <f aca="false">IF(OR(B393="",AND(A393=A392 ,B393=B392)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A393,$B$5:$B$504,B393)+SUMIFS($E$5:$E$504,$A$5:$A$504,A393,$B$5:$B$504,B393))</f>
+        <f aca="false">IF(OR(B393="",AND(A393=A392 ,B393=B392)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A393,$B$5:$B$504,B393)+SUMIFS($E$5:$E$504,$A$5:$A$504,A393,$B$5:$B$504,B393)-SUMIFS($F$5:$F$504,$A$5:$A$504,A393,$B$5:$B$504,B393))</f>
         <v/>
       </c>
       <c r="H393" s="33" t="str">
@@ -22695,7 +22863,7 @@
       <c r="E394" s="25"/>
       <c r="F394" s="25"/>
       <c r="G394" s="33" t="str">
-        <f aca="false">IF(OR(B394="",AND(A394=A393 ,B394=B393)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A394,$B$5:$B$504,B394)+SUMIFS($E$5:$E$504,$A$5:$A$504,A394,$B$5:$B$504,B394))</f>
+        <f aca="false">IF(OR(B394="",AND(A394=A393 ,B394=B393)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A394,$B$5:$B$504,B394)+SUMIFS($E$5:$E$504,$A$5:$A$504,A394,$B$5:$B$504,B394)-SUMIFS($F$5:$F$504,$A$5:$A$504,A394,$B$5:$B$504,B394))</f>
         <v/>
       </c>
       <c r="H394" s="33" t="str">
@@ -22713,7 +22881,7 @@
       <c r="E395" s="25"/>
       <c r="F395" s="25"/>
       <c r="G395" s="33" t="str">
-        <f aca="false">IF(OR(B395="",AND(A395=A394 ,B395=B394)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A395,$B$5:$B$504,B395)+SUMIFS($E$5:$E$504,$A$5:$A$504,A395,$B$5:$B$504,B395))</f>
+        <f aca="false">IF(OR(B395="",AND(A395=A394 ,B395=B394)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A395,$B$5:$B$504,B395)+SUMIFS($E$5:$E$504,$A$5:$A$504,A395,$B$5:$B$504,B395)-SUMIFS($F$5:$F$504,$A$5:$A$504,A395,$B$5:$B$504,B395))</f>
         <v/>
       </c>
       <c r="H395" s="33" t="str">
@@ -22731,7 +22899,7 @@
       <c r="E396" s="25"/>
       <c r="F396" s="25"/>
       <c r="G396" s="33" t="str">
-        <f aca="false">IF(OR(B396="",AND(A396=A395 ,B396=B395)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A396,$B$5:$B$504,B396)+SUMIFS($E$5:$E$504,$A$5:$A$504,A396,$B$5:$B$504,B396))</f>
+        <f aca="false">IF(OR(B396="",AND(A396=A395 ,B396=B395)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A396,$B$5:$B$504,B396)+SUMIFS($E$5:$E$504,$A$5:$A$504,A396,$B$5:$B$504,B396)-SUMIFS($F$5:$F$504,$A$5:$A$504,A396,$B$5:$B$504,B396))</f>
         <v/>
       </c>
       <c r="H396" s="33" t="str">
@@ -22749,7 +22917,7 @@
       <c r="E397" s="25"/>
       <c r="F397" s="25"/>
       <c r="G397" s="33" t="str">
-        <f aca="false">IF(OR(B397="",AND(A397=A396 ,B397=B396)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A397,$B$5:$B$504,B397)+SUMIFS($E$5:$E$504,$A$5:$A$504,A397,$B$5:$B$504,B397))</f>
+        <f aca="false">IF(OR(B397="",AND(A397=A396 ,B397=B396)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A397,$B$5:$B$504,B397)+SUMIFS($E$5:$E$504,$A$5:$A$504,A397,$B$5:$B$504,B397)-SUMIFS($F$5:$F$504,$A$5:$A$504,A397,$B$5:$B$504,B397))</f>
         <v/>
       </c>
       <c r="H397" s="33" t="str">
@@ -22767,7 +22935,7 @@
       <c r="E398" s="25"/>
       <c r="F398" s="25"/>
       <c r="G398" s="33" t="str">
-        <f aca="false">IF(OR(B398="",AND(A398=A397 ,B398=B397)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A398,$B$5:$B$504,B398)+SUMIFS($E$5:$E$504,$A$5:$A$504,A398,$B$5:$B$504,B398))</f>
+        <f aca="false">IF(OR(B398="",AND(A398=A397 ,B398=B397)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A398,$B$5:$B$504,B398)+SUMIFS($E$5:$E$504,$A$5:$A$504,A398,$B$5:$B$504,B398)-SUMIFS($F$5:$F$504,$A$5:$A$504,A398,$B$5:$B$504,B398))</f>
         <v/>
       </c>
       <c r="H398" s="33" t="str">
@@ -22785,7 +22953,7 @@
       <c r="E399" s="25"/>
       <c r="F399" s="25"/>
       <c r="G399" s="33" t="str">
-        <f aca="false">IF(OR(B399="",AND(A399=A398 ,B399=B398)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A399,$B$5:$B$504,B399)+SUMIFS($E$5:$E$504,$A$5:$A$504,A399,$B$5:$B$504,B399))</f>
+        <f aca="false">IF(OR(B399="",AND(A399=A398 ,B399=B398)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A399,$B$5:$B$504,B399)+SUMIFS($E$5:$E$504,$A$5:$A$504,A399,$B$5:$B$504,B399)-SUMIFS($F$5:$F$504,$A$5:$A$504,A399,$B$5:$B$504,B399))</f>
         <v/>
       </c>
       <c r="H399" s="33" t="str">
@@ -22803,7 +22971,7 @@
       <c r="E400" s="25"/>
       <c r="F400" s="25"/>
       <c r="G400" s="33" t="str">
-        <f aca="false">IF(OR(B400="",AND(A400=A399 ,B400=B399)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A400,$B$5:$B$504,B400)+SUMIFS($E$5:$E$504,$A$5:$A$504,A400,$B$5:$B$504,B400))</f>
+        <f aca="false">IF(OR(B400="",AND(A400=A399 ,B400=B399)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A400,$B$5:$B$504,B400)+SUMIFS($E$5:$E$504,$A$5:$A$504,A400,$B$5:$B$504,B400)-SUMIFS($F$5:$F$504,$A$5:$A$504,A400,$B$5:$B$504,B400))</f>
         <v/>
       </c>
       <c r="H400" s="33" t="str">
@@ -22821,7 +22989,7 @@
       <c r="E401" s="25"/>
       <c r="F401" s="25"/>
       <c r="G401" s="33" t="str">
-        <f aca="false">IF(OR(B401="",AND(A401=A400 ,B401=B400)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A401,$B$5:$B$504,B401)+SUMIFS($E$5:$E$504,$A$5:$A$504,A401,$B$5:$B$504,B401))</f>
+        <f aca="false">IF(OR(B401="",AND(A401=A400 ,B401=B400)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A401,$B$5:$B$504,B401)+SUMIFS($E$5:$E$504,$A$5:$A$504,A401,$B$5:$B$504,B401)-SUMIFS($F$5:$F$504,$A$5:$A$504,A401,$B$5:$B$504,B401))</f>
         <v/>
       </c>
       <c r="H401" s="33" t="str">
@@ -22839,7 +23007,7 @@
       <c r="E402" s="25"/>
       <c r="F402" s="25"/>
       <c r="G402" s="33" t="str">
-        <f aca="false">IF(OR(B402="",AND(A402=A401 ,B402=B401)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A402,$B$5:$B$504,B402)+SUMIFS($E$5:$E$504,$A$5:$A$504,A402,$B$5:$B$504,B402))</f>
+        <f aca="false">IF(OR(B402="",AND(A402=A401 ,B402=B401)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A402,$B$5:$B$504,B402)+SUMIFS($E$5:$E$504,$A$5:$A$504,A402,$B$5:$B$504,B402)-SUMIFS($F$5:$F$504,$A$5:$A$504,A402,$B$5:$B$504,B402))</f>
         <v/>
       </c>
       <c r="H402" s="33" t="str">
@@ -22857,7 +23025,7 @@
       <c r="E403" s="25"/>
       <c r="F403" s="25"/>
       <c r="G403" s="33" t="str">
-        <f aca="false">IF(OR(B403="",AND(A403=A402 ,B403=B402)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A403,$B$5:$B$504,B403)+SUMIFS($E$5:$E$504,$A$5:$A$504,A403,$B$5:$B$504,B403))</f>
+        <f aca="false">IF(OR(B403="",AND(A403=A402 ,B403=B402)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A403,$B$5:$B$504,B403)+SUMIFS($E$5:$E$504,$A$5:$A$504,A403,$B$5:$B$504,B403)-SUMIFS($F$5:$F$504,$A$5:$A$504,A403,$B$5:$B$504,B403))</f>
         <v/>
       </c>
       <c r="H403" s="33" t="str">
@@ -22875,7 +23043,7 @@
       <c r="E404" s="25"/>
       <c r="F404" s="25"/>
       <c r="G404" s="33" t="str">
-        <f aca="false">IF(OR(B404="",AND(A404=A403 ,B404=B403)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A404,$B$5:$B$504,B404)+SUMIFS($E$5:$E$504,$A$5:$A$504,A404,$B$5:$B$504,B404))</f>
+        <f aca="false">IF(OR(B404="",AND(A404=A403 ,B404=B403)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A404,$B$5:$B$504,B404)+SUMIFS($E$5:$E$504,$A$5:$A$504,A404,$B$5:$B$504,B404)-SUMIFS($F$5:$F$504,$A$5:$A$504,A404,$B$5:$B$504,B404))</f>
         <v/>
       </c>
       <c r="H404" s="33" t="str">
@@ -22893,7 +23061,7 @@
       <c r="E405" s="25"/>
       <c r="F405" s="25"/>
       <c r="G405" s="33" t="str">
-        <f aca="false">IF(OR(B405="",AND(A405=A404 ,B405=B404)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A405,$B$5:$B$504,B405)+SUMIFS($E$5:$E$504,$A$5:$A$504,A405,$B$5:$B$504,B405))</f>
+        <f aca="false">IF(OR(B405="",AND(A405=A404 ,B405=B404)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A405,$B$5:$B$504,B405)+SUMIFS($E$5:$E$504,$A$5:$A$504,A405,$B$5:$B$504,B405)-SUMIFS($F$5:$F$504,$A$5:$A$504,A405,$B$5:$B$504,B405))</f>
         <v/>
       </c>
       <c r="H405" s="33" t="str">
@@ -22911,7 +23079,7 @@
       <c r="E406" s="25"/>
       <c r="F406" s="25"/>
       <c r="G406" s="33" t="str">
-        <f aca="false">IF(OR(B406="",AND(A406=A405 ,B406=B405)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A406,$B$5:$B$504,B406)+SUMIFS($E$5:$E$504,$A$5:$A$504,A406,$B$5:$B$504,B406))</f>
+        <f aca="false">IF(OR(B406="",AND(A406=A405 ,B406=B405)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A406,$B$5:$B$504,B406)+SUMIFS($E$5:$E$504,$A$5:$A$504,A406,$B$5:$B$504,B406)-SUMIFS($F$5:$F$504,$A$5:$A$504,A406,$B$5:$B$504,B406))</f>
         <v/>
       </c>
       <c r="H406" s="33" t="str">
@@ -22929,7 +23097,7 @@
       <c r="E407" s="25"/>
       <c r="F407" s="25"/>
       <c r="G407" s="33" t="str">
-        <f aca="false">IF(OR(B407="",AND(A407=A406 ,B407=B406)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A407,$B$5:$B$504,B407)+SUMIFS($E$5:$E$504,$A$5:$A$504,A407,$B$5:$B$504,B407))</f>
+        <f aca="false">IF(OR(B407="",AND(A407=A406 ,B407=B406)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A407,$B$5:$B$504,B407)+SUMIFS($E$5:$E$504,$A$5:$A$504,A407,$B$5:$B$504,B407)-SUMIFS($F$5:$F$504,$A$5:$A$504,A407,$B$5:$B$504,B407))</f>
         <v/>
       </c>
       <c r="H407" s="33" t="str">
@@ -22947,7 +23115,7 @@
       <c r="E408" s="25"/>
       <c r="F408" s="25"/>
       <c r="G408" s="33" t="str">
-        <f aca="false">IF(OR(B408="",AND(A408=A407 ,B408=B407)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A408,$B$5:$B$504,B408)+SUMIFS($E$5:$E$504,$A$5:$A$504,A408,$B$5:$B$504,B408))</f>
+        <f aca="false">IF(OR(B408="",AND(A408=A407 ,B408=B407)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A408,$B$5:$B$504,B408)+SUMIFS($E$5:$E$504,$A$5:$A$504,A408,$B$5:$B$504,B408)-SUMIFS($F$5:$F$504,$A$5:$A$504,A408,$B$5:$B$504,B408))</f>
         <v/>
       </c>
       <c r="H408" s="33" t="str">
@@ -22965,7 +23133,7 @@
       <c r="E409" s="25"/>
       <c r="F409" s="25"/>
       <c r="G409" s="33" t="str">
-        <f aca="false">IF(OR(B409="",AND(A409=A408 ,B409=B408)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A409,$B$5:$B$504,B409)+SUMIFS($E$5:$E$504,$A$5:$A$504,A409,$B$5:$B$504,B409))</f>
+        <f aca="false">IF(OR(B409="",AND(A409=A408 ,B409=B408)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A409,$B$5:$B$504,B409)+SUMIFS($E$5:$E$504,$A$5:$A$504,A409,$B$5:$B$504,B409)-SUMIFS($F$5:$F$504,$A$5:$A$504,A409,$B$5:$B$504,B409))</f>
         <v/>
       </c>
       <c r="H409" s="33" t="str">
@@ -22983,7 +23151,7 @@
       <c r="E410" s="25"/>
       <c r="F410" s="25"/>
       <c r="G410" s="33" t="str">
-        <f aca="false">IF(OR(B410="",AND(A410=A409 ,B410=B409)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A410,$B$5:$B$504,B410)+SUMIFS($E$5:$E$504,$A$5:$A$504,A410,$B$5:$B$504,B410))</f>
+        <f aca="false">IF(OR(B410="",AND(A410=A409 ,B410=B409)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A410,$B$5:$B$504,B410)+SUMIFS($E$5:$E$504,$A$5:$A$504,A410,$B$5:$B$504,B410)-SUMIFS($F$5:$F$504,$A$5:$A$504,A410,$B$5:$B$504,B410))</f>
         <v/>
       </c>
       <c r="H410" s="33" t="str">
@@ -23001,7 +23169,7 @@
       <c r="E411" s="25"/>
       <c r="F411" s="25"/>
       <c r="G411" s="33" t="str">
-        <f aca="false">IF(OR(B411="",AND(A411=A410 ,B411=B410)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A411,$B$5:$B$504,B411)+SUMIFS($E$5:$E$504,$A$5:$A$504,A411,$B$5:$B$504,B411))</f>
+        <f aca="false">IF(OR(B411="",AND(A411=A410 ,B411=B410)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A411,$B$5:$B$504,B411)+SUMIFS($E$5:$E$504,$A$5:$A$504,A411,$B$5:$B$504,B411)-SUMIFS($F$5:$F$504,$A$5:$A$504,A411,$B$5:$B$504,B411))</f>
         <v/>
       </c>
       <c r="H411" s="33" t="str">
@@ -23019,7 +23187,7 @@
       <c r="E412" s="25"/>
       <c r="F412" s="25"/>
       <c r="G412" s="33" t="str">
-        <f aca="false">IF(OR(B412="",AND(A412=A411 ,B412=B411)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A412,$B$5:$B$504,B412)+SUMIFS($E$5:$E$504,$A$5:$A$504,A412,$B$5:$B$504,B412))</f>
+        <f aca="false">IF(OR(B412="",AND(A412=A411 ,B412=B411)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A412,$B$5:$B$504,B412)+SUMIFS($E$5:$E$504,$A$5:$A$504,A412,$B$5:$B$504,B412)-SUMIFS($F$5:$F$504,$A$5:$A$504,A412,$B$5:$B$504,B412))</f>
         <v/>
       </c>
       <c r="H412" s="33" t="str">
@@ -23037,7 +23205,7 @@
       <c r="E413" s="25"/>
       <c r="F413" s="25"/>
       <c r="G413" s="33" t="str">
-        <f aca="false">IF(OR(B413="",AND(A413=A412 ,B413=B412)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A413,$B$5:$B$504,B413)+SUMIFS($E$5:$E$504,$A$5:$A$504,A413,$B$5:$B$504,B413))</f>
+        <f aca="false">IF(OR(B413="",AND(A413=A412 ,B413=B412)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A413,$B$5:$B$504,B413)+SUMIFS($E$5:$E$504,$A$5:$A$504,A413,$B$5:$B$504,B413)-SUMIFS($F$5:$F$504,$A$5:$A$504,A413,$B$5:$B$504,B413))</f>
         <v/>
       </c>
       <c r="H413" s="33" t="str">
@@ -23055,7 +23223,7 @@
       <c r="E414" s="25"/>
       <c r="F414" s="25"/>
       <c r="G414" s="33" t="str">
-        <f aca="false">IF(OR(B414="",AND(A414=A413 ,B414=B413)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A414,$B$5:$B$504,B414)+SUMIFS($E$5:$E$504,$A$5:$A$504,A414,$B$5:$B$504,B414))</f>
+        <f aca="false">IF(OR(B414="",AND(A414=A413 ,B414=B413)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A414,$B$5:$B$504,B414)+SUMIFS($E$5:$E$504,$A$5:$A$504,A414,$B$5:$B$504,B414)-SUMIFS($F$5:$F$504,$A$5:$A$504,A414,$B$5:$B$504,B414))</f>
         <v/>
       </c>
       <c r="H414" s="33" t="str">
@@ -23073,7 +23241,7 @@
       <c r="E415" s="25"/>
       <c r="F415" s="25"/>
       <c r="G415" s="33" t="str">
-        <f aca="false">IF(OR(B415="",AND(A415=A414 ,B415=B414)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A415,$B$5:$B$504,B415)+SUMIFS($E$5:$E$504,$A$5:$A$504,A415,$B$5:$B$504,B415))</f>
+        <f aca="false">IF(OR(B415="",AND(A415=A414 ,B415=B414)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A415,$B$5:$B$504,B415)+SUMIFS($E$5:$E$504,$A$5:$A$504,A415,$B$5:$B$504,B415)-SUMIFS($F$5:$F$504,$A$5:$A$504,A415,$B$5:$B$504,B415))</f>
         <v/>
       </c>
       <c r="H415" s="33" t="str">
@@ -23091,7 +23259,7 @@
       <c r="E416" s="25"/>
       <c r="F416" s="25"/>
       <c r="G416" s="33" t="str">
-        <f aca="false">IF(OR(B416="",AND(A416=A415 ,B416=B415)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A416,$B$5:$B$504,B416)+SUMIFS($E$5:$E$504,$A$5:$A$504,A416,$B$5:$B$504,B416))</f>
+        <f aca="false">IF(OR(B416="",AND(A416=A415 ,B416=B415)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A416,$B$5:$B$504,B416)+SUMIFS($E$5:$E$504,$A$5:$A$504,A416,$B$5:$B$504,B416)-SUMIFS($F$5:$F$504,$A$5:$A$504,A416,$B$5:$B$504,B416))</f>
         <v/>
       </c>
       <c r="H416" s="33" t="str">
@@ -23109,7 +23277,7 @@
       <c r="E417" s="25"/>
       <c r="F417" s="25"/>
       <c r="G417" s="33" t="str">
-        <f aca="false">IF(OR(B417="",AND(A417=A416 ,B417=B416)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A417,$B$5:$B$504,B417)+SUMIFS($E$5:$E$504,$A$5:$A$504,A417,$B$5:$B$504,B417))</f>
+        <f aca="false">IF(OR(B417="",AND(A417=A416 ,B417=B416)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A417,$B$5:$B$504,B417)+SUMIFS($E$5:$E$504,$A$5:$A$504,A417,$B$5:$B$504,B417)-SUMIFS($F$5:$F$504,$A$5:$A$504,A417,$B$5:$B$504,B417))</f>
         <v/>
       </c>
       <c r="H417" s="33" t="str">
@@ -23127,7 +23295,7 @@
       <c r="E418" s="25"/>
       <c r="F418" s="25"/>
       <c r="G418" s="33" t="str">
-        <f aca="false">IF(OR(B418="",AND(A418=A417 ,B418=B417)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A418,$B$5:$B$504,B418)+SUMIFS($E$5:$E$504,$A$5:$A$504,A418,$B$5:$B$504,B418))</f>
+        <f aca="false">IF(OR(B418="",AND(A418=A417 ,B418=B417)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A418,$B$5:$B$504,B418)+SUMIFS($E$5:$E$504,$A$5:$A$504,A418,$B$5:$B$504,B418)-SUMIFS($F$5:$F$504,$A$5:$A$504,A418,$B$5:$B$504,B418))</f>
         <v/>
       </c>
       <c r="H418" s="33" t="str">
@@ -23145,7 +23313,7 @@
       <c r="E419" s="25"/>
       <c r="F419" s="25"/>
       <c r="G419" s="33" t="str">
-        <f aca="false">IF(OR(B419="",AND(A419=A418 ,B419=B418)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A419,$B$5:$B$504,B419)+SUMIFS($E$5:$E$504,$A$5:$A$504,A419,$B$5:$B$504,B419))</f>
+        <f aca="false">IF(OR(B419="",AND(A419=A418 ,B419=B418)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A419,$B$5:$B$504,B419)+SUMIFS($E$5:$E$504,$A$5:$A$504,A419,$B$5:$B$504,B419)-SUMIFS($F$5:$F$504,$A$5:$A$504,A419,$B$5:$B$504,B419))</f>
         <v/>
       </c>
       <c r="H419" s="33" t="str">
@@ -23163,7 +23331,7 @@
       <c r="E420" s="25"/>
       <c r="F420" s="25"/>
       <c r="G420" s="33" t="str">
-        <f aca="false">IF(OR(B420="",AND(A420=A419 ,B420=B419)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A420,$B$5:$B$504,B420)+SUMIFS($E$5:$E$504,$A$5:$A$504,A420,$B$5:$B$504,B420))</f>
+        <f aca="false">IF(OR(B420="",AND(A420=A419 ,B420=B419)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A420,$B$5:$B$504,B420)+SUMIFS($E$5:$E$504,$A$5:$A$504,A420,$B$5:$B$504,B420)-SUMIFS($F$5:$F$504,$A$5:$A$504,A420,$B$5:$B$504,B420))</f>
         <v/>
       </c>
       <c r="H420" s="33" t="str">
@@ -23181,7 +23349,7 @@
       <c r="E421" s="25"/>
       <c r="F421" s="25"/>
       <c r="G421" s="33" t="str">
-        <f aca="false">IF(OR(B421="",AND(A421=A420 ,B421=B420)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A421,$B$5:$B$504,B421)+SUMIFS($E$5:$E$504,$A$5:$A$504,A421,$B$5:$B$504,B421))</f>
+        <f aca="false">IF(OR(B421="",AND(A421=A420 ,B421=B420)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A421,$B$5:$B$504,B421)+SUMIFS($E$5:$E$504,$A$5:$A$504,A421,$B$5:$B$504,B421)-SUMIFS($F$5:$F$504,$A$5:$A$504,A421,$B$5:$B$504,B421))</f>
         <v/>
       </c>
       <c r="H421" s="33" t="str">
@@ -23199,7 +23367,7 @@
       <c r="E422" s="25"/>
       <c r="F422" s="25"/>
       <c r="G422" s="33" t="str">
-        <f aca="false">IF(OR(B422="",AND(A422=A421 ,B422=B421)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A422,$B$5:$B$504,B422)+SUMIFS($E$5:$E$504,$A$5:$A$504,A422,$B$5:$B$504,B422))</f>
+        <f aca="false">IF(OR(B422="",AND(A422=A421 ,B422=B421)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A422,$B$5:$B$504,B422)+SUMIFS($E$5:$E$504,$A$5:$A$504,A422,$B$5:$B$504,B422)-SUMIFS($F$5:$F$504,$A$5:$A$504,A422,$B$5:$B$504,B422))</f>
         <v/>
       </c>
       <c r="H422" s="33" t="str">
@@ -23217,7 +23385,7 @@
       <c r="E423" s="25"/>
       <c r="F423" s="25"/>
       <c r="G423" s="33" t="str">
-        <f aca="false">IF(OR(B423="",AND(A423=A422 ,B423=B422)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A423,$B$5:$B$504,B423)+SUMIFS($E$5:$E$504,$A$5:$A$504,A423,$B$5:$B$504,B423))</f>
+        <f aca="false">IF(OR(B423="",AND(A423=A422 ,B423=B422)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A423,$B$5:$B$504,B423)+SUMIFS($E$5:$E$504,$A$5:$A$504,A423,$B$5:$B$504,B423)-SUMIFS($F$5:$F$504,$A$5:$A$504,A423,$B$5:$B$504,B423))</f>
         <v/>
       </c>
       <c r="H423" s="33" t="str">
@@ -23235,7 +23403,7 @@
       <c r="E424" s="25"/>
       <c r="F424" s="25"/>
       <c r="G424" s="33" t="str">
-        <f aca="false">IF(OR(B424="",AND(A424=A423 ,B424=B423)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A424,$B$5:$B$504,B424)+SUMIFS($E$5:$E$504,$A$5:$A$504,A424,$B$5:$B$504,B424))</f>
+        <f aca="false">IF(OR(B424="",AND(A424=A423 ,B424=B423)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A424,$B$5:$B$504,B424)+SUMIFS($E$5:$E$504,$A$5:$A$504,A424,$B$5:$B$504,B424)-SUMIFS($F$5:$F$504,$A$5:$A$504,A424,$B$5:$B$504,B424))</f>
         <v/>
       </c>
       <c r="H424" s="33" t="str">
@@ -23253,7 +23421,7 @@
       <c r="E425" s="25"/>
       <c r="F425" s="25"/>
       <c r="G425" s="33" t="str">
-        <f aca="false">IF(OR(B425="",AND(A425=A424 ,B425=B424)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A425,$B$5:$B$504,B425)+SUMIFS($E$5:$E$504,$A$5:$A$504,A425,$B$5:$B$504,B425))</f>
+        <f aca="false">IF(OR(B425="",AND(A425=A424 ,B425=B424)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A425,$B$5:$B$504,B425)+SUMIFS($E$5:$E$504,$A$5:$A$504,A425,$B$5:$B$504,B425)-SUMIFS($F$5:$F$504,$A$5:$A$504,A425,$B$5:$B$504,B425))</f>
         <v/>
       </c>
       <c r="H425" s="33" t="str">
@@ -23271,7 +23439,7 @@
       <c r="E426" s="25"/>
       <c r="F426" s="25"/>
       <c r="G426" s="33" t="str">
-        <f aca="false">IF(OR(B426="",AND(A426=A425 ,B426=B425)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A426,$B$5:$B$504,B426)+SUMIFS($E$5:$E$504,$A$5:$A$504,A426,$B$5:$B$504,B426))</f>
+        <f aca="false">IF(OR(B426="",AND(A426=A425 ,B426=B425)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A426,$B$5:$B$504,B426)+SUMIFS($E$5:$E$504,$A$5:$A$504,A426,$B$5:$B$504,B426)-SUMIFS($F$5:$F$504,$A$5:$A$504,A426,$B$5:$B$504,B426))</f>
         <v/>
       </c>
       <c r="H426" s="33" t="str">
@@ -23289,7 +23457,7 @@
       <c r="E427" s="25"/>
       <c r="F427" s="25"/>
       <c r="G427" s="33" t="str">
-        <f aca="false">IF(OR(B427="",AND(A427=A426 ,B427=B426)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A427,$B$5:$B$504,B427)+SUMIFS($E$5:$E$504,$A$5:$A$504,A427,$B$5:$B$504,B427))</f>
+        <f aca="false">IF(OR(B427="",AND(A427=A426 ,B427=B426)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A427,$B$5:$B$504,B427)+SUMIFS($E$5:$E$504,$A$5:$A$504,A427,$B$5:$B$504,B427)-SUMIFS($F$5:$F$504,$A$5:$A$504,A427,$B$5:$B$504,B427))</f>
         <v/>
       </c>
       <c r="H427" s="33" t="str">
@@ -23307,7 +23475,7 @@
       <c r="E428" s="25"/>
       <c r="F428" s="25"/>
       <c r="G428" s="33" t="str">
-        <f aca="false">IF(OR(B428="",AND(A428=A427 ,B428=B427)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A428,$B$5:$B$504,B428)+SUMIFS($E$5:$E$504,$A$5:$A$504,A428,$B$5:$B$504,B428))</f>
+        <f aca="false">IF(OR(B428="",AND(A428=A427 ,B428=B427)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A428,$B$5:$B$504,B428)+SUMIFS($E$5:$E$504,$A$5:$A$504,A428,$B$5:$B$504,B428)-SUMIFS($F$5:$F$504,$A$5:$A$504,A428,$B$5:$B$504,B428))</f>
         <v/>
       </c>
       <c r="H428" s="33" t="str">
@@ -23325,7 +23493,7 @@
       <c r="E429" s="25"/>
       <c r="F429" s="25"/>
       <c r="G429" s="33" t="str">
-        <f aca="false">IF(OR(B429="",AND(A429=A428 ,B429=B428)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A429,$B$5:$B$504,B429)+SUMIFS($E$5:$E$504,$A$5:$A$504,A429,$B$5:$B$504,B429))</f>
+        <f aca="false">IF(OR(B429="",AND(A429=A428 ,B429=B428)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A429,$B$5:$B$504,B429)+SUMIFS($E$5:$E$504,$A$5:$A$504,A429,$B$5:$B$504,B429)-SUMIFS($F$5:$F$504,$A$5:$A$504,A429,$B$5:$B$504,B429))</f>
         <v/>
       </c>
       <c r="H429" s="33" t="str">
@@ -23343,7 +23511,7 @@
       <c r="E430" s="25"/>
       <c r="F430" s="25"/>
       <c r="G430" s="33" t="str">
-        <f aca="false">IF(OR(B430="",AND(A430=A429 ,B430=B429)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A430,$B$5:$B$504,B430)+SUMIFS($E$5:$E$504,$A$5:$A$504,A430,$B$5:$B$504,B430))</f>
+        <f aca="false">IF(OR(B430="",AND(A430=A429 ,B430=B429)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A430,$B$5:$B$504,B430)+SUMIFS($E$5:$E$504,$A$5:$A$504,A430,$B$5:$B$504,B430)-SUMIFS($F$5:$F$504,$A$5:$A$504,A430,$B$5:$B$504,B430))</f>
         <v/>
       </c>
       <c r="H430" s="33" t="str">
@@ -23361,7 +23529,7 @@
       <c r="E431" s="25"/>
       <c r="F431" s="25"/>
       <c r="G431" s="33" t="str">
-        <f aca="false">IF(OR(B431="",AND(A431=A430 ,B431=B430)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A431,$B$5:$B$504,B431)+SUMIFS($E$5:$E$504,$A$5:$A$504,A431,$B$5:$B$504,B431))</f>
+        <f aca="false">IF(OR(B431="",AND(A431=A430 ,B431=B430)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A431,$B$5:$B$504,B431)+SUMIFS($E$5:$E$504,$A$5:$A$504,A431,$B$5:$B$504,B431)-SUMIFS($F$5:$F$504,$A$5:$A$504,A431,$B$5:$B$504,B431))</f>
         <v/>
       </c>
       <c r="H431" s="33" t="str">
@@ -23379,7 +23547,7 @@
       <c r="E432" s="25"/>
       <c r="F432" s="25"/>
       <c r="G432" s="33" t="str">
-        <f aca="false">IF(OR(B432="",AND(A432=A431 ,B432=B431)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A432,$B$5:$B$504,B432)+SUMIFS($E$5:$E$504,$A$5:$A$504,A432,$B$5:$B$504,B432))</f>
+        <f aca="false">IF(OR(B432="",AND(A432=A431 ,B432=B431)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A432,$B$5:$B$504,B432)+SUMIFS($E$5:$E$504,$A$5:$A$504,A432,$B$5:$B$504,B432)-SUMIFS($F$5:$F$504,$A$5:$A$504,A432,$B$5:$B$504,B432))</f>
         <v/>
       </c>
       <c r="H432" s="33" t="str">
@@ -23397,7 +23565,7 @@
       <c r="E433" s="25"/>
       <c r="F433" s="25"/>
       <c r="G433" s="33" t="str">
-        <f aca="false">IF(OR(B433="",AND(A433=A432 ,B433=B432)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A433,$B$5:$B$504,B433)+SUMIFS($E$5:$E$504,$A$5:$A$504,A433,$B$5:$B$504,B433))</f>
+        <f aca="false">IF(OR(B433="",AND(A433=A432 ,B433=B432)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A433,$B$5:$B$504,B433)+SUMIFS($E$5:$E$504,$A$5:$A$504,A433,$B$5:$B$504,B433)-SUMIFS($F$5:$F$504,$A$5:$A$504,A433,$B$5:$B$504,B433))</f>
         <v/>
       </c>
       <c r="H433" s="33" t="str">
@@ -23415,7 +23583,7 @@
       <c r="E434" s="25"/>
       <c r="F434" s="25"/>
       <c r="G434" s="33" t="str">
-        <f aca="false">IF(OR(B434="",AND(A434=A433 ,B434=B433)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A434,$B$5:$B$504,B434)+SUMIFS($E$5:$E$504,$A$5:$A$504,A434,$B$5:$B$504,B434))</f>
+        <f aca="false">IF(OR(B434="",AND(A434=A433 ,B434=B433)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A434,$B$5:$B$504,B434)+SUMIFS($E$5:$E$504,$A$5:$A$504,A434,$B$5:$B$504,B434)-SUMIFS($F$5:$F$504,$A$5:$A$504,A434,$B$5:$B$504,B434))</f>
         <v/>
       </c>
       <c r="H434" s="33" t="str">
@@ -23433,7 +23601,7 @@
       <c r="E435" s="25"/>
       <c r="F435" s="25"/>
       <c r="G435" s="33" t="str">
-        <f aca="false">IF(OR(B435="",AND(A435=A434 ,B435=B434)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A435,$B$5:$B$504,B435)+SUMIFS($E$5:$E$504,$A$5:$A$504,A435,$B$5:$B$504,B435))</f>
+        <f aca="false">IF(OR(B435="",AND(A435=A434 ,B435=B434)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A435,$B$5:$B$504,B435)+SUMIFS($E$5:$E$504,$A$5:$A$504,A435,$B$5:$B$504,B435)-SUMIFS($F$5:$F$504,$A$5:$A$504,A435,$B$5:$B$504,B435))</f>
         <v/>
       </c>
       <c r="H435" s="33" t="str">
@@ -23451,7 +23619,7 @@
       <c r="E436" s="25"/>
       <c r="F436" s="25"/>
       <c r="G436" s="33" t="str">
-        <f aca="false">IF(OR(B436="",AND(A436=A435 ,B436=B435)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A436,$B$5:$B$504,B436)+SUMIFS($E$5:$E$504,$A$5:$A$504,A436,$B$5:$B$504,B436))</f>
+        <f aca="false">IF(OR(B436="",AND(A436=A435 ,B436=B435)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A436,$B$5:$B$504,B436)+SUMIFS($E$5:$E$504,$A$5:$A$504,A436,$B$5:$B$504,B436)-SUMIFS($F$5:$F$504,$A$5:$A$504,A436,$B$5:$B$504,B436))</f>
         <v/>
       </c>
       <c r="H436" s="33" t="str">
@@ -23469,7 +23637,7 @@
       <c r="E437" s="25"/>
       <c r="F437" s="25"/>
       <c r="G437" s="33" t="str">
-        <f aca="false">IF(OR(B437="",AND(A437=A436 ,B437=B436)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A437,$B$5:$B$504,B437)+SUMIFS($E$5:$E$504,$A$5:$A$504,A437,$B$5:$B$504,B437))</f>
+        <f aca="false">IF(OR(B437="",AND(A437=A436 ,B437=B436)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A437,$B$5:$B$504,B437)+SUMIFS($E$5:$E$504,$A$5:$A$504,A437,$B$5:$B$504,B437)-SUMIFS($F$5:$F$504,$A$5:$A$504,A437,$B$5:$B$504,B437))</f>
         <v/>
       </c>
       <c r="H437" s="33" t="str">
@@ -23487,7 +23655,7 @@
       <c r="E438" s="25"/>
       <c r="F438" s="25"/>
       <c r="G438" s="33" t="str">
-        <f aca="false">IF(OR(B438="",AND(A438=A437 ,B438=B437)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A438,$B$5:$B$504,B438)+SUMIFS($E$5:$E$504,$A$5:$A$504,A438,$B$5:$B$504,B438))</f>
+        <f aca="false">IF(OR(B438="",AND(A438=A437 ,B438=B437)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A438,$B$5:$B$504,B438)+SUMIFS($E$5:$E$504,$A$5:$A$504,A438,$B$5:$B$504,B438)-SUMIFS($F$5:$F$504,$A$5:$A$504,A438,$B$5:$B$504,B438))</f>
         <v/>
       </c>
       <c r="H438" s="33" t="str">
@@ -23505,7 +23673,7 @@
       <c r="E439" s="25"/>
       <c r="F439" s="25"/>
       <c r="G439" s="33" t="str">
-        <f aca="false">IF(OR(B439="",AND(A439=A438 ,B439=B438)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A439,$B$5:$B$504,B439)+SUMIFS($E$5:$E$504,$A$5:$A$504,A439,$B$5:$B$504,B439))</f>
+        <f aca="false">IF(OR(B439="",AND(A439=A438 ,B439=B438)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A439,$B$5:$B$504,B439)+SUMIFS($E$5:$E$504,$A$5:$A$504,A439,$B$5:$B$504,B439)-SUMIFS($F$5:$F$504,$A$5:$A$504,A439,$B$5:$B$504,B439))</f>
         <v/>
       </c>
       <c r="H439" s="33" t="str">
@@ -23523,7 +23691,7 @@
       <c r="E440" s="25"/>
       <c r="F440" s="25"/>
       <c r="G440" s="33" t="str">
-        <f aca="false">IF(OR(B440="",AND(A440=A439 ,B440=B439)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A440,$B$5:$B$504,B440)+SUMIFS($E$5:$E$504,$A$5:$A$504,A440,$B$5:$B$504,B440))</f>
+        <f aca="false">IF(OR(B440="",AND(A440=A439 ,B440=B439)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A440,$B$5:$B$504,B440)+SUMIFS($E$5:$E$504,$A$5:$A$504,A440,$B$5:$B$504,B440)-SUMIFS($F$5:$F$504,$A$5:$A$504,A440,$B$5:$B$504,B440))</f>
         <v/>
       </c>
       <c r="H440" s="33" t="str">
@@ -23541,7 +23709,7 @@
       <c r="E441" s="25"/>
       <c r="F441" s="25"/>
       <c r="G441" s="33" t="str">
-        <f aca="false">IF(OR(B441="",AND(A441=A440 ,B441=B440)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A441,$B$5:$B$504,B441)+SUMIFS($E$5:$E$504,$A$5:$A$504,A441,$B$5:$B$504,B441))</f>
+        <f aca="false">IF(OR(B441="",AND(A441=A440 ,B441=B440)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A441,$B$5:$B$504,B441)+SUMIFS($E$5:$E$504,$A$5:$A$504,A441,$B$5:$B$504,B441)-SUMIFS($F$5:$F$504,$A$5:$A$504,A441,$B$5:$B$504,B441))</f>
         <v/>
       </c>
       <c r="H441" s="33" t="str">
@@ -23559,7 +23727,7 @@
       <c r="E442" s="25"/>
       <c r="F442" s="25"/>
       <c r="G442" s="33" t="str">
-        <f aca="false">IF(OR(B442="",AND(A442=A441 ,B442=B441)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A442,$B$5:$B$504,B442)+SUMIFS($E$5:$E$504,$A$5:$A$504,A442,$B$5:$B$504,B442))</f>
+        <f aca="false">IF(OR(B442="",AND(A442=A441 ,B442=B441)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A442,$B$5:$B$504,B442)+SUMIFS($E$5:$E$504,$A$5:$A$504,A442,$B$5:$B$504,B442)-SUMIFS($F$5:$F$504,$A$5:$A$504,A442,$B$5:$B$504,B442))</f>
         <v/>
       </c>
       <c r="H442" s="33" t="str">
@@ -23577,7 +23745,7 @@
       <c r="E443" s="25"/>
       <c r="F443" s="25"/>
       <c r="G443" s="33" t="str">
-        <f aca="false">IF(OR(B443="",AND(A443=A442 ,B443=B442)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A443,$B$5:$B$504,B443)+SUMIFS($E$5:$E$504,$A$5:$A$504,A443,$B$5:$B$504,B443))</f>
+        <f aca="false">IF(OR(B443="",AND(A443=A442 ,B443=B442)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A443,$B$5:$B$504,B443)+SUMIFS($E$5:$E$504,$A$5:$A$504,A443,$B$5:$B$504,B443)-SUMIFS($F$5:$F$504,$A$5:$A$504,A443,$B$5:$B$504,B443))</f>
         <v/>
       </c>
       <c r="H443" s="33" t="str">
@@ -23595,7 +23763,7 @@
       <c r="E444" s="25"/>
       <c r="F444" s="25"/>
       <c r="G444" s="33" t="str">
-        <f aca="false">IF(OR(B444="",AND(A444=A443 ,B444=B443)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A444,$B$5:$B$504,B444)+SUMIFS($E$5:$E$504,$A$5:$A$504,A444,$B$5:$B$504,B444))</f>
+        <f aca="false">IF(OR(B444="",AND(A444=A443 ,B444=B443)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A444,$B$5:$B$504,B444)+SUMIFS($E$5:$E$504,$A$5:$A$504,A444,$B$5:$B$504,B444)-SUMIFS($F$5:$F$504,$A$5:$A$504,A444,$B$5:$B$504,B444))</f>
         <v/>
       </c>
       <c r="H444" s="33" t="str">
@@ -23613,7 +23781,7 @@
       <c r="E445" s="25"/>
       <c r="F445" s="25"/>
       <c r="G445" s="33" t="str">
-        <f aca="false">IF(OR(B445="",AND(A445=A444 ,B445=B444)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A445,$B$5:$B$504,B445)+SUMIFS($E$5:$E$504,$A$5:$A$504,A445,$B$5:$B$504,B445))</f>
+        <f aca="false">IF(OR(B445="",AND(A445=A444 ,B445=B444)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A445,$B$5:$B$504,B445)+SUMIFS($E$5:$E$504,$A$5:$A$504,A445,$B$5:$B$504,B445)-SUMIFS($F$5:$F$504,$A$5:$A$504,A445,$B$5:$B$504,B445))</f>
         <v/>
       </c>
       <c r="H445" s="33" t="str">
@@ -23631,7 +23799,7 @@
       <c r="E446" s="25"/>
       <c r="F446" s="25"/>
       <c r="G446" s="33" t="str">
-        <f aca="false">IF(OR(B446="",AND(A446=A445 ,B446=B445)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A446,$B$5:$B$504,B446)+SUMIFS($E$5:$E$504,$A$5:$A$504,A446,$B$5:$B$504,B446))</f>
+        <f aca="false">IF(OR(B446="",AND(A446=A445 ,B446=B445)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A446,$B$5:$B$504,B446)+SUMIFS($E$5:$E$504,$A$5:$A$504,A446,$B$5:$B$504,B446)-SUMIFS($F$5:$F$504,$A$5:$A$504,A446,$B$5:$B$504,B446))</f>
         <v/>
       </c>
       <c r="H446" s="33" t="str">
@@ -23649,7 +23817,7 @@
       <c r="E447" s="25"/>
       <c r="F447" s="25"/>
       <c r="G447" s="33" t="str">
-        <f aca="false">IF(OR(B447="",AND(A447=A446 ,B447=B446)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A447,$B$5:$B$504,B447)+SUMIFS($E$5:$E$504,$A$5:$A$504,A447,$B$5:$B$504,B447))</f>
+        <f aca="false">IF(OR(B447="",AND(A447=A446 ,B447=B446)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A447,$B$5:$B$504,B447)+SUMIFS($E$5:$E$504,$A$5:$A$504,A447,$B$5:$B$504,B447)-SUMIFS($F$5:$F$504,$A$5:$A$504,A447,$B$5:$B$504,B447))</f>
         <v/>
       </c>
       <c r="H447" s="33" t="str">
@@ -23667,7 +23835,7 @@
       <c r="E448" s="25"/>
       <c r="F448" s="25"/>
       <c r="G448" s="33" t="str">
-        <f aca="false">IF(OR(B448="",AND(A448=A447 ,B448=B447)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A448,$B$5:$B$504,B448)+SUMIFS($E$5:$E$504,$A$5:$A$504,A448,$B$5:$B$504,B448))</f>
+        <f aca="false">IF(OR(B448="",AND(A448=A447 ,B448=B447)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A448,$B$5:$B$504,B448)+SUMIFS($E$5:$E$504,$A$5:$A$504,A448,$B$5:$B$504,B448)-SUMIFS($F$5:$F$504,$A$5:$A$504,A448,$B$5:$B$504,B448))</f>
         <v/>
       </c>
       <c r="H448" s="33" t="str">
@@ -23685,7 +23853,7 @@
       <c r="E449" s="25"/>
       <c r="F449" s="25"/>
       <c r="G449" s="33" t="str">
-        <f aca="false">IF(OR(B449="",AND(A449=A448 ,B449=B448)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A449,$B$5:$B$504,B449)+SUMIFS($E$5:$E$504,$A$5:$A$504,A449,$B$5:$B$504,B449))</f>
+        <f aca="false">IF(OR(B449="",AND(A449=A448 ,B449=B448)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A449,$B$5:$B$504,B449)+SUMIFS($E$5:$E$504,$A$5:$A$504,A449,$B$5:$B$504,B449)-SUMIFS($F$5:$F$504,$A$5:$A$504,A449,$B$5:$B$504,B449))</f>
         <v/>
       </c>
       <c r="H449" s="33" t="str">
@@ -23703,7 +23871,7 @@
       <c r="E450" s="25"/>
       <c r="F450" s="25"/>
       <c r="G450" s="33" t="str">
-        <f aca="false">IF(OR(B450="",AND(A450=A449 ,B450=B449)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A450,$B$5:$B$504,B450)+SUMIFS($E$5:$E$504,$A$5:$A$504,A450,$B$5:$B$504,B450))</f>
+        <f aca="false">IF(OR(B450="",AND(A450=A449 ,B450=B449)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A450,$B$5:$B$504,B450)+SUMIFS($E$5:$E$504,$A$5:$A$504,A450,$B$5:$B$504,B450)-SUMIFS($F$5:$F$504,$A$5:$A$504,A450,$B$5:$B$504,B450))</f>
         <v/>
       </c>
       <c r="H450" s="33" t="str">
@@ -23721,7 +23889,7 @@
       <c r="E451" s="25"/>
       <c r="F451" s="25"/>
       <c r="G451" s="33" t="str">
-        <f aca="false">IF(OR(B451="",AND(A451=A450 ,B451=B450)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A451,$B$5:$B$504,B451)+SUMIFS($E$5:$E$504,$A$5:$A$504,A451,$B$5:$B$504,B451))</f>
+        <f aca="false">IF(OR(B451="",AND(A451=A450 ,B451=B450)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A451,$B$5:$B$504,B451)+SUMIFS($E$5:$E$504,$A$5:$A$504,A451,$B$5:$B$504,B451)-SUMIFS($F$5:$F$504,$A$5:$A$504,A451,$B$5:$B$504,B451))</f>
         <v/>
       </c>
       <c r="H451" s="33" t="str">
@@ -23739,7 +23907,7 @@
       <c r="E452" s="25"/>
       <c r="F452" s="25"/>
       <c r="G452" s="33" t="str">
-        <f aca="false">IF(OR(B452="",AND(A452=A451 ,B452=B451)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A452,$B$5:$B$504,B452)+SUMIFS($E$5:$E$504,$A$5:$A$504,A452,$B$5:$B$504,B452))</f>
+        <f aca="false">IF(OR(B452="",AND(A452=A451 ,B452=B451)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A452,$B$5:$B$504,B452)+SUMIFS($E$5:$E$504,$A$5:$A$504,A452,$B$5:$B$504,B452)-SUMIFS($F$5:$F$504,$A$5:$A$504,A452,$B$5:$B$504,B452))</f>
         <v/>
       </c>
       <c r="H452" s="33" t="str">
@@ -23757,7 +23925,7 @@
       <c r="E453" s="25"/>
       <c r="F453" s="25"/>
       <c r="G453" s="33" t="str">
-        <f aca="false">IF(OR(B453="",AND(A453=A452 ,B453=B452)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A453,$B$5:$B$504,B453)+SUMIFS($E$5:$E$504,$A$5:$A$504,A453,$B$5:$B$504,B453))</f>
+        <f aca="false">IF(OR(B453="",AND(A453=A452 ,B453=B452)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A453,$B$5:$B$504,B453)+SUMIFS($E$5:$E$504,$A$5:$A$504,A453,$B$5:$B$504,B453)-SUMIFS($F$5:$F$504,$A$5:$A$504,A453,$B$5:$B$504,B453))</f>
         <v/>
       </c>
       <c r="H453" s="33" t="str">
@@ -23775,7 +23943,7 @@
       <c r="E454" s="25"/>
       <c r="F454" s="25"/>
       <c r="G454" s="33" t="str">
-        <f aca="false">IF(OR(B454="",AND(A454=A453 ,B454=B453)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A454,$B$5:$B$504,B454)+SUMIFS($E$5:$E$504,$A$5:$A$504,A454,$B$5:$B$504,B454))</f>
+        <f aca="false">IF(OR(B454="",AND(A454=A453 ,B454=B453)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A454,$B$5:$B$504,B454)+SUMIFS($E$5:$E$504,$A$5:$A$504,A454,$B$5:$B$504,B454)-SUMIFS($F$5:$F$504,$A$5:$A$504,A454,$B$5:$B$504,B454))</f>
         <v/>
       </c>
       <c r="H454" s="33" t="str">
@@ -23793,7 +23961,7 @@
       <c r="E455" s="25"/>
       <c r="F455" s="25"/>
       <c r="G455" s="33" t="str">
-        <f aca="false">IF(OR(B455="",AND(A455=A454 ,B455=B454)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A455,$B$5:$B$504,B455)+SUMIFS($E$5:$E$504,$A$5:$A$504,A455,$B$5:$B$504,B455))</f>
+        <f aca="false">IF(OR(B455="",AND(A455=A454 ,B455=B454)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A455,$B$5:$B$504,B455)+SUMIFS($E$5:$E$504,$A$5:$A$504,A455,$B$5:$B$504,B455)-SUMIFS($F$5:$F$504,$A$5:$A$504,A455,$B$5:$B$504,B455))</f>
         <v/>
       </c>
       <c r="H455" s="33" t="str">
@@ -23811,7 +23979,7 @@
       <c r="E456" s="25"/>
       <c r="F456" s="25"/>
       <c r="G456" s="33" t="str">
-        <f aca="false">IF(OR(B456="",AND(A456=A455 ,B456=B455)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A456,$B$5:$B$504,B456)+SUMIFS($E$5:$E$504,$A$5:$A$504,A456,$B$5:$B$504,B456))</f>
+        <f aca="false">IF(OR(B456="",AND(A456=A455 ,B456=B455)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A456,$B$5:$B$504,B456)+SUMIFS($E$5:$E$504,$A$5:$A$504,A456,$B$5:$B$504,B456)-SUMIFS($F$5:$F$504,$A$5:$A$504,A456,$B$5:$B$504,B456))</f>
         <v/>
       </c>
       <c r="H456" s="33" t="str">
@@ -23829,7 +23997,7 @@
       <c r="E457" s="25"/>
       <c r="F457" s="25"/>
       <c r="G457" s="33" t="str">
-        <f aca="false">IF(OR(B457="",AND(A457=A456 ,B457=B456)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A457,$B$5:$B$504,B457)+SUMIFS($E$5:$E$504,$A$5:$A$504,A457,$B$5:$B$504,B457))</f>
+        <f aca="false">IF(OR(B457="",AND(A457=A456 ,B457=B456)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A457,$B$5:$B$504,B457)+SUMIFS($E$5:$E$504,$A$5:$A$504,A457,$B$5:$B$504,B457)-SUMIFS($F$5:$F$504,$A$5:$A$504,A457,$B$5:$B$504,B457))</f>
         <v/>
       </c>
       <c r="H457" s="33" t="str">
@@ -23847,7 +24015,7 @@
       <c r="E458" s="25"/>
       <c r="F458" s="25"/>
       <c r="G458" s="33" t="str">
-        <f aca="false">IF(OR(B458="",AND(A458=A457 ,B458=B457)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A458,$B$5:$B$504,B458)+SUMIFS($E$5:$E$504,$A$5:$A$504,A458,$B$5:$B$504,B458))</f>
+        <f aca="false">IF(OR(B458="",AND(A458=A457 ,B458=B457)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A458,$B$5:$B$504,B458)+SUMIFS($E$5:$E$504,$A$5:$A$504,A458,$B$5:$B$504,B458)-SUMIFS($F$5:$F$504,$A$5:$A$504,A458,$B$5:$B$504,B458))</f>
         <v/>
       </c>
       <c r="H458" s="33" t="str">
@@ -23865,7 +24033,7 @@
       <c r="E459" s="25"/>
       <c r="F459" s="25"/>
       <c r="G459" s="33" t="str">
-        <f aca="false">IF(OR(B459="",AND(A459=A458 ,B459=B458)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A459,$B$5:$B$504,B459)+SUMIFS($E$5:$E$504,$A$5:$A$504,A459,$B$5:$B$504,B459))</f>
+        <f aca="false">IF(OR(B459="",AND(A459=A458 ,B459=B458)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A459,$B$5:$B$504,B459)+SUMIFS($E$5:$E$504,$A$5:$A$504,A459,$B$5:$B$504,B459)-SUMIFS($F$5:$F$504,$A$5:$A$504,A459,$B$5:$B$504,B459))</f>
         <v/>
       </c>
       <c r="H459" s="33" t="str">
@@ -23883,7 +24051,7 @@
       <c r="E460" s="25"/>
       <c r="F460" s="25"/>
       <c r="G460" s="33" t="str">
-        <f aca="false">IF(OR(B460="",AND(A460=A459 ,B460=B459)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A460,$B$5:$B$504,B460)+SUMIFS($E$5:$E$504,$A$5:$A$504,A460,$B$5:$B$504,B460))</f>
+        <f aca="false">IF(OR(B460="",AND(A460=A459 ,B460=B459)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A460,$B$5:$B$504,B460)+SUMIFS($E$5:$E$504,$A$5:$A$504,A460,$B$5:$B$504,B460)-SUMIFS($F$5:$F$504,$A$5:$A$504,A460,$B$5:$B$504,B460))</f>
         <v/>
       </c>
       <c r="H460" s="33" t="str">
@@ -23901,7 +24069,7 @@
       <c r="E461" s="25"/>
       <c r="F461" s="25"/>
       <c r="G461" s="33" t="str">
-        <f aca="false">IF(OR(B461="",AND(A461=A460 ,B461=B460)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A461,$B$5:$B$504,B461)+SUMIFS($E$5:$E$504,$A$5:$A$504,A461,$B$5:$B$504,B461))</f>
+        <f aca="false">IF(OR(B461="",AND(A461=A460 ,B461=B460)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A461,$B$5:$B$504,B461)+SUMIFS($E$5:$E$504,$A$5:$A$504,A461,$B$5:$B$504,B461)-SUMIFS($F$5:$F$504,$A$5:$A$504,A461,$B$5:$B$504,B461))</f>
         <v/>
       </c>
       <c r="H461" s="33" t="str">
@@ -23919,7 +24087,7 @@
       <c r="E462" s="25"/>
       <c r="F462" s="25"/>
       <c r="G462" s="33" t="str">
-        <f aca="false">IF(OR(B462="",AND(A462=A461 ,B462=B461)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A462,$B$5:$B$504,B462)+SUMIFS($E$5:$E$504,$A$5:$A$504,A462,$B$5:$B$504,B462))</f>
+        <f aca="false">IF(OR(B462="",AND(A462=A461 ,B462=B461)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A462,$B$5:$B$504,B462)+SUMIFS($E$5:$E$504,$A$5:$A$504,A462,$B$5:$B$504,B462)-SUMIFS($F$5:$F$504,$A$5:$A$504,A462,$B$5:$B$504,B462))</f>
         <v/>
       </c>
       <c r="H462" s="33" t="str">
@@ -23937,7 +24105,7 @@
       <c r="E463" s="25"/>
       <c r="F463" s="25"/>
       <c r="G463" s="33" t="str">
-        <f aca="false">IF(OR(B463="",AND(A463=A462 ,B463=B462)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A463,$B$5:$B$504,B463)+SUMIFS($E$5:$E$504,$A$5:$A$504,A463,$B$5:$B$504,B463))</f>
+        <f aca="false">IF(OR(B463="",AND(A463=A462 ,B463=B462)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A463,$B$5:$B$504,B463)+SUMIFS($E$5:$E$504,$A$5:$A$504,A463,$B$5:$B$504,B463)-SUMIFS($F$5:$F$504,$A$5:$A$504,A463,$B$5:$B$504,B463))</f>
         <v/>
       </c>
       <c r="H463" s="33" t="str">
@@ -23955,7 +24123,7 @@
       <c r="E464" s="25"/>
       <c r="F464" s="25"/>
       <c r="G464" s="33" t="str">
-        <f aca="false">IF(OR(B464="",AND(A464=A463 ,B464=B463)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A464,$B$5:$B$504,B464)+SUMIFS($E$5:$E$504,$A$5:$A$504,A464,$B$5:$B$504,B464))</f>
+        <f aca="false">IF(OR(B464="",AND(A464=A463 ,B464=B463)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A464,$B$5:$B$504,B464)+SUMIFS($E$5:$E$504,$A$5:$A$504,A464,$B$5:$B$504,B464)-SUMIFS($F$5:$F$504,$A$5:$A$504,A464,$B$5:$B$504,B464))</f>
         <v/>
       </c>
       <c r="H464" s="33" t="str">
@@ -23973,7 +24141,7 @@
       <c r="E465" s="25"/>
       <c r="F465" s="25"/>
       <c r="G465" s="33" t="str">
-        <f aca="false">IF(OR(B465="",AND(A465=A464 ,B465=B464)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A465,$B$5:$B$504,B465)+SUMIFS($E$5:$E$504,$A$5:$A$504,A465,$B$5:$B$504,B465))</f>
+        <f aca="false">IF(OR(B465="",AND(A465=A464 ,B465=B464)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A465,$B$5:$B$504,B465)+SUMIFS($E$5:$E$504,$A$5:$A$504,A465,$B$5:$B$504,B465)-SUMIFS($F$5:$F$504,$A$5:$A$504,A465,$B$5:$B$504,B465))</f>
         <v/>
       </c>
       <c r="H465" s="33" t="str">
@@ -23991,7 +24159,7 @@
       <c r="E466" s="25"/>
       <c r="F466" s="25"/>
       <c r="G466" s="33" t="str">
-        <f aca="false">IF(OR(B466="",AND(A466=A465 ,B466=B465)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A466,$B$5:$B$504,B466)+SUMIFS($E$5:$E$504,$A$5:$A$504,A466,$B$5:$B$504,B466))</f>
+        <f aca="false">IF(OR(B466="",AND(A466=A465 ,B466=B465)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A466,$B$5:$B$504,B466)+SUMIFS($E$5:$E$504,$A$5:$A$504,A466,$B$5:$B$504,B466)-SUMIFS($F$5:$F$504,$A$5:$A$504,A466,$B$5:$B$504,B466))</f>
         <v/>
       </c>
       <c r="H466" s="33" t="str">
@@ -24009,7 +24177,7 @@
       <c r="E467" s="25"/>
       <c r="F467" s="25"/>
       <c r="G467" s="33" t="str">
-        <f aca="false">IF(OR(B467="",AND(A467=A466 ,B467=B466)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A467,$B$5:$B$504,B467)+SUMIFS($E$5:$E$504,$A$5:$A$504,A467,$B$5:$B$504,B467))</f>
+        <f aca="false">IF(OR(B467="",AND(A467=A466 ,B467=B466)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A467,$B$5:$B$504,B467)+SUMIFS($E$5:$E$504,$A$5:$A$504,A467,$B$5:$B$504,B467)-SUMIFS($F$5:$F$504,$A$5:$A$504,A467,$B$5:$B$504,B467))</f>
         <v/>
       </c>
       <c r="H467" s="33" t="str">
@@ -24027,7 +24195,7 @@
       <c r="E468" s="25"/>
       <c r="F468" s="25"/>
       <c r="G468" s="33" t="str">
-        <f aca="false">IF(OR(B468="",AND(A468=A467 ,B468=B467)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A468,$B$5:$B$504,B468)+SUMIFS($E$5:$E$504,$A$5:$A$504,A468,$B$5:$B$504,B468))</f>
+        <f aca="false">IF(OR(B468="",AND(A468=A467 ,B468=B467)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A468,$B$5:$B$504,B468)+SUMIFS($E$5:$E$504,$A$5:$A$504,A468,$B$5:$B$504,B468)-SUMIFS($F$5:$F$504,$A$5:$A$504,A468,$B$5:$B$504,B468))</f>
         <v/>
       </c>
       <c r="H468" s="33" t="str">
@@ -24045,7 +24213,7 @@
       <c r="E469" s="25"/>
       <c r="F469" s="25"/>
       <c r="G469" s="33" t="str">
-        <f aca="false">IF(OR(B469="",AND(A469=A468 ,B469=B468)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A469,$B$5:$B$504,B469)+SUMIFS($E$5:$E$504,$A$5:$A$504,A469,$B$5:$B$504,B469))</f>
+        <f aca="false">IF(OR(B469="",AND(A469=A468 ,B469=B468)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A469,$B$5:$B$504,B469)+SUMIFS($E$5:$E$504,$A$5:$A$504,A469,$B$5:$B$504,B469)-SUMIFS($F$5:$F$504,$A$5:$A$504,A469,$B$5:$B$504,B469))</f>
         <v/>
       </c>
       <c r="H469" s="33" t="str">
@@ -24063,7 +24231,7 @@
       <c r="E470" s="25"/>
       <c r="F470" s="25"/>
       <c r="G470" s="33" t="str">
-        <f aca="false">IF(OR(B470="",AND(A470=A469 ,B470=B469)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A470,$B$5:$B$504,B470)+SUMIFS($E$5:$E$504,$A$5:$A$504,A470,$B$5:$B$504,B470))</f>
+        <f aca="false">IF(OR(B470="",AND(A470=A469 ,B470=B469)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A470,$B$5:$B$504,B470)+SUMIFS($E$5:$E$504,$A$5:$A$504,A470,$B$5:$B$504,B470)-SUMIFS($F$5:$F$504,$A$5:$A$504,A470,$B$5:$B$504,B470))</f>
         <v/>
       </c>
       <c r="H470" s="33" t="str">
@@ -24081,7 +24249,7 @@
       <c r="E471" s="25"/>
       <c r="F471" s="25"/>
       <c r="G471" s="33" t="str">
-        <f aca="false">IF(OR(B471="",AND(A471=A470 ,B471=B470)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A471,$B$5:$B$504,B471)+SUMIFS($E$5:$E$504,$A$5:$A$504,A471,$B$5:$B$504,B471))</f>
+        <f aca="false">IF(OR(B471="",AND(A471=A470 ,B471=B470)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A471,$B$5:$B$504,B471)+SUMIFS($E$5:$E$504,$A$5:$A$504,A471,$B$5:$B$504,B471)-SUMIFS($F$5:$F$504,$A$5:$A$504,A471,$B$5:$B$504,B471))</f>
         <v/>
       </c>
       <c r="H471" s="33" t="str">
@@ -24099,7 +24267,7 @@
       <c r="E472" s="25"/>
       <c r="F472" s="25"/>
       <c r="G472" s="33" t="str">
-        <f aca="false">IF(OR(B472="",AND(A472=A471 ,B472=B471)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A472,$B$5:$B$504,B472)+SUMIFS($E$5:$E$504,$A$5:$A$504,A472,$B$5:$B$504,B472))</f>
+        <f aca="false">IF(OR(B472="",AND(A472=A471 ,B472=B471)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A472,$B$5:$B$504,B472)+SUMIFS($E$5:$E$504,$A$5:$A$504,A472,$B$5:$B$504,B472)-SUMIFS($F$5:$F$504,$A$5:$A$504,A472,$B$5:$B$504,B472))</f>
         <v/>
       </c>
       <c r="H472" s="33" t="str">
@@ -24117,7 +24285,7 @@
       <c r="E473" s="25"/>
       <c r="F473" s="25"/>
       <c r="G473" s="33" t="str">
-        <f aca="false">IF(OR(B473="",AND(A473=A472 ,B473=B472)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A473,$B$5:$B$504,B473)+SUMIFS($E$5:$E$504,$A$5:$A$504,A473,$B$5:$B$504,B473))</f>
+        <f aca="false">IF(OR(B473="",AND(A473=A472 ,B473=B472)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A473,$B$5:$B$504,B473)+SUMIFS($E$5:$E$504,$A$5:$A$504,A473,$B$5:$B$504,B473)-SUMIFS($F$5:$F$504,$A$5:$A$504,A473,$B$5:$B$504,B473))</f>
         <v/>
       </c>
       <c r="H473" s="33" t="str">
@@ -24135,7 +24303,7 @@
       <c r="E474" s="25"/>
       <c r="F474" s="25"/>
       <c r="G474" s="33" t="str">
-        <f aca="false">IF(OR(B474="",AND(A474=A473 ,B474=B473)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A474,$B$5:$B$504,B474)+SUMIFS($E$5:$E$504,$A$5:$A$504,A474,$B$5:$B$504,B474))</f>
+        <f aca="false">IF(OR(B474="",AND(A474=A473 ,B474=B473)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A474,$B$5:$B$504,B474)+SUMIFS($E$5:$E$504,$A$5:$A$504,A474,$B$5:$B$504,B474)-SUMIFS($F$5:$F$504,$A$5:$A$504,A474,$B$5:$B$504,B474))</f>
         <v/>
       </c>
       <c r="H474" s="33" t="str">
@@ -24153,7 +24321,7 @@
       <c r="E475" s="25"/>
       <c r="F475" s="25"/>
       <c r="G475" s="33" t="str">
-        <f aca="false">IF(OR(B475="",AND(A475=A474 ,B475=B474)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A475,$B$5:$B$504,B475)+SUMIFS($E$5:$E$504,$A$5:$A$504,A475,$B$5:$B$504,B475))</f>
+        <f aca="false">IF(OR(B475="",AND(A475=A474 ,B475=B474)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A475,$B$5:$B$504,B475)+SUMIFS($E$5:$E$504,$A$5:$A$504,A475,$B$5:$B$504,B475)-SUMIFS($F$5:$F$504,$A$5:$A$504,A475,$B$5:$B$504,B475))</f>
         <v/>
       </c>
       <c r="H475" s="33" t="str">
@@ -24171,7 +24339,7 @@
       <c r="E476" s="25"/>
       <c r="F476" s="25"/>
       <c r="G476" s="33" t="str">
-        <f aca="false">IF(OR(B476="",AND(A476=A475 ,B476=B475)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A476,$B$5:$B$504,B476)+SUMIFS($E$5:$E$504,$A$5:$A$504,A476,$B$5:$B$504,B476))</f>
+        <f aca="false">IF(OR(B476="",AND(A476=A475 ,B476=B475)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A476,$B$5:$B$504,B476)+SUMIFS($E$5:$E$504,$A$5:$A$504,A476,$B$5:$B$504,B476)-SUMIFS($F$5:$F$504,$A$5:$A$504,A476,$B$5:$B$504,B476))</f>
         <v/>
       </c>
       <c r="H476" s="33" t="str">
@@ -24189,7 +24357,7 @@
       <c r="E477" s="25"/>
       <c r="F477" s="25"/>
       <c r="G477" s="33" t="str">
-        <f aca="false">IF(OR(B477="",AND(A477=A476 ,B477=B476)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A477,$B$5:$B$504,B477)+SUMIFS($E$5:$E$504,$A$5:$A$504,A477,$B$5:$B$504,B477))</f>
+        <f aca="false">IF(OR(B477="",AND(A477=A476 ,B477=B476)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A477,$B$5:$B$504,B477)+SUMIFS($E$5:$E$504,$A$5:$A$504,A477,$B$5:$B$504,B477)-SUMIFS($F$5:$F$504,$A$5:$A$504,A477,$B$5:$B$504,B477))</f>
         <v/>
       </c>
       <c r="H477" s="33" t="str">
@@ -24207,7 +24375,7 @@
       <c r="E478" s="25"/>
       <c r="F478" s="25"/>
       <c r="G478" s="33" t="str">
-        <f aca="false">IF(OR(B478="",AND(A478=A477 ,B478=B477)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A478,$B$5:$B$504,B478)+SUMIFS($E$5:$E$504,$A$5:$A$504,A478,$B$5:$B$504,B478))</f>
+        <f aca="false">IF(OR(B478="",AND(A478=A477 ,B478=B477)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A478,$B$5:$B$504,B478)+SUMIFS($E$5:$E$504,$A$5:$A$504,A478,$B$5:$B$504,B478)-SUMIFS($F$5:$F$504,$A$5:$A$504,A478,$B$5:$B$504,B478))</f>
         <v/>
       </c>
       <c r="H478" s="33" t="str">
@@ -24225,7 +24393,7 @@
       <c r="E479" s="25"/>
       <c r="F479" s="25"/>
       <c r="G479" s="33" t="str">
-        <f aca="false">IF(OR(B479="",AND(A479=A478 ,B479=B478)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A479,$B$5:$B$504,B479)+SUMIFS($E$5:$E$504,$A$5:$A$504,A479,$B$5:$B$504,B479))</f>
+        <f aca="false">IF(OR(B479="",AND(A479=A478 ,B479=B478)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A479,$B$5:$B$504,B479)+SUMIFS($E$5:$E$504,$A$5:$A$504,A479,$B$5:$B$504,B479)-SUMIFS($F$5:$F$504,$A$5:$A$504,A479,$B$5:$B$504,B479))</f>
         <v/>
       </c>
       <c r="H479" s="33" t="str">
@@ -24243,7 +24411,7 @@
       <c r="E480" s="25"/>
       <c r="F480" s="25"/>
       <c r="G480" s="33" t="str">
-        <f aca="false">IF(OR(B480="",AND(A480=A479 ,B480=B479)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A480,$B$5:$B$504,B480)+SUMIFS($E$5:$E$504,$A$5:$A$504,A480,$B$5:$B$504,B480))</f>
+        <f aca="false">IF(OR(B480="",AND(A480=A479 ,B480=B479)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A480,$B$5:$B$504,B480)+SUMIFS($E$5:$E$504,$A$5:$A$504,A480,$B$5:$B$504,B480)-SUMIFS($F$5:$F$504,$A$5:$A$504,A480,$B$5:$B$504,B480))</f>
         <v/>
       </c>
       <c r="H480" s="33" t="str">
@@ -24261,7 +24429,7 @@
       <c r="E481" s="25"/>
       <c r="F481" s="25"/>
       <c r="G481" s="33" t="str">
-        <f aca="false">IF(OR(B481="",AND(A481=A480 ,B481=B480)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A481,$B$5:$B$504,B481)+SUMIFS($E$5:$E$504,$A$5:$A$504,A481,$B$5:$B$504,B481))</f>
+        <f aca="false">IF(OR(B481="",AND(A481=A480 ,B481=B480)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A481,$B$5:$B$504,B481)+SUMIFS($E$5:$E$504,$A$5:$A$504,A481,$B$5:$B$504,B481)-SUMIFS($F$5:$F$504,$A$5:$A$504,A481,$B$5:$B$504,B481))</f>
         <v/>
       </c>
       <c r="H481" s="33" t="str">
@@ -24279,7 +24447,7 @@
       <c r="E482" s="25"/>
       <c r="F482" s="25"/>
       <c r="G482" s="33" t="str">
-        <f aca="false">IF(OR(B482="",AND(A482=A481 ,B482=B481)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A482,$B$5:$B$504,B482)+SUMIFS($E$5:$E$504,$A$5:$A$504,A482,$B$5:$B$504,B482))</f>
+        <f aca="false">IF(OR(B482="",AND(A482=A481 ,B482=B481)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A482,$B$5:$B$504,B482)+SUMIFS($E$5:$E$504,$A$5:$A$504,A482,$B$5:$B$504,B482)-SUMIFS($F$5:$F$504,$A$5:$A$504,A482,$B$5:$B$504,B482))</f>
         <v/>
       </c>
       <c r="H482" s="33" t="str">
@@ -24297,7 +24465,7 @@
       <c r="E483" s="25"/>
       <c r="F483" s="25"/>
       <c r="G483" s="33" t="str">
-        <f aca="false">IF(OR(B483="",AND(A483=A482 ,B483=B482)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A483,$B$5:$B$504,B483)+SUMIFS($E$5:$E$504,$A$5:$A$504,A483,$B$5:$B$504,B483))</f>
+        <f aca="false">IF(OR(B483="",AND(A483=A482 ,B483=B482)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A483,$B$5:$B$504,B483)+SUMIFS($E$5:$E$504,$A$5:$A$504,A483,$B$5:$B$504,B483)-SUMIFS($F$5:$F$504,$A$5:$A$504,A483,$B$5:$B$504,B483))</f>
         <v/>
       </c>
       <c r="H483" s="33" t="str">
@@ -24315,7 +24483,7 @@
       <c r="E484" s="25"/>
       <c r="F484" s="25"/>
       <c r="G484" s="33" t="str">
-        <f aca="false">IF(OR(B484="",AND(A484=A483 ,B484=B483)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A484,$B$5:$B$504,B484)+SUMIFS($E$5:$E$504,$A$5:$A$504,A484,$B$5:$B$504,B484))</f>
+        <f aca="false">IF(OR(B484="",AND(A484=A483 ,B484=B483)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A484,$B$5:$B$504,B484)+SUMIFS($E$5:$E$504,$A$5:$A$504,A484,$B$5:$B$504,B484)-SUMIFS($F$5:$F$504,$A$5:$A$504,A484,$B$5:$B$504,B484))</f>
         <v/>
       </c>
       <c r="H484" s="33" t="str">
@@ -24333,7 +24501,7 @@
       <c r="E485" s="25"/>
       <c r="F485" s="25"/>
       <c r="G485" s="33" t="str">
-        <f aca="false">IF(OR(B485="",AND(A485=A484 ,B485=B484)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A485,$B$5:$B$504,B485)+SUMIFS($E$5:$E$504,$A$5:$A$504,A485,$B$5:$B$504,B485))</f>
+        <f aca="false">IF(OR(B485="",AND(A485=A484 ,B485=B484)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A485,$B$5:$B$504,B485)+SUMIFS($E$5:$E$504,$A$5:$A$504,A485,$B$5:$B$504,B485)-SUMIFS($F$5:$F$504,$A$5:$A$504,A485,$B$5:$B$504,B485))</f>
         <v/>
       </c>
       <c r="H485" s="33" t="str">
@@ -24351,7 +24519,7 @@
       <c r="E486" s="25"/>
       <c r="F486" s="25"/>
       <c r="G486" s="33" t="str">
-        <f aca="false">IF(OR(B486="",AND(A486=A485 ,B486=B485)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A486,$B$5:$B$504,B486)+SUMIFS($E$5:$E$504,$A$5:$A$504,A486,$B$5:$B$504,B486))</f>
+        <f aca="false">IF(OR(B486="",AND(A486=A485 ,B486=B485)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A486,$B$5:$B$504,B486)+SUMIFS($E$5:$E$504,$A$5:$A$504,A486,$B$5:$B$504,B486)-SUMIFS($F$5:$F$504,$A$5:$A$504,A486,$B$5:$B$504,B486))</f>
         <v/>
       </c>
       <c r="H486" s="33" t="str">
@@ -24369,7 +24537,7 @@
       <c r="E487" s="25"/>
       <c r="F487" s="25"/>
       <c r="G487" s="33" t="str">
-        <f aca="false">IF(OR(B487="",AND(A487=A486 ,B487=B486)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A487,$B$5:$B$504,B487)+SUMIFS($E$5:$E$504,$A$5:$A$504,A487,$B$5:$B$504,B487))</f>
+        <f aca="false">IF(OR(B487="",AND(A487=A486 ,B487=B486)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A487,$B$5:$B$504,B487)+SUMIFS($E$5:$E$504,$A$5:$A$504,A487,$B$5:$B$504,B487)-SUMIFS($F$5:$F$504,$A$5:$A$504,A487,$B$5:$B$504,B487))</f>
         <v/>
       </c>
       <c r="H487" s="33" t="str">
@@ -24387,7 +24555,7 @@
       <c r="E488" s="25"/>
       <c r="F488" s="25"/>
       <c r="G488" s="33" t="str">
-        <f aca="false">IF(OR(B488="",AND(A488=A487 ,B488=B487)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A488,$B$5:$B$504,B488)+SUMIFS($E$5:$E$504,$A$5:$A$504,A488,$B$5:$B$504,B488))</f>
+        <f aca="false">IF(OR(B488="",AND(A488=A487 ,B488=B487)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A488,$B$5:$B$504,B488)+SUMIFS($E$5:$E$504,$A$5:$A$504,A488,$B$5:$B$504,B488)-SUMIFS($F$5:$F$504,$A$5:$A$504,A488,$B$5:$B$504,B488))</f>
         <v/>
       </c>
       <c r="H488" s="33" t="str">
@@ -24405,7 +24573,7 @@
       <c r="E489" s="25"/>
       <c r="F489" s="25"/>
       <c r="G489" s="33" t="str">
-        <f aca="false">IF(OR(B489="",AND(A489=A488 ,B489=B488)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A489,$B$5:$B$504,B489)+SUMIFS($E$5:$E$504,$A$5:$A$504,A489,$B$5:$B$504,B489))</f>
+        <f aca="false">IF(OR(B489="",AND(A489=A488 ,B489=B488)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A489,$B$5:$B$504,B489)+SUMIFS($E$5:$E$504,$A$5:$A$504,A489,$B$5:$B$504,B489)-SUMIFS($F$5:$F$504,$A$5:$A$504,A489,$B$5:$B$504,B489))</f>
         <v/>
       </c>
       <c r="H489" s="33" t="str">
@@ -24423,7 +24591,7 @@
       <c r="E490" s="25"/>
       <c r="F490" s="25"/>
       <c r="G490" s="33" t="str">
-        <f aca="false">IF(OR(B490="",AND(A490=A489 ,B490=B489)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A490,$B$5:$B$504,B490)+SUMIFS($E$5:$E$504,$A$5:$A$504,A490,$B$5:$B$504,B490))</f>
+        <f aca="false">IF(OR(B490="",AND(A490=A489 ,B490=B489)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A490,$B$5:$B$504,B490)+SUMIFS($E$5:$E$504,$A$5:$A$504,A490,$B$5:$B$504,B490)-SUMIFS($F$5:$F$504,$A$5:$A$504,A490,$B$5:$B$504,B490))</f>
         <v/>
       </c>
       <c r="H490" s="33" t="str">
@@ -24441,7 +24609,7 @@
       <c r="E491" s="25"/>
       <c r="F491" s="25"/>
       <c r="G491" s="33" t="str">
-        <f aca="false">IF(OR(B491="",AND(A491=A490 ,B491=B490)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A491,$B$5:$B$504,B491)+SUMIFS($E$5:$E$504,$A$5:$A$504,A491,$B$5:$B$504,B491))</f>
+        <f aca="false">IF(OR(B491="",AND(A491=A490 ,B491=B490)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A491,$B$5:$B$504,B491)+SUMIFS($E$5:$E$504,$A$5:$A$504,A491,$B$5:$B$504,B491)-SUMIFS($F$5:$F$504,$A$5:$A$504,A491,$B$5:$B$504,B491))</f>
         <v/>
       </c>
       <c r="H491" s="33" t="str">
@@ -24459,7 +24627,7 @@
       <c r="E492" s="25"/>
       <c r="F492" s="25"/>
       <c r="G492" s="33" t="str">
-        <f aca="false">IF(OR(B492="",AND(A492=A491 ,B492=B491)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A492,$B$5:$B$504,B492)+SUMIFS($E$5:$E$504,$A$5:$A$504,A492,$B$5:$B$504,B492))</f>
+        <f aca="false">IF(OR(B492="",AND(A492=A491 ,B492=B491)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A492,$B$5:$B$504,B492)+SUMIFS($E$5:$E$504,$A$5:$A$504,A492,$B$5:$B$504,B492)-SUMIFS($F$5:$F$504,$A$5:$A$504,A492,$B$5:$B$504,B492))</f>
         <v/>
       </c>
       <c r="H492" s="33" t="str">
@@ -24477,7 +24645,7 @@
       <c r="E493" s="25"/>
       <c r="F493" s="25"/>
       <c r="G493" s="33" t="str">
-        <f aca="false">IF(OR(B493="",AND(A493=A492 ,B493=B492)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A493,$B$5:$B$504,B493)+SUMIFS($E$5:$E$504,$A$5:$A$504,A493,$B$5:$B$504,B493))</f>
+        <f aca="false">IF(OR(B493="",AND(A493=A492 ,B493=B492)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A493,$B$5:$B$504,B493)+SUMIFS($E$5:$E$504,$A$5:$A$504,A493,$B$5:$B$504,B493)-SUMIFS($F$5:$F$504,$A$5:$A$504,A493,$B$5:$B$504,B493))</f>
         <v/>
       </c>
       <c r="H493" s="33" t="str">
@@ -24495,7 +24663,7 @@
       <c r="E494" s="25"/>
       <c r="F494" s="25"/>
       <c r="G494" s="33" t="str">
-        <f aca="false">IF(OR(B494="",AND(A494=A493 ,B494=B493)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A494,$B$5:$B$504,B494)+SUMIFS($E$5:$E$504,$A$5:$A$504,A494,$B$5:$B$504,B494))</f>
+        <f aca="false">IF(OR(B494="",AND(A494=A493 ,B494=B493)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A494,$B$5:$B$504,B494)+SUMIFS($E$5:$E$504,$A$5:$A$504,A494,$B$5:$B$504,B494)-SUMIFS($F$5:$F$504,$A$5:$A$504,A494,$B$5:$B$504,B494))</f>
         <v/>
       </c>
       <c r="H494" s="33" t="str">
@@ -24513,7 +24681,7 @@
       <c r="E495" s="25"/>
       <c r="F495" s="25"/>
       <c r="G495" s="33" t="str">
-        <f aca="false">IF(OR(B495="",AND(A495=A494 ,B495=B494)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A495,$B$5:$B$504,B495)+SUMIFS($E$5:$E$504,$A$5:$A$504,A495,$B$5:$B$504,B495))</f>
+        <f aca="false">IF(OR(B495="",AND(A495=A494 ,B495=B494)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A495,$B$5:$B$504,B495)+SUMIFS($E$5:$E$504,$A$5:$A$504,A495,$B$5:$B$504,B495)-SUMIFS($F$5:$F$504,$A$5:$A$504,A495,$B$5:$B$504,B495))</f>
         <v/>
       </c>
       <c r="H495" s="33" t="str">
@@ -24531,7 +24699,7 @@
       <c r="E496" s="25"/>
       <c r="F496" s="25"/>
       <c r="G496" s="33" t="str">
-        <f aca="false">IF(OR(B496="",AND(A496=A495 ,B496=B495)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A496,$B$5:$B$504,B496)+SUMIFS($E$5:$E$504,$A$5:$A$504,A496,$B$5:$B$504,B496))</f>
+        <f aca="false">IF(OR(B496="",AND(A496=A495 ,B496=B495)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A496,$B$5:$B$504,B496)+SUMIFS($E$5:$E$504,$A$5:$A$504,A496,$B$5:$B$504,B496)-SUMIFS($F$5:$F$504,$A$5:$A$504,A496,$B$5:$B$504,B496))</f>
         <v/>
       </c>
       <c r="H496" s="33" t="str">
@@ -24549,7 +24717,7 @@
       <c r="E497" s="25"/>
       <c r="F497" s="25"/>
       <c r="G497" s="33" t="str">
-        <f aca="false">IF(OR(B497="",AND(A497=A496 ,B497=B496)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A497,$B$5:$B$504,B497)+SUMIFS($E$5:$E$504,$A$5:$A$504,A497,$B$5:$B$504,B497))</f>
+        <f aca="false">IF(OR(B497="",AND(A497=A496 ,B497=B496)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A497,$B$5:$B$504,B497)+SUMIFS($E$5:$E$504,$A$5:$A$504,A497,$B$5:$B$504,B497)-SUMIFS($F$5:$F$504,$A$5:$A$504,A497,$B$5:$B$504,B497))</f>
         <v/>
       </c>
       <c r="H497" s="33" t="str">
@@ -24567,7 +24735,7 @@
       <c r="E498" s="25"/>
       <c r="F498" s="25"/>
       <c r="G498" s="33" t="str">
-        <f aca="false">IF(OR(B498="",AND(A498=A497 ,B498=B497)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A498,$B$5:$B$504,B498)+SUMIFS($E$5:$E$504,$A$5:$A$504,A498,$B$5:$B$504,B498))</f>
+        <f aca="false">IF(OR(B498="",AND(A498=A497 ,B498=B497)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A498,$B$5:$B$504,B498)+SUMIFS($E$5:$E$504,$A$5:$A$504,A498,$B$5:$B$504,B498)-SUMIFS($F$5:$F$504,$A$5:$A$504,A498,$B$5:$B$504,B498))</f>
         <v/>
       </c>
       <c r="H498" s="33" t="str">
@@ -24585,7 +24753,7 @@
       <c r="E499" s="25"/>
       <c r="F499" s="25"/>
       <c r="G499" s="33" t="str">
-        <f aca="false">IF(OR(B499="",AND(A499=A498 ,B499=B498)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A499,$B$5:$B$504,B499)+SUMIFS($E$5:$E$504,$A$5:$A$504,A499,$B$5:$B$504,B499))</f>
+        <f aca="false">IF(OR(B499="",AND(A499=A498 ,B499=B498)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A499,$B$5:$B$504,B499)+SUMIFS($E$5:$E$504,$A$5:$A$504,A499,$B$5:$B$504,B499)-SUMIFS($F$5:$F$504,$A$5:$A$504,A499,$B$5:$B$504,B499))</f>
         <v/>
       </c>
       <c r="H499" s="33" t="str">
@@ -24603,7 +24771,7 @@
       <c r="E500" s="25"/>
       <c r="F500" s="25"/>
       <c r="G500" s="33" t="str">
-        <f aca="false">IF(OR(B500="",AND(A500=A499 ,B500=B499)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A500,$B$5:$B$504,B500)+SUMIFS($E$5:$E$504,$A$5:$A$504,A500,$B$5:$B$504,B500))</f>
+        <f aca="false">IF(OR(B500="",AND(A500=A499 ,B500=B499)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A500,$B$5:$B$504,B500)+SUMIFS($E$5:$E$504,$A$5:$A$504,A500,$B$5:$B$504,B500)-SUMIFS($F$5:$F$504,$A$5:$A$504,A500,$B$5:$B$504,B500))</f>
         <v/>
       </c>
       <c r="H500" s="33" t="str">
@@ -24621,7 +24789,7 @@
       <c r="E501" s="25"/>
       <c r="F501" s="25"/>
       <c r="G501" s="33" t="str">
-        <f aca="false">IF(OR(B501="",AND(A501=A500 ,B501=B500)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A501,$B$5:$B$504,B501)+SUMIFS($E$5:$E$504,$A$5:$A$504,A501,$B$5:$B$504,B501))</f>
+        <f aca="false">IF(OR(B501="",AND(A501=A500 ,B501=B500)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A501,$B$5:$B$504,B501)+SUMIFS($E$5:$E$504,$A$5:$A$504,A501,$B$5:$B$504,B501)-SUMIFS($F$5:$F$504,$A$5:$A$504,A501,$B$5:$B$504,B501))</f>
         <v/>
       </c>
       <c r="H501" s="33" t="str">
@@ -24639,7 +24807,7 @@
       <c r="E502" s="25"/>
       <c r="F502" s="25"/>
       <c r="G502" s="33" t="str">
-        <f aca="false">IF(OR(B502="",AND(A502=A501 ,B502=B501)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A502,$B$5:$B$504,B502)+SUMIFS($E$5:$E$504,$A$5:$A$504,A502,$B$5:$B$504,B502))</f>
+        <f aca="false">IF(OR(B502="",AND(A502=A501 ,B502=B501)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A502,$B$5:$B$504,B502)+SUMIFS($E$5:$E$504,$A$5:$A$504,A502,$B$5:$B$504,B502)-SUMIFS($F$5:$F$504,$A$5:$A$504,A502,$B$5:$B$504,B502))</f>
         <v/>
       </c>
       <c r="H502" s="33" t="str">
@@ -24657,7 +24825,7 @@
       <c r="E503" s="25"/>
       <c r="F503" s="25"/>
       <c r="G503" s="33" t="str">
-        <f aca="false">IF(OR(B503="",AND(A503=A502 ,B503=B502)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A503,$B$5:$B$504,B503)+SUMIFS($E$5:$E$504,$A$5:$A$504,A503,$B$5:$B$504,B503))</f>
+        <f aca="false">IF(OR(B503="",AND(A503=A502 ,B503=B502)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A503,$B$5:$B$504,B503)+SUMIFS($E$5:$E$504,$A$5:$A$504,A503,$B$5:$B$504,B503)-SUMIFS($F$5:$F$504,$A$5:$A$504,A503,$B$5:$B$504,B503))</f>
         <v/>
       </c>
       <c r="H503" s="33" t="str">
@@ -24675,7 +24843,7 @@
       <c r="E504" s="25"/>
       <c r="F504" s="25"/>
       <c r="G504" s="33" t="str">
-        <f aca="false">IF(OR(B504="",AND(A504=A503 ,B504=B503)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A504,$B$5:$B$504,B504)+SUMIFS($E$5:$E$504,$A$5:$A$504,A504,$B$5:$B$504,B504))</f>
+        <f aca="false">IF(OR(B504="",AND(A504=A503 ,B504=B503)),"",SUMIFS($D$5:$D$504,$A$5:$A$504,A504,$B$5:$B$504,B504)+SUMIFS($E$5:$E$504,$A$5:$A$504,A504,$B$5:$B$504,B504)-SUMIFS($F$5:$F$504,$A$5:$A$504,A504,$B$5:$B$504,B504))</f>
         <v/>
       </c>
       <c r="H504" s="33" t="str">
@@ -24737,13 +24905,14 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -24753,7 +24922,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -24769,9 +24938,9 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>50</v>
@@ -24786,12 +24955,12 @@
         <v>53</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="29" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B5" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A5)</f>
@@ -24806,7 +24975,7 @@
         <v>600</v>
       </c>
       <c r="E5" s="18" t="n">
-        <f aca="false">B5-D5</f>
+        <f aca="false">B5+C5-D5</f>
         <v>-100</v>
       </c>
       <c r="F5" s="18" t="n">
@@ -24816,7 +24985,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="29" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B6" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A6)</f>
@@ -24831,7 +25000,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="18" t="n">
-        <f aca="false">B6-D6</f>
+        <f aca="false">B6+C6-D6</f>
         <v>2500</v>
       </c>
       <c r="F6" s="18" t="n">
@@ -24841,7 +25010,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="29" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B7" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A7)</f>
@@ -24856,7 +25025,7 @@
         <v>101</v>
       </c>
       <c r="E7" s="18" t="n">
-        <f aca="false">B7-D7</f>
+        <f aca="false">B7+C7-D7</f>
         <v>199</v>
       </c>
       <c r="F7" s="18" t="n">
@@ -24866,7 +25035,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="29" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A8)</f>
@@ -24881,7 +25050,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="18" t="n">
-        <f aca="false">B8-D8</f>
+        <f aca="false">B8+C8-D8</f>
         <v>50</v>
       </c>
       <c r="F8" s="18" t="n">
@@ -24891,7 +25060,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B9" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A9)</f>
@@ -24906,7 +25075,7 @@
         <v>206</v>
       </c>
       <c r="E9" s="18" t="n">
-        <f aca="false">B9-D9</f>
+        <f aca="false">B9+C9-D9</f>
         <v>144</v>
       </c>
       <c r="F9" s="18" t="n">
@@ -24916,7 +25085,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B10" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A10)</f>
@@ -24931,7 +25100,7 @@
         <v>955</v>
       </c>
       <c r="E10" s="18" t="n">
-        <f aca="false">B10-D10</f>
+        <f aca="false">B10+C10-D10</f>
         <v>-355</v>
       </c>
       <c r="F10" s="18" t="n">
@@ -24941,7 +25110,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="29" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B11" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A11)</f>
@@ -24956,7 +25125,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="18" t="n">
-        <f aca="false">B11-D11</f>
+        <f aca="false">B11+C11-D11</f>
         <v>4000</v>
       </c>
       <c r="F11" s="18" t="n">
@@ -24966,7 +25135,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B12" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A12)</f>
@@ -24981,8 +25150,8 @@
         <v>0</v>
       </c>
       <c r="E12" s="18" t="n">
-        <f aca="false">B12-D12</f>
-        <v>300</v>
+        <f aca="false">B12+C12-D12</f>
+        <v>20300</v>
       </c>
       <c r="F12" s="18" t="n">
         <f aca="false">COUNTIFS('Giao dịch TK'!$C$5:$C$504,$A12)</f>
@@ -24991,7 +25160,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B13" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A13)</f>
@@ -25006,8 +25175,8 @@
         <v>0</v>
       </c>
       <c r="E13" s="18" t="n">
-        <f aca="false">B13-D13</f>
-        <v>5000</v>
+        <f aca="false">B13+C13-D13</f>
+        <v>10000</v>
       </c>
       <c r="F13" s="18" t="n">
         <f aca="false">COUNTIFS('Giao dịch TK'!$C$5:$C$504,$A13)</f>
@@ -25016,7 +25185,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B14" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A14)</f>
@@ -25031,7 +25200,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="18" t="n">
-        <f aca="false">B14-D14</f>
+        <f aca="false">B14+C14-D14</f>
         <v>2100</v>
       </c>
       <c r="F14" s="18" t="n">
@@ -25041,7 +25210,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="29" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B15" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A15)</f>
@@ -25056,7 +25225,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="18" t="n">
-        <f aca="false">B15-D15</f>
+        <f aca="false">B15+C15-D15</f>
         <v>100</v>
       </c>
       <c r="F15" s="18" t="n">
@@ -25066,7 +25235,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="29" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B16" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A16)</f>
@@ -25081,7 +25250,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="18" t="n">
-        <f aca="false">B16-D16</f>
+        <f aca="false">B16+C16-D16</f>
         <v>200</v>
       </c>
       <c r="F16" s="18" t="n">
@@ -25091,7 +25260,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="29" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B17" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A17)</f>
@@ -25106,7 +25275,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="18" t="n">
-        <f aca="false">B17-D17</f>
+        <f aca="false">B17+C17-D17</f>
         <v>50</v>
       </c>
       <c r="F17" s="18" t="n">
@@ -25116,7 +25285,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="29" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B18" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A18)</f>
@@ -25131,8 +25300,8 @@
         <v>0</v>
       </c>
       <c r="E18" s="18" t="n">
-        <f aca="false">B18-D18</f>
-        <v>3000</v>
+        <f aca="false">B18+C18-D18</f>
+        <v>9000</v>
       </c>
       <c r="F18" s="18" t="n">
         <f aca="false">COUNTIFS('Giao dịch TK'!$C$5:$C$504,$A18)</f>
@@ -25141,7 +25310,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B19" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A19)</f>
@@ -25156,7 +25325,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="18" t="n">
-        <f aca="false">B19-D19</f>
+        <f aca="false">B19+C19-D19</f>
         <v>50</v>
       </c>
       <c r="F19" s="18" t="n">
@@ -25166,7 +25335,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="29" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B20" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A20)</f>
@@ -25181,7 +25350,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="18" t="n">
-        <f aca="false">B20-D20</f>
+        <f aca="false">B20+C20-D20</f>
         <v>1000</v>
       </c>
       <c r="F20" s="18" t="n">
@@ -25191,7 +25360,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="29" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B21" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A21)</f>
@@ -25206,7 +25375,7 @@
         <v>307</v>
       </c>
       <c r="E21" s="18" t="n">
-        <f aca="false">B21-D21</f>
+        <f aca="false">B21+C21-D21</f>
         <v>-257</v>
       </c>
       <c r="F21" s="18" t="n">
@@ -25216,7 +25385,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="29" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B22" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A22)</f>
@@ -25231,7 +25400,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="18" t="n">
-        <f aca="false">B22-D22</f>
+        <f aca="false">B22+C22-D22</f>
         <v>500</v>
       </c>
       <c r="F22" s="18" t="n">
@@ -25241,7 +25410,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="29" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B23" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A23)</f>
@@ -25256,7 +25425,7 @@
         <v>700</v>
       </c>
       <c r="E23" s="18" t="n">
-        <f aca="false">B23-D23</f>
+        <f aca="false">B23+C23-D23</f>
         <v>-600</v>
       </c>
       <c r="F23" s="18" t="n">
@@ -25266,7 +25435,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="29" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B24" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A24)</f>
@@ -25281,7 +25450,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="18" t="n">
-        <f aca="false">B24-D24</f>
+        <f aca="false">B24+C24-D24</f>
         <v>1000</v>
       </c>
       <c r="F24" s="18" t="n">
@@ -25291,7 +25460,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="29" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B25" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A25)</f>
@@ -25306,7 +25475,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="18" t="n">
-        <f aca="false">B25-D25</f>
+        <f aca="false">B25+C25-D25</f>
         <v>3000</v>
       </c>
       <c r="F25" s="18" t="n">
@@ -25316,7 +25485,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B26" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A26)</f>
@@ -25331,7 +25500,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="18" t="n">
-        <f aca="false">B26-D26</f>
+        <f aca="false">B26+C26-D26</f>
         <v>1000</v>
       </c>
       <c r="F26" s="18" t="n">
@@ -25341,7 +25510,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B27" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A27)</f>
@@ -25356,7 +25525,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="18" t="n">
-        <f aca="false">B27-D27</f>
+        <f aca="false">B27+C27-D27</f>
         <v>3000</v>
       </c>
       <c r="F27" s="18" t="n">
@@ -25366,7 +25535,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="29" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B28" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A28)</f>
@@ -25381,7 +25550,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="18" t="n">
-        <f aca="false">B28-D28</f>
+        <f aca="false">B28+C28-D28</f>
         <v>200</v>
       </c>
       <c r="F28" s="18" t="n">
@@ -25391,7 +25560,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B29" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A29)</f>
@@ -25406,8 +25575,8 @@
         <v>0</v>
       </c>
       <c r="E29" s="18" t="n">
-        <f aca="false">B29-D29</f>
-        <v>1000</v>
+        <f aca="false">B29+C29-D29</f>
+        <v>5000</v>
       </c>
       <c r="F29" s="18" t="n">
         <f aca="false">COUNTIFS('Giao dịch TK'!$C$5:$C$504,$A29)</f>
@@ -25416,7 +25585,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="29" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B30" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A30)</f>
@@ -25431,7 +25600,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="18" t="n">
-        <f aca="false">B30-D30</f>
+        <f aca="false">B30+C30-D30</f>
         <v>1000</v>
       </c>
       <c r="F30" s="18" t="n">
@@ -25441,7 +25610,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="29" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B31" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A31)</f>
@@ -25456,7 +25625,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="18" t="n">
-        <f aca="false">B31-D31</f>
+        <f aca="false">B31+C31-D31</f>
         <v>500</v>
       </c>
       <c r="F31" s="18" t="n">
@@ -25466,7 +25635,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="29" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B32" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A32)</f>
@@ -25481,7 +25650,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="18" t="n">
-        <f aca="false">B32-D32</f>
+        <f aca="false">B32+C32-D32</f>
         <v>50</v>
       </c>
       <c r="F32" s="18" t="n">
@@ -25491,7 +25660,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="29" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B33" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A33)</f>
@@ -25506,7 +25675,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="18" t="n">
-        <f aca="false">B33-D33</f>
+        <f aca="false">B33+C33-D33</f>
         <v>1200</v>
       </c>
       <c r="F33" s="18" t="n">
@@ -25516,7 +25685,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="29" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B34" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A34)</f>
@@ -25531,7 +25700,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="18" t="n">
-        <f aca="false">B34-D34</f>
+        <f aca="false">B34+C34-D34</f>
         <v>1000</v>
       </c>
       <c r="F34" s="18" t="n">
@@ -25541,7 +25710,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B35" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A35)</f>
@@ -25556,7 +25725,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="18" t="n">
-        <f aca="false">B35-D35</f>
+        <f aca="false">B35+C35-D35</f>
         <v>3000</v>
       </c>
       <c r="F35" s="18" t="n">
@@ -25566,7 +25735,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="29" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B36" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A36)</f>
@@ -25581,7 +25750,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="18" t="n">
-        <f aca="false">B36-D36</f>
+        <f aca="false">B36+C36-D36</f>
         <v>500</v>
       </c>
       <c r="F36" s="18" t="n">
@@ -25591,7 +25760,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="29" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B37" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A37)</f>
@@ -25606,7 +25775,7 @@
         <v>251</v>
       </c>
       <c r="E37" s="18" t="n">
-        <f aca="false">B37-D37</f>
+        <f aca="false">B37+C37-D37</f>
         <v>-101</v>
       </c>
       <c r="F37" s="18" t="n">
@@ -25616,7 +25785,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="29" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B38" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A38)</f>
@@ -25631,8 +25800,8 @@
         <v>500</v>
       </c>
       <c r="E38" s="18" t="n">
-        <f aca="false">B38-D38</f>
-        <v>7300</v>
+        <f aca="false">B38+C38-D38</f>
+        <v>16500</v>
       </c>
       <c r="F38" s="18" t="n">
         <f aca="false">COUNTIFS('Giao dịch TK'!$C$5:$C$504,$A38)</f>
@@ -25641,7 +25810,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="29" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B39" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A39)</f>
@@ -25656,7 +25825,7 @@
         <v>0</v>
       </c>
       <c r="E39" s="18" t="n">
-        <f aca="false">B39-D39</f>
+        <f aca="false">B39+C39-D39</f>
         <v>2580</v>
       </c>
       <c r="F39" s="18" t="n">
@@ -25666,7 +25835,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="29" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B40" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A40)</f>
@@ -25681,7 +25850,7 @@
         <v>1120</v>
       </c>
       <c r="E40" s="18" t="n">
-        <f aca="false">B40-D40</f>
+        <f aca="false">B40+C40-D40</f>
         <v>2980</v>
       </c>
       <c r="F40" s="18" t="n">
@@ -25691,7 +25860,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="29" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B41" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A41)</f>
@@ -25706,7 +25875,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="18" t="n">
-        <f aca="false">B41-D41</f>
+        <f aca="false">B41+C41-D41</f>
         <v>160</v>
       </c>
       <c r="F41" s="18" t="n">
@@ -25716,7 +25885,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="29" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B42" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A42)</f>
@@ -25731,7 +25900,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="18" t="n">
-        <f aca="false">B42-D42</f>
+        <f aca="false">B42+C42-D42</f>
         <v>1000</v>
       </c>
       <c r="F42" s="18" t="n">
@@ -25741,7 +25910,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="29" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B43" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A43)</f>
@@ -25756,8 +25925,8 @@
         <v>0</v>
       </c>
       <c r="E43" s="18" t="n">
-        <f aca="false">B43-D43</f>
-        <v>10000</v>
+        <f aca="false">B43+C43-D43</f>
+        <v>29190</v>
       </c>
       <c r="F43" s="18" t="n">
         <f aca="false">COUNTIFS('Giao dịch TK'!$C$5:$C$504,$A43)</f>
@@ -25766,7 +25935,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B44" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A44)</f>
@@ -25781,8 +25950,8 @@
         <v>0</v>
       </c>
       <c r="E44" s="18" t="n">
-        <f aca="false">B44-D44</f>
-        <v>3000</v>
+        <f aca="false">B44+C44-D44</f>
+        <v>9000</v>
       </c>
       <c r="F44" s="18" t="n">
         <f aca="false">COUNTIFS('Giao dịch TK'!$C$5:$C$504,$A44)</f>
@@ -25791,7 +25960,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="29" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B45" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A45)</f>
@@ -25806,7 +25975,7 @@
         <v>100</v>
       </c>
       <c r="E45" s="18" t="n">
-        <f aca="false">B45-D45</f>
+        <f aca="false">B45+C45-D45</f>
         <v>100</v>
       </c>
       <c r="F45" s="18" t="n">
@@ -25816,7 +25985,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="29" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B46" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A46)</f>
@@ -25831,7 +26000,7 @@
         <v>0</v>
       </c>
       <c r="E46" s="18" t="n">
-        <f aca="false">B46-D46</f>
+        <f aca="false">B46+C46-D46</f>
         <v>200</v>
       </c>
       <c r="F46" s="18" t="n">
@@ -25841,7 +26010,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="29" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B47" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A47)</f>
@@ -25856,7 +26025,7 @@
         <v>0</v>
       </c>
       <c r="E47" s="18" t="n">
-        <f aca="false">B47-D47</f>
+        <f aca="false">B47+C47-D47</f>
         <v>1000</v>
       </c>
       <c r="F47" s="18" t="n">
@@ -25866,7 +26035,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B48" s="18" t="n">
         <f aca="false">SUMIFS('Giao dịch TK'!$D$5:$D$504,'Giao dịch TK'!$C$5:$C$504,$A48)</f>
@@ -25881,8 +26050,8 @@
         <v>0</v>
       </c>
       <c r="E48" s="18" t="n">
-        <f aca="false">B48-D48</f>
-        <v>5000</v>
+        <f aca="false">B48+C48-D48</f>
+        <v>20000</v>
       </c>
       <c r="F48" s="18" t="n">
         <f aca="false">COUNTIFS('Giao dịch TK'!$C$5:$C$504,$A48)</f>
@@ -25918,7 +26087,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -25928,7 +26097,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -25946,30 +26115,30 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="54" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C5" s="25" t="n">
         <v>34550</v>
@@ -25989,10 +26158,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="54" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C6" s="25" t="n">
         <v>408</v>
@@ -26012,10 +26181,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="54" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C7" s="25" t="n">
         <v>19850</v>
@@ -26035,10 +26204,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="54" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C8" s="25" t="n">
         <v>1215</v>
@@ -26058,10 +26227,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="54" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C9" s="25" t="n">
         <v>9250</v>
@@ -26081,10 +26250,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="54" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C10" s="25" t="n">
         <v>10000</v>
@@ -26104,10 +26273,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="54" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C11" s="25" t="n">
         <v>8200</v>
@@ -26127,10 +26296,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="54" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C12" s="25" t="n">
         <v>150</v>
@@ -26150,10 +26319,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="54" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C13" s="25" t="n">
         <v>9</v>
@@ -26173,10 +26342,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="54" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C14" s="25" t="n">
         <v>50</v>
@@ -26196,10 +26365,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="54" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C15" s="25" t="n">
         <v>42572</v>
@@ -26235,7 +26404,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -26245,7 +26414,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -26255,7 +26424,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -26265,7 +26434,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -26275,7 +26444,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -26285,7 +26454,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -26295,7 +26464,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -26305,7 +26474,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -26315,7 +26484,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -26325,7 +26494,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>

--- a/SoTheoDoiThuChi_T10_2026.xlsx
+++ b/SoTheoDoiThuChi_T10_2026.xlsx
@@ -7481,11 +7481,11 @@
       <c r="E5" s="31"/>
       <c r="F5" s="31"/>
       <c r="G5" s="38" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A5,$B$5:$B$504,B5)+SUMIFS($E$5:$E$504,$A$5:$A$504,A5,$B$5:$B$504,B5)-SUMIFS($F$5:$F$504,$A$5:$A$504,A5,$B$5:$B$504,B5)</f>
+        <f aca="false">SUM(D5:D13)+SUM(E5:E13)-SUM(F5:F13)</f>
         <v>34142</v>
       </c>
       <c r="H5" s="38" t="n">
-        <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A5,$B$5:$B$504,B5)</f>
+        <f aca="false">SUM(F5:F13)</f>
         <v>408</v>
       </c>
       <c r="I5" s="39" t="s">
@@ -7695,11 +7695,11 @@
         <v>206</v>
       </c>
       <c r="G14" s="43" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A14,$B$5:$B$504,B14)+SUMIFS($E$5:$E$504,$A$5:$A$504,A14,$B$5:$B$504,B14)-SUMIFS($F$5:$F$504,$A$5:$A$504,A14,$B$5:$B$504,B14)</f>
+        <f aca="false">SUM(D14:D19)+SUM(E14:E19)-SUM(F14:F19)</f>
         <v>18689</v>
       </c>
       <c r="H14" s="43" t="n">
-        <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A14,$B$5:$B$504,B14)</f>
+        <f aca="false">SUM(F14:F19)</f>
         <v>1161</v>
       </c>
       <c r="I14" s="44" t="s">
@@ -7841,11 +7841,11 @@
       </c>
       <c r="F20" s="42"/>
       <c r="G20" s="43" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A20,$B$5:$B$504,B20)+SUMIFS($E$5:$E$504,$A$5:$A$504,A20,$B$5:$B$504,B20)-SUMIFS($F$5:$F$504,$A$5:$A$504,A20,$B$5:$B$504,B20)</f>
+        <f aca="false">SUM(D20:D21)+SUM(E20:E21)-SUM(F20:F21)</f>
         <v>9250</v>
       </c>
       <c r="H20" s="43" t="n">
-        <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A20,$B$5:$B$504,B20)</f>
+        <f aca="false">SUM(F20:F21)</f>
         <v>0</v>
       </c>
       <c r="I20" s="44" t="s">
@@ -7891,11 +7891,11 @@
       </c>
       <c r="F22" s="42"/>
       <c r="G22" s="43" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A22,$B$5:$B$504,B22)+SUMIFS($E$5:$E$504,$A$5:$A$504,A22,$B$5:$B$504,B22)-SUMIFS($F$5:$F$504,$A$5:$A$504,A22,$B$5:$B$504,B22)</f>
+        <f aca="false">D22+E22-F22</f>
         <v>10000</v>
       </c>
       <c r="H22" s="43" t="n">
-        <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A22,$B$5:$B$504,B22)</f>
+        <f aca="false">F22</f>
         <v>0</v>
       </c>
       <c r="I22" s="44" t="s">
@@ -7921,11 +7921,11 @@
         <v>700</v>
       </c>
       <c r="G23" s="43" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A23,$B$5:$B$504,B23)+SUMIFS($E$5:$E$504,$A$5:$A$504,A23,$B$5:$B$504,B23)-SUMIFS($F$5:$F$504,$A$5:$A$504,A23,$B$5:$B$504,B23)</f>
+        <f aca="false">D23+E23-F23</f>
         <v>-650</v>
       </c>
       <c r="H23" s="43" t="n">
-        <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A23,$B$5:$B$504,B23)</f>
+        <f aca="false">F23</f>
         <v>700</v>
       </c>
       <c r="I23" s="44" t="s">
@@ -7953,11 +7953,11 @@
         <v>100</v>
       </c>
       <c r="G24" s="43" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A24,$B$5:$B$504,B24)+SUMIFS($E$5:$E$504,$A$5:$A$504,A24,$B$5:$B$504,B24)-SUMIFS($F$5:$F$504,$A$5:$A$504,A24,$B$5:$B$504,B24)</f>
+        <f aca="false">SUM(D24:D28)+SUM(E24:E28)-SUM(F24:F28)</f>
         <v>8000</v>
       </c>
       <c r="H24" s="43" t="n">
-        <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A24,$B$5:$B$504,B24)</f>
+        <f aca="false">SUM(F24:F28)</f>
         <v>200</v>
       </c>
       <c r="I24" s="44" t="s">
@@ -8073,11 +8073,11 @@
       <c r="E29" s="42"/>
       <c r="F29" s="42"/>
       <c r="G29" s="43" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A29,$B$5:$B$504,B29)+SUMIFS($E$5:$E$504,$A$5:$A$504,A29,$B$5:$B$504,B29)-SUMIFS($F$5:$F$504,$A$5:$A$504,A29,$B$5:$B$504,B29)</f>
+        <f aca="false">SUM(D29:D30)+SUM(E29:E30)-SUM(F29:F30)</f>
         <v>150</v>
       </c>
       <c r="H29" s="43" t="n">
-        <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A29,$B$5:$B$504,B29)</f>
+        <f aca="false">SUM(F29:F30)</f>
         <v>0</v>
       </c>
       <c r="I29" s="44" t="s">
@@ -8123,11 +8123,11 @@
       <c r="E31" s="42"/>
       <c r="F31" s="42"/>
       <c r="G31" s="43" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A31,$B$5:$B$504,B31)+SUMIFS($E$5:$E$504,$A$5:$A$504,A31,$B$5:$B$504,B31)-SUMIFS($F$5:$F$504,$A$5:$A$504,A31,$B$5:$B$504,B31)</f>
+        <f aca="false">SUM(D31:D37)+SUM(E31:E37)-SUM(F31:F37)</f>
         <v>16810</v>
       </c>
       <c r="H31" s="43" t="n">
-        <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A31,$B$5:$B$504,B31)</f>
+        <f aca="false">SUM(F31:F37)</f>
         <v>1120</v>
       </c>
       <c r="I31" s="44" t="s">
@@ -8285,11 +8285,11 @@
       <c r="E38" s="42"/>
       <c r="F38" s="42"/>
       <c r="G38" s="43" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A38,$B$5:$B$504,B38)+SUMIFS($E$5:$E$504,$A$5:$A$504,A38,$B$5:$B$504,B38)-SUMIFS($F$5:$F$504,$A$5:$A$504,A38,$B$5:$B$504,B38)</f>
+        <f aca="false">SUM(D38:D46)+SUM(E38:E46)-SUM(F38:F46)</f>
         <v>25590</v>
       </c>
       <c r="H38" s="43" t="n">
-        <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A38,$B$5:$B$504,B38)</f>
+        <f aca="false">SUM(F38:F46)</f>
         <v>0</v>
       </c>
       <c r="I38" s="44" t="s">
@@ -8489,11 +8489,11 @@
       <c r="E47" s="42"/>
       <c r="F47" s="42"/>
       <c r="G47" s="43" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A47,$B$5:$B$504,B47)+SUMIFS($E$5:$E$504,$A$5:$A$504,A47,$B$5:$B$504,B47)-SUMIFS($F$5:$F$504,$A$5:$A$504,A47,$B$5:$B$504,B47)</f>
+        <f aca="false">SUM(D47:D49)+SUM(E47:E49)-SUM(F47:F49)</f>
         <v>5550</v>
       </c>
       <c r="H47" s="43" t="n">
-        <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A47,$B$5:$B$504,B47)</f>
+        <f aca="false">SUM(F47:F49)</f>
         <v>0</v>
       </c>
       <c r="I47" s="44" t="s">
@@ -8563,11 +8563,11 @@
       <c r="E50" s="42"/>
       <c r="F50" s="42"/>
       <c r="G50" s="43" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A50,$B$5:$B$504,B50)+SUMIFS($E$5:$E$504,$A$5:$A$504,A50,$B$5:$B$504,B50)-SUMIFS($F$5:$F$504,$A$5:$A$504,A50,$B$5:$B$504,B50)</f>
+        <f aca="false">SUM(D50:D51)+SUM(E50:E51)-SUM(F50:F51)</f>
         <v>9</v>
       </c>
       <c r="H50" s="43" t="n">
-        <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A50,$B$5:$B$504,B50)</f>
+        <f aca="false">SUM(F50:F51)</f>
         <v>251</v>
       </c>
       <c r="I50" s="44" t="s">
@@ -8615,11 +8615,11 @@
       <c r="E52" s="42"/>
       <c r="F52" s="42"/>
       <c r="G52" s="43" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A52,$B$5:$B$504,B52)+SUMIFS($E$5:$E$504,$A$5:$A$504,A52,$B$5:$B$504,B52)-SUMIFS($F$5:$F$504,$A$5:$A$504,A52,$B$5:$B$504,B52)</f>
+        <f aca="false">D52+E52-F52</f>
         <v>50</v>
       </c>
       <c r="H52" s="43" t="n">
-        <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A52,$B$5:$B$504,B52)</f>
+        <f aca="false">F52</f>
         <v>0</v>
       </c>
       <c r="I52" s="44" t="s">
@@ -8647,11 +8647,11 @@
         <v>500</v>
       </c>
       <c r="G53" s="43" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A53,$B$5:$B$504,B53)+SUMIFS($E$5:$E$504,$A$5:$A$504,A53,$B$5:$B$504,B53)-SUMIFS($F$5:$F$504,$A$5:$A$504,A53,$B$5:$B$504,B53)</f>
+        <f aca="false">D53+E53-F53</f>
         <v>11900</v>
       </c>
       <c r="H53" s="43" t="n">
-        <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A53,$B$5:$B$504,B53)</f>
+        <f aca="false">F53</f>
         <v>500</v>
       </c>
       <c r="I53" s="44" t="s">
@@ -8675,11 +8675,11 @@
       <c r="E54" s="42"/>
       <c r="F54" s="42"/>
       <c r="G54" s="43" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A54,$B$5:$B$504,B54)+SUMIFS($E$5:$E$504,$A$5:$A$504,A54,$B$5:$B$504,B54)-SUMIFS($F$5:$F$504,$A$5:$A$504,A54,$B$5:$B$504,B54)</f>
+        <f aca="false">D54+E54-F54</f>
         <v>100</v>
       </c>
       <c r="H54" s="43" t="n">
-        <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A54,$B$5:$B$504,B54)</f>
+        <f aca="false">F54</f>
         <v>0</v>
       </c>
       <c r="I54" s="44" t="s">
@@ -8703,11 +8703,11 @@
       </c>
       <c r="F55" s="49"/>
       <c r="G55" s="43" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A55,$B$5:$B$504,B55)+SUMIFS($E$5:$E$504,$A$5:$A$504,A55,$B$5:$B$504,B55)-SUMIFS($F$5:$F$504,$A$5:$A$504,A55,$B$5:$B$504,B55)</f>
+        <f aca="false">D55+E55-F55</f>
         <v>4600</v>
       </c>
       <c r="H55" s="43" t="n">
-        <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A55,$B$5:$B$504,B55)</f>
+        <f aca="false">F55</f>
         <v>0</v>
       </c>
       <c r="I55" s="50" t="s">
@@ -8733,11 +8733,11 @@
       <c r="E56" s="42"/>
       <c r="F56" s="42"/>
       <c r="G56" s="43" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A56,$B$5:$B$504,B56)+SUMIFS($E$5:$E$504,$A$5:$A$504,A56,$B$5:$B$504,B56)-SUMIFS($F$5:$F$504,$A$5:$A$504,A56,$B$5:$B$504,B56)</f>
+        <f aca="false">SUM(D56:D58)+SUM(E56:E58)-SUM(F56:F58)</f>
         <v>250</v>
       </c>
       <c r="H56" s="43" t="n">
-        <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A56,$B$5:$B$504,B56)</f>
+        <f aca="false">SUM(F56:F58)</f>
         <v>500</v>
       </c>
       <c r="I56" s="44" t="s">
@@ -8859,11 +8859,11 @@
       <c r="E61" s="42"/>
       <c r="F61" s="42"/>
       <c r="G61" s="43" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A61,$B$5:$B$504,B61)+SUMIFS($E$5:$E$504,$A$5:$A$504,A61,$B$5:$B$504,B61)-SUMIFS($F$5:$F$504,$A$5:$A$504,A61,$B$5:$B$504,B61)</f>
+        <f aca="false">D61+E61-F61</f>
         <v>1000</v>
       </c>
       <c r="H61" s="43" t="n">
-        <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A61,$B$5:$B$504,B61)</f>
+        <f aca="false">F61</f>
         <v>0</v>
       </c>
       <c r="I61" s="44" t="s">
@@ -8887,11 +8887,11 @@
       <c r="E62" s="42"/>
       <c r="F62" s="42"/>
       <c r="G62" s="43" t="n">
-        <f aca="false">SUMIFS($D$5:$D$504,$A$5:$A$504,A62,$B$5:$B$504,B62)+SUMIFS($E$5:$E$504,$A$5:$A$504,A62,$B$5:$B$504,B62)-SUMIFS($F$5:$F$504,$A$5:$A$504,A62,$B$5:$B$504,B62)</f>
+        <f aca="false">D62+E62-F62</f>
         <v>2500</v>
       </c>
       <c r="H62" s="43" t="n">
-        <f aca="false">SUMIFS($F$5:$F$504,$A$5:$A$504,A62,$B$5:$B$504,B62)</f>
+        <f aca="false">F62</f>
         <v>0</v>
       </c>
       <c r="I62" s="44" t="s">
